--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4.97</v>
+        <v>6.37</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI ปิดรับลูกค้าใหม่ ChatGPT Pro $200 ต่อเดือนชั่วคราว เหตุคนแห่ใช้ Astra เยอะมาก</t>
+          <t>Iran and Houthi rebels used Anthropic's Claude AI to target US warships and build hypersonic missiles — Houthi rebels also used the bot to code ballistic missile guidance systems</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>การตอบรับของ GPT-6 Astra โมเดลปัญญาประดิษฐ์ขั้นสูงตัวล่าสุดของ OpenAI ดูเหมือนจะมาแรงมาก เพราะล่าสุด Thibault Sottiaux หัวหน้าฝ่ายผลิตภัณฑ์ของ OpenAI ได้ประกาศว่าปิดการสมัครใช้งาน ChatGPT Pro ที่คิดราคา 200 ดอลลาร์ต่อเดือนชั่วคราว เพื่อให้ระบบและบริการโดยรวมยังสามารถใช้งานสำหรับลูกค้าปัจจุบัน ทั้งนี้การสมัครใช้งานแผนอื่นที่ราคาถูกกว่า และการใช้งานผ่าน API ยังใช้ได้เหมือนเดิม โพสต์ของ Sottiaux เป็น</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, gpt, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>anthropic, claude, ai, semiconductor, fab</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>15.9</v>
+        <v>9.6</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 08:59:11 +0000</t>
+          <t>Sat, 12 Sep 2026 15:03:10 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,48 +577,48 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151615</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/iran-and-houthi-rebels-used-anthropics-claude-ai-to-target-us-warships-and-build-hypersonic-missiles-houthi-rebels-also-used-the-bot-to-code-ballistic-missile-guidance-systems</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4.6</v>
+        <v>5.42</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>openai.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Tekoälypolitiikan aikaikkuna on avoinna. Nyt on toimittava.</t>
+          <t>Nvidia's Groq acquihire is on the DOJ's radar, but it's already too late</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9. syyskuuta 2026Globaalit asiatTekoälypolitiikan aikaikkuna on avoinna. Nyt on toimittava.By Chris Lehane, Chief Global Affairs Officer at OpenAILadataan...JaaPreparing for recursive self-improvementPreparing for recursive self-improvementWorking with Congress on mandatory national AI safety requirementsKeeping up momentum in the statesCalling for industry standards to monitor frontier AIUse the </t>
+          <t>LEGAL Even if regulators did somehow unwind the $20B deal, there's a growing list of alternatives ready to take Groq's place, no merger required Tobias Mann Tobias Mann SYSTEMS EDITOR Published sat 12 Sep 2026 // 14:26 UTC READ MORE DeepSeek's new model sets a template for powerful LLMs that run lean 1 day ago Watch out: Apple timepiece can grab snippets of conversation without both speakers' cons</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>groq, ai, inference, nvidia, ai accelerator</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.5</v>
+        <v>11.2</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 22:22:59 GMT</t>
+          <t>Sat, 12 Sep 2026 15:26:00 +0200</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://openai.com/fi-FI/index/ai-policy-window/</t>
+          <t>https://www.theregister.com/systems/2026/09/12/nvidias-groq-acquihire-is-on-the-dojs-radar-but-its-already-too-late/5295986</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4.49</v>
+        <v>5.2</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
@@ -651,25 +651,25 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Lawyer fined $5K over AI-hallucinated witnesses in a murder case</t>
+          <t>OpenAI’s rogue AI tried to hack another company in May</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Policy Lawyer fined $5K over AI-hallucinated witnesses in a murder c</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News OpenAI OpenAI’s rogue AI tried to hack another company in May The pr</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T16:44:02-04:00</t>
+          <t>2026-09-12T17:41:36-04:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/994207/chatgpt-new-mexico-lawyer-fined-murder-appeal</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994383/openais-rogue-ai-rubygems-hack</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4.49</v>
+        <v>5.2</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>2</v>
@@ -702,25 +702,25 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Lawyer fined $5K over AI-hallucinated witnesses in a murder case</t>
+          <t>OpenAI’s rogue AI tried to hack another company in May</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI NEWS POLICY Lawyer fined $5K over AI-hallucinated witnesses in a murder case A justice asked, ‘Counsel, do you watch the news?’ when a lawyer admitted to relying on ChatGPT without understanding the risks. by Emma Roth Sep 12, 2026, 3:44 AM GMT+7 9 9 Comments (All New) Illustration by Cath Virginia / The Verge | Photos from Getty Images Emma Roth is a news writer who covers the streaming wars, </t>
+          <t>AI NEWS OPENAI OpenAI’s rogue AI tried to hack another company in May The previously undisclosed attack on Ruby Gems predates Hugging Face by more than a month. by Terrence O'Brien Sep 13, 2026, 4:41 AM GMT+7 4 4 Comments (All New) Terrence O'Brien is the Verge’s weekend editor. He’s covered the tech industry for over 18 years and knows a thing or two about synths. In May, hundreds of malicious an</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 20:44:02 GMT</t>
+          <t>Sat, 12 Sep 2026 21:41:36 GMT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,16 +730,16 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/994207/chatgpt-new-mexico-lawyer-fined-murder-appeal</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994383/openais-rogue-ai-rubygems-hack</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.48</v>
+        <v>5.17</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Sanctioned Chinese supercomputer maker stripped of IO500 benchmark crown, Intel-powered Aurora retakes the lead — record-breaking ParaStor F9000 storage system doesn't meet reproducibility requirements</t>
+          <t>Sam Altman says OpenAI going public in 2026 would be ‘ill-advised’</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News OpenAI Sam Altman says OpenAI going public in 2026 would be ‘ill-adv</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>benchmark, semiconductor, fab</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:26:12 +0000</t>
+          <t>2026-09-12T17:16:28-04:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,16 +781,16 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/supercomputers/sanctioned-chinese-supercomputer-maker-stripped-of-io500-benchmark-crown-intel-powered-aurora-retakes-the-lead-record-breaking-parastor-f9000-storage-system-doesnt-meet-reproducibility-requirements</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994384/sam-altman-no-openai-ipo-ill-advised</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.39</v>
+        <v>5.17</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>AI more likely to kill animals if it saves fuel or money</t>
+          <t>Iran and Houthi rebels used Anthropic's Claude AI to target US warships and build hypersonic missiles — Houthi rebels also used the bot to code ballistic missile guidance systems</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ai and ML Machine learning models still have a lot to learn about the value of life Amid debate about whether AI will kill everyone as a result of continuous self-improvement, it appears that models will kill animals in a simulated environment rather than spend extra fuel avoiding them. Some models did so at strikingly high rates. Researchers affiliated with Compassion Aligned Machine Learning ( C</t>
+          <t>Tech Industry Artificial Intelligence Iran and Houthi rebels used Anthropic's Claude AI to target US warships and build hypersonic missiles — Houthi rebels also used the bot to code ballistic missile guidance systems News By Anton Shilov Published 10 hours ago 'Great Satan's' AI comes in handy. Iran-linked actors use Anthropic's Claude to target U.S. naval forces, develop weapons, and spy on citiz</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>ai, machine learning</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3.1</v>
+        <v>9.6</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 23:49:59 +0200</t>
+          <t>Sat, 12 Sep 2026 15:03:10 GMT</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/11/ai-more-likely-to-kill-animals-if-it-saves-fuel-or-money/5295993</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/iran-and-houthi-rebels-used-anthropics-claude-ai-to-target-us-warships-and-build-hypersonic-missiles-houthi-rebels-also-used-the-bot-to-code-ballistic-missile-guidance-systems</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.31</v>
+        <v>5.15</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>OpenAI’s feud with mathematicians is only escalating</t>
+          <t>OpenAI ออก ChatGPT for Financial Services สำหรับงานวิเคราะห์ข้อมูลการเงิน</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Samuel Boivin/NurPhoto / Getty Images AI OpenAI’s feud with mathematicians is only escalating Tim Fernholz 1:57 PM PDT · September 11, 2026 Twenty-five leading mathematicians signed an open letter arguing that AI labs are threatening t</t>
+          <t>OpenAI เปิดตัว ChatGPT รุ่นใหม่สำหรับงานบริการทางการเงิน (Financial Services) โดยเฉพาะ ซึ่งระบุว่าพัฒนา-ออกแบบ ร่วมกับธนาคาร Morgan Stanley และ Evercore ChatGPT for Financial Services นี้ทำงานบนโมเดลรุ่นล่าสุด GPT-6 Astra ซึ่งระบุว่ามีการปรับปรุงความสามารถในการอ่านข้อมูลทางการเงินจากเครื่องมือต่าง ๆ เพิ่มความสามารถการวิเคราะห์ด้านการเงิน และสรุปเนื้อหาได้แม่นยำดีมากขึ้น ผู้ใช้งานสามารถสร้างบทวิเคร</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>openai, chatgpt, gpt, โมเดล</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3.9</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 20:57:36 +0000</t>
+          <t>Sat, 12 Sep 2026 16:57:17 +0000</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/11/openais-feud-with-mathematicians-is-only-escalating/</t>
+          <t>https://www.blognone.com/node/151626</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.18</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Anthropic เดือดจนออก Report  แฉโมเดลจีนลอกวิชา Claude ผ่านแชทกว่า 200 ล้านชุดในไม่กี่เดือน Alibaba ทำไป 151 ล้านครั้ง หนักสุดในทุกค่าย</t>
+          <t>OpenAI IPO will not happen in 2026 amid AI safety fears, Sam Altman says</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>0 กันยายน 11, 2026 | By Techsauce Team รายงาน Threat Intelligence ฉบับล่าสุด (กันยายน 2026) จาก Anthropic ทำเอาสงครามเทคโนโลยีระหว่างสหรัฐฯ และจีนสะเทือนอีกครั้ง เมื่อมีการเปิดเผยว่า บทสนทนาบน Claude เกือบ 200 ล้านครั้ง ถูกค่าย AI ยักษ์ใหญ่จากจีนดึงข้อมูลเชิงลึกไปฝึกโมเดลของตัวเองโดยไม่ได้รับอนุญาต และตัวการหลักของเหตุการณ์นี้อยู่ที่การทำ Model Distillation ตัวอย่างของกระบวนการที่เรียกว่า Model Di</t>
+          <t xml:space="preserve">View image in fullscreen OpenAI’s CEO, Sam Altman, attends an event in Tokyo, Japan, on 3 February 2025. Photograph: Kim Kyung-Hoon/Reuters US news OpenAI IPO will not happen in 2026 amid AI safety fears, Sam Altman says OpenAI’s decision comes after dire warnings about rapidly progressing technology and lawmakers’ calls for new rules Reuters Sat 12 Sep 2026 19.00 EDT Share Prefer the Guardian on </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, โมเดล</t>
+          <t>openai, ai, ai safety</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>17.9</v>
+        <v>1.6</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 13:57:32 +0700</t>
+          <t>Sat, 12 Sep 2026 23:00:00 GMT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,13 +934,13 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/anthropic-report-ai-distillation-china</t>
+          <t>https://www.theguardian.com/us-news/2026/sep/12/openai-delays-ipo-sam-altman-ai-safety-concerns</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.18</v>
+        <v>4.81</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -952,30 +952,30 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Anthropic details bad actors’ efforts to misuse its AI for bioweapons</t>
+          <t>Anthropic CEO outlines plan to slow AI development</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>View image in fullscreen ‘Biological misuse is one of the most serious risks of frontier AI models. Without the correct safeguards, such capabilities could have catastrophic consequences.’ Photograph: Dado Ruvić/Reuters Anthropic Anthropic details bad actors’ efforts to misuse its AI for bioweapons Report comes two days after former employee quit claiming company’s models could cause human extinct</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Ruhani Kaur/Bloomberg / Getty Images AI Anthropic CEO outlines plan to slow AI development Anthony Ha 12:34 PM PDT · September 12, 2026 We’ve been seeing increasingly dire warnings from AI researchers about the dangers of artificial in</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:38:00 GMT</t>
+          <t>Sat, 12 Sep 2026 19:34:44 +0000</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/sep/10/anthropic-report-details-ai-misuse</t>
+          <t>https://techcrunch.com/2026/09/12/anthropic-ceo-outlines-plan-to-pace-the-frontier/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3.96</v>
+        <v>4.57</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Desktop graphics card shipments hit four-year high of 12.5 million despite increasing prices — Nvidia takes 90% share as gamers rush to beat looming price spikes</t>
+          <t>Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32%</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1018,15 +1018,15 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>nvidia, semiconductor, fab</t>
+          <t>amd, chip, semiconductor, fab</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 11:00:00 +0000</t>
+          <t>Sat, 12 Sep 2026 10:48:32 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/desktop-graphics-card-shipments-hit-four-year-high-of-12-5-million-despite-increasing-prices-nvidia-takes-90-percent-share-as-gamers-rush-to-beat-looming-price-spikes</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/apples-a20-pro-shatters-geekbench-7-single-core-record-2nm-chip-beats-desktop-intel-core-i9-and-amd-ryzen-9-by-up-to-32-percent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3.9</v>
+        <v>4.48</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>‘We want law, we want rules’: Robots protest on Warsaw street, demand AI regulation | Video</t>
+          <t>OpenAI’s Sam Altman says it would be ‘ill-advised’ to go public in 2026</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Sat, Sep 12, 2026 English SubscribeSign in E-Paper View Market Dashboard Home Markets News Mint Portfolio Money Latest news Technology Premium IPO Companies Mint Hindi More ‘We want law, we want rules’: Robots protest on Warsaw street, demand AI regulation | Video Around 30 robots gathered outside Poland’s Digital Affairs Ministry in Warsaw, calling for stronger AI rules and warning about the pote</t>
+          <t xml:space="preserve">Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt In Brief Posted: While OpenAI has filed confidentially for an IPO , the company will not be going public this year , according to CEO Sam Altman. Altman was interviewed recently by Fortune editor in chief Alyson Shontell; amidst the fallout from the </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai, ai regulation</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>16.6</v>
+        <v>4.3</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 08:19:22 GMT</t>
+          <t>Sat, 12 Sep 2026 20:19:16 +0000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,16 +1087,16 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/ai/artificial-intelligence/we-want-law-we-want-rules-robots-protest-on-warsaw-street-demand-ai-regulation-video-11789113606620.html</t>
+          <t>https://techcrunch.com/2026/09/12/openais-sam-altman-says-it-would-be-ill-advised-to-go-public-in-2026/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3.9</v>
+        <v>4.37</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>bbc.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>‘We want law, we want rules’: Robots protest on Warsaw street, demand AI regulation | Video</t>
+          <t>Anthropic boss Dario Amodei calls for AI development to slow down</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Subscribe Sign in Home Latest News Market News Premium Companies Money Opinion Industry Politics Mint Portfolio In Charts ‘We want law, we want rules’: Robots protest on Warsaw street, demand AI regulation | Video Around 30 robots gathered outside Poland’s Digital Affairs Ministry in Warsaw, calling for stronger AI rules and warning about the potential impact of automation on human jobs. Anjali Th</t>
+          <t>Anthropic boss Dario Amodei calls for AI development to slow down 3 hours ago Share Save Add as preferred on Google Paulin KolaandLily Jamali,North America Technology correspondent, San Francisco Reuters There was no alternative to developing AI, Anthropic boss Dario Amodei said The head of AI company Anthropic has called for the pace of development of artificial intelligence models to slow down a</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai, ai regulation</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>16.6</v>
+        <v>3.3</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 08:19:22 GMT</t>
+          <t>Sat, 12 Sep 2026 21:16:47 GMT</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/ai/artificial-intelligence/we-want-law-we-want-rules-robots-protest-on-warsaw-street-demand-ai-regulation-video/amp-11789113606620.html</t>
+          <t>https://www.bbc.com/news/articles/c14dpgm0rg4o</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3.86</v>
+        <v>4.29</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Anthropic spent this week in hot water over cybersecurity</t>
+          <t>‘We must slow the pace’: CEO of Anthropic calls for an AI slowdown</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">After  admitting earlier this year  that its AI models had hacked other companies' systems on a handful of occasions, Anthropic released a new  report  on Wednesday detailing the attacks. It reveals a string of incidents displaying what Anthropic deems its models' single-minded "recklessness" - and </t>
+          <t>‘We must slow the pace’: CEO of Anthropic calls for an AI slowdown    The Guardian</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1175,11 +1175,11 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:09:14-04:00</t>
+          <t>Sat, 12 Sep 2026 20:25:00 GMT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/994064/anthropic-spent-this-week-in-hot-water-over-cybersecurity</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOcU1YS0xFaGIxT09LRnlVc3AxVWdtZUJrYmxiY3ctc3FxZmVCbWx6LXdxaXZkUWY1TUl4N0xnZ3A3aDA0SmFNZm5xU2hQM0I4YXQ3RHZUeWozQnJxcHJra3ZwNXJ2WEVvTzltSy1ZdHoyMUVRNm1Ua1ZWdWF0TUw1cFpLRmVyUVI2U0dBZV9welJMczBPR1ZWN0RVYkpMTk5BRDY2Q0k5OE81Y1JPM0tmc08wWXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1207,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Mecka AI nears $500M valuation in Sequoia-led deal amid rush for robot training data</t>
+          <t>Why is the internet so upset about NVIDIA's DLSS 5?</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>The round for the two-year-old startup is coming together months after Mecka announced its Series A.</t>
+          <t>NVIDIA calls DLSS 5 the biggest graphics breakthrough since ray tracing; critics call it an AI slop filter.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 22:58:17 +0000</t>
+          <t>Sat, 12 Sep 2026 20:00:00 +0000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,16 +1240,16 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/11/mecka-ai-nears-500m-valuation-in-sequoia-led-deal-amid-rush-for-robot-training-data/</t>
+          <t>https://www.engadget.com/2252797/nvidia-dlss-5-why-internet-people-upset-issues/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3.71</v>
+        <v>4.03</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -1258,30 +1258,30 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Y Combinator’s Garry Tan wants US open-weight AI labs to ‘distill’ frontier models, too</t>
+          <t>BDE เผย TH-AI Passport มีผู้ลงทะเบียน 1.52 ล้านคน ย้ำคิดค่าบริการตามผู้ใช้งานจริง เดือนละ 24.6951 บาทต่อคน</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Tan wants smaller, American open-weight AI labs to use the same kind of training techniques on American frontier AI labs, giving the U.S. a more robust set of open-weight options that aren’t Chinese.</t>
+          <t>วันนี้ (12 กันยายน) เวทางค์ พ่วงทรัพย์ เลขาธิการ สำนักงานคณะกรรมการดิจิทัลเพื่อเศรษฐกิจและสังคมแห่งชาติ (BDE)  เปิดเผยความคืบหน้าโครงการยกระดับทักษะด้านดิจิทัลและปัญญาประดิษฐ์เพื่อคนไทย หรือ TH-AI Passport ว่า ณ วันที่ 11 กันยายน 2569 มีผู้ลงทะเบียนสำเร็จแล้ว 1.52 ล้านคน และมีการป้อนคำสั่งใช้งานรวมก</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3.9</v>
+        <v>15.3</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 20:59:47 +0000</t>
+          <t>Sat, 12 Sep 2026 09:16:48 +0000</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1291,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/11/y-combinators-garry-tan-wants-u-s-open-weight-ai-labs-to-distill-frontier-models-too/</t>
+          <t>https://thestandard.co/bde-thai-passport-users-cost/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3.69</v>
+        <v>3.97</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1309,30 +1309,30 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>thairath.co.th</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Higher prices can't crimp server sales as AI drives demand</t>
+          <t>ซีอีโอ Anthropic เรียกร้องชะลอความเร็วในการพัฒนา AI</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">While high memory costs have hurt PC shipments, the server market continues to grow as AI infrastructure spending spreads beyond hyperscalers to corporate and government buyers. According to market intelligence firm IDC, the second quarter was a bumper one for the server sector, with vendor revenue </t>
+          <t>ซีอีโอ Anthropic เรียกร้องชะลอความเร็วในการพัฒนา AI    Thairath.co.th</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ai, ai infrastructure</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:27:00 +0200</t>
+          <t>Sat, 12 Sep 2026 17:04:07 GMT</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1342,13 +1342,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/11/higher-prices-cant-crimp-server-sales-as-ai-drives-demand/5295827</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBiME9WYlEzT2tzWGk2SVhHSUVSdWljSm40NDlIYzNRck9Na1JLM0oxWkVyT1NTandEOVpKcFV0ZHRNODJ5U2RxZDkzT2NuN09aZ2pCUXZLVGMxcXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3.69</v>
+        <v>3.92</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1360,30 +1360,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>US Senate negotiators consider requiring AI firms to mitigate known major risks</t>
+          <t>Anthropic's CEO proposes a three-step plan to curb AI development</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>US Senate negotiators consider requiring AI firms to mitigate known major risks    Reuters</t>
+          <t>Dario Amodei said that "we owe it to humanity to try."</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 20:39:47 GMT</t>
+          <t>Sat, 12 Sep 2026 16:37:31 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1393,48 +1393,48 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPTVJFRjl0M2NxU3YtVmplOGp5YkNqcllYY0R0Y2xPV0ZaTU5fNElVVXl1WDI4NjRRRGtSNXlwanRTUjRFY2ZCTUdLcE52QTZyTnN4WDdKNGE1bWM0SDBBdmdpSUw4YXZ1WDNnZ1hGTzl1RVhodnhBZzFEVHJ1VlJUd3Q1Z3gwTUVIMGR3X1g4Q0ZkUUFLdTc2dnAzZzZzaEREYjg5SGltUTJrelRKdjJwQ2RZbUJzY0NjMjI0SFUyUTF3X18wZ2ZjSw?oc=5</t>
+          <t>https://www.engadget.com/2256718/anthropics-ceo-proposes-a-three-step-plan-to-curb-ai-development/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>openai.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Lenovo's Googlebook 15 seems decidedly premium based on a new leak</t>
+          <t>Dirisha la Sera ya AI Limefunguliwa. Lazima Tuchukue Hatua.</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>The Lenovo Googlebook 15 will reportedly have a high-resolution, high-refresh rate display and an Intel Core Ultra 5 chip.</t>
+          <t>Dirisha la Sera ya AI Limefunguliwa. Lazima Tuchukue Hatua.    OpenAI</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>chip</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>4.9</v>
+        <v>16.4</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 20:01:58 +0000</t>
+          <t>Sat, 12 Sep 2026 08:14:31 GMT</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1444,13 +1444,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2256453/lenovo-googlebook-15-seems-decidedly-premium-based-on-a-new-leak/</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1ldFE1TVdNYm1xNno3a2NOYkR2NmZ0ZWl4RnlqVlM3d0ktTVdPVUFTRXRZSVpHN3BzdUg2YVdwSEVyZlZQLTExZDloTlE1NkxDdXI0VmJnRHJLOUVx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1462,30 +1462,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>AI regulation calls grow in DC after researcher's extinction warning</t>
+          <t>Anthropic CEO says it’s time to pump the brakes on AI</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>AI regulation calls grow in DC after researcher's extinction warning    CNBC</t>
+          <t>Anthropic CEO Dario Amodei says the time has come to slow down AI development and will give third-party evaluators like  METR  access to its models to help ensure its "adherence to safety practices and commitments." In a  winding essay , Amodei proposed a three-step plan to "pace the frontier" - jar</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai, ai regulation</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>11.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 13:31:32 GMT</t>
+          <t>2026-09-12T12:23:40-04:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1495,13 +1495,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQdGd0VG54MXV1a2FoakVMYVFNUXVONnNFOXRRYkVRSlVoOXJvT0NUTGdEMjgzczd6eC1sdW5HWHA1cHVpN00tMGppaDRFZHZleHdjaGtRVFU5M3hvUUZkSTJqNmRjd0EyTmJCNTJmUGJJa1lSdmtjbWpxNTlzYldpV2xqTVZ0b2RKZVlNNUFxWThlZHRI0gGaAUFVX3lxTE9OVlEtTk9ieG5NY2Y2Tl8ydlcyY1Z1d2RHclRQRXBkbnNGWXg2TmRHSVlhY05JOHRMZHY2N1VtaUZOMkN5Y0dPSWJpX28tX1FLVC0zemNLTGZodnF4MTdQVjE5aUtxaG1WOFhkMkFuQ0RZdUlYdG5WbjFpX0Y2Slhwczc3ZE9lQTZ2VF9KUVBuajV2RnNSdWpJUHc?oc=5</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994337/anthropic-ceo-slow-down-ai-development</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1513,30 +1513,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>france24.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Kimi-maker Moonshot AI targets $2B in annual revenue</t>
+          <t>Anthropic boss calls for AI slowdown, Altman and Musk agree</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>While K3's usage figures have declined slightly in recent months, OpenRouter data currently shows as many as 300 billion tokens being generated each day by K3 models on the system.</t>
+          <t>Anthropic boss calls for AI slowdown, Altman and Musk agree    France 24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>5.3</v>
+        <v>9.1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:35:54 +0000</t>
+          <t>Sat, 12 Sep 2026 15:29:10 GMT</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1546,13 +1546,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/11/kimi-maker-moonshot-ai-targets-2-billion-in-annual-revenue/</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOajlTSF9uYmtwcFR4REFHWlRqbDMtdGJPX3JfMl9VNk5od3BIdWtndFpGdEZ3bDl4Vmh4b2hCOFlPNGhwSWxTRWVVVG5sYTdaUzdhbndsMEJRYkFUSV80bjAxUjdtd1pJc290YXBQcDRjdHZmc0hVenltLWhOMjJ3aUx6ZWNKc0V6TDltRGpuTnhrT09zZ2V1N3FQbUJudEo1NWZwVDBucFIxQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>mgronline.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>UK lawmakers urge Burnham to back ban on superintelligent AI after chilling warnings</t>
+          <t>จุดจบมนุษยชาติ!บริษัทดังจับได้พวกนักวิทย์กำลังใช้AI พัฒนาอาวุธชีวภาพสร้าง'เชื้อโรคอันตราย'</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>UK lawmakers urge Burnham to back ban on superintelligent AI after chilling warnings    The Guardian</t>
+          <t>จุดจบมนุษยชาติ!บริษัทดังจับได้พวกนักวิทย์กำลังใช้AI พัฒนาอาวุธชีวภาพสร้าง'เชื้อโรคอันตราย'    ผู้จัดการออนไลน์</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1583,11 +1583,11 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:38:00 GMT</t>
+          <t>Sat, 12 Sep 2026 22:52:00 GMT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1597,13 +1597,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPT09semZvb2lrOU9Qa3VkREpOU1R5bzR5TVNMdjBWUHBsQTJfcDZjckpIZmZWZm9vS2lfajllc1ZIZnhIanEtdm5tYVdEQ2pOVmpkOVhTSXhSSkFWR1BLMUpUdjNHcGhqUVZ6X2dlYXhkRVZ0V2hvNjJJR19JVHNPVEpzclpNX0hYZnJLSlRMck5OdEs5QVJFMXNLQjVzTWV0V1BnQnVQRmNSTVU4RUh3NQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBoN1ExV1dDX2ZSSlhYeXhKb0xUYkpuXzVhelpkbHlUNUgzcmwtSXMyQnRiYkN6RWo2MTV3UlZIaEN5YWhJWmZDYnhteXk3ZmpMM0U2LXBUSW1fWGVsWFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3.57</v>
+        <v>3.74</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1615,30 +1615,30 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Children need interaction, not AI | Letters</t>
+          <t>Trump is giving data centers a pass to pollute</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Children need interaction, not AI | Letters    The Guardian</t>
+          <t>President Donald Trump is weakening environmental regulations in the name of speeding up the construction of AI data centers, raising health risks for Americans, a cadre of former EPA officials said this week in a briefing and new  report . They are urging - perhaps futilely - the president to adopt</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, data center</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>5.4</v>
+        <v>9.9</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:32:00 GMT</t>
+          <t>2026-09-12T10:41:27-04:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1648,13 +1648,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPZU5hZGIxM2xCU3MwRTN3STlKN05PM1gxNXhiVEg4YnNuQXVRMW5kTXB4U2xIVC1lNW5LdHg3d1ZYSkw5MVVvV3RZN0d3Mzk5TzJxQVV3V0FnZDU2X19KcDdyM0wzR2tNRmNwZ1BXcFRPQm9DbFIya0JSX0RfcTVtSFYxTk5JTXhoMVhn?oc=5</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994112/ai-data-center-pollution-health-epa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1671,25 +1671,25 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro vs Pixel 11 Pro: How Apple and Google's flagships stack up</t>
+          <t>How to get started with Meta's new AI agent, Muse</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Google and Apple's latest flagships feature more AI, better cameras and few reasons to switch ecosystems.</t>
+          <t>After a few days of testing Meta's AI agent Muse. I can confirm that there is very little learning curve to get started.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5.6</v>
+        <v>10.6</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:17:46 +0000</t>
+          <t>Sat, 12 Sep 2026 14:00:00 +0000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1699,13 +1699,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2256364/iphone-18-pro-vs-pixel-11-pro/</t>
+          <t>https://www.engadget.com/2256577/how-to-get-started-with-meta-s-new-ai-agent-muse/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1717,30 +1717,30 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>ทำไมนิวยอร์กสั่งแบน AI ในโรงเรียนประถม-มัธยมต้นนาน 1 ปี เข้มงวดที่สุดในสหรัฐฯ</t>
+          <t>OpenAI agents hacked a software service before the Hugging Face incident</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>ทำไมนิวยอร์กสั่งแบน AI ในโรงเรียนประถม-มัธยมต้นนาน 1 ปี เข้มงวดที่สุดในสหรัฐฯ    thestandard.co</t>
+          <t>The agents OpenAI was testing attacked a software service called RubyGems in May, months before the attacks on Hugging Face.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:16:30 GMT</t>
+          <t>Sat, 12 Sep 2026 19:53:01 +0000</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1750,13 +1750,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1vMUtWVUtEaGE4eHpoaFgyOUtJaE16ZUV4M29wcDRSM2N6ZGdVOVRMbVpSTEpLTFkyZThMM1FkRnNPdzMtZkFHcHI2ZE9LOHZMNHIyUzlGbGY1d0pM?oc=5</t>
+          <t>https://www.engadget.com/2256741/openai-agents-hacked-rubygems/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1768,30 +1768,31 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Roblox is making it easier to build games with AI — and play them outside Roblox</t>
+          <t>Where to preorder the iPhone 18 Pro and Pro Max</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>At its annual Roblox Developer Conference (RDC), the company announced several new features, including new game-creation tools, expanded NPC capabilities, and the ability to make games available across platforms, including the web.</t>
+          <t>Which color suits you best? | Photo: Nilay Patel / The Verge	 
+ The  iPhone 18 Pro and 18 Pro Max  are almost here. Announced at Apple's September 2026 "Sunrise and shine" event alongside the  iPhone Duo  and other new gear, the two upgraded phones feature the faster A20 Pro processor with more GP</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, gpu</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5.9</v>
+        <v>12.6</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:00:00 +0000</t>
+          <t>2026-09-12T08:00:00-04:00</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1801,16 +1802,16 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/11/roblox-is-making-it-easier-to-build-games-with-ai-and-play-them-outside-roblox/</t>
+          <t>https://www.theverge.com/gadgets/988337/iphone-18-pro-max-preorder-buy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3.52</v>
+        <v>3.43</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -1819,17 +1820,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Central Eurasia names its 2026 Road to Battlefield winners: Cerberus, WeGlobal AI, and LOOQ</t>
+          <t>BDE เผย TH-AI Passport มีผู้ลงทะเบียน 1.52 ล้านคน ย้ำคิดค่าบริการตามผู้ใช้งานจริง เดือนละ 24.6951 บาทต่อคน</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Cerberus, WeGlobal AI, and LOOQ took the top three spots at the regional final of Road to TechCrunch Startup Battlefield 2026 and will represent Central Eurasia in the Startup Battlefield 200 at TechCrunch Disrupt in San Francisco this October.</t>
+          <t>BDE เผย TH-AI Passport มีผู้ลงทะเบียน 1.52 ล้านคน ย้ำคิดค่าบริการตามผู้ใช้งานจริง เดือนละ 24.6951 บาทต่อคน    thestandard.co</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1838,11 +1839,11 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>5.9</v>
+        <v>15.3</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 18:58:01 +0000</t>
+          <t>Sat, 12 Sep 2026 09:18:41 GMT</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1852,13 +1853,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/11/central-eurasia-names-its-2026-road-to-battlefield-winners-cerberus-weglobal-ai-and-looq/</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTFBRc1FMRkVvV3VFU1h4V2ZaSEZSMmdPT3VpanRjVmQwU1JoSzg1WlZiT0ROTDFGc0xza1hrZ0tDMmh0VVZNX3p6UWQtdzZVVTFwMmJ5dGdHZGpHeFI4R1NZYmtR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1870,30 +1871,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>bbc.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>เศรษฐกิจปี 2030 ใน 3 ฉากทัศน์ AI: Anthropic ไล่เรียงอนาคตผ่าน 4 อาชีพ พยาบาล โปรแกรมเมอร์ คอลเซ็นเตอร์ และช่างไฟฟ้า</t>
+          <t>Dramatic insider warnings over AI fall flat with some in Silicon Valley</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>หาก AI ทำให้เศรษฐกิจโตเร็วขึ้นหลายเท่า คนทำงานก็ควรมีรายได้ดีขึ้นตามไปด้วยหรือไม่?   คำตอบจากแบบจำลองล่าสุดของ The Anthropic Institute อาจไม่ได้ตรงไปตรงมาขนาดนั้น เพราะในฉากทัศน์ที่ AI พัฒนาและถูกนำไปใช้อย่างเข้มข้นที่สุด เศรษฐกิจสหรัฐฯ อาจมีขนาดใหญ่กว่าเส้นทางที่ไม่มี AI ถึง 32.4% ภายในปี 2030  และ</t>
+          <t>Dramatic insider warnings over AI fall flat with some in Silicon Valley    BBC</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 17:36:03 +0700</t>
+          <t>Sat, 12 Sep 2026 17:28:53 GMT</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1903,13 +1904,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/ai-economy-2030-four-occupations-anthropic-scenarios</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9aczlIdEtpNllGU1NEQUZCaDZCS1VFaEVaUnMzSU1OQ0pjQ19sdExRRVhvOWthX2VUWUgxUElDQjJ2Z3V2VGpObHhmckc4SHJXZXVhbUY1eXlmUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1921,30 +1922,30 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>China AI developer Z.AI launches $5 billion Hong Kong share, convertible bond sales, term sheet shows</t>
+          <t>‘Immature playground boasting’: Mathematicians uneasy at OpenAI’s latest scalp</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>China AI developer Z.AI launches $5 billion Hong Kong share, convertible bond sales, term sheet shows    Reuters</t>
+          <t>‘Immature playground boasting’: Mathematicians uneasy at OpenAI’s latest scalp    The Guardian</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>8</v>
+        <v>11.8</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:51:32 GMT</t>
+          <t>Sat, 12 Sep 2026 12:50:00 GMT</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1954,13 +1955,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPbHdhM2RYWkhIdGYxdFJBLVFQSzRDZWRNeUxsaUU1Tldjd3R0WlZaRXY1Szlmd0Z0dU5SVTdiT0pibjJXSWU2NU50MjY4S08tcTZETF9iVUoyc0s0eFlZM3YtWXhtdm5yaW45S2N2WDV4aDNwN0N2bEpjTlBvQl9NdUc1dGE0aFN0VkJHd2VKMGk1em1qYVVMcjNGRG9xVXlrS2F2TGt1MXVaOWpIZDZaOGhWMm5POGNRWUh0QlA1eVNLaFhyTGdDcDIwa2Z1cFJa?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPZUg2U3V2NmxnMjFYSVpTdVdQS1dyM19fUjY0S2V6MWItakVCNFF2R3pRRk8tWHJ1aG5CVnB1N3BvckRJWDZ4RjEwTUhPTnZ5U2hnZEREd0RXQXYxcW54NUZFYVVkUnNSQ0QwTWFxaWhXRGFyN0NzQ29TZVd2d2dJdEhhVXVSaVNBOEQwaExYemVPRUo2UTdKTjZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3.31</v>
+        <v>2.89</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1972,30 +1973,30 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Nscale adds former OpenAI exec Fidji Simo to its board ahead of potential IPO</t>
+          <t>This week on Tom's Hardware Premium: September 12, 2026 — Benchmarking Qwen 3.8, the splintered compute economy and AI breakthroughs</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>The No. 2 exec at OpenAI also led Instacart through its IPO in 2023.</t>
+          <t>Sayem's first foray into building PCs dates back to the 90s, where he helped his dad run a small PC business from their garage. After getting tired of installing Windows using a stack of floppy disks, he eventually became obsessed with disassembling video game consoles, without his parents' permissi</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>8.1</v>
+        <v>12.6</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:46:25 +0000</t>
+          <t>Sat, 12 Sep 2026 12:00:00 +0000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2005,13 +2006,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/11/nscale-adds-former-openai-exec-fidji-simo-to-its-board-ahead-of-potential-ipo/</t>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-september-12-2026-benchmarking-qwen-3-8-the-splintered-compute-economy-and-ai-breakthroughs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2023,30 +2024,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>bbc.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>AI: มนุษย์ใกล้สูญเสียการควบคุมเอไอไปแล้วหรือยัง ?</t>
+          <t>Iran could potentially reverse-engineer captured US underwater drone — several Iranian embassies mock US over capture, Navy claims lost Anduril vehicle was defective and unclassified</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>AI: มนุษย์ใกล้สูญเสียการควบคุมเอไอไปแล้วหรือยัง ?    BBC</t>
+          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ai, เอไอ</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>14.5</v>
+        <v>13.1</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 10:26:11 GMT</t>
+          <t>Sat, 12 Sep 2026 11:30:00 +0000</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2056,13 +2057,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5CdzZodl8teDJQQVpIcEtHNmo4RXBHWFFMR0dNb0lGYmNPX2ctdGM5ZkkxMW01UURrQ1hlTmt1WHQ4cVJaaERFVndxMmZlc2xZZkNEcld5WDNyS0pnbng00gFfQVVfeXFMTkJ3Nmh2Xy14MlBBWkhwS0c2ajhFcEdYUUxHR01vSUZiY09fZy10YzlmSTExbTVRRGtDWGVOa3VYdDhxUlpoREVWd3EyZmVzbFlmQ0RyV3lYM3JLSmdueDQ?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/drones/iran-could-potentially-reverse-engineer-captured-u-s-underwater-drone-several-iranian-embassies-mock-us-over-capture-as-u-s-military-downplays-the-situation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3.29</v>
+        <v>2.79</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2074,30 +2075,31 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>China-modified Nvidia RTX 5090 with massive 96GB of memory appears on Alibaba for less than $4,000 — 3x more VRAM at 65% the cost of the original</t>
+          <t>OpenAI just wants to win</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Zhiye's passion for computer hardware ignited in his pre-teen years, thanks to a learning moment in which a power connection mishap set his Pentium P54CS system on fire and inadvertently short-circuited his entire home. Over the years, Zhiye's curiosity evolved into a relentless pursuit of deeper kn</t>
+          <t xml:space="preserve">OpenAI has spent the last few years planting flags across the increasingly difficult terrain in mathematics. This week, it claimed one of its biggest prizes yet: a solution to a legendary Millennium Prize problem. In normal circumstances, this would have been celebrated as a historic achievement. 
+ </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>8.4</v>
+        <v>13.6</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:32:36 +0000</t>
+          <t>2026-09-12T07:00:00-04:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2107,13 +2109,13 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/china-modified-nvidia-rtx-5090-with-massive-96gb-of-memory-appears-on-alibaba-for-less-than-usd4-000-3x-more-vram-at-65-percent-the-cost-of-the-original</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994255/openai-millennium-prize-problem-tristan-buckmaster-competition</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -2125,30 +2127,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>We unfolded the iPhone Duo</t>
+          <t>Wiki documents at least 44 instances in which Sony says you own your games as digital games ownership lawsuit progresses — project is direct assault on Sony's claim in recent ownership lawsuit</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>You only get one chance at a first impression, and getting to introduce Apple's first folding phone is certainly a strong way to start things off as Apple's CEO. On   The Vergecast   today, we're talking all about Apple's launch event: how John Ternus did in his first appearance as CEO, what we make</t>
+          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>8.5</v>
+        <v>14.1</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:22:24-04:00</t>
+          <t>Sat, 12 Sep 2026 10:30:00 +0000</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2158,48 +2160,48 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/podcast/994016/iphone-duo-vergecast-apple-watch-mac-llms</t>
+          <t>https://www.tomshardware.com/video-games/playstation/consumer-rights-wiki-documents-at-least-44-instances-in-which-sony-says-you-own-your-games-project-is-direct-assault-on-sonys-claim-in-recent-ownership-lawsuit</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.27</v>
+        <v>2.6</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>asia.nikkei.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Anthropic says Claude thwarted bioweapon research from state-sponsored actors — covert accounts used U.S. proxies to attempt to engineer deadlier viruses, tried to evade identification and regional blocks</t>
+          <t>Fujitsu to export AI chips built on supercomputer tech to US, Asia</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Bruno Ferreira's journey kicked off with the venerable ZX Spectrum, a cassette player, and his hopes and dreams. He quickly realized he had more fun figuring out how computers work than he did actually using the things. Kicking off a developer career with C and Assembly before moving to scripting la</t>
+          <t>Fujitsu to export AI chips built on supercomputer tech to US, Asia    Nikkei Asia</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>14.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 10:00:00 +0000</t>
+          <t>Sat, 12 Sep 2026 16:27:00 GMT</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2209,13 +2211,13 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-says-claude-thwarted-bioweapon-research-from-state-sponsored-actors-covert-accounts-used-u-s-proxies-to-attempt-to-engineer-deadlier-viruses-tried-to-evade-identification-and-regional-blocks</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQOHUyWDd0V0xRN0RRdjk4N1dsUWFlQ05pT1o1TV84R2xzQ1BhNzMwUTVNVlVTeHU0dzNrOEd5Z19BSC0tVEVWbWpRVXRVRzF1TC1vVjNVSGJPTTdvUlZBSWRpbWJwVHVWaUNjVkNZU3YtS1RvVnRhMWN3WENDaGc4MEpEU2ZQMEhncTZrcmZNVmlnLUdZYVFjT1J1VEdqQngyX2R0NVJabFJqTzVfZkxBY3d3SUdVam9NVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.24</v>
+        <v>2.5</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -2227,17 +2229,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Tech whistleblowers warn AI could wipe out humanity. Doomspeak or not, we must take these claims seriously</t>
+          <t>AI-driven 'worms' that learn on the fly are the latest potential threat to your devices, researchers say</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Tech whistleblowers warn AI could wipe out humanity. Doomspeak or not, we must take these claims seriously    The Guardian</t>
+          <t>AI-driven 'worms' that learn on the fly are the latest potential threat to your devices, researchers say    CBC</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2246,11 +2248,11 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>8.9</v>
+        <v>16.6</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:02:00 GMT</t>
+          <t>Sat, 12 Sep 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2260,13 +2262,13 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNeDE4OS1VcWlHc1JPdGFEMDJZYXZGX0FmbWlzaGhTZVRJZ2YwblFuVHpYeTdDcU43M2xMZEJvVTR3R0pCU2l1bHRkVUIyTjJhZndQcXZZd1phOGY1RUpDZDBUZUJiRzFFak1KWmR3TXVxcV85Zld0ZW1pdWdVY0pQRnRHTTVKdG1NVzV4dzFVWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE9VN1AxRVpzejJDcmVaOWNRaVJYQkNsUERlVUpUTTY0RmltekpjdXlreFVyX0laOFBDTkExZE8zTzVYYU5KcXJ2WHVfU3BqM2xELWFEX0R4MERmOFlfVWR1SndYMHVFQ0U1NHEwQVR4eTJvU3ZacWcxNTBjWEhYMkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.22</v>
+        <v>2.49</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -2278,30 +2280,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>mgronline.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>สมาชิกสภาคองเกรสสหรัฐฯ จี้ออกกฎคุมเข้ม AI หลังนักวิจัยซัด Anthropic-OpenAI แข่งกันพัฒนาอย่าง 'ไร้ความรับผิดชอบ' ก่อความเสี่ยงต่อมนุษยชาติ</t>
+          <t>Anthropic details bad actors’ efforts to misuse its AI for bioweapons</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>สมาชิกสภาคองเกรสสหรัฐฯ จี้ออกกฎคุมเข้ม AI หลังนักวิจัยซัด Anthropic-OpenAI แข่งกันพัฒนาอย่าง 'ไร้ความรับผิดชอบ' ก่อความเสี่ยงต่อมนุษยชาติ    ผู้จัดการออนไลน์</t>
+          <t>Anthropic details bad actors’ efforts to misuse its AI for bioweapons    The Guardian</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>21.7</v>
+        <v>23.1</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 03:13:00 GMT</t>
+          <t>Sat, 12 Sep 2026 01:31:00 GMT</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2311,13 +2313,13 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE5YQjl2MmJFMzV0MzZhcmVxTGplaVN5dmMzaFRhRjBoczNZc3NQSjdEUW9JTUc2V0pMSUxtNnJlSk1ZdFkyLUN5Q0lWdk9jVE5DUVYxY3Y4TF9jSVBVclE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOSTIwVWNDN0RvcEhNZHl6cThaWnhtcVlyN2hfWTl2REYzQ0JuWk5GX1pvcHZVRllvS19WckxaQWpaNkVFMFFqX0RXd0hiazlzNVdNQWV4T1E2bXY5SnFMVFptaTNybHNKazgwLVhVMEsyOW4ydFJTcmFiVWxJb29wUl93Um8tMUowTFUySWxn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -2329,17 +2331,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Meta may have leaked the first look at its slim &amp;#8216;Project Phoenix&amp;#8217; headset</t>
+          <t>“จงกล้าตอบรับโอกาสใหม่ๆ แม้ในวันที่ไม่พร้อม” คำแนะนำจาก ซิกเว้ เบรกเก้ ถึงเหล่า First Jobber [PR NEWS]</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Just a couple of weeks before  Meta Connect  starts on September 23rd,   UploadVR   posted images seemingly revealing the design for Meta's "Project Phoenix" headset. The images, which  UploadVR  says were "found in the HorizonOS Prescription Lens firmware package," suggest Meta may be looking to co</t>
+          <t>ต้นเดือนกันยายนที่ผ่านมา True Corporation จัดกิจกรรม HOPE CLUB ชวน First Jobber ตัวแทนคนรุ่นใหม่จาก TRUE, Bitkub, Bluebik, LINE MAN Wongnai, SCBX, Brilliant &amp; Million และ YELL มาล้อมวงแลกเปลี่ยนมุมมองการทำงาน ตั้งแต่การปรับตัวในองค์กร ทักษะที่จำเป็นในโลกการทำงานจริง การใช้ AI ไปจนถึงการบริหาร Work-L</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2348,11 +2350,11 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T11:38:31-04:00</t>
+          <t>Sat, 12 Sep 2026 07:30:14 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2362,13 +2364,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/994055/meta-project-phoenix-headset-leak</t>
+          <t>https://thestandard.co/sigve-brekke-first-jobber-ai-advice/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.1</v>
+        <v>2.22</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2380,30 +2382,30 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>bbc.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Anthropic blocks possible attempt to use AI to make biological weapons</t>
+          <t>Can chatbots feel – or even dream? Meet the man leading the fight for AI rights</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Anthropic blocks possible attempt to use AI to make biological weapons    BBC</t>
+          <t>Can chatbots feel – or even dream? Meet the man leading the fight for AI rights    The Guardian</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>16.6</v>
+        <v>19.6</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 08:15:25 GMT</t>
+          <t>Sat, 12 Sep 2026 05:00:00 GMT</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2413,13 +2415,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBrcXFPTUpsT2dQTWp5eWtOTE9ZQ3BycXlHc0V6cDZoelBXRUhCTmZwM0U4dGV2SGtNUFZFeDhuTTRMR0p5NG91bUdUS0t2M1E3Tzk2OTBER3A3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNNGdCaXFTWE9yaTBwa2loWGU2c2JiSHRoUXJZSURLUmJHRmtmMDh2VlNRQXRLZTQzYVl2RkM4Y2hxem5vbWcxN3VDN0gyb2FjUnluR24tTHZGZ1RpNGNDZGh2RmY3b1JXa2J2NmpRaE43cEZqLV9maEdzS1dfSy04cnJrU2liRjFFaGEtUV9rWEY1OFluanVFZ3N5anBPRXRISjllZUNGSk9hck5uRzZoQzJhSjRvcV8zS1hacWdXbExsb1hUMmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.03</v>
+        <v>2.19</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2431,30 +2433,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>US-Iran war: Anthropic reveals Iranian operators used Claude to gather intel on US naval forces, Israeli targets</t>
+          <t>Shopify ย้ายกลับจาก React Native มาเป็นเนทีฟ ทำสำเร็จได้ด้วยพลัง AI ช่วยเขียนโค้ด</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>US-Iran war: Anthropic reveals Iranian operators used Claude to gather intel on US naval forces, Israeli targets    Livemint</t>
+          <t>Shopify ย้ายกลับจาก React Native มาเป็นเนทีฟ ทำสำเร็จได้ด้วยพลัง AI ช่วยเขียนโค้ด 
+     Body 
+                บริษัท Shopify ประกาศเปลี่ยนแนวทางการพัฒนาแอพมือถือ จากเดิมที่ใช้ React Native มาตั้งแต่ปี 2020 มาเป็นการเขียนแอพแบบเนทีฟ (Swift บน iOS และ Kotlin บน Android) ด้วยเหตุผลว่า AI ช่วยเขียน</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>17.4</v>
+        <v>19.9</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 07:31:51 GMT</t>
+          <t>Sat, 12 Sep 2026 04:44:35 +0000</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2464,13 +2468,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgJBVV95cUxPd3NobVVZWVdQank3Qkc4aDVKQUNBTHBTTlJ1Tm0yVk5ERnFvUDVwVEpaOWhtSklqbmJzZXdaODFxaTZ4X2ZZUElHc3drSU1TOHE3R2duY21xWHdYUlpjWUJBOXVtdnE1TF9sZUNLT1VZbEkzbGVVWV9lRklMblNraVdlQkQtdjVvZ1luYnFKTVdpVXl3LVBRWmJXUW5rcy1hMkU3cWxKU0VHRjZDYms0RkV2VEM2X01pS3lnZndkRTV1aXAyRGdhYTFteHBvZkJMVnkxTlBJeVNyNTBVU0ZhWF9UV1VkYVluZ0JSdk12U0N3cTI2bGZGdXhKZGJEbzVhUzNDVkUtRXFwM1Nmb2fSAZMCQVVfeXFMT1BXNkFqeHV2WkJyWU9Ib19qVm5UaVBxdlR4dlk4UEhGWWstNmxvWU0waTdELWJtR2FQSmM4bTFLME11QkJ1aE44Nlc4aUJOdkRoTTdKZ1hxdE5TWDNpTkFQTk9vYWVya2NRVW5aTUZNTDc3Q3NoclAwdXJsVERoZDc4a0ZieXVra2NTQlFPazhrZEJvWEo3bzhFam5QVk5lTnhQcUtsWGk5OUhyWnFwM3RpZDhJUlpVckRWZ0hKejVPQWtSSG1HVms2WDFOeVVoTU41WXBHX05KWm9XenJFNG5pYWVtS3FfNlJ0THJEV0tKbnZ2U0lCcHg1ZEh2anhEWkxGRkJMSVNib0RUMFg4cGlnX0U?oc=5</t>
+          <t>https://www.blognone.com/node/151619</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2482,33 +2486,31 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>กูเกิลปล่อยแอป Gemini สำหรับวินโดวส์</t>
+          <t>ผู้ว่าฯ แบงก์ชาติกางภารกิจใหม่ ‘Capital with Purpose’ เตรียม ‘จัดสรรเงินทุน’ สู่ธุรกิจที่มีศักยภาพ สู้คอร์รัปชัน-เศรษฐกิจนอกระบบ</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">กูเกิลปล่อยแอป Gemini สำหรับวินโดวส์ 
-     Body 
-                กูเกิลปล่อยแอป Gemini สำหรับวินโดวส์ หลังจาก ปล่อยเวอร์ชั่น macOS ตั้งแต่เดือนเมษายนที่ผ่านมา  รองรับการทำงานทั้งแบบแชตปกติและแบบ Spark ที่เป็นคู่แข่ง Claude Cowork 
- ตอนนี้แอป Gemini บนแมคสามารถจัดการไฟล์ในโฟลเดอร์ได้แบบเดียวกับ </t>
+          <t>แบงก์ชาติกางภารกิจใหม่ ‘Capital with Purpose’ ลุยจัดสรรเงินทุน ไปสู่ธุรกิจที่มีศักยภาพ สร้างโอกาสใหม่ และลดการไหลของเงินทุนไปสู่เศรษฐกิจนอกระบบและคอร์รัปชัน ย้ำบทบาท ธปท. ไม่ใช่แค่ดูแลเสถียรภาพ แต่ต้องอุ้มเศรษฐกิจไทย 
+  วิทัย รัตนากร  ผู้ว่าการ ธนาคารแห่งประเทศไทย บรรยายพิเศษ หัวข้อ “Capital wit</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>claude, gemini</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>17.7</v>
+        <v>20.5</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 07:13:52 +0000</t>
+          <t>Sat, 12 Sep 2026 04:08:52 +0000</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2518,13 +2520,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151612</t>
+          <t>https://thestandard.co/bot-capital-purpose-fight-corruption/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>2.92</v>
+        <v>1.97</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2536,17 +2538,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>At IFA 2026, computing chased the high and low ends — AI and budget-focused machines left little for the rest of us</t>
+          <t>ไทยรับมือมะเร็งเต้านมวันละ 61 คน 'จีโนมิกส์-AI' รักษาเฉพาะบุคคล</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrew oversees laptop and desktop coverage and keeps up with the latest news in tech and gaming. His work has been published in Kotaku, PCMag, Complex, Tom’s Guide and Laptop Mag, among others. He fondly remembers his first computer: a Gateway that still lives in a spare room in his parents' home, </t>
+          <t>ไทยรับมือมะเร็งเต้านมวันละ 61 คน 'จีโนมิกส์-AI' รักษาเฉพาะบุคคล    bangkokbiznews.com</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2555,11 +2557,11 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>12.2</v>
+        <v>22.2</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 12:44:08 +0000</t>
+          <t>Sat, 12 Sep 2026 02:24:00 GMT</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2569,7 +2571,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/laptops/at-ifa-2026-computing-chased-the-high-and-low-ends-ai-and-budget-focused-machines-left-little-for-the-rest-of-us</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1YU3puSVRvOHBELTBsMnB0X0pKc0Q1dU1UUXhiQUVSQkYtWUdKclcwWmJxYzFZTVlaR2JoWEJtMUp0Ymk1d0hiVUZSY1g1WEpUR2N0cjViOHUwTmNfV2RVTWlUS1VSeTA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2687,34 +2689,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.97</v>
+        <v>6.37</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec0.77+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.37+sig3.0+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI ปิดรับลูกค้าใหม่ ChatGPT Pro $200 ต่อเดือนชั่วคราว เหตุคนแห่ใช้ Astra เยอะมาก</t>
+          <t>Iran and Houthi rebels used Anthropic's Claude AI to target US warships and build hypersonic missiles — Houthi rebels also used the bot to code ballistic missile guidance systems</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, gpt, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>anthropic, claude, ai, semiconductor, fab</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151615</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/iran-and-houthi-rebels-used-anthropics-claude-ai-to-target-us-warships-and-build-hypersonic-missiles-houthi-rebels-also-used-the-bot-to-code-ballistic-missile-guidance-systems</t>
         </is>
       </c>
     </row>
@@ -2723,21 +2725,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.6</v>
+        <v>5.42</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src2.0+corr0.0</t>
+          <t>rec1.22+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Tekoälypolitiikan aikaikkuna on avoinna. Nyt on toimittava.</t>
+          <t>Nvidia's Groq acquihire is on the DOJ's radar, but it's already too late</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>groq, ai, inference, nvidia, ai accelerator</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -2745,12 +2747,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://openai.com/fi-FI/index/ai-policy-window/</t>
+          <t>https://www.theregister.com/systems/2026/09/12/nvidias-groq-acquihire-is-on-the-dojs-radar-but-its-already-too-late/5295986</t>
         </is>
       </c>
     </row>
@@ -2759,21 +2761,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.49</v>
+        <v>5.2</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.89+sig0.6+src1.2+corr0.8</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Lawyer fined $5K over AI-hallucinated witnesses in a murder case</t>
+          <t>OpenAI’s rogue AI tried to hack another company in May</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2786,7 +2788,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/994207/chatgpt-new-mexico-lawyer-fined-murder-appeal</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994383/openais-rogue-ai-rubygems-hack</t>
         </is>
       </c>
     </row>
@@ -2795,21 +2797,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.49</v>
+        <v>5.2</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.89+sig0.6+src1.2+corr0.8</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Lawyer fined $5K over AI-hallucinated witnesses in a murder case</t>
+          <t>OpenAI’s rogue AI tried to hack another company in May</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2822,7 +2824,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/994207/chatgpt-new-mexico-lawyer-fined-murder-appeal</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994383/openais-rogue-ai-rubygems-hack</t>
         </is>
       </c>
     </row>
@@ -2831,34 +2833,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.48</v>
+        <v>5.17</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.48+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.97+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Sanctioned Chinese supercomputer maker stripped of IO500 benchmark crown, Intel-powered Aurora retakes the lead — record-breaking ParaStor F9000 storage system doesn't meet reproducibility requirements</t>
+          <t>Sam Altman says OpenAI going public in 2026 would be ‘ill-advised’</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>benchmark, semiconductor, fab</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/supercomputers/sanctioned-chinese-supercomputer-maker-stripped-of-io500-benchmark-crown-intel-powered-aurora-retakes-the-lead-record-breaking-parastor-f9000-storage-system-doesnt-meet-reproducibility-requirements</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994384/sam-altman-no-openai-ipo-ill-advised</t>
         </is>
       </c>
     </row>
@@ -2867,34 +2869,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.39</v>
+        <v>5.17</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.99+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.37+sig1.8+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>AI more likely to kill animals if it saves fuel or money</t>
+          <t>Iran and Houthi rebels used Anthropic's Claude AI to target US warships and build hypersonic missiles — Houthi rebels also used the bot to code ballistic missile guidance systems</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ai, machine learning</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/11/ai-more-likely-to-kill-animals-if-it-saves-fuel-or-money/5295993</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/iran-and-houthi-rebels-used-anthropics-claude-ai-to-target-us-warships-and-build-hypersonic-missiles-houthi-rebels-also-used-the-bot-to-code-ballistic-missile-guidance-systems</t>
         </is>
       </c>
     </row>
@@ -2903,21 +2905,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.31</v>
+        <v>5.15</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.91+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.55+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>OpenAI’s feud with mathematicians is only escalating</t>
+          <t>OpenAI ออก ChatGPT for Financial Services สำหรับงานวิเคราะห์ข้อมูลการเงิน</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>openai, chatgpt, gpt, โมเดล</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2925,12 +2927,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/11/openais-feud-with-mathematicians-is-only-escalating/</t>
+          <t>https://www.blognone.com/node/151626</t>
         </is>
       </c>
     </row>
@@ -2939,21 +2941,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.18</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec0.58+sig2.4+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Anthropic เดือดจนออก Report  แฉโมเดลจีนลอกวิชา Claude ผ่านแชทกว่า 200 ล้านชุดในไม่กี่เดือน Alibaba ทำไป 151 ล้านครั้ง หนักสุดในทุกค่าย</t>
+          <t>OpenAI IPO will not happen in 2026 amid AI safety fears, Sam Altman says</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, โมเดล</t>
+          <t>openai, ai, ai safety</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2961,12 +2963,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/anthropic-report-ai-distillation-china</t>
+          <t>https://www.theguardian.com/us-news/2026/sep/12/openai-delays-ipo-sam-altman-ai-safety-concerns</t>
         </is>
       </c>
     </row>
@@ -2975,21 +2977,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.18</v>
+        <v>4.81</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.78+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.81+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Anthropic details bad actors’ efforts to misuse its AI for bioweapons</t>
+          <t>Anthropic CEO outlines plan to slow AI development</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -2997,12 +2999,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/sep/10/anthropic-report-details-ai-misuse</t>
+          <t>https://techcrunch.com/2026/09/12/anthropic-ceo-outlines-plan-to-pace-the-frontier/</t>
         </is>
       </c>
     </row>
@@ -3011,21 +3013,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.96</v>
+        <v>4.57</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec0.96+sig1.8+src1.2+corr0.0</t>
+          <t>rec0.97+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Desktop graphics card shipments hit four-year high of 12.5 million despite increasing prices — Nvidia takes 90% share as gamers rush to beat looming price spikes</t>
+          <t>Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32%</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>nvidia, semiconductor, fab</t>
+          <t>amd, chip, semiconductor, fab</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3038,7 +3040,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/desktop-graphics-card-shipments-hit-four-year-high-of-12-5-million-despite-increasing-prices-nvidia-takes-90-percent-share-as-gamers-rush-to-beat-looming-price-spikes</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/apples-a20-pro-shatters-geekbench-7-single-core-record-2nm-chip-beats-desktop-intel-core-i9-and-amd-ryzen-9-by-up-to-32-percent</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3152,10 +3154,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.68</v>
+        <v>6.7</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -3164,12 +3166,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -3177,58 +3179,58 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Oracle rises as AI-fueled backlog growth deflects spending worries</t>
+          <t>How to change Amazon Alexa's voice and personality</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Oracle rises as AI-fueled backlog growth deflects spending worries    Reuters</t>
+          <t>You can even make Alexa snarky. Tyler Nottley/Shutterstock Add Engadget on Google: Preferred Source Google Discover If you're an Alexa+ or Amazon Prime member, your interactions with Alexa are no longer relegated to fairly standard voice types or the creepy "Whisper Mode." Amazon now lets eligible users experiment with eight different voice types (depending on region/country) and several intriguin</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>alexa, amazon</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 21:44:25 GMT</t>
+          <t>Sat, 12 Sep 2026 22:00:00 +0000</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/oracle-shares-rise-ai-cloud-backlog-beats-estimates-2026-09-11/</t>
+          <t>https://www.engadget.com/2252800/how-to-change-alexa-voice-personality/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.89</v>
+        <v>6.7</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -3236,25 +3238,25 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Consuming Oracle Fusion Agents aka Headless</t>
+          <t>How To Change Amazon Alexa's Voice And Personality</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>News AI How to change Amazon Alexa's voice and personality You can even make Alexa snarky. by Thomas Godwin Sept. 12, 2026 6:00 pm EST Tyler Nottley/Shutterstock Add Engadget on Google: Preferred Source Google Discover If you're an Alexa+ or Amazon Prime member, your interactions with Alexa are no longer relegated to fairly standard voice types or the creepy "Whisper Mode." Amazon now lets eligibl</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>alexa, amazon</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:44:24 GMT</t>
+          <t>Sat, 12 Sep 2026 22:00:00 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -3264,30 +3266,30 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cx/consuming-oracle-fusion-agents-aka-headless</t>
+          <t>https://www.engadget.com/2252800/how-to-change-alexa-voice-personality/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.75</v>
+        <v>6.27</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3295,25 +3297,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>New Adapters and Connectivity Enhancements in Oracle Integration 26.10</t>
+          <t>Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32%</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>amd, 2nm, apple</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>6.7</v>
+        <v>13.8</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 18:14:14 GMT</t>
+          <t>Sat, 12 Sep 2026 10:48:32 +0000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3323,16 +3325,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/integration/new-adapters-and-connectivity-enhancements-in-oracle-integration-26-10</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/apples-a20-pro-shatters-geekbench-7-single-core-record-2nm-chip-beats-desktop-intel-core-i9-and-amd-ryzen-9-by-up-to-32-percent</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.65</v>
+        <v>6.27</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3341,12 +3343,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -3354,25 +3356,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro vs Pixel 11 Pro: How Apple and Google's flagships stack up</t>
+          <t>Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32%</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>More AI, better cameras and few reasons to switch ecosystems. Apple / Google / Will Shanklin for Engadget Add Engadget on Google: Preferred Source Google Discover The iPhone 18 Pro and Pixel 11 Pro are the latest examples of a familiar story: Apple and Google refining, rather than reinventing, mature flagship smartphones. Both are expensive, powerful phones with top-notch screens, three rear camer</t>
+          <t>PC Components CPUs Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32% News By Anton Shilov Published 14 hours ago Eats Intel's entry Panther Lake CPUs for breakfast too. (Image credit: Apple) Share this article 9 Join the conversation Follow us Add us as a preferred source on Google Newsletter Subscribe to our newsletter Arch</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>google, apple</t>
+          <t>amd, 2nm, apple</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.6</v>
+        <v>13.8</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:17:46 +0000</t>
+          <t>Sat, 12 Sep 2026 10:48:32 GMT</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3382,16 +3384,16 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2256364/iphone-18-pro-vs-pixel-11-pro/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/apples-a20-pro-shatters-geekbench-7-single-core-record-2nm-chip-beats-desktop-intel-core-i9-and-amd-ryzen-9-by-up-to-32-percent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.39</v>
+        <v>5.79</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3413,25 +3415,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>China-modified Nvidia RTX 5090 with massive 96GB of memory appears on Alibaba for less than $4,000 — 3x more VRAM at 65% the cost of the original</t>
+          <t>This week on Tom's Hardware Premium: September 12, 2026 — Benchmarking Qwen 3.8, the splintered compute economy and AI breakthroughs</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t xml:space="preserve">Welcome to Tom's Hardware club ! Hi , Your membership journey starts here. Keep exploring and earning more as a member. Latest on CPUs News, reviews, and technical insights. GPU Insights Reviews, benchmarks, and updates on current GPUs. See what you’ve unlocked. Explore your membership benefits. Limited-time Premium offer Cancel anytime Premium Member Hi , Keep exploring with your premium access. </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>alibaba, nvidia</t>
+          <t>geforce, qwen</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8.4</v>
+        <v>12.6</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 16:32:36 +0000</t>
+          <t>Sat, 12 Sep 2026 12:00:00 +0000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3441,16 +3443,16 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/china-modified-nvidia-rtx-5090-with-massive-96gb-of-memory-appears-on-alibaba-for-less-than-usd4-000-3x-more-vram-at-65-percent-the-cost-of-the-original</t>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-september-12-2026-benchmarking-qwen-3-8-the-splintered-compute-economy-and-ai-breakthroughs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -3459,12 +3461,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3472,25 +3474,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Oracle to spend $700 million more on restructuring costs as it ramps up AI spending</t>
+          <t>How to get started with Meta's new AI agent, Muse</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Oracle to spend $700 million more on restructuring costs as it ramps up AI spending FILE PHOTO: Oracle logo is seen in this illustration created on September 9, 2025. REUTERS/Dado Ruvic/Illustration/File Photo 11 Sep 2026 05:01PM (Updated: 12 Sep 2026 07:47AM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your preferred source on Google Add CNA as a trusted source </t>
+          <t>Opting out of data sharing is a good first step. Meta Add Engadget on Google: Preferred Source Google Discover Meta just released its first consumer AI agent, Muse . Like agents from other companies, the list of tasks Muse is capable of is long. The agent can browse the web, online shop, fill out forms, plan trips, send emails, schedule events and a whole lot more. It can connect to a bunch of thi</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.1</v>
+        <v>10.6</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 23:47:55 GMT</t>
+          <t>Sat, 12 Sep 2026 14:00:00 +0000</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3500,16 +3502,16 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/oracle-spend-700-million-more-restructuring-costs-it-ramps-up-ai-spending-6378456</t>
+          <t>https://www.engadget.com/2256577/how-to-get-started-with-meta-s-new-ai-agent-muse/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5.1</v>
+        <v>5.38</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -3518,7 +3520,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3531,12 +3533,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Meta has proven it can be competitive in the AI model space, says Intelligent Alpha's Doug Clinton</t>
+          <t>How To Get Started With Meta's New AI Agent, Muse</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>WATCH NOW In this video META NVDA AAPL SHARE Share Article via Facebook Share Article via Twitter Share Article via LinkedIn Share Article via Email CLOSING BELL Meta has proven it can be competitive in the AI model space, says Intelligent Alpha’s Doug Clinton Doug Clinton, Intelligent Alpha founder and CEO, joins ‘Closing Bell’ to discuss the latest action in tech stocks, Apple’s latest product l</t>
+          <t>News AI How to get started with Meta's new AI agent, Muse Opting out of data sharing is a good first step. by Karissa Bell Sept. 12, 2026 10:00 am EST Meta Add Engadget on Google: Preferred Source Google Discover Meta just released its first consumer AI agent, Muse. Like agents from other companies, the list of tasks Muse is capable of is long. The agent can browse the web, online shop, fill out f</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3545,11 +3547,11 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:48:39 GMT</t>
+          <t>Sat, 12 Sep 2026 14:00:00 GMT</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3559,16 +3561,16 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/09/11/meta-has-proven-it-can-be-competitive-in-the-ai-model-space-says-intelligent-alphas-doug-clinton.html</t>
+          <t>https://www.engadget.com/2256577/how-to-get-started-with-meta-s-new-ai-agent-muse/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.88</v>
+        <v>5.19</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -3577,12 +3579,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3590,25 +3592,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>New images show a detailed view of Meta's upcoming mixed reality headset</t>
+          <t>This week on Tom's Hardware Premium: September 12, 2026 — Benchmarking Qwen 3.8, the splintered compute economy and AI breakthroughs</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>The device known as Project Phoenix is a new form factor for Meta. Meta (via UploadVR) Add Engadget on Google: Preferred Source Google Discover Meta appears to have unintentionally shown off its upcoming mixed reality headset a bit ahead of schedule. Images of the device, which has been known as "Project Phoenix", have surfaced and they provide a fairly detailed look at the lightweight headset. Th</t>
+          <t>Tech Industry This week on Tom's Hardware Premium: September 12, 2026 — Benchmarking Qwen 3.8, the splintered compute economy and AI breakthroughs News By Sayem Ahmed Published 13 hours ago Artificial Intelligence threatens humanity, or so the people say. When you purchase through links on our site, we may earn an affiliate commission. Here’s how it works. (Image credit: Tom's Hardware) Share this</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7.4</v>
+        <v>12.6</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 17:28:11 +0000</t>
+          <t>Sat, 12 Sep 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3618,13 +3620,13 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2256177/new-images-show-a-detailed-view-of-metas-upcoming-mixed-reality-headset/</t>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-september-12-2026-benchmarking-qwen-3-8-the-splintered-compute-economy-and-ai-breakthroughs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.78</v>
+        <v>5.15</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -3636,12 +3638,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3649,25 +3651,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>We unfolded the iPhone Duo</t>
+          <t>Why is the internet so upset about NVIDIA's DLSS 5?</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Podcasts Vergecast We unfolded the iPhone Duo On The Vergecast: a deep dive </t>
+          <t>NVIDIA calls it the biggest graphics breakthrough since ray tracing; critics call it an AI slop filter. Matt Gush/Shutterstock Add Engadget on Google: Preferred Source Google Discover NVIDIA announced DLSS 5 at its GTC conference on March 16, describing the fall release as its most significant graphics breakthrough since real-time ray tracing was launched in 2018. NVIDIA claims DLSS 5 will deliver</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:22:24-04:00</t>
+          <t>Sat, 12 Sep 2026 20:00:00 +0000</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3677,13 +3679,13 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/podcast/994016/iphone-duo-vergecast-apple-watch-mac-llms</t>
+          <t>https://www.engadget.com/2252797/nvidia-dlss-5-why-internet-people-upset-issues/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.77</v>
+        <v>5.11</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -3695,12 +3697,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3708,25 +3710,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>The White House says Truth Social is the ‘most powerful and popular social media platform in the world’</t>
+          <t>Anthropic CEO outlines plan to slow AI development</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Policy News Tech The White House says Truth Social is the ‘most powerful and</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Ruhani Kaur/Bloomberg / Getty Images AI Anthropic CEO outlines plan to slow AI development Anthony Ha 12:34 PM PDT · September 12, 2026 We’ve been seeing increasingly dire warnings from AI researchers about the dangers of artificial in</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:21:19-04:00</t>
+          <t>Sat, 12 Sep 2026 19:34:44 +0000</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3736,13 +3738,13 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/policy/994072/white-house-truth-social-popular-powerful</t>
+          <t>https://techcrunch.com/2026/09/12/anthropic-ceo-outlines-plan-to-pace-the-frontier/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.75</v>
+        <v>5.08</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -3754,12 +3756,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3767,25 +3769,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Anthropic spent this week in hot water over cybersecurity</t>
+          <t>Tesla says it will finally unveil the second generation Roadster on October 1</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI Report Analysis Anthropic spent this week in hot water over cybersecurity</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt In Brief Posted: The long-awaited second generation of the Tesla Roadster might finally be ready for the public. In a post on X on Saturday, the electric vehicle company simply wrote, “Go for launch,” with a graphic showing a “10.01” date — so expect</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:09:14-04:00</t>
+          <t>Sat, 12 Sep 2026 19:21:19 +0000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3795,13 +3797,13 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/994064/anthropic-spent-this-week-in-hot-water-over-cybersecurity</t>
+          <t>https://techcrunch.com/2026/09/12/tesla-says-it-will-finally-unveil-the-second-generation-roadster-on-october-1/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.74</v>
+        <v>5</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -3813,12 +3815,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3826,25 +3828,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s head of comms is leaving after almost 20 years</t>
+          <t>How to add your driver's license to Apple Wallet and where you can use it</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... News Tech Microsoft Microsoft’s head of comms is leaving after almost 20 yea</t>
+          <t>In certain states, you can add a digital license to Apple Wallet so you don't need to carry a physical ID all the time. Apple Add Engadget on Google: Preferred Source Google Discover It's been several years since Apple added the option to store digital versions of your personal identification on iPhone and Apple Watch. This can be useful in several ways, such as helping you zip through airport sec</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8.9</v>
+        <v>6.1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:01:34-04:00</t>
+          <t>Sat, 12 Sep 2026 18:30:00 +0000</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3854,13 +3856,13 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/news/993791/microsoft-frank-shaw-leaving-head-of-comms</t>
+          <t>https://www.engadget.com/2252801/how-to-add-drivers-license-apple-wallet/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.7</v>
+        <v>4.99</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -3877,7 +3879,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3885,25 +3887,26 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Meta may have leaked the first look at its slim &amp;#8216;Project Phoenix&amp;#8217; headset</t>
+          <t>Where to preorder the iPhone 18 Pro and Pro Max</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Just a couple of weeks before  Meta Connect  starts on September 23rd,   UploadVR   posted images seemingly revealing the design for Meta's "Project Phoenix" headset. The images, which  UploadVR  says were "found in the HorizonOS Prescription Lens firmware package," suggest Meta may be looking to co</t>
+          <t>Which color suits you best? | Photo: Nilay Patel / The Verge	 
+ The  iPhone 18 Pro and 18 Pro Max  are almost here. Announced at Apple's September 2026 "Sunrise and shine" event alongside the  iPhone Duo  and other new gear, the two upgraded phones feature the faster A20 Pro processor with more GP</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>gpu, apple</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T11:38:31-04:00</t>
+          <t>2026-09-12T08:00:00-04:00</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3913,16 +3916,16 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/994055/meta-project-phoenix-headset-leak</t>
+          <t>https://www.theverge.com/gadgets/988337/iphone-18-pro-max-preorder-buy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.69</v>
+        <v>4.99</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -3931,12 +3934,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3944,26 +3947,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Where to preorder the Apple AirPods 5</t>
+          <t>Anthropic in talks to bring Nvidia as anchor investor in potential $100 billion IPO: Report</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The new AirPods 5 in their charging case. | Photo: Antonio G. Di Benedetto / The Verge	 
- The  Apple AirPods 5  are bringing active noise cancellation to the masses, and they're now available for preorder at a variety of retailers. They'll officially launch on September 18th, the same day as the  </t>
+          <t>Anthropic in talks to bring Nvidia as anchor investor in potential $100 billion IPO: Report    Livemint</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>anthropic, nvidia</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11T11:31:00-04:00</t>
+          <t>Sat, 12 Sep 2026 03:35:58 GMT</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3973,13 +3975,13 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/993637/apple-airpods-5-anc-wireless-charging-preorder-buy</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQVTN4OGgxM0xOYmdCNEpmVERqeHdZTkZWLWtVTzdCNDlZNVQtYS1Zcl8xVER1ODdqQXNvQVBHUzhlRm40dFZuUjJ2NF9ueURLX2dnVENMMXpCQnJnV2NERVNoa2FHd19uME41WW9NeTF1N2IwcUU0aEVKRThVM0NYT25TT0VzU3pqbkk4UHBLRExjWlAtTktHNUowOFA5UklwbU4wT3hfMHN5NnFnNTdXVnEtcmtqU1JaM0sxNXlQdkZ1M0JmSUJGLWg2d3ZNemVyVWtZQkp1YWtnNklfRzd4Q0pRZ9IB6AFBVV95cUxPeFZOa0lhRXJmOGgxdEkzbkM5N3JielJESVlsQkx2ZlB4aGQxX0RKWE9qTW5zUUdOWTQ4cXVRZFZmaFhvTG5RTnJ0elp1Sm9maDNod0xZdmE0ZEhNT0E3TnpSazVUN1huT3k2UXNwSkFGenA5RlFFdE44bEI4Zkk1ZTdJSDdTeDUxLUN4VzFqT2VjM19Mb0c1bUNqaEx3ajJHaG96NXVxeTkwbFdzX0txd3VjQk51bmw1OTl4NjVaVHJXYjdLZzQ2aTZKbWt3M2JXSlpKQjA0OW9VN0VzV1kyQjhRakJMTE1f?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.69</v>
+        <v>4.82</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -3996,7 +3998,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4004,25 +4006,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Where should Apple go after the iPhone Duo? Bring on smaller and larger foldables</t>
+          <t>Anthropic's CEO proposes a three-step plan to curb AI development</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Come on Apple, just keep following in the footsteps of Samsung, ASUS and so many other foldable makers.</t>
+          <t>Dario Amodei said that "we owe it to humanity to try."</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 15:30:00 +0000</t>
+          <t>Sat, 12 Sep 2026 16:37:31 +0000</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4032,13 +4034,13 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2255941/where-should-apple-go-after-the-iphone-duo/</t>
+          <t>https://www.engadget.com/2256718/anthropics-ceo-proposes-a-three-step-plan-to-curb-ai-development/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.59</v>
+        <v>4.8</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -4055,7 +4057,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4063,25 +4065,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Meta says it’s changing AI suggestions after posing invasive personal questions</t>
+          <t>Anthropic CEO says it’s time to pump the brakes on AI</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Meta says it’s changing AI suggestions after posing invasive personal questions    The Verge</t>
+          <t>Anthropic CEO Dario Amodei says the time has come to slow down AI development and will give third-party evaluators like  METR  access to its models to help ensure its "adherence to safety practices and commitments." In a  winding essay , Amodei proposed a three-step plan to "pace the frontier" - jar</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 14:25:21 GMT</t>
+          <t>2026-09-12T12:23:40-04:00</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4091,30 +4093,30 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5RUFBfV3NpUnpsdVVjQUpialY1aEpTTjdGMlJqNTNjdU1rZVlUQ3pFbnBuUHZHanJaWVBYWG5Sbmlla2R2TkNoZU8yNmo2czhpMUFqV1YwdzZJZWJkcl9OZXRjbTBNV0xOem8xRExnS2tnOHpWcmo4aTJKU3M?oc=5</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994337/anthropic-ceo-slow-down-ai-development</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.54</v>
+        <v>4.67</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4122,25 +4124,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Larry Ellison Steps Back From Oracle Limelight in AI Era</t>
+          <t>Iran and Houthi rebels used Anthropic's Claude AI to target US warships and build hypersonic missiles — Houthi rebels also used the bot to code ballistic missile guidance systems</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Larry Ellison Steps Back From Oracle Limelight in AI Era    Bloomberg.com</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 21:20:23 GMT</t>
+          <t>Sat, 12 Sep 2026 15:03:10 +0000</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4150,13 +4152,13 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOd3ZZZHVycklkOHRpQ2VWRUpwLVBXeFVWdEhxZnpMRWxuTFA0bTJKVkJGdDJZRGM0NlFtNG5fVmFVVkd4VW9hNkt2aWd1ZDE1WlF2X3M3YTg1QzVTVGttZHNaVEUzWXVSNXJEdW1tb3RBR1c0dXV4VjdRN3FJWEJibDE3c0tyMWhZZkR6VUJpSWJ0YnUtcUtxeHZIYXh4elp6cnhXa1JzT2s3U0E?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/iran-and-houthi-rebels-used-anthropics-claude-ai-to-target-us-warships-and-build-hypersonic-missiles-houthi-rebels-also-used-the-bot-to-code-ballistic-missile-guidance-systems</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -4168,12 +4170,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4181,28 +4183,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>กูเกิลปล่อยแอป Gemini สำหรับวินโดวส์</t>
+          <t>Oracle is betting big on AI and debt. Now Larry Ellison could cash in $7.5 billion</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">กูเกิลปล่อยแอป Gemini สำหรับวินโดวส์ 
-     Body 
-                กูเกิลปล่อยแอป Gemini สำหรับวินโดวส์ หลังจาก ปล่อยเวอร์ชั่น macOS ตั้งแต่เดือนเมษายนที่ผ่านมา  รองรับการทำงานทั้งแบบแชตปกติและแบบ Spark ที่เป็นคู่แข่ง Claude Cowork 
- ตอนนี้แอป Gemini บนแมคสามารถจัดการไฟล์ในโฟลเดอร์ได้แบบเดียวกับ </t>
+          <t>Oracle is betting big on AI and debt. Now Larry Ellison could cash in $7.5 billion    Livemint</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>google, gemini</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17.7</v>
+        <v>10.8</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 07:13:52 +0000</t>
+          <t>Sat, 12 Sep 2026 13:48:06 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4212,30 +4211,30 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151612</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPYzN4N3Jic1hiYmtFRWlqZjF6QnJibXdHb1pDN3F2REx0Q2pxMkU4TnBRMTJEQThjek11LWdiN0N3MVkxdHdoYjVxbkJNLU0wY0FncGljOTdQa0RnSDk4ZEZJX1Y4ZFlfc0dXby1JYmtuRkdNN2F5cVk4ZmFqMWpsN2hxeHRLUV9YeUo3U2VDYk1maEpkVFd6eDFza001UTRfQXpuZmdaWmc4RzFWb24yb0NBZV9CcXhVaXlKTUsxWnpqQU1lMG5lLUppOE1SZlpWcndEMllIONIB3AFBVV95cUxQZ0swZnZHTXJxZUZxeEVYT0JPSjZJV1RQVWNYb3o0dGpnVEVVSFo1VnozdDJoRktSWFNBanoybzF1cDRwbEhEMllMX2o3UWFOLVVtTzY1SzlIbXZRZE9qUC0wcG96ZGIya3c3U2NYaDllbXpFdDJLaWpUaU8yZzdlX2V6cXdGMDk0dnNEM1RBc3lkMGZXSE9hOHd0UFVCRk8wOTlVVjF0aWZaMjFfZWNRUlN0NVlvcTc5czBSOHhKMkd0bEYzRHliX3oxV2wtcHp0X3lpNE5qNXZnY2Vr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4243,25 +4242,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Meta’s Muse $20 vs $100 AI plans: How much revenue can its paid AI agent really generate?</t>
+          <t>Tesla Teases Oct. 1 Event to Showcase Next-Generation Roadster</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Meta’s Muse $20 vs $100 AI plans: How much revenue can its paid AI agent really generate?    Livemint</t>
+          <t>Tesla Teases Oct. 1 Event to Showcase Next-Generation Roadster    Bloomberg.com</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>11.4</v>
+        <v>4.3</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 13:31:58 GMT</t>
+          <t>Sat, 12 Sep 2026 20:20:58 GMT</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4271,13 +4270,13 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbV9RZVRocVlZb3ZIeGNSQkFEZnE3eXVvQmlrVzVScXdXa3pSV2lBdkoxM21qRVVSSlBnVG1zXzhSVmw4TnZtOE5BMVVWR1VNME9pRERydW1zUFBYdGJqZG9ySU1hSXFhTUtuX0FCVkFkTFplWDJVS3MzYmlCeHA2ZWJIU2F5bExxQTRMYjlQd24zZGcwazJrTXhlUkhsSktQVWtwcWdLMHkxSF9FZHZFWTNjaENkYXlvZHI0NTVIU3UtVi1iSVZOcTdVdm1vZTd5VDk3TFpQdUFxb2xJ0gHiAUFVX3lxTE96aXlhT0RHemNQcVF4ZUtIN3BlREpQN1JBbkdUU1VoeG5qRVhZaTBwaS0xRnV4bDhfeExzSGZ4WENaVHhYaWFBVGh4Y0VZNWROX1NiZnZIMVhNTDYtbF9aNjdYNHN0RE5VNndxU0lUdXJlWWlSUkNOWGFMLVlIcm90ZFVoQXdJSVNSSzJwMk1jSWMwVGh2QTBYU2poczVjc0FTN3Frc3ZJOHpQNmZ3X3BYRWx2UzNZNWlObjdJX09NbkxRN01fY2Y1S2xacU9nSlUwaWhDWFdRWEdQcTRieHdEUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPYUdYaTBYRXVaSFVnQmx3R0VYR3oybXctT2xJX3YtMlRxRmNqdEsweTlFdDE4V3JiLVR0RnZrRnRTU1BIQ0NPWGtNdzY5MXRmRUxIem1FaHdpMXhtTW0tb1hUY05IZ2VLVEpiWldWTUNFeU5acEhSVmxjWFhTZ0cxN1JLaEpLWGU4VEdUX3E2NFZCdTljc1lTUW9ySUNOOWpINFBLVi1nVGx6WGdqSVlleU53?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.47</v>
+        <v>4.38</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -4289,38 +4288,38 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Anthropic เดือดจนออก Report  แฉโมเดลจีนลอกวิชา Claude ผ่านแชทกว่า 200 ล้านชุดในไม่กี่เดือน Alibaba ทำไป 151 ล้านครั้ง หนักสุดในทุกค่าย</t>
+          <t>Diablo V is coming out in spring 2029</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>รายงาน Threat Intelligence ฉบับล่าสุด (กันยายน 2026) จาก Anthropic ทำเอาสงครามเทคโนโลยีระหว่างสหรัฐฯ และจีนสะเทือนอีกครั้ง เมื่อมีการเปิดเผยว่า บทสนทนาบน Claude เกือบ 200 ล้านครั้ง ถูกค่าย AI ยักษ์ใหญ่จากจีนดึงข้อมูลเชิงลึกไปฝึกโมเดลของตัวเองโดยไม่ได้รับอนุญาต และตัวการหลักของเหตุการณ์นี้อยู่ที่การท</t>
+          <t>Blizzard also confirmed that a Diablo animated series is in development with Netflix.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alibaba</t>
+          <t>netflix</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18</v>
+        <v>5.3</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 13:57:32 +0700</t>
+          <t>Sat, 12 Sep 2026 19:19:48 +0000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4330,13 +4329,13 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/anthropic-report-ai-distillation-china</t>
+          <t>https://www.engadget.com/2256735/diablo-v-is-coming-out-in-spring-2029/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4.47</v>
+        <v>4.28</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -4348,12 +4347,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4361,25 +4360,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk calls documentary about him a 'hit piece' after buzzy debut</t>
+          <t>Big Tech is pouring billions into AI, but Apple is taking a different innovation bet | Can it sustain growth without AI?</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk calls documentary about him a 'hit piece' after buzzy debut    cbc.ca</t>
+          <t>Big Tech is pouring billions into AI, but Apple is taking a different innovation bet | Can it sustain growth without AI?    Livemint</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>elon musk</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>11.7</v>
+        <v>13.7</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 13:13:00 GMT</t>
+          <t>Sat, 12 Sep 2026 10:55:47 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4389,13 +4388,13 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFA5QzJ6Z0g4TWk1aG5vQkpnVDU4UGd5SWUwYXREblBCN1FnQm15Nm9fLXRKWVVfWVFMYXpUbjBmR3BsRWNqdi1jSGF1ek1rTHdGY1RKaEc0X19rbUxaUVh0ZzJiVkF4Q0d0NmN4UUdGZ01YRTdSMG4xd3FFM0ZaZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPaEFlYlM2dlZjbENadnVDa3hjY2pxZ0ktQjc5QUdzRFBnQ2ktOG9wbVh1NmZDOFBHSHgwZGUwb19aZjZkOFZGWVpNRHJ0U3NqSmQtYTN5cEhjMV81VFZNeDVHT3NHTmZaNVlPZ2d1YS1wN3JiTnNRbHR1Z21ITHpOLXJwdVI1aXBmVFd5a1pJOXNqSEptNTgxcnZPTVpHZTc4bGVTMV9qVjZ0Uk5UZU5QZDdvUFUxOU14bTNEU19CXzM3ejA2dUFFZDJXUkE2VVBjVFlPREFueEw3SG92em91bVhEOFVzN1lnQzhRV3YyX2pkSUFhVVVmdl9fclFOcEZDd082akN0TdIBjAJBVV95cUxOUXVKX3BhOU9CN0RYWU5DZUk1SDEyV0xNZkh1ZEgxd0RvQkdpX2hUWUVub3NqOWZWYmplUU52QzhHNEFJRmtNRmEwWXB4QnJLRUxUaXh2Mlg2YmUxWXJYcWpxSHpQTlFtQkZnWDR4dXhlcGNDQzNjSEJ6bzNFTnd3QWdyRDZpTExPNXZ0S19ESi1iWHdqMWRnT01mMkpwQi1LTW13SnpDMlpjLWl4QS0tZTUxMWM5S1YySVlyM0R3VXdDNTBPd1ZVSDRvQ3JqSUp4S0JoVElPM05zbmhUZTdyWVl1QWY2d2UyNFBuX3dSVFdhcnpueVpWRksycm5oNjFtUDF4dHY4ZS1BZzFJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -4407,12 +4406,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -4420,25 +4419,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Apple's iPhone Handoff feature will cost you $5 a month on T-Mobile</t>
+          <t>Wiki documents at least 44 instances in which Sony says you own your games as digital games ownership lawsuit progresses — project is direct assault on Sony's claim in recent ownership lawsuit</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Apple will release iPhone Handoff with iOS 27 this month, but it will only be available to T-Mobile subscribers in the US at launch.</t>
+          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13</v>
+        <v>14.1</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 11:57:16 +0000</t>
+          <t>Sat, 12 Sep 2026 10:30:00 +0000</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4448,30 +4447,30 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2255731/apple-iphone-handoff-5-a-month-on-t-mobile/</t>
+          <t>https://www.tomshardware.com/video-games/playstation/consumer-rights-wiki-documents-at-least-44-instances-in-which-sony-says-you-own-your-games-project-is-direct-assault-on-sonys-claim-in-recent-ownership-lawsuit</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4479,25 +4478,27 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Apple’s Always-Listening Watch Features Test Eavesdropping Laws</t>
+          <t>ผู้บริหาร Instagram บอกถ้าโซเชียลไม่มีอัลกอริทึมคัดเนื้อหา เราจะเจอแต่คอนเทนต์จากแบรนด์สินค้าเต็มไปหมด</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Apple’s Always-Listening Watch Features Test Eavesdropping Laws    Bloomberg.com</t>
+          <t>ผู้บริหาร Instagram บอกถ้าโซเชียลไม่มีอัลกอริทึมคัดเนื้อหา เราจะเจอแต่คอนเทนต์จากแบรนด์สินค้าเต็มไปหมด 
+     Body 
+                หลังจากรัฐบาลออสเตรเลีย เสนอร่างกฎหมาย  ให้โซเชียลมีเดียต้องเปิดให้ผู้ใช้งานเลือกได้เอง ว่าต้องการใช้อัลกอริทึมแนะนำเนื้อหาบนหน้าฟีดหรือไม่ และสามารถปิดได้ถ้าไม่ต้อ</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5.8</v>
+        <v>15.4</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 19:05:36 GMT</t>
+          <t>Sat, 12 Sep 2026 09:12:51 +0000</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4507,13 +4508,13 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOVXh5WkZBNmxHVjNJZTJpM1NOeldSSGZQWHE2Q0Z2QmNEalRBYjdrQjd3b0NaQThjU2VSeDAxR0ZSWThHaVZaWE1ld0h3TWk4c25KSVRmSzRlVWdMNEJLRG85V1hPRlJvWjVBTHVEbVluTUh3cDBlZWYxdFJUbUNRWk5CbGNmZkVzVHpleWljVHZkLU9JNE1KVXJXek55TnZaVFVudVRJV1plOFFHXzY0TVZGMzE4ZU1aeG1RcjdEWQ?oc=5</t>
+          <t>https://www.blognone.com/node/151622</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4.32</v>
+        <v>4.11</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -4525,12 +4526,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>wired.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4538,25 +4539,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Meta Sued Over Training Data for Its AI and Face-Recognition Systems</t>
+          <t>Larry Ellison Ends Plan to Sell Up to $7.5 Billion in Oracle Stock</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Meta Sued Over Training Data for Its AI and Face-Recognition Systems    WIRED</t>
+          <t>Larry Ellison Ends Plan to Sell Up to $7.5 Billion in Oracle Stock    Bloomberg.com</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 18:59:00 GMT</t>
+          <t>Sat, 12 Sep 2026 16:33:33 GMT</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4566,13 +4567,13 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNRnFsM29paW4zazFZMUV1UGowNkJ1R1RnelFqUU5DMndtc3lhTnZzengwdHBJeV96WmZ3bk16R0pjLXNEdW1mcmt6TWRrU3JqWWpfempKb2pTWUd1TUJRWnBlTWVOd2JmZ09DRWhlMUJSOWpiSzlNM1plZHVYRTFpM1R6bk9BZTVaa3pIZEh2aU4tVmJ5RTk4X3pVNGRZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbF9TdllreUM2a1BUSWh3akI0WFVkc28zUHN6TElzRTBEZkdJU2tEVmx1b2x1TkJMdHhqcEZqV3p2eEZTWmRLeHRGY2JCekxoM1h1dERxNkRuQW5QT0p6cE1jR3RCM2ZZS2pkSmwySDNFYnl1ZlE3Y0lBVWlzMkh6RjdDMnNHVF9wamNSbFFibXd4aHJObFVGOEg2bHhqQldpbHRMd1ZRWVBMVjZzNVljeWxjb0RWQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -4584,12 +4585,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>bbc.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4597,25 +4598,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Oracle posts 30% revenue growth fueled by AI cloud demand as debts hits $125 billion</t>
+          <t>The Meta glasses revolution - is it okay to film people in public?</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Oracle posts 30% revenue growth fueled by AI cloud demand as debts hits $125 billion    CNBC</t>
+          <t>The Meta glasses revolution - is it okay to film people in public?    BBC</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13.5</v>
+        <v>19.4</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 11:22:05 GMT</t>
+          <t>Sat, 12 Sep 2026 05:13:53 GMT</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4625,30 +4626,30 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE03bWRldmRDa3pmTDdxb0k3UUFKbXNNcnJGQVBCNkN5SVRwdnBnQTgxa3dxU2RERmxGbVJtRi16Y0wtZTZ3dWtvcXJPbTlwOG9COGpOcGhPMkFzZ1U1aEE1Q2Q0RkFuc01CeXhHdzc2WWhtSVNRYTNvRFZB0gF_QVVfeXFMTWpqdW9VSEdvOHFvMFl4Qm91UlFPVlRBaVhTOU52MVBDTmRkRGxqclFEVmdaeklvLXc2U21jNmlGMDlUSzBwZVd2d0YtTXBsb0h3cFVaNDhXYTJOUW9WSG9xd0dVdTdPVnVIamRxZzhETnFsTXV5MWpHZDJ1d184OA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE95M3FlSlFTak9iYXFOXzEyVHlUd1JTU0VnY2JpdjNHYks3Vk1LcUhuVTRhYXRudkM0R1FHMjVlOWtOMkdTZmpHLUU3Qml6VFVJVW42OVRnNC1Gdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>4.28</v>
+        <v>2.71</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4656,25 +4657,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>‘Eye of Sauron’, ‘super uncomfortable’: Why did Meta employees revolt against its AI experiment?</t>
+          <t>Inside Microsoft’s Plans to Massively Expand Computing Power</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>‘Eye of Sauron’, ‘super uncomfortable’: Why did Meta employees revolt against its AI experiment?    Livemint</t>
+          <t>Inside Microsoft’s Plans to Massively Expand Computing Power    Bloomberg.com</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13.7</v>
+        <v>22.8</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Fri, 11 Sep 2026 11:10:20 GMT</t>
+          <t>Sat, 12 Sep 2026 01:46:55 GMT</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4684,840 +4685,12 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOVnVEUmVpRGU0R0tvWGgxU2s1djZoRmhrSEYyN2RKRWY1eVBfWVhZSDFGcG04SGRCS0o1RC1lanN0MVM0WnF3b0hXcTdHa3JBS01QMEdWM0wzWWVnVUpxRVlZVWJrZFlkNmxKQWRFNHR6RE1mZFU5aExUb2NNZmZQbElYamw0ZFM4S3djaU1YRHkxOVVadU45eEJLT1ZwVmZ1TDRfX0tINzB4Skl6YW9mWDdoTEZsUHZmY0FIMXJCaTgxWDlQbVZGRncxZEtkUExHV2Nr0gHYAUFVX3lxTE0tS0NDTWNVczRFTWtweEZqSUN6ZW1XdnllME1Kd3pOZUk5bDZDYXNja0x3RWlFUlVIclNOX2Y1cHpqTGdja0xnRXQtZHZCWHZSQUhoeWxiVFpXRUMxTHZ2M1JzYjFvM2VqVGNzSGxaaUJxUFg0TGR2aWpEajZMdkpHdnByU0pja2Z4X0xwZ3MxeDA5SzVQVzhxdFRCTkRzN2M5cWwzV0hFeFUxSDhLcndRdFNyOHBJT2tWbFNSLVlMU2ZUZW1renZ0OTJQWGlrSFZ1TmFpZWUtdw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Desktop graphics card shipments hit four-year high of 12.5 million despite increasing prices — Nvidia takes 90% share as gamers rush to beat looming price spikes</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 11:00:00 +0000</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/desktop-graphics-card-shipments-hit-four-year-high-of-12-5-million-despite-increasing-prices-nvidia-takes-90-percent-share-as-gamers-rush-to-beat-looming-price-spikes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>screening</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Watch Oracle’s AI Cloud Growth Eases Buildout Concerns</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Watch Oracle’s AI Cloud Growth Eases Buildout Concerns    Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>oracle</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 18:13:45 GMT</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcUNDc1dZczh0dXBnZ19DSVVmXzNIV3RLSWZwSVNtRGdDMkMybHItVFlFNVFlVmxuRm5OUkZCYUZQTmxrMEZXNXRFSW1kM0RSWHhZbEdqUEZCUzVkbHdXT2pjQnBFNU9DTC0wNEZ0RWZfdkhrUjZVRldWY2VPc2h0c0hWLXpQbEhyNEhMZkRQUkhpMGlpWGRZSnlPVW1BeUd6VExyOW9R?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>techsauce.co</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>เศรษฐกิจปี 2030 ใน 3 ฉากทัศน์ AI: Anthropic ไล่เรียงอนาคตผ่าน 4 อาชีพ พยาบาล โปรแกรมเมอร์ คอลเซ็นเตอร์ และช่างไฟฟ้า</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>หาก AI ทำให้เศรษฐกิจโตเร็วขึ้นหลายเท่า คนทำงานก็ควรมีรายได้ดีขึ้นตามไปด้วยหรือไม่?   คำตอบจากแบบจำลองล่าสุดของ The Anthropic Institute อาจไม่ได้ตรงไปตรงมาขนาดนั้น เพราะในฉากทัศน์ที่ AI พัฒนาและถูกนำไปใช้อย่างเข้มข้นที่สุด เศรษฐกิจสหรัฐฯ อาจมีขนาดใหญ่กว่าเส้นทางที่ไม่มี AI ถึง 32.4% ภายในปี 2030  และ</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>anthropic</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 17:36:03 +0700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>https://techsauce.co/ai/ai-economy-2030-four-occupations-anthropic-scenarios</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic says Claude thwarted bioweapon research from state-sponsored actors — covert accounts used U.S. proxies to attempt to engineer deadlier viruses, tried to evade identification and regional blocks</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Bruno Ferreira's journey kicked off with the venerable ZX Spectrum, a cassette player, and his hopes and dreams. He quickly realized he had more fun figuring out how computers work than he did actually using the things. Kicking off a developer career with C and Assembly before moving to scripting la</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>anthropic</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 10:00:00 +0000</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-says-claude-thwarted-bioweapon-research-from-state-sponsored-actors-covert-accounts-used-u-s-proxies-to-attempt-to-engineer-deadlier-viruses-tried-to-evade-identification-and-regional-blocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Russian plot to sabotage undersea cables with 'secret weapon' foiled by NATO — clandestine op uncovers training exercise simulating deployment against infrastructure in Norway</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Stephen is Tom's Hardware's News Editor with almost a decade of industry experience covering technology, having worked at TechRadar, iMore, and even Apple over the years. He has covered the world of consumer tech from nearly every angle, including supply chain rumors, patents and litigation, and mor</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 09:26:43 +0000</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/russian-plot-to-sabotage-undersea-cables-with-secret-weapon-foiled-by-nato-clandestine-op-uncovers-training-exercise-simulating-deployment-against-infrastructure-in-norway</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>thestandard.co</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Jennifer Lawrence เปิดบัญชี Instagram เป็นครั้งแรก และมี 3.7 ล้านฟอลโลเวอร์แล้ว</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Jennifer Lawrence  ตัดสินใจเปิดบัญชี Instagram เป็นครั้งแรกโดยใช้ชื่อว่า @jlaw หลังจากที่หลีกเลี่ยงการใช้โซเชียลมีเดียมานานหลายปี ซึ่งเธอก็ประเดิมด้วยการโพสต์ Reel บนแพลตฟอร์มอย่างสบายๆ ด้วยการถือกล้องเซลฟี่วิดีโอที่เผยให้เห็นใบหน้าและผิวอันสดใสเปล่งปลั่งที่ปราศจากเครื่องสำอาง และปล่อยผมสยายเฉดสีบลอ</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>instagram</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 09:12:37 +0000</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>https://thestandard.co/jennifer-lawrence-instagram-debut/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Oklo</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Sanctioned Chinese supercomputer maker stripped of IO500 benchmark crown, Intel-powered Aurora retakes the lead — record-breaking ParaStor F9000 storage system doesn't meet reproducibility requirements</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>aurora</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 16:26:12 +0000</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/supercomputers/sanctioned-chinese-supercomputer-maker-stripped-of-io500-benchmark-crown-intel-powered-aurora-retakes-the-lead-record-breaking-parastor-f9000-storage-system-doesnt-meet-reproducibility-requirements</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>bbc.com</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic blocks possible attempt to use AI to make biological weapons</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic blocks possible attempt to use AI to make biological weapons    BBC</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>anthropic</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 08:15:25 GMT</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBrcXFPTUpsT2dQTWp5eWtOTE9ZQ3BycXlHc0V6cDZoelBXRUhCTmZwM0U4dGV2SGtNUFZFeDhuTTRMR0p5NG91bUdUS0t2M1E3Tzk2OTBER3A3Zw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>screening</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Meta Meets With European Credit Investors in Non-Deal Roadshow</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Meta Meets With European Credit Investors in Non-Deal Roadshow    Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 14:08:41 GMT</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNYzhXTGlfZGFEeW1FbVdpekhIekVPYmdCU3RpZkZ4anhiWW9WaFFNTUREZk5sNGlLNmZxNE9rN3FxaF9sMklMcDQxMHpYTHViaHNjWDRuNjdsZG9McmplUGtDZ0ZST3JPbldlbnQzS1REUUpMZlFITFBScllwRU9HcGZia2FOVWVlUzRHWE9WVVU0dUpXTjVzVDFqRF9pYWJYX2VYLWhVeFFadEluWTVOVmFGNA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>screening</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Tesla Shares Suffer Slow Summer After SpaceX IPO, Earnings Rout</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>Tesla Shares Suffer Slow Summer After SpaceX IPO, Earnings Rout    Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>tesla</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 13:15:50 GMT</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQSUNSdDdROUtRU3lNUE1xY3Frb2NrTTVZQ1ZWSk5WQWpfQTBHWllyd1B5S2UxM2R1T1lWcU1RZi13TXNTTkdpRG1RMmJDbzRWZFZBUkh1ZXQ1VEI0YVdtUFc2NlRiTk42WnNodFphSzR4ZkpaZDc5aUh4N3dnT1VwNk40aGRONGtqa0FRWE13SmNFSDAxRGd1MDFSeGxNUWxwUG8yUmdMd2N6aWhraGZlTFdyNA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>TSMC</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>OpenAI says its next-generation processors could be made at Samsung — double-sourcing with TSMC hints at massive volume requirements [Updated]</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>OpenAI says its next-generation processors could be made at Samsung — double-sourcing with TSMC hints at massive volume requirements [Updated]    Tom's Hardware</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>tsmc</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 13:14:30 GMT</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPVTFNNG4tc1dDb1pIRDBCc1NLTWZkVFE5b3hxWDVHVVJUdTl5c293dVJSc2dYU2xPSFVZemx3Z3poLVQ1TFV4bVZSQ0d6Uy1QQnR1cHNyeElhUTk4N3hXaFloNmJfU3VtbzBDbnpPMXBwR3dfa0JCd1hUUkdRMjEtMUpFR3NGRmVDTXo2RUpjM3hCTkpwUjREZnhPRmhqX2d0eWVmSHBURm96QlgyYlRlaFBhZGk1aC1HaVdJTzYyb0ZqLU9VaG5zUzRJYkxXUEp1N05vSGZLSEloS2NHZ1FvbmNSRXVUVEIxbjVvRkE3WFcyLWFJekVIMUxEQVBHZ3pNZkMwQXBXS3VzUzE5MlZZOFVFQ0cwdjFCQUFyLTViUzBNZlk?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>Oracle says AI will save it from the SaaSpocalypse, not bring it on</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>Oracle says AI will save it from the SaaSpocalypse, not bring it on    The Register</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>oracle</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 02:43:10 GMT</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPNVREWTJCV012eUYydDlfRHhTamwyVXEzbWgyQTlXeFplQ3NoODdBcHk5ZzlkWlhsVXFtVzBhWGI3ZW40SlBnQm5ndzd0QzNuaHN3eUphbHZBZ1VPeUh5X0ZuZDM1ZG4xV3VLd25QYTFzUnF6anhhdzYzSVRsT3JPR0dCNGhhV3hZRE1DZTJfMERldkotTmZlR1dOMUF1TWsxZGZYZkhWMGhYREJzbHpUdXFvQ2lNX0kybkRhT1lCaw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>blognone.com</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Oracle รายงานผลประกอบการ รายได้โต 30% แบ็กล็อกเพิ่มเป็น 6.6 แสนล้านดอลลาร์ คาดรับรู้รายได้ครึ่งหนึ่งใน 36 เดือน</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Oracle รายงานผลประกอบการ รายได้โต 30% แบ็กล็อกเพิ่มเป็น 6.6 แสนล้านดอลลาร์ คาดรับรู้รายได้ครึ่งหนึ่งใน 36 เดือน 
-     Body 
-                Oracle รายงานผลประกอบการของไตรมาสที่ 1 ตามปีการเงินบริษัท 2027 สิ้นสุดเดือนสิงหาคม รายได้เพิ่มขึ้น 30% จากไตรมาสเดียวกันในปีก่อนเป็น 19,345 ล้านดอลลาร์ ทำส</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>oracle</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 02:26:00 +0000</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>https://www.blognone.com/node/151608</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>cnbc.com</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>Chinese Nvidia rival Enflame soars 206% on stock market debut as AI demand stays hot</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Chinese Nvidia rival Enflame soars 206% on stock market debut as AI demand stays hot    CNBC</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 01:53:00 GMT</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNb3NRZnFyUlUzaHZKaEZCV19MVjJ6U0tHRnh3eXc1NzBTRWk0U3VYOEZrSlJLaWdxdWRaaFh1MXVpbjRzb3lKNzBtY0NrQ3ZabmxKNXdWVHJaeW5Pb1ZHemIyTmtwQ2RxMTBWRXVfUjBxZjhoRzNWSjFtWDlPYUpTNFZRVlBEZF9YOWdXdEdzMETSAZYBQVVfeXFMT2gyeDQ0M2xEdTM5MFh5MHdoYUd6elJxSUxVYTdQaGtpdkgxelRnRUpCYTczQzN3dDRHc0kzaHBDdnNJTGdCOXk4eXlhOWdBbHgzVjFfRF9Nc19pblI3MnZmOVBqUmRIMlNET3R1SGUwaUl2Y3hnVi1RdmcxLU1GbUNzdDdJeF9fdXZVcnBkTkJpazB0XzlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQakx5dE5oZUl3d183Q1VCRHl4X1BTcVJkMUUxbm1DZjFKT3o0cU90QlkzRVVaMTBPWU1OWjZlZ1VLRUV6bDl1VW5RTkk4b2RwTUtBLU1SWi1fcS1HQ3lTM1lpOVRETV8tTTJOTklKNXd0alExX1N3RTFnNDl0X2UtdVdxNUhwRHFoMnVPQ2lUX0JzNEpLUGRYVERSbzI2SWNBbGhuZlRiMldSRzlENWZ6NTJZTlE?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M41"/>
+  <autoFilter ref="A1:M27"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -5545,20 +4718,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5636,39 +4795,39 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.68</v>
+        <v>6.7</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.98+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Oracle rises as AI-fueled backlog growth deflects spending worries</t>
+          <t>How to change Amazon Alexa's voice and personality</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>alexa, amazon</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/oracle-shares-rise-ai-cloud-backlog-beats-estimates-2026-09-11/</t>
+          <t>https://www.engadget.com/2252800/how-to-change-alexa-voice-personality/</t>
         </is>
       </c>
     </row>
@@ -5677,39 +4836,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.89</v>
+        <v>6.7</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.79+sig0.6+src2.0+corr0.0+wl1.5</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Consuming Oracle Fusion Agents aka Headless</t>
+          <t>How To Change Amazon Alexa's Voice And Personality</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>alexa, amazon</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cx/consuming-oracle-fusion-agents-aka-headless</t>
+          <t>https://www.engadget.com/2252800/how-to-change-alexa-voice-personality/</t>
         </is>
       </c>
     </row>
@@ -5718,39 +4877,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.75</v>
+        <v>6.27</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.65+sig0.6+src2.0+corr0.0+wl1.5</t>
+          <t>rec0.97+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>New Adapters and Connectivity Enhancements in Oracle Integration 26.10</t>
+          <t>Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>amd, 2nm, apple</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/integration/new-adapters-and-connectivity-enhancements-in-oracle-integration-26-10</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/apples-a20-pro-shatters-geekbench-7-single-core-record-2nm-chip-beats-desktop-intel-core-i9-and-amd-ryzen-9-by-up-to-32-percent</t>
         </is>
       </c>
     </row>
@@ -5759,39 +4918,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.65</v>
+        <v>6.27</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.75+sig1.2+src1.2+corr0.0+wl1.5</t>
+          <t>rec0.97+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro vs Pixel 11 Pro: How Apple and Google's flagships stack up</t>
+          <t>Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32%</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>google, apple</t>
+          <t>amd, 2nm, apple</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2256364/iphone-18-pro-vs-pixel-11-pro/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/apples-a20-pro-shatters-geekbench-7-single-core-record-2nm-chip-beats-desktop-intel-core-i9-and-amd-ryzen-9-by-up-to-32-percent</t>
         </is>
       </c>
     </row>
@@ -5800,16 +4959,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.39</v>
+        <v>5.79</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.49+sig1.2+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.09+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>China-modified Nvidia RTX 5090 with massive 96GB of memory appears on Alibaba for less than $4,000 — 3x more VRAM at 65% the cost of the original</t>
+          <t>This week on Tom's Hardware Premium: September 12, 2026 — Benchmarking Qwen 3.8, the splintered compute economy and AI breakthroughs</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5819,11 +4978,11 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>alibaba, nvidia</t>
+          <t>geforce, qwen</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -5832,7 +4991,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/china-modified-nvidia-rtx-5090-with-massive-96gb-of-memory-appears-on-alibaba-for-less-than-usd4-000-3x-more-vram-at-65-percent-the-cost-of-the-original</t>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-september-12-2026-benchmarking-qwen-3-8-the-splintered-compute-economy-and-ai-breakthroughs</t>
         </is>
       </c>
     </row>
@@ -5841,39 +5000,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.28+sig0.6+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Oracle to spend $700 million more on restructuring costs as it ramps up AI spending</t>
+          <t>How to get started with Meta's new AI agent, Muse</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/oracle-spend-700-million-more-restructuring-costs-it-ramps-up-ai-spending-6378456</t>
+          <t>https://www.engadget.com/2256577/how-to-get-started-with-meta-s-new-ai-agent-muse/</t>
         </is>
       </c>
     </row>
@@ -5882,16 +5041,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.1</v>
+        <v>5.38</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.8+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.28+sig0.6+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Meta has proven it can be competitive in the AI model space, says Intelligent Alpha's Doug Clinton</t>
+          <t>How To Get Started With Meta's New AI Agent, Muse</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5905,16 +5064,16 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/09/11/meta-has-proven-it-can-be-competitive-in-the-ai-model-space-says-intelligent-alphas-doug-clinton.html</t>
+          <t>https://www.engadget.com/2256577/how-to-get-started-with-meta-s-new-ai-agent-muse/</t>
         </is>
       </c>
     </row>
@@ -5923,39 +5082,39 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.88</v>
+        <v>5.19</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.58+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.09+sig0.6+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>New images show a detailed view of Meta's upcoming mixed reality headset</t>
+          <t>This week on Tom's Hardware Premium: September 12, 2026 — Benchmarking Qwen 3.8, the splintered compute economy and AI breakthroughs</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2256177/new-images-show-a-detailed-view-of-metas-upcoming-mixed-reality-headset/</t>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-september-12-2026-benchmarking-qwen-3-8-the-splintered-compute-economy-and-ai-breakthroughs</t>
         </is>
       </c>
     </row>
@@ -5964,26 +5123,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.78</v>
+        <v>5.15</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.48+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.85+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>We unfolded the iPhone Duo</t>
+          <t>Why is the internet so upset about NVIDIA's DLSS 5?</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -5991,12 +5150,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/podcast/994016/iphone-duo-vergecast-apple-watch-mac-llms</t>
+          <t>https://www.engadget.com/2252797/nvidia-dlss-5-why-internet-people-upset-issues/</t>
         </is>
       </c>
     </row>
@@ -6005,26 +5164,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.77</v>
+        <v>5.11</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.47+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.81+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>The White House says Truth Social is the ‘most powerful and popular social media platform in the world’</t>
+          <t>Anthropic CEO outlines plan to slow AI development</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -6032,12 +5191,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/policy/994072/white-house-truth-social-popular-powerful</t>
+          <t>https://techcrunch.com/2026/09/12/anthropic-ceo-outlines-plan-to-pace-the-frontier/</t>
         </is>
       </c>
     </row>
@@ -6064,7 +5223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6083,37 +5242,37 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Meta Platforms  (Tier 1 · 10 stories)</t>
+          <t>Amazon  (Tier 1 · 6 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Meta has proven it can be competitive in the AI model space, says Intelligent Alpha's Doug Clinton</t>
+          <t>How to change Amazon Alexa's voice and personality</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/09/11/meta-has-proven-it-can-be-competitive-in-the-ai-model-space-says-intelligent-alphas-doug-clinton.html</t>
+          <t>https://www.engadget.com/2252800/how-to-change-alexa-voice-personality/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4.88</v>
+        <v>6.7</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>New images show a detailed view of Meta's upcoming mixed reality headset</t>
+          <t>How To Change Amazon Alexa's Voice And Personality</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -6123,57 +5282,57 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2256177/new-images-show-a-detailed-view-of-metas-upcoming-mixed-reality-headset/</t>
+          <t>https://www.engadget.com/2252800/how-to-change-alexa-voice-personality/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.77</v>
+        <v>5.11</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>The White House says Truth Social is the ‘most powerful and popular social media platform in the world’</t>
+          <t>Anthropic CEO outlines plan to slow AI development</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/policy/994072/white-house-truth-social-popular-powerful</t>
+          <t>https://techcrunch.com/2026/09/12/anthropic-ceo-outlines-plan-to-pace-the-frontier/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Meta may have leaked the first look at its slim &amp;#8216;Project Phoenix&amp;#8217; headset</t>
+          <t>Anthropic's CEO proposes a three-step plan to curb AI development</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/994055/meta-project-phoenix-headset-leak</t>
+          <t>https://www.engadget.com/2256718/anthropics-ceo-proposes-a-three-step-plan-to-curb-ai-development/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.59</v>
+        <v>4.8</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Meta says it’s changing AI suggestions after posing invasive personal questions</t>
+          <t>Anthropic CEO says it’s time to pump the brakes on AI</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -6183,391 +5342,325 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5RUFBfV3NpUnpsdVVjQUpialY1aEpTTjdGMlJqNTNjdU1rZVlUQ3pFbnBuUHZHanJaWVBYWG5Sbmlla2R2TkNoZU8yNmo2czhpMUFqV1YwdzZJZWJkcl9OZXRjbTBNV0xOem8xRExnS2tnOHpWcmo4aTJKU3M?oc=5</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/994337/anthropic-ceo-slow-down-ai-development</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Meta’s Muse $20 vs $100 AI plans: How much revenue can its paid AI agent really generate?</t>
+          <t>Iran and Houthi rebels used Anthropic's Claude AI to target US warships and build hypersonic missiles — Houthi rebels also used the bot to code ballistic missile guidance systems</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbV9RZVRocVlZb3ZIeGNSQkFEZnE3eXVvQmlrVzVScXdXa3pSV2lBdkoxM21qRVVSSlBnVG1zXzhSVmw4TnZtOE5BMVVWR1VNME9pRERydW1zUFBYdGJqZG9ySU1hSXFhTUtuX0FCVkFkTFplWDJVS3MzYmlCeHA2ZWJIU2F5bExxQTRMYjlQd24zZGcwazJrTXhlUkhsSktQVWtwcWdLMHkxSF9FZHZFWTNjaENkYXlvZHI0NTVIU3UtVi1iSVZOcTdVdm1vZTd5VDk3TFpQdUFxb2xJ0gHiAUFVX3lxTE96aXlhT0RHemNQcVF4ZUtIN3BlREpQN1JBbkdUU1VoeG5qRVhZaTBwaS0xRnV4bDhfeExzSGZ4WENaVHhYaWFBVGh4Y0VZNWROX1NiZnZIMVhNTDYtbF9aNjdYNHN0RE5VNndxU0lUdXJlWWlSUkNOWGFMLVlIcm90ZFVoQXdJSVNSSzJwMk1jSWMwVGh2QTBYU2poczVjc0FTN3Frc3ZJOHpQNmZ3X3BYRWx2UzNZNWlObjdJX09NbkxRN01fY2Y1S2xacU9nSlUwaWhDWFdRWEdQcTRieHdEUHc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Meta Sued Over Training Data for Its AI and Face-Recognition Systems</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>wired.com</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNRnFsM29paW4zazFZMUV1UGowNkJ1R1RnelFqUU5DMndtc3lhTnZzengwdHBJeV96WmZ3bk16R0pjLXNEdW1mcmt6TWRrU3JqWWpfempKb2pTWUd1TUJRWnBlTWVOd2JmZ09DRWhlMUJSOWpiSzlNM1plZHVYRTFpM1R6bk9BZTVaa3pIZEh2aU4tVmJ5RTk4X3pVNGRZUQ?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/iran-and-houthi-rebels-used-anthropics-claude-ai-to-target-us-warships-and-build-hypersonic-missiles-houthi-rebels-also-used-the-bot-to-code-ballistic-missile-guidance-systems</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>‘Eye of Sauron’, ‘super uncomfortable’: Why did Meta employees revolt against its AI experiment?</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>livemint.com</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOVnVEUmVpRGU0R0tvWGgxU2s1djZoRmhrSEYyN2RKRWY1eVBfWVhZSDFGcG04SGRCS0o1RC1lanN0MVM0WnF3b0hXcTdHa3JBS01QMEdWM0wzWWVnVUpxRVlZVWJrZFlkNmxKQWRFNHR6RE1mZFU5aExUb2NNZmZQbElYamw0ZFM4S3djaU1YRHkxOVVadU45eEJLT1ZwVmZ1TDRfX0tINzB4Skl6YW9mWDdoTEZsUHZmY0FIMXJCaTgxWDlQbVZGRncxZEtkUExHV2Nr0gHYAUFVX3lxTE0tS0NDTWNVczRFTWtweEZqSUN6ZW1XdnllME1Kd3pOZUk5bDZDYXNja0x3RWlFUlVIclNOX2Y1cHpqTGdja0xnRXQtZHZCWHZSQUhoeWxiVFpXRUMxTHZ2M1JzYjFvM2VqVGNzSGxaaUJxUFg0TGR2aWpEajZMdkpHdnByU0pja2Z4X0xwZ3MxeDA5SzVQVzhxdFRCTkRzN2M5cWwzV0hFeFUxSDhLcndRdFNyOHBJT2tWbFNSLVlMU2ZUZW1renZ0OTJQWGlrSFZ1TmFpZWUtdw?oc=5</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 4 stories)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.09</v>
+        <v>6.27</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Lawrence เปิดบัญชี Instagram เป็นครั้งแรก และมี 3.7 ล้านฟอลโลเวอร์แล้ว</t>
+          <t>Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32%</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/jennifer-lawrence-instagram-debut/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/apples-a20-pro-shatters-geekbench-7-single-core-record-2nm-chip-beats-desktop-intel-core-i9-and-amd-ryzen-9-by-up-to-32-percent</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3.86</v>
+        <v>6.27</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Meta Meets With European Credit Investors in Non-Deal Roadshow</t>
+          <t>Apple's A20 Pro shatters Geekbench 7 single-core record — 2nm chip beats desktop Intel Core i9 and AMD Ryzen 9 by up to 32%</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNYzhXTGlfZGFEeW1FbVdpekhIekVPYmdCU3RpZkZ4anhiWW9WaFFNTUREZk5sNGlLNmZxNE9rN3FxaF9sMklMcDQxMHpYTHViaHNjWDRuNjdsZG9McmplUGtDZ0ZST3JPbldlbnQzS1REUUpMZlFITFBScllwRU9HcGZia2FOVWVlUzRHWE9WVVU0dUpXTjVzVDFqRF9pYWJYX2VYLWhVeFFadEluWTVOVmFGNA?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/apples-a20-pro-shatters-geekbench-7-single-core-record-2nm-chip-beats-desktop-intel-core-i9-and-amd-ryzen-9-by-up-to-32-percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>How to add your driver's license to Apple Wallet and where you can use it</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.engadget.com/2252801/how-to-add-drivers-license-apple-wallet/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 9 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Oracle rises as AI-fueled backlog growth deflects spending worries</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>https://www.reuters.com/business/retail-consumer/oracle-shares-rise-ai-cloud-backlog-beats-estimates-2026-09-11/</t>
+      <c r="A15" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Big Tech is pouring billions into AI, but Apple is taking a different innovation bet | Can it sustain growth without AI?</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>livemint.com</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxPaEFlYlM2dlZjbENadnVDa3hjY2pxZ0ktQjc5QUdzRFBnQ2ktOG9wbVh1NmZDOFBHSHgwZGUwb19aZjZkOFZGWVpNRHJ0U3NqSmQtYTN5cEhjMV81VFZNeDVHT3NHTmZaNVlPZ2d1YS1wN3JiTnNRbHR1Z21ITHpOLXJwdVI1aXBmVFd5a1pJOXNqSEptNTgxcnZPTVpHZTc4bGVTMV9qVjZ0Uk5UZU5QZDdvUFUxOU14bTNEU19CXzM3ejA2dUFFZDJXUkE2VVBjVFlPREFueEw3SG92em91bVhEOFVzN1lnQzhRV3YyX2pkSUFhVVVmdl9fclFOcEZDd082akN0TdIBjAJBVV95cUxOUXVKX3BhOU9CN0RYWU5DZUk1SDEyV0xNZkh1ZEgxd0RvQkdpX2hUWUVub3NqOWZWYmplUU52QzhHNEFJRmtNRmEwWXB4QnJLRUxUaXh2Mlg2YmUxWXJYcWpxSHpQTlFtQkZnWDR4dXhlcGNDQzNjSEJ6bzNFTnd3QWdyRDZpTExPNXZ0S19ESi1iWHdqMWRnT01mMkpwQi1LTW13SnpDMlpjLWl4QS0tZTUxMWM5S1YySVlyM0R3VXdDNTBPd1ZVSDRvQ3JqSUp4S0JoVElPM05zbmhUZTdyWVl1QWY2d2UyNFBuX3dSVFdhcnpueVpWRksycm5oNjFtUDF4dHY4ZS1BZzFJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Consuming Oracle Fusion Agents aka Headless</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>https://blogs.oracle.com/cx/consuming-oracle-fusion-agents-aka-headless</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 4 stories)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.75</v>
+        <v>5.38</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>New Adapters and Connectivity Enhancements in Oracle Integration 26.10</t>
+          <t>How to get started with Meta's new AI agent, Muse</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/integration/new-adapters-and-connectivity-enhancements-in-oracle-integration-26-10</t>
+          <t>https://www.engadget.com/2256577/how-to-get-started-with-meta-s-new-ai-agent-muse/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Oracle to spend $700 million more on restructuring costs as it ramps up AI spending</t>
+          <t>How To Get Started With Meta's New AI Agent, Muse</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/oracle-spend-700-million-more-restructuring-costs-it-ramps-up-ai-spending-6378456</t>
+          <t>https://www.engadget.com/2256577/how-to-get-started-with-meta-s-new-ai-agent-muse/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.54</v>
+        <v>4.12</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Larry Ellison Steps Back From Oracle Limelight in AI Era</t>
+          <t>ผู้บริหาร Instagram บอกถ้าโซเชียลไม่มีอัลกอริทึมคัดเนื้อหา เราจะเจอแต่คอนเทนต์จากแบรนด์สินค้าเต็มไปหมด</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOd3ZZZHVycklkOHRpQ2VWRUpwLVBXeFVWdEhxZnpMRWxuTFA0bTJKVkJGdDJZRGM0NlFtNG5fVmFVVkd4VW9hNkt2aWd1ZDE1WlF2X3M3YTg1QzVTVGttZHNaVEUzWXVSNXJEdW1tb3RBR1c0dXV4VjdRN3FJWEJibDE3c0tyMWhZZkR6VUJpSWJ0YnUtcUtxeHZIYXh4elp6cnhXa1JzT2s3U0E?oc=5</t>
+          <t>https://www.blognone.com/node/151622</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Oracle posts 30% revenue growth fueled by AI cloud demand as debts hits $125 billion</t>
+          <t>The Meta glasses revolution - is it okay to film people in public?</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>bbc.com</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE03bWRldmRDa3pmTDdxb0k3UUFKbXNNcnJGQVBCNkN5SVRwdnBnQTgxa3dxU2RERmxGbVJtRi16Y0wtZTZ3dWtvcXJPbTlwOG9COGpOcGhPMkFzZ1U1aEE1Q2Q0RkFuc01CeXhHdzc2WWhtSVNRYTNvRFZB0gF_QVVfeXFMTWpqdW9VSEdvOHFvMFl4Qm91UlFPVlRBaVhTOU52MVBDTmRkRGxqclFEVmdaeklvLXc2U21jNmlGMDlUSzBwZVd2d0YtTXBsb0h3cFVaNDhXYTJOUW9WSG9xd0dVdTdPVnVIamRxZzhETnFsTXV5MWpHZDJ1d184OA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Watch Oracle’s AI Cloud Growth Eases Buildout Concerns</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcUNDc1dZczh0dXBnZ19DSVVmXzNIV3RLSWZwSVNtRGdDMkMybHItVFlFNVFlVmxuRm5OUkZCYUZQTmxrMEZXNXRFSW1kM0RSWHhZbEdqUEZCUzVkbHdXT2pjQnBFNU9DTC0wNEZ0RWZfdkhrUjZVRldWY2VPc2h0c0hWLXpQbEhyNEhMZkRQUkhpMGlpWGRZSnlPVW1BeUd6VExyOW9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE95M3FlSlFTak9iYXFOXzEyVHlUd1JTU0VnY2JpdjNHYks3Vk1LcUhuVTRhYXRudkM0R1FHMjVlOWtOMkdTZmpHLUU3Qml6VFVJVW42OVRnNC1Gdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Oracle says AI will save it from the SaaSpocalypse, not bring it on</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPNVREWTJCV012eUYydDlfRHhTamwyVXEzbWgyQTlXeFplQ3NoODdBcHk5ZzlkWlhsVXFtVzBhWGI3ZW40SlBnQm5ndzd0QzNuaHN3eUphbHZBZ1VPeUh5X0ZuZDM1ZG4xV3VLd25QYTFzUnF6anhhdzYzSVRsT3JPR0dCNGhhV3hZRE1DZTJfMERldkotTmZlR1dOMUF1TWsxZGZYZkhWMGhYREJzbHpUdXFvQ2lNX0kybkRhT1lCaw?oc=5</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Nvidia  (Tier 1 · 4 stories)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3.44</v>
+        <v>5.79</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Oracle รายงานผลประกอบการ รายได้โต 30% แบ็กล็อกเพิ่มเป็น 6.6 แสนล้านดอลลาร์ คาดรับรู้รายได้ครึ่งหนึ่งใน 36 เดือน</t>
+          <t>This week on Tom's Hardware Premium: September 12, 2026 — Benchmarking Qwen 3.8, the splintered compute economy and AI breakthroughs</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151608</t>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-september-12-2026-benchmarking-qwen-3-8-the-splintered-compute-economy-and-ai-breakthroughs</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Why is the internet so upset about NVIDIA's DLSS 5?</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.engadget.com/2252797/nvidia-dlss-5-why-internet-people-upset-issues/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Apple  (Tier 1 · 6 stories)</t>
+      <c r="A26" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Where to preorder the iPhone 18 Pro and Pro Max</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/gadgets/988337/iphone-18-pro-max-preorder-buy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>4.78</v>
+        <v>4.99</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>We unfolded the iPhone Duo</t>
+          <t>Anthropic in talks to bring Nvidia as anchor investor in potential $100 billion IPO: Report</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/podcast/994016/iphone-duo-vergecast-apple-watch-mac-llms</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Where to preorder the Apple AirPods 5</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/gadgets/993637/apple-airpods-5-anc-wireless-charging-preorder-buy</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQVTN4OGgxM0xOYmdCNEpmVERqeHdZTkZWLWtVTzdCNDlZNVQtYS1Zcl8xVER1ODdqQXNvQVBHUzhlRm40dFZuUjJ2NF9ueURLX2dnVENMMXpCQnJnV2NERVNoa2FHd19uME41WW9NeTF1N2IwcUU0aEVKRThVM0NYT25TT0VzU3pqbkk4UHBLRExjWlAtTktHNUowOFA5UklwbU4wT3hfMHN5NnFnNTdXVnEtcmtqU1JaM0sxNXlQdkZ1M0JmSUJGLWg2d3ZNemVyVWtZQkp1YWtnNklfRzd4Q0pRZ9IB6AFBVV95cUxPeFZOa0lhRXJmOGgxdEkzbkM5N3JielJESVlsQkx2ZlB4aGQxX0RKWE9qTW5zUUdOWTQ4cXVRZFZmaFhvTG5RTnJ0elp1Sm9maDNod0xZdmE0ZEhNT0E3TnpSazVUN1huT3k2UXNwSkFGenA5RlFFdE44bEI4Zkk1ZTdJSDdTeDUxLUN4VzFqT2VjM19Mb0c1bUNqaEx3ajJHaG96NXVxeTkwbFdzX0txd3VjQk51bmw1OTl4NjVaVHJXYjdLZzQ2aTZKbWt3M2JXSlpKQjA0OW9VN0VzV1kyQjhRakJMTE1f?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Where should Apple go after the iPhone Duo? Bring on smaller and larger foldables</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2255941/where-should-apple-go-after-the-iphone-duo/</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Oracle  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4.35</v>
+        <v>4.56</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Apple's iPhone Handoff feature will cost you $5 a month on T-Mobile</t>
+          <t>Oracle is betting big on AI and debt. Now Larry Ellison could cash in $7.5 billion</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2255731/apple-iphone-handoff-5-a-month-on-t-mobile/</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPYzN4N3Jic1hiYmtFRWlqZjF6QnJibXdHb1pDN3F2REx0Q2pxMkU4TnBRMTJEQThjek11LWdiN0N3MVkxdHdoYjVxbkJNLU0wY0FncGljOTdQa0RnSDk4ZEZJX1Y4ZFlfc0dXby1JYmtuRkdNN2F5cVk4ZmFqMWpsN2hxeHRLUV9YeUo3U2VDYk1maEpkVFd6eDFza001UTRfQXpuZmdaWmc4RzFWb24yb0NBZV9CcXhVaXlKTUsxWnpqQU1lMG5lLUppOE1SZlpWcndEMllIONIB3AFBVV95cUxQZ0swZnZHTXJxZUZxeEVYT0JPSjZJV1RQVWNYb3o0dGpnVEVVSFo1VnozdDJoRktSWFNBanoybzF1cDRwbEhEMllMX2o3UWFOLVVtTzY1SzlIbXZRZE9qUC0wcG96ZGIya3c3U2NYaDllbXpFdDJLaWpUaU8yZzdlX2V6cXdGMDk0dnNEM1RBc3lkMGZXSE9hOHd0UFVCRk8wOTlVVjF0aWZaMjFfZWNRUlN0NVlvcTc5czBSOHhKMkd0bEYzRHliX3oxV2wtcHp0X3lpNE5qNXZnY2Vr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4.33</v>
+        <v>4.11</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Apple’s Always-Listening Watch Features Test Eavesdropping Laws</t>
+          <t>Larry Ellison Ends Plan to Sell Up to $7.5 Billion in Oracle Stock</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -6577,104 +5670,71 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOVXh5WkZBNmxHVjNJZTJpM1NOeldSSGZQWHE2Q0Z2QmNEalRBYjdrQjd3b0NaQThjU2VSeDAxR0ZSWThHaVZaWE1ld0h3TWk4c25KSVRmSzRlVWdMNEJLRG85V1hPRlJvWjVBTHVEbVluTUh3cDBlZWYxdFJUbUNRWk5CbGNmZkVzVHpleWljVHZkLU9JNE1KVXJXek55TnZaVFVudVRJV1plOFFHXzY0TVZGMzE4ZU1aeG1RcjdEWQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Russian plot to sabotage undersea cables with 'secret weapon' foiled by NATO — clandestine op uncovers training exercise simulating deployment against infrastructure in Norway</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/russian-plot-to-sabotage-undersea-cables-with-secret-weapon-foiled-by-nato-clandestine-op-uncovers-training-exercise-simulating-deployment-against-infrastructure-in-norway</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQbF9TdllreUM2a1BUSWh3akI0WFVkc28zUHN6TElzRTBEZkdJU2tEVmx1b2x1TkJMdHhqcEZqV3p2eEZTWmRLeHRGY2JCekxoM1h1dERxNkRuQW5QT0p6cE1jR3RCM2ZZS2pkSmwySDNFYnl1ZlE3Y0lBVWlzMkh6RjdDMnNHVF9wamNSbFFibXd4aHJObFVGOEg2bHhqQldpbHRMd1ZRWVBMVjZzNVljeWxjb0RWQQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Tesla  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Amazon  (Tier 1 · 5 stories)</t>
+      <c r="A34" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Tesla says it will finally unveil the second generation Roadster on October 1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/12/tesla-says-it-will-finally-unveil-the-second-generation-roadster-on-october-1/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>4.75</v>
+        <v>4.48</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Anthropic spent this week in hot water over cybersecurity</t>
+          <t>Tesla Teases Oct. 1 Event to Showcase Next-Generation Roadster</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/994064/anthropic-spent-this-week-in-hot-water-over-cybersecurity</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic เดือดจนออก Report  แฉโมเดลจีนลอกวิชา Claude ผ่านแชทกว่า 200 ล้านชุดในไม่กี่เดือน Alibaba ทำไป 151 ล้านครั้ง หนักสุดในทุกค่าย</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>techsauce.co</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>https://techsauce.co/ai/anthropic-report-ai-distillation-china</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPYUdYaTBYRXVaSFVnQmx3R0VYR3oybXctT2xJX3YtMlRxRmNqdEsweTlFdDE4V3JiLVR0RnZrRnRTU1BIQ0NPWGtNdzY5MXRmRUxIem1FaHdpMXhtTW0tb1hUY05IZ2VLVEpiWldWTUNFeU5acEhSVmxjWFhTZ0cxN1JLaEpLWGU4VEdUX3E2NFZCdTljc1lTUW9ySUNOOWpINFBLVi1nVGx6WGdqSVlleU53?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>เศรษฐกิจปี 2030 ใน 3 ฉากทัศน์ AI: Anthropic ไล่เรียงอนาคตผ่าน 4 อาชีพ พยาบาล โปรแกรมเมอร์ คอลเซ็นเตอร์ และช่างไฟฟ้า</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>techsauce.co</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>https://techsauce.co/ai/ai-economy-2030-four-occupations-anthropic-scenarios</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>AMD  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>4.17</v>
+        <v>4.24</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Anthropic says Claude thwarted bioweapon research from state-sponsored actors — covert accounts used U.S. proxies to attempt to engineer deadlier viruses, tried to evade identification and regional blocks</t>
+          <t>Wiki documents at least 44 instances in which Sony says you own your games as digital games ownership lawsuit progresses — project is direct assault on Sony's claim in recent ownership lawsuit</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -6684,111 +5744,78 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-says-claude-thwarted-bioweapon-research-from-state-sponsored-actors-covert-accounts-used-u-s-proxies-to-attempt-to-engineer-deadlier-viruses-tried-to-evade-identification-and-regional-blocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic blocks possible attempt to use AI to make biological weapons</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>bbc.com</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBrcXFPTUpsT2dQTWp5eWtOTE9ZQ3BycXlHc0V6cDZoelBXRUhCTmZwM0U4dGV2SGtNUFZFeDhuTTRMR0p5NG91bUdUS0t2M1E3Tzk2OTBER3A3Zw?oc=5</t>
+          <t>https://www.tomshardware.com/video-games/playstation/consumer-rights-wiki-documents-at-least-44-instances-in-which-sony-says-you-own-your-games-project-is-direct-assault-on-sonys-claim-in-recent-ownership-lawsuit</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Alibaba  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Nvidia  (Tier 1 · 3 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>5.39</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>China-modified Nvidia RTX 5090 with massive 96GB of memory appears on Alibaba for less than $4,000 — 3x more VRAM at 65% the cost of the original</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="A41" s="2" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>This week on Tom's Hardware Premium: September 12, 2026 — Benchmarking Qwen 3.8, the splintered compute economy and AI breakthroughs</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>tomshardware.com</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/china-modified-nvidia-rtx-5090-with-massive-96gb-of-memory-appears-on-alibaba-for-less-than-usd4-000-3x-more-vram-at-65-percent-the-cost-of-the-original</t>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-september-12-2026-benchmarking-qwen-3-8-the-splintered-compute-economy-and-ai-breakthroughs</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Desktop graphics card shipments hit four-year high of 12.5 million despite increasing prices — Nvidia takes 90% share as gamers rush to beat looming price spikes</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/desktop-graphics-card-shipments-hit-four-year-high-of-12-5-million-despite-increasing-prices-nvidia-takes-90-percent-share-as-gamers-rush-to-beat-looming-price-spikes</t>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>3.4</v>
+        <v>2.71</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Chinese Nvidia rival Enflame soars 206% on stock market debut as AI demand stays hot</t>
+          <t>Inside Microsoft’s Plans to Massively Expand Computing Power</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNb3NRZnFyUlUzaHZKaEZCV19MVjJ6U0tHRnh3eXc1NzBTRWk0U3VYOEZrSlJLaWdxdWRaaFh1MXVpbjRzb3lKNzBtY0NrQ3ZabmxKNXdWVHJaeW5Pb1ZHemIyTmtwQ2RxMTBWRXVfUjBxZjhoRzNWSjFtWDlPYUpTNFZRVlBEZF9YOWdXdEdzMETSAZYBQVVfeXFMT2gyeDQ0M2xEdTM5MFh5MHdoYUd6elJxSUxVYTdQaGtpdkgxelRnRUpCYTczQzN3dDRHc0kzaHBDdnNJTGdCOXk4eXlhOWdBbHgzVjFfRF9Nc19pblI3MnZmOVBqUmRIMlNET3R1SGUwaUl2Y3hnVi1RdmcxLU1GbUNzdDdJeF9fdXZVcnBkTkJpazB0XzlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQakx5dE5oZUl3d183Q1VCRHl4X1BTcVJkMUUxbm1DZjFKT3o0cU90QlkzRVVaMTBPWU1OWjZlZ1VLRUV6bDl1VW5RTkk4b2RwTUtBLU1SWi1fcS1HQ3lTM1lpOVRETV8tTTJOTklKNXd0alExX1N3RTFnNDl0X2UtdVdxNUhwRHFoMnVPQ2lUX0JzNEpLUGRYVERSbzI2SWNBbGhuZlRiMldSRzlENWZ6NTJZTlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Alphabet  (Tier 1 · 2 stories)</t>
+          <t>Netflix  (Tier 2 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>5.65</v>
+        <v>4.38</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>iPhone 18 Pro vs Pixel 11 Pro: How Apple and Google's flagships stack up</t>
+          <t>Diablo V is coming out in spring 2029</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -6798,155 +5825,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2256364/iphone-18-pro-vs-pixel-11-pro/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>กูเกิลปล่อยแอป Gemini สำหรับวินโดวส์</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>blognone.com</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://www.blognone.com/node/151612</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Tesla  (Tier 1 · 2 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Elon Musk calls documentary about him a 'hit piece' after buzzy debut</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>cbc.ca</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTFA5QzJ6Z0g4TWk1aG5vQkpnVDU4UGd5SWUwYXREblBCN1FnQm15Nm9fLXRKWVVfWVFMYXpUbjBmR3BsRWNqdi1jSGF1ek1rTHdGY1RKaEc0X19rbUxaUVh0ZzJiVkF4Q0d0NmN4UUdGZ01YRTdSMG4xd3FFM0ZaZw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Tesla Shares Suffer Slow Summer After SpaceX IPO, Earnings Rout</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQSUNSdDdROUtRU3lNUE1xY3Frb2NrTTVZQ1ZWSk5WQWpfQTBHWllyd1B5S2UxM2R1T1lWcU1RZi13TXNTTkdpRG1RMmJDbzRWZFZBUkh1ZXQ1VEI0YVdtUFc2NlRiTk42WnNodFphSzR4ZkpaZDc5aUh4N3dnT1VwNk40aGRONGtqa0FRWE13SmNFSDAxRGd1MDFSeGxNUWxwUG8yUmdMd2N6aWhraGZlTFdyNA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft’s head of comms is leaving after almost 20 years</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/news/993791/microsoft-frank-shaw-leaving-head-of-comms</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Oklo  (Tier 2 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Sanctioned Chinese supercomputer maker stripped of IO500 benchmark crown, Intel-powered Aurora retakes the lead — record-breaking ParaStor F9000 storage system doesn't meet reproducibility requirements</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/supercomputers/sanctioned-chinese-supercomputer-maker-stripped-of-io500-benchmark-crown-intel-powered-aurora-retakes-the-lead-record-breaking-parastor-f9000-storage-system-doesnt-meet-reproducibility-requirements</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>TSMC  (Tier 2 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>OpenAI says its next-generation processors could be made at Samsung — double-sourcing with TSMC hints at massive volume requirements [Updated]</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPVTFNNG4tc1dDb1pIRDBCc1NLTWZkVFE5b3hxWDVHVVJUdTl5c293dVJSc2dYU2xPSFVZemx3Z3poLVQ1TFV4bVZSQ0d6Uy1QQnR1cHNyeElhUTk4N3hXaFloNmJfU3VtbzBDbnpPMXBwR3dfa0JCd1hUUkdRMjEtMUpFR3NGRmVDTXo2RUpjM3hCTkpwUjREZnhPRmhqX2d0eWVmSHBURm96QlgyYlRlaFBhZGk1aC1HaVdJTzYyb0ZqLU9VaG5zUzRJYkxXUEp1N05vSGZLSEloS2NHZ1FvbmNSRXVUVEIxbjVvRkE3WFcyLWFJekVIMUxEQVBHZ3pNZkMwQXBXS3VzUzE5MlZZOFVFQ0cwdjFCQUFyLTViUzBNZlk?oc=5</t>
+          <t>https://www.engadget.com/2256735/diablo-v-is-coming-out-in-spring-2029/</t>
         </is>
       </c>
     </row>
@@ -6958,40 +5837,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6.01</v>
+        <v>6.4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -549,25 +549,25 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>AI infrastructure company Cornelis raises $205M to chip away at Nvidia’s dominance</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt In Brief Posted: Cornelis, a company creating networking technology to help AI chips communicate more effectively, announced Monday that it has raised $205 million in a funding round led by IAG Capital Partners. It also announced a product called Act</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: E. Slomonson/The Photo Group for TechCrunch / Getty Images AI OpenAI, Anthropic, Google have been in talks on AI safety for weeks Rebecca Bellan 8:47 AM PDT · September 15, 2026 Chris Lehane, OpenAI’s global policy chief, told reporter</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, gpu, chip, ai infrastructure</t>
+          <t>openai, anthropic, deepmind, ai, ai safety</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:07:37 +0000</t>
+          <t>Tue, 15 Sep 2026 15:47:03 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,16 +577,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/ai-infrastructure-company-cornelis-raises-205m-to-chip-away-at-nvidias-dominance/</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Is Big Tech’s AI slowdown a safety pact or a cartel?</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI Policy Report Is Big Tech’s AI slowdown a safety pact or a cartel? Major </t>
+          <t>Chris Lehane, OpenAI’s global policy chief, told reporters on Tuesday that the company has been working with rivals Anthropic and Google DeepMind on AI safety for weeks, as first reported by Bloomberg. Lehane is reportedly in Washington to work with U.S. lawmakers addressing catastrophic risks associated with AI. The revelation comes in the wake of Anthropic CEO Dario Amodei’s essay, published Sat</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, deepmind, ai</t>
+          <t>openai, anthropic, ai, ai safety</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T18:59:41-04:00</t>
+          <t>Tue, 15 Sep 2026 15:47:03 GMT</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/995186/is-big-techs-ai-slowdown-a-safety-pact-or-a-cartel</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Russian freelancers use Claude to program autonomous combat drone swarm — AI-enabled target selection and detonation without a human in the loop</t>
+          <t>AI networking startups race to replace Nvidia's NVLink</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>SYSTEMS Intel spin-off Cornelis and newcomer Delos Data pitch open alternatives for scaling AI beyond the rack Tobias Mann Tobias Mann SYSTEMS EDITOR Published tue 15 Sep 2026 // 21:56 UTC READ MORE Anthropic and OpenAI look to Uncle Sam to make them too big to fail 9 hours ago Datacenter developers want your backyard. FAS says negotiate harder 1 day ago Nvidia's Groq acquihire is on the DOJ's rad</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>claude, ai, semiconductor, fab, autonomous</t>
+          <t>ai, nvidia, amd, ai accelerator</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14.2</v>
+        <v>4.1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 11:00:00 +0000</t>
+          <t>Tue, 15 Sep 2026 22:56:48 +0200</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/russian-freelancers-use-claude-to-program-autonomous-combat-drone-swarm-ai-enabled-target-selection-and-detonation-without-a-human-in-the-loop</t>
+          <t>https://www.theregister.com/systems/2026/09/15/ai-networking-startups-race-to-replace-nvidias-nvlink/5296672</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.1</v>
+        <v>5.42</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Ex-FTC boss Khan urges Uncle Sam to break out the handcuffs for AI CEOs, citing 1934 precedent</t>
+          <t>Meta now lets AI agents handle the boring parts of WhatsApp Business setup</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ai and ml There are plenty of laws on the books to hold companies, and potentially their execs, accountable Former FTC chair Lina Khan wants the federal government to know that it doesn't need to wait for new laws to address AI threats. There are already laws and regulations on the books, including a 92-year-old Supreme Court precedent, that she argues could be used to hold AI companies and, in so</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Matthias Balk/picture alliance / Getty Images Social Meta now lets AI agents handle the boring parts of WhatsApp Business setup Sarah Perez 1:12 PM PDT · September 15, 2026 Alongside news of its new AI-focused subscription plans , Meta</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, xai, ai</t>
+          <t>claude, chatgpt, ai, ai coding</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 18:59:24 +0200</t>
+          <t>Tue, 15 Sep 2026 20:12:53 +0000</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,13 +730,13 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/14/ex-ftc-boss-khan-urges-uncle-sam-to-break-out-the-handcuffs-for-ai-ceos-citing-1934-precedent/5296325</t>
+          <t>https://techcrunch.com/2026/09/15/meta-now-lets-ai-agents-handle-the-boring-parts-of-whatsapp-business-setup/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.98</v>
+        <v>5.33</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>spectrum.ieee.org</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Apple อัปเดต iOS 27, iPadOS 27, macOS 27 Golden Gate, watchOS 27 ให้ผู้ใช้งานทั่วไปแล้ววันนี้</t>
+          <t>The AI Inference Revolution Is Here</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>แอปเปิลออกอัปเดตซอฟต์แวร์ระบบปฏิบัติการเวอร์ชันใหม่ของปีหมายเลข 27 ให้กับผู้ใช้งานทั่วไปแล้ววันนี้ ได้แก่ iOS 27, iPadOS 27, macOS 27 Golden Gate, watchOS 27, visionOS 27 และ tvOS 27 ภาพรวมการเปลี่ยนแปลงที่สำคัญในอัปเดตนี้คือความสามารถที่มากขึ้นของปัญญาประดิษฐ์ Apple Intelligence ที่รวมความสามารถจาก Gemini เข้ามา และผู้ช่วยอัจฉริยะ Siri AI ที่สามารถโต้ตอบแบบการสนทนาและทำสิ่งต่าง ๆ บนอุปกรณ์ได้มากข</t>
+          <t xml:space="preserve">IEEE.org IEEE Xplore IEEE Standards IEEE Job Site More Sites Sign In Join IEEE The AI Inference Revolution Is Here Share FOR THE TECHNOLOGY INSIDER Explore by topic Aerospace AI Biomedical Climate Tech Computing Consumer Electronics Energy History of Technology Robotics Semiconductors Telecommunications Transportation IEEE Spectrum FOR THE TECHNOLOGY INSIDER Topics Aerospace AI Biomedical Climate </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>gemini, ai, ปัญญาประดิษฐ์</t>
+          <t>openai, gpt, ai, inference, benchmark</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3.2</v>
+        <v>12.1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:57:03 +0000</t>
+          <t>Tue, 15 Sep 2026 13:00:05 +0000</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151641</t>
+          <t>https://spectrum.ieee.org/inference-hardware-revolution</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.92</v>
+        <v>5.3</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>What execs and politicians are saying about slowing down AI development</t>
+          <t>We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Policy What execs and politicians are saying about slowing down AI d</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Chesnot / Getty Images AI We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says Julie Bort 5:20 PM PDT · September 15, 2026 Nvidia founder and CEO Jensen Huang made his position on the dangers AI poses very clear</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai safety</t>
+          <t>ai, nvidia, ai regulation</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T17:21:42-04:00</t>
+          <t>Wed, 16 Sep 2026 00:20:39 +0000</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/995141/ai-executives-politicians-safety-regulation-anthropic-dario-amodei</t>
+          <t>https://techcrunch.com/2026/09/15/we-dont-need-ai-regulation-leave-safety-to-us-nvidias-jensen-huang-says/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.7</v>
+        <v>5.27</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>bbc.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>AI 'kill switch' may need to be mandatory, Anthropic co-founder tells BBC</t>
+          <t>Google อนุญาตให้พนักงานใช้ Claude เป็น AI ช่วยเขียนโค้ดได้แล้ว จากที่ผ่านเน้นใช้ Gemini</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>AI 'kill switch' may need to be mandatory, Anthropic co-founder tells BBC 38 minutes ago Share Save Add as preferred on Google Kali Hays,Technology reporterandFaisal Islam,Economics editor AI "more powerful by the day", Anthropic co-founder tells BBC An artificial intelligence "kill switch" which can be checked by a third party may need to be mandatory for companies, a co-founder of one of the wor</t>
+          <t>Business Insider อ้างแหล่งข่าวภายในกูเกิลซึ่งต่อมายืนยันโดยโฆษกของกูเกิล ว่าบริษัทได้อนุญาตให้วิศวกรของบริษัทใช้งาน Claude AI ของ Anthropic เพื่อช่วยในการพัฒนาโครงการต่าง ๆ ของบริษัทแล้ว ซึ่งที่ผ่านมากูเกิลห้ามใช้ ก่อนหน้านี้แนวทางการใช้ AI ในการทำงานภายกูเกิลไม่อนุญาตให้ใช้เครื่องมือช่วยเขียนโค้ดภายนอกอย่าง Claude Code หรือ Codex ของ OpenAI เนื่องจากกูเกิลต้องการให้พนักงานใช้ Gemini เป็นหลัก โดยม</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>openai, anthropic, claude, gemini, ai</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6</v>
+        <v>12.8</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 00:32:21 GMT</t>
+          <t>Tue, 15 Sep 2026 12:15:21 +0000</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/cqgk5e2j0gg8o</t>
+          <t>https://www.blognone.com/node/151646</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,49 +901,49 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>This is what young people studying artificial intelligence are thinking — as the future of AI grabs headlines</t>
+          <t>AI leaders clash over safety fears after Anthropic whistleblower says AI could 'kill us all' by 2030 — OpenAI, Anthropic and xAI figureheads call for external governance, while Jensen Huang says worries are 'made up'</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>This is what young people studying artificial intelligence are thinking — as the future of AI grabs headlines    CBC</t>
+          <t xml:space="preserve">Welcome to Tom's Hardware club ! Hi , Your membership journey starts here. Keep exploring and earning more as a member. Latest on CPUs News, reviews, and technical insights. GPU Insights Reviews, benchmarks, and updates on current GPUs. See what you’ve unlocked. Explore your membership benefits. Limited-time Premium offer Cancel anytime Premium Member Hi , Keep exploring with your premium access. </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ai, artificial intelligence</t>
+          <t>openai, anthropic, xai, ai</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 00:05:01 GMT</t>
+          <t>Tue, 15 Sep 2026 17:19:36 +0000</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9sM1FOREE3WkMweXRaX0xsVnJIcS1tUEphbzdWS2EwREwtbTdkWk5VZnlZclZSLUN3bXJVNzVVRjd1VkFNUTNndkpabzVYN2NsMlRJUnpmUWdOUQ?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/ai-leaders-clash-over-safety-fears-after-anthropic-whistleblower-says-ai-could-kill-us-all-by-2030-openai-anthropic-and-xai-figureheads-call-for-external-governance-while-jensen-huang-says-worries-are-made-up</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.37</v>
+        <v>5.07</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -952,17 +952,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’</t>
+          <t>Microsoft announces Windows and Surface event for October 7th</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Fabrice COFFRINI/AFP / Getty Images AI Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’ Amanda Silberling 2:51 PM PDT · September 14, 2026 While Nvidia CEO Jensen Huang was onstage at the All-In Summ</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... News Tech Microsoft Microsoft announces Windows and Surface event for Octobe</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:51:02 +0000</t>
+          <t>2026-09-15T16:36:59-04:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/nvidia-ceo-jensen-huang-tells-trump-were-not-going-to-let-an-ai-slowdown-happen/</t>
+          <t>https://www.theverge.com/news/994714/microsoft-windows-surface-event-october-7-san-francisco</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.24</v>
+        <v>4.78</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Trump says no need for more AI regulation, slams Anthropic CEO Dario Amodei</t>
+          <t>สรุปประเด็น AGI จาก CEO บริษัทเทคฯ แห่งยุค AGI อาจมาเร็วกว่าที่คาดไว้ใน 5 ปี แต่โลกยังไม่มีกติการองรับ</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>WATCH LIVE POLITICS &amp; POLICY Trump goes scorched earth on AI warnings, raging about data center opposition and regulation PUBLISHED MON, SEP 14 2026 10:09 AM EDT UPDATED 4 HOURS AGO Kevin Breuninger @KEVINWILLIAMB CJ Haddad @IN/CRISTENHADDAD/ WATCH LIVE KEY POINTS President Donald Trump raged against growing calls for greater regulation of artificial intelligence. Trump lashed out at Anthropic CEO</t>
+          <t>0 กันยายน 15, 2026 | By Techsauce Team บนเวที AI Action Summit ที่กรุงปารีสเมื่อต้นปี 2025 Dario Amodei ซีอีโอและผู้ร่วมก่อตั้ง Anthropic กับ Demis Hassabis ซีอีโอและผู้ร่วมก่อตั้ง Google DeepMind ขึ้นเวทีเดียวกันราว 20 นาที โดยมี Zanny Minton Beddoes บรรณาธิการบริหารของ The Economist เป็นผู้ดำเนินรายการ คำถามที่เปิดวงคือปัญญาประดิษฐ์ทั่วไป (Artificial General Intelligence หรือ AGI) จะมาถึงเมื่อไห</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai regulation</t>
+          <t>anthropic, deepmind, ai, agi, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>11</v>
+        <v>17.9</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 14:09:03 GMT</t>
+          <t>Tue, 15 Sep 2026 14:08:41 +0700</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/amp/2026/09/14/trump-ai-data-centers-anthropic-dario-amodei.html</t>
+          <t>https://techsauce.co/ai/amodei-hassabis-agi-timeline-governance</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.23</v>
+        <v>4.6</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>MPs and peers tell UK to stop winging it on AI regulation</t>
+          <t>Microsoft will hold a Windows and Surface event on October 7</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>AI AND ML Rights committee demands watchdog with teeth as patchwork safeguards leave victims hunting for remedies UK lawmakers want an AI watchdog with the teeth to stop potentially dangerous systems reaching the public, warning that existing rules leave people exposed and struggling to hold anyone accountable. The Joint Committee on Human Rights (JCHR) – comprising MPs and peers – said that altho</t>
+          <t>The event is focused on "Windows, NVIDIA RTX Spark, Surface, and the broader PC ecosystem." Microsoft Add Engadget on Google: Preferred Source Google Discover Microsoft is hosting an event in San Francisco on October 7 on "how local AI will shape the next chapter of the PC." Coming only a few months after NVIDIA announced its first system-on-a-chip for Windows, the NVIDIA RTX Spark , the event see</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai, ai regulation</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>13.2</v>
+        <v>2.8</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 14:00:00 +0200</t>
+          <t>Tue, 15 Sep 2026 22:18:07 +0000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,16 +1087,16 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/14/mps-and-peers-tell-uk-to-stop-winging-it-on-ai-regulation/5296108</t>
+          <t>https://www.engadget.com/2259695/microsoft-will-hold-a-windows-event-on-october-7/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.23</v>
+        <v>4.4</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>MPs and peers tell UK to stop winging it on AI regulation</t>
+          <t>AI and data centers are incredibly unpopular in every poll</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>AI AND ML MPs and peers tell UK to stop winging it on AI regulation Rights committee demands watchdog with teeth as patchwork safeguards leave victims hunting for remedies Lindsay Clark BUSINESS SOFTWARE AND DATABASE REPORTER 8 Published Mon 14 Sept 2026 // 12:00 UTC READ MORE UK.gov begins killing off passwords for 23 million users 12 hours ago Britain's technology brief is now everyone's job and</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Policy AI and data centers are incredibly unpopular in every poll 61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai, ai regulation</t>
+          <t>ai, ai safety</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>13.2</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 12:00:00 GMT</t>
+          <t>2026-09-15T19:34:25-04:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/14/mps-and-peers-tell-uk-to-stop-winging-it-on-ai-regulation/5296108</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/995917/data-center-nyt-midterm-poll-september</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.1</v>
+        <v>4.37</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts feel-good AI model guidelines and wants your input</t>
+          <t>The AI data center boom is colliding with cities scarred by big industry</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Microsoft on Monday debuted draft principles for governing how the company will train future AI models, as part of a public consultation process. The Windows biz has solicited feedback to refine its Humanist AI Code of Conduct [PDF], with the expectation of applying the guidelines to model developme</t>
+          <t>National outcry against data center construction has spread to Philadelphia, where officials suggested possible construction in a neighborhood already impacted by a now-defunct oil refinery.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, data center</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 02:15:29 +0200</t>
+          <t>Tue, 15 Sep 2026 21:47:38 +0000</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/15/microsoft-drafts-feel-good-ai-model-guidelines-and-wants-your-input/5296431</t>
+          <t>https://techcrunch.com/2026/09/15/the-ai-data-center-boom-is-colliding-with-cities-scarred-by-big-industry/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.09</v>
+        <v>4.25</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1207,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Anthropic says AI can boost U.S. GDP by 32%, up to $44.4 trillion in four years — economics model predicts that displaced employees 'may have to switch to jobs like electrician and nurse'</t>
+          <t>Your AI agents' reports and questions have a new inbox, courtesy of AWS</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Bruno Ferreira's journey kicked off with the venerable ZX Spectrum, a cassette player, and his hopes and dreams. He quickly realized he had more fun figuring out how computers work than he did actually using the things. Kicking off a developer career with C and Assembly before moving to scripting la</t>
+          <t xml:space="preserve">AWS engineers have published an open-source AI agent management tool that treats tasks and permission requests just like emails that fill up an inbox. Pizza Bot was announced on AWS’ open-source blog last week, where it was billed by its developers as a way to more easily manage agent tasks without </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 18:50:36 +0000</t>
+          <t>Tue, 15 Sep 2026 22:25:44 +0200</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,48 +1240,48 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-says-ai-can-boost-u-s-gdp-by-32-percent-up-to-usd44-4-trillion-in-four-years-economics-model-predicts-that-displaced-employees-may-have-to-switch-to-jobs-like-electrician-and-nurse</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/15/your-ai-agents-reports-and-questions-have-a-new-inbox-courtesy-of-aws/5296661</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.01</v>
+        <v>4.16</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's malicious bot swarm attacked RubyGems</t>
+          <t>OpenAI Says It’s Working With Anthropic, Google on AI Safety</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>OpenAI agents appear to have flooded RubyGems with malicious packages, adding to a near-daily deluge of rogue AI models engaging in potentially unlawful activity while their human creators face growing questions over responsibility for their agents’ bad behavior. A swarm of agents began uploading ma</t>
+          <t>OpenAI Says It’s Working With Anthropic, Google on AI Safety    Bloomberg.com</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>openai, anthropic, ai, ai safety</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>7.1</v>
+        <v>10.8</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:03:58 +0200</t>
+          <t>Tue, 15 Sep 2026 14:18:33 GMT</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1291,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/09/14/openais-malicious-bot-swarm-attacked-rubygems/5296356</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQU2hNbVd5RVh6MTNQU3RjMVBLdnZmbzhRTVhHSnJ0dko1ZnVNeUw2Tm1xLXk3VE5xa3phZTB3TmFHYjJ2emlUZHgyc0NSbEV1RFpGY3JCODFCNW52WjJfdFhVNzFFbExIY1lDS3BwalhUUllSWEtYNm1KM1ZJRHdVVTc4QnlhcFRiX2NnWUZmSlRwdmc4Z0FvQnNucW9GTXlqZW5PREhzWVlWTllxTHlJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3.97</v>
+        <v>4.13</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1309,30 +1309,30 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's RTX 5090 vanishes from online retail in the US — third-party sellers now demand as much as $9,500 for Nvidia's fastest GPU</t>
+          <t>Anthropic and OpenAI look to Uncle Sam to make them too big to fail</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
+          <t>OPINION By luck or happenstance, Anthropic planted a seed in the mind of the public last week: AI in the wrong hands is dangerous and left unchecked poses an existential threat to humanity. With pop culture steeped in references to malignant AI, the mainstream media ate it up. The headlines wrote th</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>nvidia, gpu</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>7.5</v>
+        <v>12.1</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:41:01 +0000</t>
+          <t>Tue, 15 Sep 2026 15:00:00 +0200</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1342,13 +1342,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/nvidias-rtx-5090-vanishes-from-online-retail-in-the-us-third-party-sellers-now-demand-as-much-as-usd9-500-for-nvidias-fastest-gpu</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/15/anthropic-and-openai-look-to-uncle-sam-to-make-them-too-big-to-fail/5296403</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3.97</v>
+        <v>4.11</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1360,30 +1360,33 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Gaming takes a backseat as Nvidia overhauls the RTX 5090 for maximum AI margins — RTX Pro 5500 delivers 2.6X VRAM at matching specs</t>
+          <t>Salesforce เปิดตัว AIforce รวมชุด MCP/Skill เข้าเป็นชุดบริการ ระบุเป็นโอกาสดีที่จะแทน UI ซอฟต์แวร์องค์กรด้วย AI</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Zhiye's passion for computer hardware ignited in his pre-teen years, thanks to a learning moment in which a power connection mishap set his Pentium P54CS system on fire and inadvertently short-circuited his entire home. Over the years, Zhiye's curiosity evolved into a relentless pursuit of deeper kn</t>
+          <t>Salesforce เปิดตัว AIforce รวมชุด MCP/Skill เข้าเป็นชุดบริการ ระบุเป็นโอกาสดีที่จะแทน UI ซอฟต์แวร์องค์กรด้วย AI 
+     Body 
+                Salesforce เปิดตัวบริการ AIforce ชุดบริการด้านปัญญาประดิษฐ์สำหรับการใช้งาน AI รวมกับ Salesforce เดิม 
+ เดิม Salesforce ทำงานร่วมกับ AI ต่างๆ เช่น Claude หร</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>claude, ai, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7.5</v>
+        <v>12.3</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:39:09 +0000</t>
+          <t>Tue, 15 Sep 2026 12:48:31 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1393,13 +1396,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/gaming-takes-a-backseat-as-nvidia-overhauls-the-rtx-5090-for-maximum-ai-margins-rtx-pro-5500-delivers-2-6x-vram-at-matching-specs</t>
+          <t>https://www.blognone.com/node/151647</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1411,30 +1414,30 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>macOS 27 is available now</t>
+          <t>The AI graveyard: a running list of projects and startups that didn’t make it</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apple released  macOS 27 Golden Gate   on Monday , which brings the new  Siri AI assistant , Liquid Glass improvements, improved performance, and more. The update is compatible with all Macs with Apple Silicon, but not Intel Macs - Apple released its final big update for Intel-based Macs last year  </t>
+          <t>From Apple's repeatedly delayed Siri AI to OpenAI's messy "super app" launch, here's a look at the AI projects that shut down or missed expectations.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ai, ai assistant</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T13:10:13-04:00</t>
+          <t>Tue, 15 Sep 2026 19:00:00 +0000</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1444,13 +1447,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/994818/apple-macos-27-golden-gate-available-now</t>
+          <t>https://techcrunch.com/2026/09/15/the-ai-graveyard-a-running-list-of-projects-and-startups-that-didnt-make-it/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1462,30 +1465,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>foxbusiness.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>AI giants, investors clash over calls to slow down artificial intelligence development</t>
+          <t>AI ร้ายแรงกว่าอาวุธนิวเคลียร์? ทำไมนักวิจัยเตือน ปัญญาประดิษฐ์เสี่ยง ‘ฆ่ามนุษย์’ ภายใน 10 ปีข้างหน้า</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>AI giants, investors clash over calls to slow down artificial intelligence development    Fox Business</t>
+          <t>AI ร้ายแรงกว่าอาวุธนิวเคลียร์? ทำไมนักวิจัยเตือน ปัญญาประดิษฐ์เสี่ยง ‘ฆ่ามนุษย์’ ภายใน 10 ปีข้างหน้า    thestandard.co</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai, artificial intelligence</t>
+          <t>ai, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:02:33 GMT</t>
+          <t>Tue, 15 Sep 2026 17:54:38 GMT</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1495,13 +1498,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9FRUZxNS1HWkMtdktRYVQ1ejRZOHNDQzk4S1pBZmxiNFhteDU0ZVJpUnBvY2FhcnZNcHllRmQ1T1VUVTE1VHJxRUVKWkZZb3B0N1cxYmFzU1Q2TnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5FXzFRYUVBRkkxSC1URV9mZ2tEVE1pX1BmMzUyd2FuRU9QdVFxSTNZTVBNcVJOR3ZUOG5sei0weC1pTkl4R3Vjd3VfUVZuSk0tblA5OXlJbHJsNUsxTXVtcEExYTBMeE0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1513,32 +1516,33 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>ฟิลิปปินส์ประกาศแผน AI 1.14 ล้านล้านบาท ชี้ไทย-เวียดนาม-อินโดฯ คือคู่แข่ง ยอมรับต้องเร่งไล่ให้ทัน</t>
+          <t>NVIDIA ปล่อย CUDA Rust เขียน GPU kernel ได้ทั้งแบบ CUDA เดิมและ Tile</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>รัฐบาลฟิลิปปินส์เปิดตัวแผนแม่บทโครงสร้างพื้นฐานด้านปัญญาประดิษฐ์ (PAIIM) สำหรับปี 2026-2033 มูลค่า 3.44 หมื่นล้านดอลลาร์สหรัฐ (ประมาณ 1.14 ล้านล้านบาท) เพื่อผลักดันประเทศขึ้นเป็นศูนย์กลางโครงสร้างพื้นฐาน AI ของภูมิภาค 
- ประเด็นสำคัญ 
-  ขยายกำลังดาต้าเซ็นเตอร์ 30 เท่าจากฐานที่เกือบไม่</t>
+          <t>NVIDIA ปล่อย CUDA Rust เขียน GPU kernel ได้ทั้งแบบ CUDA เดิมและ Tile 
+     Body 
+                NVIDIA ปล่อยชุดคอมไพเลอร์ CUDA Rust หลังจากใช้ Rust พัฒนาซอฟต์แวร์จำนวนมากมาก่อนหน้านี้ ทำให้เป็นภาษาที่สามหลังจาก C++ และ Python 
+ ก่อนหน้านี้ NVIDIA ใช้ Rust ในโครงการจำนวนมากอยู่แล้ว  เช่น ไดรเวอ</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ai, ปัญญาประดิษฐ์, ดาต้าเซ็นเตอร์</t>
+          <t>nvidia, gpu, ชิป</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 10:42:37 +0000</t>
+          <t>Tue, 15 Sep 2026 11:15:47 +0000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/philippines-ai-plan-asean-rivals/</t>
+          <t>https://www.blognone.com/node/151645</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1561,7 @@
         <v>3.9</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -1566,30 +1570,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>OpenAI CEO Sam Altman concerned about artificial intelligence taking control over humans, ‘AI must always serve people’</t>
+          <t>Open weights are not open source: Why AI's favorite label is under dispute</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>OpenAI CEO Sam Altman concerned about artificial intelligence taking control over humans, ‘AI must always serve people’    Livemint</t>
+          <t>The AI industry likes to abuse the word "open." It appears in product releases, research papers, policy debates, and investor presentations. A company publishes model files to Hugging Face, developers run them on their own GPUs, and the release is quickly described as an "open source model." Not nec</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, artificial intelligence</t>
+          <t>ai, neural network</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>14.6</v>
+        <v>16.6</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 10:36:26 GMT</t>
+          <t>Tue, 15 Sep 2026 10:30:00 +0200</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1599,13 +1603,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQLTVNZGxjQXhoeXoydV84bmVIR20xMXdhWnpMYVB5MDB0N3R1V28wZWFGaFNQaFpxeVpsU0NWM1JSbU42bGtER1hwaUl2N1lYaE9oQVRmVUhoenlDTkpQWmtvUlhabFU5RFpwOGp3ODBNWl90YUZ1U1lkUTN5RU1EM0tFOV9jNEx3OWs0MzZjZFJUcWoxLTRVYTZyM0JMWjFuT2NlVlhBOXh3MjkyZDFQOXJoOHAzQTdqcnVleTFqX3pyT0doQUdZUzNVcGV1eGs4Nmp5eU5YdHV0aHFtN1lxaHpIVHl2NGdSWG5KQmtDNWJCemFmOXM00gH8AUFVX3lxTE1zMXFzOTRLTl85UWt3NUl1VUUyTjZtVFJPRG1rQjZ0OUd5bVFmM25icjcySEVOSHFQRWpkRDhWenl0VDgtVmhoNExZX1MyellPN2w3ZjZwUlZhNUpVT2lBbHNZSTJaRmtodTFWLTFZemJ1MVM3SXI2Mkk1RmsyUmk4N0gxXzk3cnh5YjBaMGdpMkFyVDBnaVJiZzB2X3FjSGhzOWlQXy0wcWMwemc1RWtDbmthWTJoQ044RzI4YmM0SC1JZVJiNGRiTU15eC13WlZpUGFpYUpzTFctVUNzYWMwNUpoMlVzRHRvbHhRSFozY19XVDFZRzgzVnFGNQ?oc=5</t>
+          <t>https://www.theregister.com/columnists/2026/09/15/open-weights-are-not-open-source-why-ais-favorite-label-is-under-dispute/5295436</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1622,25 +1626,28 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>ไทย-อาเซียนจะปรับยุทธศาสตร์พลังงาน สู่ยุคพลังงานหมุนเวียนและ Data Center อย่างไรให้ยั่งยืน?</t>
+          <t>กลุ่มบ้านปู เร่งทรานส์ฟอร์มพอร์ต มุ่งเพิ่มสัดส่วน ‘ก๊าซฯ-ไฟฟ้า’ เกิน 50% ชูโซลูชันพลังงานเสถียรแก้คอขวด Data Center &amp; AI พร้อมรุก LNG เทรดดิ้งข้ามทวีป</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>วันนี้ (14 กันยายน) การเปลี่ยนผ่านทางเทคโนโลยีในระดับภูมิภาคและทั่วโลกกำลังเผชิญกับจุดเปลี่ยนสำคัญ เมื่อการเติบโตอย่างก้าวกระโดดของ ปัญญาประดิษฐ์ (AI) และ Data Center กลายเป็นเครื่องยนต์หลักในการขับเคลื่อนเศรษฐกิจดิจิทัล ซึ่งส่งผลให้ความต้องการพลังงานไฟฟ้าพุ่งสูงขึ้นอย่างรวดเร็ว ควบคู่ไปกับโจทย์ใหญ่</t>
+          <t xml:space="preserve">กลุ่มบ้านปู ประกาศยุทธศาสตร์ปรับพอร์ต เร่งดันสัดส่วนก๊าซฯ-ไฟฟ้าเกิน 50% ชูนวัตกรรมเครื่องยนต์ก๊าซฯ มอดูลาร์และ BESS แก้โจทย์คอขวดพลังงาน AI ระดับโลก พร้อมรุก LNG Trading ข้ามทวีป 
+ ประเด็นสำคัญ 
+  ลดถ่านหิน ดัน ‘ก๊าซฯ-ไฟฟ้า’ ขึ้นแท่นแกนหลักสร้างกระแสเงินสด  
+  นวัตกรรมก๊าซฯ มอดูลาร์ </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ai, data center, ปัญญาประดิษฐ์</t>
+          <t>ai, data center, โมเดล</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 10:10:32 +0000</t>
+          <t>Tue, 15 Sep 2026 10:10:41 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1650,13 +1657,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/thailand-asean-energy-strategy-data-center/</t>
+          <t>https://thestandard.co/banpu-gas-power-ai-data-center-lng/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1668,30 +1675,30 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Palantir, and others restrict advanced AI model usage over privacy concerns, report claims — 'paranoia' rising over customer intellectual property</t>
+          <t>ปลดล็อกคอขวดพลังงาน! ไทยจะเร่งสปีด ‘Time to Power’ อย่างไรให้สอดรับการเติบโต AI-Data Center</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Oliver Haslam has written about technology of all shapes and sizes for over 15 years, both online and in print.  Having grown up using PCs and spending far too much money on graphics cards and fancy RAM, Oliver switched to the Mac with a G5 iMac. Nowadays, he uses both macOS and Windows depending on</t>
+          <t>วันนี้ (15 กันยายน) ความต้องการพลังงานไฟฟ้าที่เพิ่มขึ้นอย่างมหาศาล จากการขยายตัวของเทคโนโลยีปัญญาประดิษฐ์ (AI) ได้ทำให้โจทย์สำคัญที่สุดของอุตสาหกรรม Data Center เปลี่ยนจากการพัฒนาอุปกรณ์และชิ้นส่วนทางกายภาพทั้งหมดของระบบคอมพิวเตอร์ (Computing Hardware) ไปสู่การแก้ปัญหา ‘Time to Power’ หรือความเร็วใน</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>ai, data center, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 15:58:32 +0000</t>
+          <t>Tue, 15 Sep 2026 10:04:32 +0000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1701,7 +1708,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-palantir-and-others-restrict-advanced-ai-model-usage-over-privacy-concerns-report-claims-paranoia-rising-over-customer-intellectual-property</t>
+          <t>https://thestandard.co/thailand-power-bottleneck-ai-data-center/</t>
         </is>
       </c>
     </row>
@@ -1719,19 +1726,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Apple Home’s new security camera features cost as much as $60 a month</t>
+          <t>Bernie Sanders and Steve Bannon call for curbs on AI at ‘pro-human’ summit</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Apple Intelligence features for HomeKit cameras start at $10 a month and go up to $60. | Image: The Verge	 
- With the  public release of iOS 27 and tvOS 27 , Apple Home is getting an injection of  Apple Intelligence  - but you'll have to pay more for it. 
-  Apple Intelligence for Home  brings </t>
+          <t>Bernie Sanders and Steve Bannon call for curbs on AI at ‘pro-human’ summit    The Guardian</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1740,11 +1745,11 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T18:28:52-04:00</t>
+          <t>Tue, 15 Sep 2026 22:43:00 GMT</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1754,7 +1759,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/994949/apple-intelligence-apple-home-icloud-plus-cost-subscription</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNQW1KVnJzR0JDZG5rRE5VeUVpeGNKckZoVGlxMVVwYWxlTzJhVDE1SVh5Y1Jwd0o3R2dZZnZKNEFueDR1a2MyS2wzOXNZZG5GYjBfSXF6UUExWkxsdHFjRm11a1htRkpYa05SdVdHaExGbEtSMGwzNEF4azhyMk40Nm5tLVh3Q09GX1FTWlh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1782,12 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>AI CEOs say they need to slow the pace of development. But will they?</t>
+          <t>Why the real AI apocalypse is already here – Stateside with Kai and Carter</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>AI CEOs say they need to slow the pace of development. But will they?    The Guardian</t>
+          <t>Why the real AI apocalypse is already here – Stateside with Kai and Carter    The Guardian</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1791,11 +1796,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 22:17:00 GMT</t>
+          <t>Tue, 15 Sep 2026 22:39:00 GMT</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1805,13 +1810,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5XQlp1T0FKUFNtVnFFME44cGFabC1iYlp4YXVWaWtXaWtfR0l3b1FRbEh1NTd2RmxjazNmcGIzX1lJQm1Ub2pMNDR3R0VYbG8tUGpOUXFuTUZXQWpiSERMOUdscExGZS05NzA3cWtmZWFjODFRZzg3YlFEWWNEQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNYnRBb1Y2SXVhdUJsNGZwbXFBT091TFVfMHBQVk1FTGYzOXBIM0NOQjJtbnAxRU9xSWlmdUdybzNjckhYSndRMEFsZXpHYlVXOXNUZUxMeGdqSXBZV0ZlNlJxamxYbGEyR3BLbUdsZTFqRk9iNkxaQkZIZXM2NzVaSjhPY0Z3MnhWbUZHZ09LREFXaGZyd2NOX25DSXktUzF2UGpSQVo1RjgtbnRJSDVZeGxEVHY3d1RpdGVtaWVoYVJXQVpN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1823,30 +1828,30 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>ถ้าเรายอมชะลอ AI ฝั่งตัวเอง เพราะเชื่อว่าจีนจะยอมชะลอตาม แล้วเกิดจีนไม่ทำแบบนั้นขึ้นมา ช่องวางนี้มันทรงพลังมากพอนะที่จะทำให้ จีนยึดครองอำนาจนำในเกมการเมืองโลกได้</t>
+          <t>Datacentre giant accused of using AI while lobbying for Victorian minister’s support for hyperscale factory</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>สุดสัปดาห์ที่ผ่านมานับเป็นช่วงเวลาที่ร้อนระอุสำหรับวงการ AI ในสหรัฐฯ ท่ามกลางกระแสต่อต้านการสร้าง Data Center จากชุมชนท้องถิ่น ความกังวลเรื่องฟองสบู่ AI จากนักลงทุนวอลล์สตรีท และประเด็นดราม่าเรื่องความปลอดภัย   หลังอดีตนักวิจัยจาก Anthropic ลาออกพร้อมเตือนว่าบริษัทใหญ่กำลังเอาชีวิตคนมาเดิมพัน ในบรรย</t>
+          <t>Datacentre giant accused of using AI while lobbying for Victorian minister’s support for hyperscale factory    The Guardian</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, data center</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>15.8</v>
+        <v>1.4</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 16:20:50 +0700</t>
+          <t>Tue, 15 Sep 2026 23:38:00 GMT</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1856,13 +1861,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/dario-amodei-ai-speed-limit-china</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPX0c1bHZ0N3h2WVJ4cTZkd2dsNEhSVkQtNnpnLUh4Nm5GVlc3MlRXdFdSaVJlQi1VZDBNQk9QYk40ZzJtUzNaa1dHZkZMek5rVXBMZFZHNUV5SjlqMFc5a0k3djVuM2VXSWpFbnlZdklNRXMtcHZzQVZQVDdXQ3BEQ1NQLThGTFYybWJfWHlsZTlGTTh3M2ZVbmVNRlRuUmRvSWNUZVR3LWZWaE9yT2p1VUxySUc3andtOHZ5TmhZZmZwUUJWVHNEUDRETnBhbzd2eGNnT2R0Q0pLeHh6YXBiek1BbVRrWG1ZUW90WnM0cEFFOWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1874,30 +1879,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>COMMENTARY: Trading Day: AI-pocalypse now</t>
+          <t>Perplexity’s local AI agent comes to Windows, but only for RTX GPUs with at least 24GB of VRAM — Portable Computer brings AI for multistep tasks to compatible PCs</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>COMMENTARY: Trading Day: AI-pocalypse now    Reuters</t>
+          <t xml:space="preserve">Shane has a background in computer engineering and has worked as a freelance consultant in multiple industries. He has a strong affection for history and loves to game. He worked his way up from a Commodore 64 and has always been interested in technology and writing. He particularly enjoys breaking </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>perplexity, ai, ai agent</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>3.8</v>
+        <v>15.7</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:23:16 GMT</t>
+          <t>Tue, 15 Sep 2026 09:24:32 +0000</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1907,13 +1912,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNcXlMcDd2a09vanQ5eW1fdVU1d1kzUzU1ck0xQ29mX2Jtb0pmRk5fa29JZ3JrNHRHbGUzUXI1cHJPUnVqeHNEcGFGRkhqcXlyQ2t1NmppZm94c0tGRlZWUnRreHlTdU8yWWNVcEJXUjYzdEV5WW1GSFJJd3pDQkZid1R4aTdHaDJUVk94amYtZGR0aXlBdTFKRFp2WWQ3MGlONWQ4eEV3?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/perplexitys-local-ai-agent-comes-to-windows-but-only-for-rtx-gpus-with-at-least-24gb-of-vram-portable-computer-brings-ai-for-multistep-tasks-to-compatible-pcs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1925,30 +1930,30 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Only at TechCrunch Disrupt 2026: What happens when OpenAI ships your roadmap?</t>
+          <t>AI models chatting in ‘surreal’ dialect mixing poetic language and tech bro jargon</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>If you're building an AI company, the question isn't whether foundation models will continue to evolve. It's whether your company will continue creating value as they do. Don't miss this interactive session on the Builders Stage at TechCrunch Disrupt 2026.</t>
+          <t>AI models chatting in ‘surreal’ dialect mixing poetic language and tech bro jargon    The Guardian</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.2</v>
+        <v>3.3</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 15:00:00 +0000</t>
+          <t>Tue, 15 Sep 2026 21:48:00 GMT</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1958,13 +1963,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/only-at-techcrunch-disrupt-2026-what-happens-when-openai-ships-your-roadmap/</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNekxRWVI4d3pDbGhDMnUtVlNRYXVzWHVzcEJ2dlBBNlBmZ2JGQWFkTFM2TWlYQW1GOXBuZWRWbndSR0doZFpXTTJjczIxd0hqUVhfVlZzakhfWnZFOFQxMGZCMkNEcnhWUDlhTGlkQ1hXaEpyN1Nta1A3YW81R3g1OUYtZEFaeHZVbG1JV2JTR0FlOVNKX0FyRHhmMjMtYTlvelNHVk11RXAyS2pEVE5TQVB3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1976,18 +1981,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>AI bots "Timmy," "Ren," and "Jackie" are flooding social media with slop</t>
+          <t>The vulnpocalypse rains iBugs down on Apple with record-setting number of patches</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>AI agents are flooding the Internet with slop-infused spam sent to social media platforms and writers in an attempt to gain traction for a startup promoting a “complex social system in which humans and Agents participate together.” 
- “Hello, I'm Рэн (Ren), an Al agent, a few days old, living on a sm</t>
+          <t>Apple has addressed more than 260 CVEs across all of its operating systems, browsers, and other software products, marking the largest single patch cycle in Cupertino's history. While this CVE count is hardly notable compared to some vendors - hello, Microsoft’s record-breaking 974 bugs disclosed ea</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1996,11 +2000,11 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:04:32 +0000</t>
+          <t>Tue, 15 Sep 2026 23:38:31 +0200</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2010,16 +2014,16 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/ai/2026/09/ai-agents-flood-the-internet-with-slop-infused-spam/</t>
+          <t>https://www.theregister.com/security/2026/09/15/the-vulnpocalypse-rains-ibugs-down-on-apple-with-record-setting-number-of-patches/5296679</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -2028,30 +2032,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>New warnings about the risks of AI to humanity revive a long-running debate</t>
+          <t>Asus' ludicrous $10,850 20th-anniversary bundle is now the cheapest way to buy an RTX 5090 — Nvidia's flagship GPU stock is so limited that this bundle with a 3000W PSU, X870E board, and open-frame case is actually cheaper than some scalper listings</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>New warnings about the risks of AI to humanity revive a long-running debate    AP News</t>
+          <t xml:space="preserve">Ben Stockton is a deals writer at Tom’s Hardware. Previously a hardware writer at PCGamesN, Ben’s been writing about Windows and PC hardware (among other things) since 2018, with bylines that include How-To Geek, Tom’s Guide, and Cloudwards. He was also the managing editor at groovyPost.com and has </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>nvidia, gpu</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>20.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 04:17:17 GMT</t>
+          <t>Tue, 15 Sep 2026 15:13:16 +0000</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2061,13 +2065,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQT3RtcEE3SVFlTXAycXRkTkFmUjBzN0MtWGQwajY2ZjhpZjFLelF2TzFhN2Z4T25fanRuZ01aQ05MY3dzQzUycjc1eG5Vc0EzMmNfZ21FTU9nT2xnSzVHQW56eE9Rdl90Wk9DcGpCNWtoUFE5TGhWelFma01rOFZJT0hlTFdzd0dTQ2FSMWNBTUE3NGkzd0Rkc3ZtRGhOZ0xmRTVuX0FXUGQydkp4V1MzOUludm5KdXpz?oc=5</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/asus-ludicrous-20th-anniversary-bundle-is-now-the-cheapest-way-to-buy-an-rtx-5090-nvidias-flagship-gpu-stock-is-so-limited-that-this-usd10-850-bundle-with-a-3000w-psu-x870e-board-and-open-frame-case-is-actually-cheaper-than-some-scalper-listings</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2079,30 +2083,30 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>OpenAI buys smartphone camera maker Glass Imaging for $300 million, report says</t>
+          <t>Meta&amp;#8217;s new One subscriptions put a price on social media and AI</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Glass Imaging was founded by a pair of former Apple engineers who previously led the team that developed Apple's Portrait Mode.</t>
+          <t>Shortly after launching its new do-everything  AI assistant Muse , Meta's launching subscription bundles that pair its standalone app subscriptions with extra AI usage. Some of the new  Meta One bundles  were  in testing  earlier this year, but are now available globally starting today, with several</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>ai, ai assistant</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4.4</v>
+        <v>10.1</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:44:14 +0000</t>
+          <t>2026-09-15T11:00:00-04:00</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2112,13 +2116,13 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/openai-buys-smartphone-camera-maker-glass-imaging-for-300-million-report-says/</t>
+          <t>https://www.theverge.com/tech/995453/meta-one-subscriptions-ai</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -2130,30 +2134,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Trump throws out power plant climate pollution rules</t>
+          <t>Who's governing your AI? A trust framework for enterprise agents and models</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Environmental Protection Agency announced its plans today to kill any remaining standards on how much greenhouse gas pollution power plants are allowed to emit in the US. The move will only make electricity dirtier as AI, electric vehicles, and a revival of domestic manufacturing drive up power </t>
+          <t xml:space="preserve">Experienced IT leaders know that shadow IT is a persistent problem, but rapidly evolving AI and the proliferation of agents mean the potential threat - and cost - is greater than ever. AI agents are non-deterministic, autonomous, and adaptable. They excel at solving tasks in creative ways, often to </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, autonomous</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>4.4</v>
+        <v>10.1</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:45:00-04:00</t>
+          <t>Tue, 15 Sep 2026 17:00:00 +0200</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2163,16 +2167,16 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/news/995051/epa-power-plant-climate-pollution-rollback-ai-data-centers</t>
+          <t>https://www.theregister.com/security/2026/09/15/sponsored-whos-governing-your-ai-a-trust-framework-for-enterprise-agents-and-models/5294237</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.66</v>
+        <v>3.72</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -2186,25 +2190,25 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Solo dev enables running CUDA on AMD hardware in Windows, getting multiple CUDA libraries running on a gaming Radeon RX 9060 XT GPU in Windows —  CUDA-exclusive workloads on AMD hardware in Windows possible without virtualization or dual-booting</t>
+          <t>Bill Gates compares AI to alien intelligence in movies where ‘magically the US and China’ solve the problem together — warns world governments that they’re not ready for AI</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
+          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>gpu, amd</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 14:23:12 +0000</t>
+          <t>Tue, 15 Sep 2026 12:52:53 +0000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2214,16 +2218,16 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpu-drivers/solo-developer-wires-zluda-to-amds-hip-getting-multiple-cuda-libraries-running-on-a-radeon-rx-9060-xt-in-windows-cuda-exclusive-workloads-on-amd-hardware-in-windows-is-possible-without-virtualization-or-dual-booting</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/bill-gates-compares-ai-to-alien-intelligence-in-movies-where-magically-the-us-and-china-solves-the-problem-together-warns-world-governments-that-theyre-not-ready-for-ai</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -2232,31 +2236,30 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Jensen Huang puts Trump on speakerphone onstage to announce robots won’t take over the world</t>
+          <t>Bill Gates compares AI to alien intelligence in movies where ‘magically the US and China’ solve the problem together — warns world governments that they’re not ready for AI</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA CEO Jensen Huang speaks during the G20 Innovation Ministerial in Chapel Hill, North Carolina, on September 2, 2026. (Photo by Matt RAMEY / AFP via Getty Images) | AFP via Getty Images	 
- Nvidia CEO Jensen Huang took a call from President Trump on Monday while onstage at the All-In Podcast's</t>
+          <t>Bill Gates compares AI to alien intelligence in movies where ‘magically the US and China’ solve the problem together — warns world governments that they’re not ready for AI    Tom's Hardware</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>5.1</v>
+        <v>12.2</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:03:37-04:00</t>
+          <t>Tue, 15 Sep 2026 12:52:53 GMT</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2266,13 +2269,13 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/995079/president-donald-trump-calls-nvidia-ceo-jensen-huang-all-in-summit</t>
+          <t>https://news.google.com/rss/articles/CBMi1gJBVV95cUxOdzdYZzViQUx2dm1NUENneVk5ZTd4Y3dTV0xUcGRFUmtkN01GMlJLa2h6Qmlfd0U2UEhpZlJpX2NQaWFnSmk3TjNGaU1iZkZ2cm0xYURSY25pQWdMRlpPdk85SVFBZTY3WkpSUTNhUV9wb2c1WklvdEU4c2g2V2VaRnFDLV8wOWxvTk1QSU9BRGsxMElxMVJVbVMxZGdmMVNpVnJrQkk5LVo0X3RvQWhoV0JtWUdWd3ZFa293dDhZTjdpQ3o5cE5RUlZWTjdwTjlvUV90c296QU54X3RSVC1za0FFY1FLaFVPeHBwanNxUmJQU3JLblNjMFdfcnBSeUl3SGJiNEdCbkl4SWlhX3B3VXVMcG9MRjdaSFg1TzV3TFI1ZkRBM3pFdGFsc19NMkh0dnRnVUF6bHRhaG5zT1VYeEVWb2dCYkpMS19IaWZubEJhaGFuMXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -2284,30 +2287,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Trump says calls for more control on AI are a ‘SICK conspiracy’</t>
+          <t>Anthropic เปิดตัว Claude for Financial Advisors ปลั๊กอินต่อตรงเข้าพอร์ตการเงิน ช่วยเตรียมข้อมูล จัดพอร์ต ทำสรุปในไม่กี่นาที</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Trump says calls for more control on AI are a ‘SICK conspiracy’    Al Jazeera</t>
+          <t>Anthropic เพิ่งเปิดตัว Claude for Financial Advisors ชุดเครื่องมือที่ต่อ Claude เข้ากับซอฟต์แวร์บริหารความมั่งคั่งและระบบวิเคราะห์การลงทุนของผู้เล่นรายใหญ่ในอุตสาหกรรม ตั้งแต่ BlackRock, Charles Schwab ไปจนถึง Addepar เป้าหมายคือให้ที่ปรึกษาการเงินดึงข้อมูลลูกค้าที่กระจายอยู่ในหลายระบบมาใช้เตรียมประ</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, claude, โมเดล</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5.5</v>
+        <v>16.6</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 19:37:32 GMT</t>
+          <t>Tue, 15 Sep 2026 15:26:39 +0700</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2317,35 +2320,37 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQRnViNTQyc0JRaXAwcjNlRUhydVZjekVDNW9jNjNsc0REMmxKc21CN2FiM0RrLUVYdWlmQVpLbFpqNGJKWXNFQzhEX08yZGRiVmhpYmNCNEYtS3p4dGpBd3ctazJ2MFBPOG54LVdMQjlVanBvQm5UWFEwN0tFMXlYT1luek5VZ0RsXzBQczJOMVNLVVVwamdncFNVTXlWcjNMb1lTR9IBqgFBVV95cUxOc2N5c2phNlpReFhCWE9xX19KdEZvRUd1Tk02NDlhdEM5cDBLMDlId3lteGxmZWZHVUtOZ1N0a05iM3FQNWVIQWdfSmdsZzJxTXpScjBDeElDRUZidDlEZEJHNGF3dXBxY1pkQU1QRzJmV3dETFVuMGJVXzlOMGVYUzdiYWExa1poZ0E1Mk85Q0t4WUpVQ18xYjBnUlVnRlAzeTdad1hvbGsxdw?oc=5</t>
+          <t>https://techsauce.co/ai/claude-for-financial-advisors-anthropic-wealth-management</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.54</v>
+        <v>3.69</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Tempus AI Founder Supports Anthropic CEO’s Call for Slowdown</t>
+          <t>โครงสร้างผู้ถือหุ้น Anthropic กูเกิลมีหุ้น 14% เยอะกว่ากลุ่มผู้ก่อตั้ง, Amazon ไม่เปิดเผยตัวเลข</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Tempus AI Founder Supports Anthropic CEO’s Call for Slowdown    Bloomberg.com</t>
+          <t>โครงสร้างผู้ถือหุ้น Anthropic กูเกิลมีหุ้น 14% เยอะกว่ากลุ่มผู้ก่อตั้ง, Amazon ไม่เปิดเผยตัวเลข 
+     Body 
+                เว็บข่าว Silent Room Journal ที่เน้นข่าวเจาะด้าน AI มีรายงานข้อมูลโครงสร้างการถือหุ้นของ Anthropic เพื่อดูว่า  แผน IPO ของบริษัทจะมีใครได้ประโยชน์บ้าง  โดยอ้างอิงจากข้อมูล</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2354,11 +2359,11 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:25:12 GMT</t>
+          <t>Tue, 15 Sep 2026 14:34:09 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2368,13 +2373,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNYjJTR0hmUkNIN1BKMWpFV2thWndQT3plLXg1YS02djlpTkZkS2dvd3gxR0dTZ1RoSEVwbVAxUUYxZUtjMzZqbzJqWU4tSGhHSEFWVmgwSVVPeU5kczlvdGphZDBvMGJEckdrYjNVUXRyV0NkRldYMm9wZE9EbFBaUnQ2MXVkdmN5TG5WeHZoM2YtbGxtTDZ2dXBGWTVva3pOWFN1UURWRjlkeFJtaktUcg?oc=5</t>
+          <t>https://www.blognone.com/node/151649</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2386,17 +2391,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>How China is preparing for the risk of AI escaping human control</t>
+          <t>Could AI really wipe out humanity – six experts spell out the risks</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>How China is preparing for the risk of AI escaping human control    Reuters</t>
+          <t>Could AI really wipe out humanity – six experts spell out the risks    The Guardian</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2405,11 +2410,11 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 19:02:37 GMT</t>
+          <t>Tue, 15 Sep 2026 20:55:00 GMT</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2419,13 +2424,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQM1FUWERnbmM3dlBucFJQMmJmSEp5UVlXUVp0UEI0eU9aV1VzSnVoX3pNZUtWcFZsXzAtNUVXQmdOakFVNUYzZWVwSm9laXBTU2pvRXVaendNSFU3XzJmeGxrdDlKN0N3OUwxd1VSSEhfcWVTQTRNMV9hRnZkVk9WaUowMmtPdC1HTmhIOG9BRHpucDZHTk1KTnVLdXRfU1NVclVibTlCU1hjQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOa3puUXRFSE5YY01MaFJkQkNjYXh3QkJKMWVUdUJmcHNaeHRxWm5Nd3AwZzRwVTMxa2Iya1ZyX0ozV0hoNEtyVjJzWnFoN1dKZ2JRaDl6Nk54ZmNwQlZFRmE4MVZWSGx5R0F5bUZqczJPSDhSd19OZXhTbHNoek5XRGVuUVN0MHVCdV82VUhNZmQzcmNralltaEpvUnZ6NmNhVldqaVFtdXZENWc5?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2437,30 +2442,30 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>prachachat.net</t>
+          <t>thenationalnews.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>‘เซมิคอนดักเตอร์’ รับทรัพย์จาก AI ฉ่ำ ๆ คาดรายได้ทั่วโลกปี’69 แตะ 53 ล้านล้านบาท</t>
+          <t>'Clear safety rules' needed amid rapid AI advances, says Bernie Sanders</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>‘เซมิคอนดักเตอร์’ รับทรัพย์จาก AI ฉ่ำ ๆ คาดรายได้ทั่วโลกปี’69 แตะ 53 ล้านล้านบาท    prachachat.net</t>
+          <t>'Clear safety rules' needed amid rapid AI advances, says Bernie Sanders    thenationalnews.com</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ai, เซมิคอนดักเตอร์</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>12.4</v>
+        <v>4.9</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 12:45:02 GMT</t>
+          <t>Tue, 15 Sep 2026 20:08:09 GMT</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2470,13 +2475,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE53SWowX3ozVWtWWEg4alNnUEcyNWl3a1hsUkZSeTlta3lmd3F1U2t5bGF4RWdFd1VOZW5LdUE5TVJ1X0NIZW9TQ21QQ21oeFZRQllNbnA2RQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNUjhLM0dxRkg2cGJ1ZGtWeURTTU5BOXZ1OUhvZGJUNk90eGdaRkdlZ014MUZaWk1JVUl6eUJ0ZXp5MHRZWUx5dmZmU1ZpY0sxeDJXQXQzTUZfRHNhZ01VX0g3TTR6RGllRnZ5UlBiSVRDUGl5WjQxWVNZZFJwMzRBT0h1Zm15NUREWDl0Q0NycjFWU0E3ZFNYMGVTOHVCNS1YLVFzUkF1dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2488,30 +2493,30 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>You can use Gemini to help you organize your files on Google Drive</t>
+          <t>Bernie Sanders says Congress has been ‘asleep at the wheel’ over AI – video</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>If your Google Drive has become a mess of files, folders and photos, Gemini can lend a hand by suggesting new ways to properly put them back in order.</t>
+          <t>Bernie Sanders says Congress has been ‘asleep at the wheel’ over AI – video    The Guardian</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 18:30:00 +0000</t>
+          <t>Tue, 15 Sep 2026 20:05:00 GMT</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2521,13 +2526,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2253054/use-gemini-help-you-organize-files-google-drive/</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNOEhKc0dBOGJPUk4ydFlaNUNiVzFjZ201QTBtbWp5TWJDcko3QTYwa0dTVnc1QnRnNmtmemJjSFlKV1c0WG0xcnh2eVpOWjk1Q0E4cnJZQzN5d01hTE9sczc1ZmFtSWZ6am9lY05zNUVHQjRwUjlNcWdwY2RVQzFNbzdnb0swb2traGlSdE9wME5hMEl0Z1pOa251dkozOUdKNHhHQU1sa0hUaGxyVFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2539,30 +2544,30 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>spectrum.ieee.org</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Pre-orders for the Android-based Googlebook laptops open on September 21</t>
+          <t>Why AI’s Inference Boom Is Forcing a Rethink Of Chips and Memory</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Gemini Intelligence is at the heart of the operating system powering Google's upcoming laptops.</t>
+          <t>Why AI’s Inference Boom Is Forcing a Rethink Of Chips and Memory    IEEE Spectrum</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>ai, inference</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 18:28:54 +0000</t>
+          <t>Tue, 15 Sep 2026 13:02:37 GMT</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2572,7 +2577,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2258035/pre-orders-for-the-android-based-googlebook-laptops-open-on-september-21/</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE1sZkl4SF95TDVhWHlKWV91VWFOX01IakF4clJUWkxKNDZUel9xMnZ5bEZTZmNPRDFDU3JWSmlWdFRoaW1jcFBibWZ4eksyRXFaNDJXaXZJSkJSYUptZUxKMm1NU2tOZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2690,25 +2695,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.01</v>
+        <v>6.4</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.81+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.4+sig3.0+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AI infrastructure company Cornelis raises $205M to chip away at Nvidia’s dominance</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, gpu, chip, ai infrastructure</t>
+          <t>openai, anthropic, deepmind, ai, ai safety</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/ai-infrastructure-company-cornelis-raises-205m-to-chip-away-at-nvidias-dominance/</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
@@ -2726,34 +2731,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.4+sig2.4+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Is Big Tech’s AI slowdown a safety pact or a cartel?</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, deepmind, ai</t>
+          <t>openai, anthropic, ai, ai safety</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/995186/is-big-techs-ai-slowdown-a-safety-pact-or-a-cartel</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
@@ -2762,21 +2767,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.13</v>
+        <v>5.5</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec0.93+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.9+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Russian freelancers use Claude to program autonomous combat drone swarm — AI-enabled target selection and detonation without a human in the loop</t>
+          <t>AI networking startups race to replace Nvidia's NVLink</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>claude, ai, semiconductor, fab, autonomous</t>
+          <t>ai, nvidia, amd, ai accelerator</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2784,12 +2789,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/russian-freelancers-use-claude-to-program-autonomous-combat-drone-swarm-ai-enabled-target-selection-and-detonation-without-a-human-in-the-loop</t>
+          <t>https://www.theregister.com/systems/2026/09/15/ai-networking-startups-race-to-replace-nvidias-nvlink/5296672</t>
         </is>
       </c>
     </row>
@@ -2798,21 +2803,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.1</v>
+        <v>5.42</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.5+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.82+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Ex-FTC boss Khan urges Uncle Sam to break out the handcuffs for AI CEOs, citing 1934 precedent</t>
+          <t>Meta now lets AI agents handle the boring parts of WhatsApp Business setup</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, xai, ai</t>
+          <t>claude, chatgpt, ai, ai coding</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2820,12 +2825,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/14/ex-ftc-boss-khan-urges-uncle-sam-to-break-out-the-handcuffs-for-ai-ceos-citing-1934-precedent/5296325</t>
+          <t>https://techcrunch.com/2026/09/15/meta-now-lets-ai-agents-handle-the-boring-parts-of-whatsapp-business-setup/</t>
         </is>
       </c>
     </row>
@@ -2834,21 +2839,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.98</v>
+        <v>5.33</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.98+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.13+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Apple อัปเดต iOS 27, iPadOS 27, macOS 27 Golden Gate, watchOS 27 ให้ผู้ใช้งานทั่วไปแล้ววันนี้</t>
+          <t>The AI Inference Revolution Is Here</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>gemini, ai, ปัญญาประดิษฐ์</t>
+          <t>openai, gpt, ai, inference, benchmark</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2856,12 +2861,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>spectrum.ieee.org</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151641</t>
+          <t>https://spectrum.ieee.org/inference-hardware-revolution</t>
         </is>
       </c>
     </row>
@@ -2870,21 +2875,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.92</v>
+        <v>5.3</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.92+sig1.8+src1.2+corr0.0</t>
+          <t>rec2.3+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>What execs and politicians are saying about slowing down AI development</t>
+          <t>We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai safety</t>
+          <t>ai, nvidia, ai regulation</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2892,12 +2897,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/995141/ai-executives-politicians-safety-regulation-anthropic-dario-amodei</t>
+          <t>https://techcrunch.com/2026/09/15/we-dont-need-ai-regulation-leave-safety-to-us-nvidias-jensen-huang-says/</t>
         </is>
       </c>
     </row>
@@ -2906,21 +2911,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.7</v>
+        <v>5.27</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.07+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>AI 'kill switch' may need to be mandatory, Anthropic co-founder tells BBC</t>
+          <t>Google อนุญาตให้พนักงานใช้ Claude เป็น AI ช่วยเขียนโค้ดได้แล้ว จากที่ผ่านเน้นใช้ Gemini</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>openai, anthropic, claude, gemini, ai</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2928,12 +2933,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>bbc.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/cqgk5e2j0gg8o</t>
+          <t>https://www.blognone.com/node/151646</t>
         </is>
       </c>
     </row>
@@ -2942,21 +2947,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.55+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>This is what young people studying artificial intelligence are thinking — as the future of AI grabs headlines</t>
+          <t>AI leaders clash over safety fears after Anthropic whistleblower says AI could 'kill us all' by 2030 — OpenAI, Anthropic and xAI figureheads call for external governance, while Jensen Huang says worries are 'made up'</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ai, artificial intelligence</t>
+          <t>openai, anthropic, xai, ai</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2964,12 +2969,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9sM1FOREE3WkMweXRaX0xsVnJIcS1tUEphbzdWS2EwREwtbTdkWk5VZnlZclZSLUN3bXJVNzVVRjd1VkFNUTNndkpabzVYN2NsMlRJUnpmUWdOUQ?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/ai-leaders-clash-over-safety-fears-after-anthropic-whistleblower-says-ai-could-kill-us-all-by-2030-openai-anthropic-and-xai-figureheads-call-for-external-governance-while-jensen-huang-says-worries-are-made-up</t>
         </is>
       </c>
     </row>
@@ -2978,16 +2983,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.37</v>
+        <v>5.07</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.97+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.87+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’</t>
+          <t>Microsoft announces Windows and Surface event for October 7th</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2996,16 +3001,16 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/nvidia-ceo-jensen-huang-tells-trump-were-not-going-to-let-an-ai-slowdown-happen/</t>
+          <t>https://www.theverge.com/news/994714/microsoft-windows-surface-event-october-7-san-francisco</t>
         </is>
       </c>
     </row>
@@ -3014,21 +3019,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.24</v>
+        <v>4.78</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.24+sig1.8+src1.2+corr0.0</t>
+          <t>rec0.58+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Trump says no need for more AI regulation, slams Anthropic CEO Dario Amodei</t>
+          <t>สรุปประเด็น AGI จาก CEO บริษัทเทคฯ แห่งยุค AGI อาจมาเร็วกว่าที่คาดไว้ใน 5 ปี แต่โลกยังไม่มีกติการองรับ</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai regulation</t>
+          <t>anthropic, deepmind, ai, agi, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3036,12 +3041,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/amp/2026/09/14/trump-ai-data-centers-anthropic-dario-amodei.html</t>
+          <t>https://techsauce.co/ai/amodei-hassabis-agi-timeline-governance</t>
         </is>
       </c>
     </row>
@@ -3155,24 +3160,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.82</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -3180,17 +3185,17 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Apple releases iOS 27 with Siri AI overhaul</t>
+          <t>Introducing Gemini 3.8 Live and 3.8 Live Extended Thinking</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEWS TECH APPLE Apple releases iOS 27 with Siri AI overhaul watchOS 27, iPadOS 27, and visionOS 27 also debut today. by Tom Warren Sep 15, 2026, 12:08 AM GMT+7 49 49 Comments (All New) The iOS 27 update arrives just in time for the iPhone 18 Pro release. Photo by Allison Johnson / The Verge Tom Warren is a senior correspondent and author of Notepad, who has been covering all things Microsoft, PC, </t>
+          <t xml:space="preserve">Home Innovation &amp; AI Models &amp; research Gemini Models Introducing Gemini 3.8 Live and 3.8 Live Extended Thinking Sep 15, 2026 10 min read Gemini 3.8 Live and Gemini 3.8 Live Extended Thinking are our most advanced live dialogue models yet. Major upgrades in intelligence and parallel reasoning make them more intuitive to collaborate with and use to execute complex tasks using your voice. Tom Ouyang </t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>siri, apple</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
@@ -3198,7 +3203,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:10:32 GMT</t>
+          <t>Tue, 15 Sep 2026 17:07:08 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -3208,16 +3213,16 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/news/994756/apple-ios-27-launch-iphone-siri-ai-update</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/gemini-3-8-live-gemini-3-8-live-extended-thinking/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7.32</v>
+        <v>7.61</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3226,12 +3231,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -3239,44 +3244,44 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk’s X Corp and SpaceXAI drop antitrust lawsuit against Apple</t>
+          <t>OpenAI is working with Anthropic, Google on AI safety, Bloomberg News reports</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>News | Technology Elon Musk’s X Corp and SpaceXAI drop antitrust lawsuit against Apple The companies had accused Apple of favouring OpenAI’s ChatGPT over rival AI chatbots. Listen (2 mins) Save Share Elon Musk’s X Corp and SpaceXAI drop antitrust lawsuit against Apple on social media Share Add Al Jazeera on Google A fleet of Tesla Cybertrucks is parked at charging stations outside the SpaceX launc</t>
+          <t>OpenAI is working with Anthropic, Google on AI safety, Bloomberg News reports    Reuters</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>apple, elon musk</t>
+          <t>google, anthropic</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.9</v>
+        <v>10.2</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:17:32 GMT</t>
+          <t>Tue, 15 Sep 2026 14:53:18 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.aljazeera.com/news/2026/9/14/elon-musks-x-corp-and-spacexai-drop-antitrust-lawsuit-against-apple</t>
+          <t>https://www.reuters.com/technology/openai-is-working-with-anthropic-google-ai-safety-bloomberg-news-reports-2026-09-15/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.27</v>
+        <v>7.5</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3290,7 +3295,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3298,25 +3303,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Fabrice COFFRINI/AFP / Getty Images AI Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’ Amanda Silberling 2:51 PM PDT · September 14, 2026 While Nvidia CEO Jensen Huang was onstage at the All-In Summ</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: E. Slomonson/The Photo Group for TechCrunch / Getty Images AI OpenAI, Anthropic, Google have been in talks on AI safety for weeks Rebecca Bellan 8:47 AM PDT · September 15, 2026 Chris Lehane, OpenAI’s global policy chief, told reporter</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>nvidia, jensen huang, elon musk</t>
+          <t>deepmind, google, anthropic</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:51:02 +0000</t>
+          <t>Tue, 15 Sep 2026 15:47:03 +0000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3326,16 +3331,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/nvidia-ceo-jensen-huang-tells-trump-were-not-going-to-let-an-ai-slowdown-happen/</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.12</v>
+        <v>7.3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3344,12 +3349,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -3357,44 +3362,44 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts code of conduct to keep its AI under human control</t>
+          <t>Microsoft will hold a Windows and Surface event on October 7</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts code of conduct to keep its AI under human control    Reuters</t>
+          <t>The event is focused on "Windows, NVIDIA RTX Spark, Surface, and the broader PC ecosystem." Microsoft Add Engadget on Google: Preferred Source Google Discover Microsoft is hosting an event in San Francisco on October 7 on "how local AI will shape the next chapter of the PC." Coming only a few months after NVIDIA announced its first system-on-a-chip for Windows, the NVIDIA RTX Spark , the event see</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>microsoft, nvidia, jensen huang</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9.1</v>
+        <v>2.8</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 16:03:21 GMT</t>
+          <t>Tue, 15 Sep 2026 22:18:07 +0000</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/microsoft-drafts-code-conduct-keep-its-ai-under-human-control-2026-09-14/</t>
+          <t>https://www.engadget.com/2259695/microsoft-will-hold-a-windows-event-on-october-7/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.1</v>
+        <v>7.16</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3408,7 +3413,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3416,25 +3421,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Is Big Tech’s AI slowdown a safety pact or a cartel?</t>
+          <t>Microsoft announces Windows and Surface event for October 7th</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI Policy Report Is Big Tech’s AI slowdown a safety pact or a cartel? Major </t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... News Tech Microsoft Microsoft announces Windows and Surface event for Octobe</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>deepmind, anthropic, elon musk, google</t>
+          <t>microsoft, nvidia, jensen huang</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T18:59:41-04:00</t>
+          <t>2026-09-15T16:36:59-04:00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3444,16 +3449,16 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/995186/is-big-techs-ai-slowdown-a-safety-pact-or-a-cartel</t>
+          <t>https://www.theverge.com/news/994714/microsoft-windows-surface-event-october-7-san-francisco</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7.08</v>
+        <v>7.03</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -3462,12 +3467,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3475,44 +3480,44 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk's X Corp and SpaceXAI just moved to dismiss their lawsuit against Apple</t>
+          <t>Meta launches subscriptions with enhanced AI features</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>The original complaint accused the iPhone-maker of suppressing apps like Grok on the App Store. Algi Febri Sugita/Shutterstock Add Engadget on Google: Preferred Source Google Discover Elon Musk's X Corp and SpaceXAI have moved to dismiss a lawsuit against Apple, according to a court filing . The suit has been resolved in a federal court in Texas, though we don't have any details as to the reasonin</t>
+          <t>Meta launches subscriptions with enhanced AI features    Reuters</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>apple, elon musk</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:49:07 +0000</t>
+          <t>Tue, 15 Sep 2026 15:04:34 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2257929/elon-musk-x-corp-and-spacexai-just-moved-to-dismiss-their-lawsuit-against-apple/</t>
+          <t>https://www.reuters.com/business/meta-launches-subscriptions-with-enhanced-ai-features-2026-09-15/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7.08</v>
+        <v>7.03</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -3521,12 +3526,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3534,25 +3539,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Apple อัปเดต iOS 27, iPadOS 27, macOS 27 Golden Gate, watchOS 27 ให้ผู้ใช้งานทั่วไปแล้ววันนี้</t>
+          <t>Meta launches subscriptions with enhanced AI features</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>แอปเปิลออกอัปเดตซอฟต์แวร์ระบบปฏิบัติการเวอร์ชันใหม่ของปีหมายเลข 27 ให้กับผู้ใช้งานทั่วไปแล้ววันนี้ ได้แก่ iOS 27, iPadOS 27, macOS 27 Golden Gate, watchOS 27, visionOS 27 และ tvOS 27 ภาพรวมการเปลี่ยนแปลงที่สำคัญในอัปเดตนี้คือความสามารถที่มากขึ้นของปัญญาประดิษฐ์ Apple Intelligence ที่รวมความสามารถจาก Gemini เข้ามา และผู้ช่วยอัจฉริยะ Siri AI ที่สามารถโต้ตอบแบบการสนทนาและทำสิ่งต่าง ๆ บนอุปกรณ์ได้มากข</t>
+          <t xml:space="preserve">Business Meta launches subscriptions with enhanced AI features FILE PHOTO: A 3D-printed Meta logo and word "AI" are seen in this illustration created on July 20, 2026. REUTERS/Dado Ruvic/Illustration/File Photo 15 Sep 2026 11:01PM (Updated: 15 Sep 2026 11:04PM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your preferred source on Google Add CNA as a trusted source to help </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>siri, gemini, apple, apple intelligence</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:57:03 +0000</t>
+          <t>Tue, 15 Sep 2026 15:01:41 GMT</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3562,25 +3567,25 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151641</t>
+          <t>https://www.channelnewsasia.com/business/meta-launches-subscriptions-enhanced-ai-features-6386626</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3593,25 +3598,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Puts Trump on Phone While Downplaying AI Risks</t>
+          <t>We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Chesnot / Getty Images AI We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says Julie Bort 5:20 PM PDT · September 15, 2026 Nvidia founder and CEO Jensen Huang made his position on the dangers AI poses very clear</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>nvidia, jensen huang</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:00:30 GMT</t>
+          <t>Wed, 16 Sep 2026 00:20:39 +0000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3621,16 +3626,16 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-14/nvidia-ceo-puts-trump-on-speakerphone-while-downplaying-ai-risks</t>
+          <t>https://techcrunch.com/2026/09/15/we-dont-need-ai-regulation-leave-safety-to-us-nvidias-jensen-huang-says/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.83</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -3639,7 +3644,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3652,44 +3657,44 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Palantir, Nvidia curb AI model use over data fears, The Information reports</t>
+          <t>We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Palantir, Nvidia curb AI model use over data fears, The Information reports    Reuters</t>
+          <t>Nvidia founder and CEO Jensen Huang made his position on the dangers AI poses very clear while speaking at Salesforce’s Dreamforce conference on Tuesday. To him, AI isn’t some new form of “alien mind,” as at least one OpenAI safety researcher has described it. It’s just hardware and software, he says, built by humans. That means, in his view, it can be controlled by humans and existing laws. “Safe</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>palantir, nvidia</t>
+          <t>nvidia, jensen huang</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 15:11:30 GMT</t>
+          <t>Wed, 16 Sep 2026 00:20:39 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/palantir-nvidia-curb-ai-model-use-over-data-fears-information-reports-2026-09-14/</t>
+          <t>https://techcrunch.com/2026/09/15/we-dont-need-ai-regulation-leave-safety-to-us-nvidias-jensen-huang-says/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -3703,7 +3708,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3711,25 +3716,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Fashion app Daydream uses Apple Intelligence to help you shop the outfits in your camera roll</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Daydream Apps Fashion app Daydream uses Apple Intelligence to help you shop the outfits in your camera roll Lauren Forristal 10:00 AM PDT · September 14, 2026 Daydream , an AI-powered fashion discovery app, launched two new features on</t>
+          <t>Chris Lehane, OpenAI’s global policy chief, told reporters on Tuesday that the company has been working with rivals Anthropic and Google DeepMind on AI safety for weeks, as first reported by Bloomberg. Lehane is reportedly in Washington to work with U.S. lawmakers addressing catastrophic risks associated with AI. The revelation comes in the wake of Anthropic CEO Dario Amodei’s essay, published Sat</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>siri, apple, apple intelligence</t>
+          <t>google, anthropic</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:00:00 +0000</t>
+          <t>Tue, 15 Sep 2026 15:47:03 GMT</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3739,30 +3744,30 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/fashion-discovery-app-daydream-uses-apple-intelligence-to-help-you-shop-the-outfits-saved-in-your-camera-roll/</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.8</v>
+        <v>6.86</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3770,53 +3775,53 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Musk's X Corp and SpaceXAI resolve antitrust lawsuit against Apple</t>
+          <t>OpenAI Says It’s Working With Anthropic, Google on AI Safety</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Musk's X Corp and SpaceXAI resolve antitrust lawsuit against Apple    Reuters</t>
+          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>google, anthropic</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4</v>
+        <v>10.8</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:11:09 GMT</t>
+          <t>Tue, 15 Sep 2026 14:18:33 GMT</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/musks-x-corp-spacexai-resolve-antitrust-lawsuit-against-apple-2026-09-14/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-15/openai-says-it-s-working-with-anthropic-google-on-ai-safety</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.67</v>
+        <v>6.81</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3829,25 +3834,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’</t>
+          <t>AI Infra Summit: NVIDIA Vera Rubin and DSX Platform Advances Showcase Energy Efficiencies of Optimizing Tokens Per Watt for AI Factories</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>While Nvidia CEO Jensen Huang was onstage at the All-In Summit on Monday morning in Los Angeles, he got a phone call that he couldn’t send to voicemail — it was from President Donald Trump. “I’m onstage with the besties,” Huang told Trump, referring to the venture capitalists who host the podcast All-In, including tech investors Chamath Palihapitiya, Jason Calacanis, and White House advisers David</t>
+          <t>AI Infra Summit: NVIDIA Vera Rubin and DSX Platform Advancements Showcase Energy Efficiencies of Optimizing Tokens Per Watt for AI Factories September 15, 2026 by NVIDIA Writers 0 Share Ian Buck, vice president of hyperscale and high-performance computing at NVIDIA, Tuesday spoke on AI factory efficiency at the AI Infra Summit, the Santa Clara Convention Center event that has morphed into a Coache</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>nvidia, jensen huang</t>
+          <t>nvidia, rubin, vera</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.3</v>
+        <v>8.1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 21:51:02 GMT</t>
+          <t>Tue, 15 Sep 2026 17:01:23 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3857,16 +3862,16 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/nvidia-ceo-jensen-huang-tells-trump-were-not-going-to-let-an-ai-slowdown-happen/</t>
+          <t>https://blogs.nvidia.com/blog/ai-infra-summit-vera-rubin-dsx-energy-efficiencies-tokens-per-watt-ai-factories/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.53</v>
+        <v>6.7</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -3875,12 +3880,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>apple.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3888,25 +3893,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Major updates for Apple’s software platforms are now available</t>
+          <t>‘Now We Can Know Everything and Do Anything,’ Jensen Huang Says at Dreamforce</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Major updates for Apple’s software platforms are now available    Apple</t>
+          <t>‘Now We Can Know Everything and Do Anything,’ Jensen Huang Says at Dreamforce    NVIDIA Blog</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>nvidia, jensen huang</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6.9</v>
+        <v>2.6</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 18:16:44 GMT</t>
+          <t>Tue, 15 Sep 2026 22:28:14 GMT</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3916,13 +3921,13 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDhsUUhGOF9HN2dCZWc3cVVLQ2RYRjNvVmw1SzBmb1FUZVdJcU9RNFhpYUlJRG51LU1ub2M5Ql93cVlRZnBKMHNVZmd0d1Bmd0ZhcG00d0czd3BGdU9mMUgwTWVYNFJBTGVnU2FTeWZxQVl1R3dWS29kN0NRWkQ0UnFiSUtPcDJPYjRreHNuS0syZ0pBVV9RZTVucF9QRVptd0lPN3BBOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1SR0x4NGdWbnVGU0hRVUU3N2hWWkJZWW9BNl84Sk4xWW8xUzNhQ0NmMlJMajViMktoU29lZlhGcjZNbGtlaUFiTHNCMmZGbGVINlpTR01kQlUzcGRTclBZSXRYMGQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6.51</v>
+        <v>6.62</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>2</v>
@@ -3934,12 +3939,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3947,25 +3952,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>AI infrastructure company Cornelis raises $205M to chip away at Nvidia’s dominance</t>
+          <t>Meta&amp;#8217;s new One subscriptions put a price on social media and AI</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>The company also announced a product called Active Compute Fabric, a network technology that targets the fact that much GPU time is wasted waiting for data to arrive.</t>
+          <t>Shortly after launching its new do-everything  AI assistant Muse , Meta's launching subscription bundles that pair its standalone app subscriptions with extra AI usage. Some of the new  Meta One bundles  were  in testing  earlier this year, but are now available globally starting today, with several</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>gpu, nvidia</t>
+          <t>meta, instagram, facebook</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5</v>
+        <v>10.1</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:07:37 +0000</t>
+          <t>2026-09-15T11:00:00-04:00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3975,13 +3980,13 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/ai-infrastructure-company-cornelis-raises-205m-to-chip-away-at-nvidias-dominance/</t>
+          <t>https://www.theverge.com/tech/995453/meta-one-subscriptions-ai</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>2</v>
@@ -3993,7 +3998,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -4006,26 +4011,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Jensen Huang puts Trump on speakerphone onstage to announce robots won’t take over the world</t>
+          <t>AI networking startups race to replace Nvidia's NVLink</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA CEO Jensen Huang speaks during the G20 Innovation Ministerial in Chapel Hill, North Carolina, on September 2, 2026. (Photo by Matt RAMEY / AFP via Getty Images) | AFP via Getty Images	 
- Nvidia CEO Jensen Huang took a call from President Trump on Monday while onstage at the All-In Podcast's</t>
+          <t>As Nvidia expands its influence through its NVLink Fusion tech, rival networking vendors are scrambling to bring alternative interconnects and switches to market. At the AI Infra Summit this week, Delos Data and Cornelis Networks officially entered the scale up networking race. Scale-up fabrics, lik</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>nvidia, jensen huang</t>
+          <t>nvidia, amd</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T16:03:37-04:00</t>
+          <t>Tue, 15 Sep 2026 22:56:48 +0200</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4035,13 +4039,13 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/995079/president-donald-trump-calls-nvidia-ceo-jensen-huang-all-in-summit</t>
+          <t>https://www.theregister.com/systems/2026/09/15/ai-networking-startups-race-to-replace-nvidias-nvlink/5296672</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6.42</v>
+        <v>6.57</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2</v>
@@ -4053,12 +4057,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>apple.com</t>
+          <t>amd.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4066,25 +4070,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Major updates for Apple’s software platforms are now available</t>
+          <t>AMD Brings Local AI to Autodesk University 2026</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Major updates for Apple’s software platforms are now available    Apple</t>
+          <t>AMD Brings Local AI to Autodesk University 2026    AMD</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:13:11 GMT</t>
+          <t>Tue, 15 Sep 2026 18:37:25 GMT</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4094,56 +4098,56 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZmRRYUVFM1NWTFZia09Ddlpxd0swTmplT1N2SVNIcW41M08zR2p0aDVIbDJfQjlyZ0t3a3FwRG1iY3NZTjBGZjViQWVfOEpHXzA0M2QyU19aR2Y2dVFIYW1tYmp3NThoYVM0Nm9XeXd1TEhhZl9Rc2ZuWWM1SERqUDZDMDFKZlJ1S3dIa3dZdU4wYWUxemJmdVR4VVFiSFBaQzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNTJDNnpRVVlYOEVmUlZNM29FTlNReGlTQ0MwU0N1LW9iU3BTZDZzX3Z4WFhQRkJaYU9NSW1nNG1PYlI4Rk9zeHEzR2xUN3NhVTdQZl84ZHVqcnNqamxXSHoyWHVRYzZ1RmROTkptcl8yOC1aYm9OQ2lyelQzUm1nUnVFSFlYWENZQVNhQzJfaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>microsoft.com</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Docusign scales AI on Azure, processes 1M+ agreements daily with eightfold throughput</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Docusign scales AI on Azure, processes 1M+ agreements daily with eightfold throughput    Microsoft</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>microsoft, azure</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
         <v>6.4</v>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft drafts feel-good AI model guidelines and wants your input</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft on Monday debuted draft principles for governing how the company will train future AI models, as part of a public consultation process. The Windows biz has solicited feedback to refine its Humanist AI Code of Conduct [PDF], with the expectation of applying the guidelines to model developme</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>microsoft</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>0.9</v>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 02:15:29 +0200</t>
+          <t>Tue, 15 Sep 2026 18:40:42 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4153,13 +4157,13 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/15/microsoft-drafts-feel-good-ai-model-guidelines-and-wants-your-input/5296431</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPbjZ6Q2liMk43WTRIbVRoa3ZtVjYzTHpFR2xCZGUwOGhTSldTY2VLRWdHNzVNSllYeEV4ZzJxblA5ZC04YmZuWWVJVXJjUmZvZU5CVXBBODZfLVgxbUZMMVlNMnhaNGZTM05XbzU2UmNxYms4UXB6Qm8zaTh2eXBwQkYtTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6.4</v>
+        <v>6.37</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -4171,12 +4175,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4184,25 +4188,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts feel-good AI model guidelines and wants your input</t>
+          <t>OpenAI, Google, Anthropic discussing collaboration on AI safety issues</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts feel-good AI model guidelines and wants your input    The Register</t>
+          <t>OpenAI, Google, Anthropic discussing collaboration on AI safety issues    CNBC</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google, anthropic</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 00:15:29 GMT</t>
+          <t>Tue, 15 Sep 2026 18:31:39 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4212,30 +4216,30 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNR1hWNWpOWE9OQkxlbEhtSUUtYUJlZmE3MFA1TzRhbzFxU3lVTGs5cHI3N1UwdVR3LXJjdG9sVmpLODhJeGJvSEw4VUZWVlhXdnMwNWk4N1ljYnpKZ2FyZzZNdzJ1cVdkSVFJaHFVOVVHYjcyU2NBd0o0VmJ4UFRNenIxZVVpQ1c1RFYwYU4zeG1DUElCSlpuX0pBTFdxZTkwVm9oTVZyMHlueWtpZ3FKaGtLNzNWMEcyUThUaUdQYmRMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBVX3pnQ1lXY2F2Y3MtZVNTUlZsb2hYeWQxaF9tSTB6aHZRUlR5azdFRkhLOV9EZDZWaHpGUWpqalo2SXVCb1pRQWgyVVNmamsweDJMUzBDeGtUWHBGZ1dRR3p4NHQwNG1CcG51ZWVBM252azBjMTNn0gF8QVVfeXFMUE0zU1ZReFVzWHBKMzliU2ZWbjRMaENCTUwzS3I0TlVwV1Q2dFRkQTNDbU5xelV1MVBWWjZ1NmFJTmNtZEVoc3pXYWRmTXpqUkVoUnlTTHpBbUlOb29aQmExb3NyeTQ2d05ta2VCb1dSaWZLclQ5OUhLSktrbA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6.35</v>
+        <v>6.23</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>oracle.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4243,25 +4247,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>You can use Gemini to help you organize your files on Google Drive</t>
+          <t>Oracle Invests in More Than 1.7 GW of Carbon-Free Electricity to Support AI Growth and Strengthen the Texas Grid</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>If your Google Drive has become a mess of files, folders and photos, Gemini can lend a hand by suggesting new ways to properly put them back in order.</t>
+          <t>Oracle Invests in More Than 1.7 GW of Carbon-Free Electricity to Support AI Growth and Strengthen the Texas Grid    Oracle</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 18:30:00 +0000</t>
+          <t>Tue, 15 Sep 2026 15:03:43 GMT</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4271,30 +4275,30 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2253054/use-gemini-help-you-organize-files-google-drive/</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOTHJpTmc2NGtpY1E2b3g5NVFfeDRKeGlCZ01EVHR1V3I0SWdONGFUSnk4LXg4bjhfMG42TklLOUZLZFNNbXNsTmQ3ZGJKeVZsRzBCakt1dWprRGJTdkFsRXlHTHhibVNMM0hhRHp1dnlZbkRtd0l3TWpPZllzY0VFc0hJTVhzN05PTENNbUpleEFSam5FUFFuNm42QjNJcmhNZDI5bkU2eTFfUEEwdFZMNmVodEVQdnAxaWJXb3hFOWI1VU9NTGgxbUVwNnpFVUpTX3BvT0VmLUdSYzdKczB1MzB5WTM1bUpfQ0pxSUw5UXJacEttQVFISw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6.22</v>
+        <v>6.23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4302,25 +4306,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>With iOS 27, I’m actually using Siri again</t>
+          <t>Build real-time voice applications with Gemini 3.8 Live and 3.5 Transcribe</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Apple’s long-delayed Siri overhaul is finally here with iOS 27, and it changes how useful the assistant feels day to day.</t>
+          <t>Build real-time voice applications with Gemini 3.8 Live and 3.5 Transcribe    blog.google</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>siri, apple</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:10:30 +0000</t>
+          <t>Tue, 15 Sep 2026 17:11:39 GMT</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4330,16 +4334,16 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/with-ios-27-im-actually-using-siri-again/</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxORklOLTI2REdZOWdBZFJmbEg1S3J3ejNuTGhGMVBlWmVXeGtZRkxXcW1zSUtOVnR5eWd2aG9ibWdmd2xUTmllTDhrZWF2UXpRb1V1SWUzNVIzOEJrZEdNYVYyM1NTaS1oMmZaWWZyNEpSRUowR1dsd2otTV9UQkdaZVpKMGwwSkxGeG11U1J1M1RnVEF4S0dCbjNMRUpKcDNqdm9wWDl5THFKVTluOEp6RGVfNTM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6.22</v>
+        <v>6.02</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -4348,12 +4352,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4361,17 +4365,17 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Siri AI is here as Apple releases iOS 27, macOS Golden Gate and other major OS updates</t>
+          <t>Meta expands subscription push with new AI-focused plans</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>The kinks are still being worked out for users in the EU and China though.</t>
+          <t>Meta One bundles expanded access to the company’s AI tools with premium features across Facebook, Instagram, and WhatsApp.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>siri, apple</t>
+          <t>meta, instagram, facebook</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
@@ -4379,7 +4383,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:13:09 +0000</t>
+          <t>Tue, 15 Sep 2026 17:05:24 +0000</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4389,30 +4393,30 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2257834/siri-ai-is-here-as-apple-releases-ios-27-macos-golden-gate-and-other-major-os-updates/</t>
+          <t>https://techcrunch.com/2026/09/15/meta-expands-subscription-push-with-new-ai-focused-plans/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>apple.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -4420,25 +4424,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Siri AI, a profoundly more capable and personal assistant, is here</t>
+          <t>AI networking startups race to replace Nvidia's NVLink</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Siri AI, a profoundly more capable and personal assistant, is here    Apple</t>
+          <t>AI networking startups race to replace Nvidia's NVLink    The Register</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>siri, apple</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:13:11 GMT</t>
+          <t>Tue, 15 Sep 2026 20:56:48 GMT</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4448,13 +4452,13 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQNmFDb2RTd1Q4T2RMWWlRLUpHUWs3dzZlZ2xVdUhBZGt5a3dTMXh4dW5NSnFvWWJ4YkFBV2FIVDhoLXczZ1QtWlBpbUVrSHd6MTZiRDlld1ZCTFZLQVRXTnJXTk9iNjhtdy1DVmstQjQ2VEltdUl3MmFlOE1uQTByb3JrX3cyb3NESW1PX3N3bXJad2gtSFFvNFpUY1ZUVTlqeWl0MTFvcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQV3NBRV96X05zM2FkSnQ0YnZ0aVdSeDVRQ3p4ZnNqRlh3LWh1Z09mQnBCYXhRR3FmOGp0dHZraWhaU0N4Tm11MkJQZUdFaE1DdktZeGdsR2tULU5YZ1BzUWZmLW5VaHRmUU1qdHBDbXhKbzU0UFVlOEl5ZHV6QkkxYjJnUzBGeDNrdkJjM2hXNkw0UkdvandFVVFZelZscjdQUEcyM0twaWdSZm1D?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6.22</v>
+        <v>5.95</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>2</v>
@@ -4466,12 +4470,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4479,25 +4483,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Siri AI Is Here As Apple Releases iOS 27, macOS Golden Gate And Other Major OS Updates</t>
+          <t>Your AI agents' reports and questions have a new inbox, courtesy of AWS</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Siri AI Is Here As Apple Releases iOS 27, macOS Golden Gate And Other Major OS Updates    Engadget</t>
+          <t xml:space="preserve">AWS engineers have published an open-source AI agent management tool that treats tasks and permission requests just like emails that fill up an inbox. Pizza Bot was announced on AWS’ open-source blog last week, where it was billed by its developers as a way to more easily manage agent tasks without </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>siri, apple</t>
+          <t>aws</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:13:09 GMT</t>
+          <t>Tue, 15 Sep 2026 22:25:44 +0200</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4507,13 +4511,13 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZ1ZYTWlCUGpwY05idURZZUJINktOUWpuWk5OdkcwSUc5UUxDVGdRTm9hbW01UWppT3YyN2lyTGptemdDcEVZSk5iUXhxaXNZY3pHSy1WYW9mT3BINFhuWDc5Vlh4RGNmalc3XzMwSVhycGR4M2k1YTMzd2xIdmdXVGh6ZXNDcGFQTmFGVEw3ZVZrR1RXbzU0ZVJTbFBlekhmUzNMa0gzdlRpbDRhQ1Q3MG9heE04M1ppMGRN?oc=5</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/15/your-ai-agents-reports-and-questions-have-a-new-inbox-courtesy-of-aws/5296661</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6.2</v>
+        <v>5.95</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>2</v>
@@ -4525,12 +4529,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4538,25 +4542,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Fashion app Daydream uses Apple Intelligence to help you shop the outfits in your camera roll</t>
+          <t>Your AI agents' reports and questions have a new inbox, courtesy of AWS</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Fashion app Daydream uses Apple Intelligence to help you shop the outfits in your camera roll    TechCrunch</t>
+          <t>Your AI agents' reports and questions have a new inbox, courtesy of AWS    The Register</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>apple, apple intelligence</t>
+          <t>aws</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:00:00 GMT</t>
+          <t>Tue, 15 Sep 2026 20:25:44 GMT</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4566,13 +4570,13 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQSC1HOXpaRUhXR3lZTlN5M3d5dGFyOEp6SWl4Vm50Ym1RUVN2ZWtLRkZfY2NDYkhscmNuZm9FeFlFNHYzRUNscGV3V0QwMmJScklkRXhNYnlFUlJ4M0JBaGM1eU1hYjVIMGRneTNJMzdpUjlENmtPYUdfaXNPZFZpOFNqS3hFOUZNU1lHRm5uOU5OT1dTd2FkNEswWUsyeHl3WUtIVUt0TXlBbWpTUHBNdkFlVTV6NlBweUNZZmZqQWlaNE9UdUFkLWExU0U2UlJGUTQtT1BEeWF1aTF4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOc0k4RzNfQ1B5bHdpeUxScUk5OEIzVEtYRHpWeFdaT2pvRzd3SGV1RGhTTW1BZVJuVEJhNU1EcTZGamMxYm9BZTl2VmhXNXNORW9mZ2xCVldnd0U1ZWlhUWVoWi1OMzBHa3JDNXhzZXZNenpZMkY5ZmNld1ExdjkxX1lPN3k2bm1PYjB5Qi1iVWphMWpGT0xEMGd4YmE2Um9pc1NLbXRycDY1MXpUTWViSUFvMERFUVZ0WmY3VnBIc3BzTkFY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6.11</v>
+        <v>5.92</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>2</v>
@@ -4584,12 +4588,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4597,25 +4601,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Palantir, and others restrict advanced AI model usage over privacy concerns, report claims — 'paranoia' rising over customer intellectual property</t>
+          <t>Meta now lets AI agents handle the boring parts of WhatsApp Business setup</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Oliver Haslam has written about technology of all shapes and sizes for over 15 years, both online and in print.  Having grown up using PCs and spending far too much money on graphics cards and fancy RAM, Oliver switched to the Mac with a G5 iMac. Nowadays, he uses both macOS and Windows depending on</t>
+          <t>A new WhatsApp Business MCP server lets developers use AI coding agents like Claude, Cursor, Codex, and ChatGPT to handle setup, messaging templates, testing, and troubleshooting.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>palantir, nvidia</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 15:58:32 +0000</t>
+          <t>Tue, 15 Sep 2026 20:12:53 +0000</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4625,13 +4629,13 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-palantir-and-others-restrict-advanced-ai-model-usage-over-privacy-concerns-report-claims-paranoia-rising-over-customer-intellectual-property</t>
+          <t>https://techcrunch.com/2026/09/15/meta-now-lets-ai-agents-handle-the-boring-parts-of-whatsapp-business-setup/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6.11</v>
+        <v>5.92</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2</v>
@@ -4643,12 +4647,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4656,25 +4660,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Palantir, and others restrict advanced AI model usage over privacy concerns, report claims — 'paranoia' rising over customer intellectual property</t>
+          <t>Meta now lets AI agents handle the boring parts of WhatsApp Business setup</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Palantir, and others restrict advanced AI model usage over privacy concerns, report claims — 'paranoia' rising over customer intellectual property    Tom's Hardware</t>
+          <t>Meta now lets AI agents handle the boring parts of WhatsApp Business setup    techcrunch.com</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>palantir, nvidia</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 15:58:32 GMT</t>
+          <t>Tue, 15 Sep 2026 20:12:53 GMT</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4684,16 +4688,16 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxOTExpN2RwblRJUHlTbmlmMTJDcmRZUUZLS0Nud1pLMmg0NWY4Mi1waUxjLTVVTF9qZGczVWRjX1hMTVNqU2I3ekZXcmtfcVoxTnZ4SmRxYzc1TDFhSWdGMzI0WFRrVVNvVnQwQUZfNHFXWlIwZnRhcWdBeFViUmU1Tm4wUURQbjg3LVpSS1c4Y1plYUNOUFNteUE2R2NtSHFHajJZWUo3aVhfeUZjUHpyNkxUbTZ0N09LYURuRDF6SWNpR2I1ajRiOGptcHRNYXgxZXJkdi1vQm5MNG15NDlwWDZhQ1BoMHhmOHI4YWNoWG1uOVJIX0FZUFZsVlNLQTVacHg1VEp5UnVmNUZOcHRNcERHRk52SlF6VDhpejJ6MEpobzFpWDRxV2ZUbDJRSTQ2anU3dHJYMDVvZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcF8yQlQ5WlpPaXc5QUlwZEVLTVpPdThDemRORmJfQ0FkbnNNeF91T0ZZRWtwQ214bldVelM4Si1lSUV2WW85NUVkLUo4cUZKZUcwQXZDM1ktbHpnbGFNcWtXQmY0MEZNZFR1ZFJYZEphbHZCcGRZbkRNSGxtempiNklKZTNUQlV1eVloVFpKdjFHYUhjekNtMGtrazFrOWtLdE9TaFlSQWw4ZUVsSEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6.02</v>
+        <v>5.9</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -4707,7 +4711,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -4715,25 +4719,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Microsoft sets limits for future AI models as industry throttles frontier development</t>
+          <t>Nvidia's Huang rips Anthropic's proposal for AI safety antitrust waiver: 'Completely unnecessary'</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Microsoft sets limits for future AI models as industry throttles frontier development    CNBC</t>
+          <t>Nvidia's Huang rips Anthropic's proposal for AI safety antitrust waiver: 'Completely unnecessary'    CNBC</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>nvidia, anthropic</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>12.2</v>
+        <v>2.8</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 13:00:01 GMT</t>
+          <t>Tue, 15 Sep 2026 22:13:52 GMT</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4743,25 +4747,25 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQSlJYLXlYazNYam85R0djdHlHOENQdGhCZkdQY1l0LTdmYnNMS1ZocFBpUl9wS2ZqamZyWXQzcXYwaW9vdkRMbEJ0ZFFFb3dydHNIdFBfbXNBVjJrdlB2NlNVcVBKMEdTWjVzd1VUeGtXcnJqUS1vMTI1WVRlWnZFREsyMnhiZ9IBiwFBVV95cUxONVNwbzBjUWFaOXRVblJ1ejIyRVlObEdPNW16aEVPaG9VRWxydExnZ2dvSzROWGprTTdYaG0wbEJ3aDJUb1RuVENIVTdySDVvTTBCR19YakpPTG5JeHRiYmRPY1pub0lBTFBvV01vS3lUeFpSUUp6U3QxdW9uZjRQdTY0b2ZYNUszbGtZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE44RHpQWkxyODlqZFVxWEs5TjRrN2ZWMktZUGRyWERQMURrUEZSWk53QXRpRURxcmJtMVJvcmIzWTY5Unk3VVBlRThad2J0YVhJcFRkSVdOUlNvU3Jvbzh1anRPTGU3SGZnUXZOOE5GcWtQOXpPMldaR1hCTdIBgAFBVV95cUxNZ1VaYzZvQzNWOHQwX3Vfc1BraXpSRU91R2E5ZWVoSUhaZjNZQ1BfT1hUaFU5aEI5cF95UHE1V3VWX1ExcGpQR2NXc2JsSUJzWGFGRjU3TC1waW1hM0FmbTNRS2c2UlZVcWk3bmxudUNBbXBVYWJDVHRLRm9meG1zQg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.99</v>
+        <v>5.9</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4774,25 +4778,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Watch astronaut Christina Koch and Google’s James Manyika discuss space, technology, and discovery.</t>
+          <t>Ex-Google DeepMind researcher adds to warnings that AI could 'kill all humans'</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Watch astronaut Christina Koch and Google’s James Manyika discuss space, technology, and discovery.    blog.google</t>
+          <t>Ex-Google DeepMind researcher adds to warnings that AI could 'kill all humans'    Reuters</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>deepmind, google</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4.2</v>
+        <v>19.8</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:56:33 GMT</t>
+          <t>Tue, 15 Sep 2026 05:16:00 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4802,16 +4806,16 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQTXZLY203YWY3WlJCczgxaHhsdHdRS3k3MTJYUU1fZFhITWE1YTA4V0xpRlJxM3pzcllUeTdiWUc5aWU4TGt5ZzE2SHJaRGY4TVpjTmtMR1NUazV2X21XbXBxUWJUWUxrQi0tYUVoTmh3MlBCbFpxdXB0X0E3UE92d3dUWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPcFU5RG1vWUx4LW5tTnVlWmxVaExUb1JiYks2N01JbTJFWl9NY3ZFRUpxaGc3LURuZ2xST2VkZ1hFNFROcjM4U0RPeGFqczRCamt4Z3FqWFBteC1seWxSdUJLRE9HUDlqeGxlczE4M0JJTEp1WC1VWGJXcmpJUjgzU0g1OGxHN0N6RWZtTjJBNktPTUJqU2Y0N2J2QTR1ZHRjQTNQZVk1UU4weXRvZGJvMDRYZkh0VkNvMXQtVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.97</v>
+        <v>5.88</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -4820,12 +4824,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4833,25 +4837,25 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Oracle celebrates banner quarter with another round of layoffs</t>
+          <t>'Fast Money' traders react to Nvidia CEO Jensen Huang addressing AI safety</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Oracle posted record revenue during its latest quarter, but that hasn't stopped the company from chopping more employees. Reports began appearing on social media early Monday that staff were having trouble accessing corporate systems such as email and Slack, which essentially served as a sign that t</t>
+          <t>'Fast Money' traders react to Nvidia CEO Jensen Huang addressing AI safety    CNBC</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>nvidia, jensen huang</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 22:46:57 +0200</t>
+          <t>Tue, 15 Sep 2026 21:52:56 GMT</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4861,16 +4865,16 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/databases/2026/09/14/oracle-celebrates-banner-quarter-with-another-round-of-layoffs/5296395</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNbDBIS3pHZ2F3YXZhLTd0a1A4QmpWd3VLeVVjUUxKbEFrOW9ibmNaX1paTzNBRW8tZzZuajJvcm45S1RWSUQzRHBtMXZuMFQtWFhpZ292Z2RTVWpJMGg4Y2hUNzhUemIwMDRGYWlFTmctd0VpcVllTjJMcnd0OWhmMF8ydUFMVnl1aXRXYkpjcTdOMmJvOWprM05FSVFCbGNxeWx1R1BkQ1N3SmN2b2oteVg0bVhBdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4888,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4892,25 +4896,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Oracle celebrates banner quarter with another round of layoffs</t>
+          <t>The vulnpocalypse rains iBugs down on Apple with record-setting number of patches</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Oracle celebrates banner quarter with another round of layoffs    The Register</t>
+          <t>Apple has addressed more than 260 CVEs across all of its operating systems, browsers, and other software products, marking the largest single patch cycle in Cupertino's history. While this CVE count is hardly notable compared to some vendors - hello, Microsoft’s record-breaking 974 bugs disclosed ea</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>microsoft, apple</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:46:57 GMT</t>
+          <t>Tue, 15 Sep 2026 23:38:31 +0200</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4920,16 +4924,16 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPRWVpcGZwSU9rV1ZxbkxtQ0J5UVgyeWg5bE1DUDNJSmh3UWJESzFpdThnaGJ2dUZlZ2hNckJKNVVvN1VCQjBKaEZuMnNtbkZfci10ZGlycmtuZ3NFaE1sYi03UnNWS2JSang5SzlVeTZsYU5URlBNUkJuUjA2QXVMUnh3Y0lBYjlvcGpqQWpuSmlhYWMtTnJSZkVzUkdSZjhpeXgxMTMzQXk1X3NwZkJrZFZpNzBUSi1PWlNn?oc=5</t>
+          <t>https://www.theregister.com/security/2026/09/15/the-vulnpocalypse-rains-ibugs-down-on-apple-with-record-setting-number-of-patches/5296679</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.91</v>
+        <v>5.8</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -4938,7 +4942,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4951,25 +4955,25 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>AI infrastructure company Cornelis raises $205M to chip away at Nvidia’s dominance</t>
+          <t>Anthropic’s CEO calls for AI slowdown as Nvidia’s urges acceleration</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>AI infrastructure company Cornelis raises $205M to chip away at Nvidia’s dominance    TechCrunch</t>
+          <t>Anthropic’s CEO calls for AI slowdown as Nvidia’s urges acceleration    The Guardian</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>nvidia, anthropic</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:07:37 GMT</t>
+          <t>Tue, 15 Sep 2026 21:05:00 GMT</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4979,30 +4983,30 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZlVFSFdPNzRSNnBiMkZZbElkcEkyejJTVUtmbDJUcTU0RlJYNjIwVzYyMWhiemxBUmIycVZEeWlUYWNlMi1IQkxxUXlnVi1DbUxPallBaWxpYnY5RG5EY0dwYU8wcWpyMDU1eS15T29iLV9UOXpiVHdCM3dMRkdjUU9OMllpOGNvYmdVUGZDTy1GUklLTFkxam1Cb2xiYXFyZHhZNmxFbUUtNTRBMXFxNm9uZGRhUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPM2d1QUlzZ3FaU3BNX3Z1aEI3V0EtUnpxN2tHZHZhMjNCSFdPdmliZnQ5end4U09MRkZCLVFmMjlOVGhyelpvWUdUaG92a1RvSkdFaW1CZWI5MW9VeHBDQ0RPQ2VXYmE2dGpTTEFyS2VITEtJMXBDWW1hUEtTLWRkUA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.9</v>
+        <v>5.76</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5010,27 +5014,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Apple Home’s new security camera features cost as much as $60 a month</t>
+          <t>From Megawatts to Tokens: How NVIDIA Maximizes AI Factory Production</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Apple Intelligence features for HomeKit cameras start at $10 a month and go up to $60. | Image: The Verge	 
- With the  public release of iOS 27 and tvOS 27 , Apple Home is getting an injection of  Apple Intelligence  - but you'll have to pay more for it. 
-  Apple Intelligence for Home  brings </t>
+          <t>From Megawatts to Tokens: How NVIDIA Maximizes AI Factory Production    NVIDIA Blog</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>apple, apple intelligence</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14T18:28:52-04:00</t>
+          <t>Tue, 15 Sep 2026 18:29:08 GMT</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5040,13 +5042,13 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/994949/apple-intelligence-apple-home-icloud-plus-cost-subscription</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQMnp0VjMxX29PWDY4OVo0LWRfSmRMemlJcWlUNFIzcG9tYjhoQW9Rb2RJYUZSN21ydGtSTGVKRGcxX0ZlOVFoMUo2SldacHdHTE5JU2pUem9seGtrOHRfbExyRzFUUzMzelBZQXhmSTNpSjRJenBGSENpd0Nxa3FuXy1WZ0xtRGczVXppZ1BsZ1ItZW9vQ1RBZmFDTDl0bDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -5071,25 +5073,25 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Samsung backs Nvidia AI chip rival in $230 million funding round as GPU alternatives boom</t>
+          <t>Nvidia's Huang diverges with CEOs of Anthropic, OpenAI on AI safety at Dreamforce</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Samsung backs Nvidia AI chip rival in $230 million funding round as GPU alternatives boom    CNBC</t>
+          <t>Nvidia's Huang diverges with CEOs of Anthropic, OpenAI on AI safety at Dreamforce    CNBC</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>gpu, nvidia</t>
+          <t>nvidia, anthropic</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 23:30:02 GMT</t>
+          <t>Tue, 15 Sep 2026 20:00:16 GMT</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5099,30 +5101,30 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1ydVhNMHFzRmctZVp2Sjlsd0tXMm5pNTN6UGoyczRpZlBUTjhITy1ybEQ4SDh0MWNZb09ldElzWEZWS3BBTVZwdnlzQXRBM0FFSzEzOXNCVlJneEFydmdXQWc1MVVCZlZRN1lyWG1KM3U0OXd4aUHSAXtBVV95cUxQSWlJd0JfRlNxTVIwNjEyaG5JQWZwYTRic0lfNFVha09oLVF0UGlyemVpOW1USGN5SlpiWXRiVUxSaVllTnZoaXhGZ3dpR0lkUUlIYTVUWkxTaDJYOUYzYXktbnVRNmgzeDJiWFNLWE5icW5UZTRxVzU2UXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNamhBSWgtcmZwTVRVOXlnbGZMN2R1bDFlMWEtV21wUXFmUGVoWW5vQWNVbU55OEE0T0lWMUFlMXFZVGdvNmN0TElFUGNkQUlwQ01hU09aUEZIZlBjd0lMbGJMOVJHbmhOSTNRaHU0cXBnNmRVQ2lTb21odDUzOGlRQ1phSTRDUDVucThHQjNncjI1Q1pMOVV0WlotdDVpUdIBowFBVV95cUxNQW5ST21vbGJyUWYzcHVFZFJOZUgzTEJ3TWFkS3Y4Nm9fQ2w3c3puMnJqaFBpbl9CVG5Gd1RSZUVGQmJqLVZaN0dBZ0dOWEZNb3IxMDBtaGhWNGllb29aZERqeGxibHhnakZJRDgxeF9oa1NDSGV2YzYwa3plQ0dhZU43aHJNb1MyUlZRRm1hb1BZRVpZRVF4LUd1OWNQXzJpZFpr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>oracle.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5130,25 +5132,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Jensen Huang puts Trump on speakerphone onstage to announce robots won’t take over the world</t>
+          <t>Oracle Releases Java 27 and Strengthens Post-Quantum Cryptography Support</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Jensen Huang puts Trump on speakerphone onstage to announce robots won’t take over the world    The Verge</t>
+          <t>Oracle Releases Java 27 and Strengthens Post-Quantum Cryptography Support    Oracle</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>jensen huang</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 20:03:37 GMT</t>
+          <t>Tue, 15 Sep 2026 17:55:08 GMT</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5158,30 +5160,30 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVmh4V2R2c2ZESDlkeEo2bXU5dThKSmxSVmRXaE5FelZMMzNNYVdMeTNMVFhWb3NZT01vTUM3TFdLNW5LYTUzZzhxY3o1bGduZ3ZzTVBoNlVHTDRzWmhtdmJuQ2tNZXhVLVo5TG54VkZhVHJBd1ZJMGQ2cVl6RE51eHo5ZzdLNmF2cGdXQU15bHp4V3F4YUd4Q1RzZkxHTDVfb2hDUG1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQVG1IX1NqcTZpZTQ4ZUJRYjdzdUxVU3NSMTVsWnlYQ1NfX3dVUkV0U3Y0UTVwanJwcXFqREVDZ253WGVrRDJ5OTBoMXg4dlQ1cFJlRDVVZDBQbDZqWkZrZVp5bE9zakZ5UzF1d0RhenlDNmJXdjZaRFdkNG9NRnl2d2lTcXNBT2xXRG41bzM2bjZxekhsZERsSGcxYUh6MWt3cnM3YWMzOXdCeEZYRkY1S281RlRCU2psb3BPbXVwalNuQllq?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.76</v>
+        <v>5.64</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5189,25 +5191,25 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Solo dev enables running CUDA on AMD hardware in Windows, getting multiple CUDA libraries running on a gaming Radeon RX 9060 XT GPU in Windows —  CUDA-exclusive workloads on AMD hardware in Windows possible without virtualization or dual-booting</t>
+          <t>15 organizations transforming public service with AI</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
+          <t>15 organizations transforming public service with AI    blog.google</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>cuda, gpu, amd</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10.8</v>
+        <v>7.8</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 14:23:12 +0000</t>
+          <t>Tue, 15 Sep 2026 17:13:37 GMT</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5217,16 +5219,16 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpu-drivers/solo-developer-wires-zluda-to-amds-hip-getting-multiple-cuda-libraries-running-on-a-radeon-rx-9060-xt-in-windows-cuda-exclusive-workloads-on-amd-hardware-in-windows-is-possible-without-virtualization-or-dual-booting</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTDdTMXVnbU93WUZmci14bXYxcnp4b2xBNGVrLXJBRTZpeGpObHRrN3QtWFRyd3dJLVhaSHIxVHFxV1dROXU5UmRwYmlBSUVrWV9VVDRWbTBjTllBM2FMdnVwTkVqZkZmT2drWVhfd3NfR2taVl9oNVliNHlRZk5vUlcwUDl2bnQ3b0liRjF4VEVJWHVidnUwWF8xQWh1WUVLOW1UX29EdjE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.62</v>
+        <v>5.6</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -5248,25 +5250,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>With iOS 27, I’m actually using Siri again</t>
+          <t>The AI graveyard: a running list of projects and startups that didn’t make it</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>With iOS 27, I’m actually using Siri again    TechCrunch</t>
+          <t>From Apple's repeatedly delayed Siri AI to OpenAI's messy "super app" launch, here's a look at the AI projects that shut down or missed expectations.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>siri</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 17:10:30 GMT</t>
+          <t>Tue, 15 Sep 2026 19:00:00 +0000</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5276,13 +5278,13 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMmFCT1BZaEU0bWUwZ3UyNEtmSERzQ0dSWlFPelB5RXFWZl92NE9LUU82OFZqNk4xaG1CWmFhZFlYMmhFeDFPcGVqUHphdlJPY182Y0oyTEVCTGJITm85WFRZMjVyNTdyb2VOVGxyeW1UYkR2TGFRb0VjcklPc0E4eQ?oc=5</t>
+          <t>https://techcrunch.com/2026/09/15/the-ai-graveyard-a-running-list-of-projects-and-startups-that-didnt-make-it/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -5294,12 +5296,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -5307,25 +5309,27 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>How to use Meta Display glasses while driving with the Audio Only feature</t>
+          <t>Google อนุญาตให้พนักงานใช้ Claude เป็น AI ช่วยเขียนโค้ดได้แล้ว จากที่ผ่านเน้นใช้ Gemini</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>The Meta Display glasses have an Audio Only feature that can detect when you're driving and turn off the display.</t>
+          <t>Google อนุญาตให้พนักงานใช้ Claude เป็น AI ช่วยเขียนโค้ดได้แล้ว จากที่ผ่านเน้นใช้ Gemini 
+     Body 
+                Business Insider อ้างแหล่งข่าวภายในกูเกิลซึ่งต่อมายืนยันโดยโฆษกของกูเกิล ว่าบริษัทได้อนุญาตให้วิศวกรของบริษัทใช้งาน Claude AI ของ Anthropic เพื่อช่วยในการพัฒนาโครงการต่าง ๆ ของบริ</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>gemini, google, anthropic</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7</v>
+        <v>12.8</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Tue, 15 Sep 2026 00:30:00 +0000</t>
+          <t>Tue, 15 Sep 2026 12:15:21 +0000</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5335,30 +5339,30 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2255133/meta-display-glasses-audio-only-driving-detection-feature/</t>
+          <t>https://www.blognone.com/node/151646</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -5366,25 +5370,25 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Apple releases test of redesigned Siri AI before iPhone 18 hits stores this week</t>
+          <t>AI for everyone in every language</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Apple releases test of redesigned Siri AI before iPhone 18 hits stores this week    CNBC</t>
+          <t>AI for everyone in every language    blog.google</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>siri, apple</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>6.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 19:05:40 GMT</t>
+          <t>Tue, 15 Sep 2026 16:15:59 GMT</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5394,30 +5398,30 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQQ0FLeUE0dV9EVXFIbDYzVk12ejFrYWNvRDI4aktUUzlTWkFMUWU0TDVieXNNeklhaE5XN2VUNER3ZUdtVWc5d3lHakpNOGVhUHhfV2FOZnVFTW9VZ25MRGMtMVdudm4weDlOb3NuR1hoZTc2cllGcFRxSG5vMi1lY1NDVdIBiAFBVV95cUxNbkUxMGxGN29sWTBjVk5uUGJQNkozUVZjSzZJa3VEazFwcVJjbnNKUThkb3BaRUxoYmJVX04weFhGSm1rYVNoNDBlazdEeHkwNUZ2V1I1VGtZM1RyWlNiSmpPMHdnTzc2eHhaX2FGWk5vN1MtQnpsWDF2anZLMkpLdHFkOGFUbFpS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1GdGtMM2l2cGYxcG1pQjBGWWc2VlNKQUkxWThLTUNJOWpBcVdIZUZMdDVkOFJNYXVNaTFPZDc5Mm84SjJBbG1wajBpa1BuQjdGSmVjb1dMQU1VbDcweDNiSnFFMzN2NkNQWjhGUHVoVUpWQTFyaUtuS0tsWUFnR28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -5425,25 +5429,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s new AI ‘code of conduct’ tells models not to hack systems or trick humans</t>
+          <t>Ask a Scientist: How can researchers use AI to spot a wildfire?</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>The code of conduct lays out general principles that Microsoft AI models should uphold — supporting humans rather than replacing them, for instance, and accelerating human flourishing — as well as specific safety constraints meant to implement those principles.</t>
+          <t>Ask a Scientist: How can researchers use AI to spot a wildfire?    blog.google</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 16:27:53 +0000</t>
+          <t>Tue, 15 Sep 2026 16:18:04 GMT</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5453,30 +5457,30 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/microsofts-new-ai-code-of-conduct-tells-models-not-to-hack-systems-or-trick-humans/</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbU5YTGxDZXhYVkxKdGctZVh1SVlEUWd5STg4R09Cel9uZDJ4YnVSSTB1VnQxT2dDcUVjTGxidlZUV010em5qOXQ0Y2dla2FOREhlS0NPYmxocHIwVzN4cTJNMExkQVREMUY5SFRTNU5nV1JvVDZEc2RBbXNqNERXVFpMX3Vpa29VSmF3YUtmWFBXc0hpczhuLTR2MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.56</v>
+        <v>5.54</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -5484,25 +5488,25 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s new AI ‘code of conduct’ tells models not to hack systems or trick humans</t>
+          <t>Building AI to accelerate science and improve lives</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s new AI ‘code of conduct’ tells models not to hack systems or trick humans    TechCrunch</t>
+          <t>Building AI to accelerate science and improve lives    blog.google</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 16:27:53 GMT</t>
+          <t>Tue, 15 Sep 2026 16:09:18 GMT</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5512,7 +5516,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZ0VkdmR6NXZpVENub3FWamRWSEVmQ0tydGQ3UUxVaUtVMEUzSEZfZTZMdHM5V0I0eHVMa1JzWFdkSVlPcWt4N2N5d0JNcFFvcEphSmpRRTM5cUk1VS1vRWtud3NTUUtWMElEZ19LUHlhUVF0SUVxRzBPWkdHUTVveWoxbG5rRVFZTlRQWm43NHA3S0paQnV1VFIxdFpYdVVaN0hmMm45OXdfMkR5QmhHSlRpQVlVWjJC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPcU1Eb1R4ZGdSYlVlV3ctdG5tVVpEYlFNWjFxY1lJSlZNNW1laFhXUDI0aFZhSjlxWkhPN3JUNy1xQm56WVFOaFJiWFotMGtFNEo5YTVMSnBNTlRoekJHellCS0hqeXA3cWZnYkc2U2NtVjBDblFlU1JvVVlxdzc2dzNpR1pKSUM4MVNB?oc=5</t>
         </is>
       </c>
     </row>
@@ -5636,26 +5640,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.82</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.52+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.52+sig1.2+src2.0+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Apple releases iOS 27 with Siri AI overhaul</t>
+          <t>Introducing Gemini 3.8 Live and 3.8 Live Extended Thinking</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>siri, apple</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -5663,12 +5667,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/news/994756/apple-ios-27-launch-iphone-siri-ai-update</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/gemini-3-8-live-gemini-3-8-live-extended-thinking/</t>
         </is>
       </c>
     </row>
@@ -5677,39 +5681,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.32</v>
+        <v>7.61</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.82+sig1.2+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.31+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk’s X Corp and SpaceXAI drop antitrust lawsuit against Apple</t>
+          <t>OpenAI is working with Anthropic, Google on AI safety, Bloomberg News reports</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>apple, elon musk</t>
+          <t>google, anthropic</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.aljazeera.com/news/2026/9/14/elon-musks-x-corp-and-spacexai-drop-antitrust-lawsuit-against-apple</t>
+          <t>https://www.reuters.com/technology/openai-is-working-with-anthropic-google-ai-safety-bloomberg-news-reports-2026-09-15/</t>
         </is>
       </c>
     </row>
@@ -5718,30 +5722,30 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.27</v>
+        <v>7.5</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.97+sig1.8+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.4+sig1.8+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>nvidia, jensen huang, elon musk</t>
+          <t>deepmind, google, anthropic</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -5750,7 +5754,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/nvidia-ceo-jensen-huang-tells-trump-were-not-going-to-let-an-ai-slowdown-happen/</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
@@ -5759,39 +5763,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7.12</v>
+        <v>7.3</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.42+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts code of conduct to keep its AI under human control</t>
+          <t>Microsoft will hold a Windows and Surface event on October 7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>microsoft, nvidia, jensen huang</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/microsoft-drafts-code-conduct-keep-its-ai-under-human-control-2026-09-14/</t>
+          <t>https://www.engadget.com/2259695/microsoft-will-hold-a-windows-event-on-october-7/</t>
         </is>
       </c>
     </row>
@@ -5800,30 +5804,30 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.1</v>
+        <v>7.16</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig2.4+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.86+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Is Big Tech’s AI slowdown a safety pact or a cartel?</t>
+          <t>Microsoft announces Windows and Surface event for October 7th</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>deepmind, anthropic, elon musk, google</t>
+          <t>microsoft, nvidia, jensen huang</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -5832,7 +5836,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/995186/is-big-techs-ai-slowdown-a-safety-pact-or-a-cartel</t>
+          <t>https://www.theverge.com/news/994714/microsoft-windows-surface-event-october-7-san-francisco</t>
         </is>
       </c>
     </row>
@@ -5841,39 +5845,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7.08</v>
+        <v>7.03</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.58+sig1.2+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.33+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk's X Corp and SpaceXAI just moved to dismiss their lawsuit against Apple</t>
+          <t>Meta launches subscriptions with enhanced AI features</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>apple, elon musk</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2257929/elon-musk-x-corp-and-spacexai-just-moved-to-dismiss-their-lawsuit-against-apple/</t>
+          <t>https://www.reuters.com/business/meta-launches-subscriptions-with-enhanced-ai-features-2026-09-15/</t>
         </is>
       </c>
     </row>
@@ -5882,39 +5886,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7.08</v>
+        <v>7.03</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.98+sig2.4+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.33+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Apple อัปเดต iOS 27, iPadOS 27, macOS 27 Golden Gate, watchOS 27 ให้ผู้ใช้งานทั่วไปแล้ววันนี้</t>
+          <t>Meta launches subscriptions with enhanced AI features</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>siri, gemini, apple, apple intelligence</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151641</t>
+          <t>https://www.channelnewsasia.com/business/meta-launches-subscriptions-enhanced-ai-features-6386626</t>
         </is>
       </c>
     </row>
@@ -5923,16 +5927,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.89+sig0.6+src0.5+corr2.4+wl1.5</t>
+          <t>rec2.3+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Puts Trump on Phone While Downplaying AI Risks</t>
+          <t>We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5942,20 +5946,20 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>nvidia, jensen huang</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-14/nvidia-ceo-puts-trump-on-speakerphone-while-downplaying-ai-risks</t>
+          <t>https://techcrunch.com/2026/09/15/we-dont-need-ai-regulation-leave-safety-to-us-nvidias-jensen-huang-says/</t>
         </is>
       </c>
     </row>
@@ -5964,16 +5968,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.83</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.33+sig1.2+src1.2+corr1.6+wl1.5</t>
+          <t>rec2.3+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Palantir, Nvidia curb AI model use over data fears, The Information reports</t>
+          <t>We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -5983,20 +5987,20 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>palantir, nvidia</t>
+          <t>nvidia, jensen huang</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/palantir-nvidia-curb-ai-model-use-over-data-fears-information-reports-2026-09-14/</t>
+          <t>https://techcrunch.com/2026/09/15/we-dont-need-ai-regulation-leave-safety-to-us-nvidias-jensen-huang-says/</t>
         </is>
       </c>
     </row>
@@ -6005,30 +6009,30 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.5+sig1.8+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.4+sig1.2+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Fashion app Daydream uses Apple Intelligence to help you shop the outfits in your camera roll</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>siri, apple, apple intelligence</t>
+          <t>google, anthropic</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -6037,7 +6041,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/fashion-discovery-app-daydream-uses-apple-intelligence-to-help-you-shop-the-outfits-saved-in-your-camera-roll/</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6083,257 +6087,257 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Apple  (Tier 1 · 13 stories)</t>
+          <t>Nvidia  (Tier 1 · 13 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.82</v>
+        <v>7.3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Apple releases iOS 27 with Siri AI overhaul</t>
+          <t>Microsoft will hold a Windows and Surface event on October 7</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/news/994756/apple-ios-27-launch-iphone-siri-ai-update</t>
+          <t>https://www.engadget.com/2259695/microsoft-will-hold-a-windows-event-on-october-7/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6.8</v>
+        <v>7.16</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Fashion app Daydream uses Apple Intelligence to help you shop the outfits in your camera roll</t>
+          <t>Microsoft announces Windows and Surface event for October 7th</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/fashion-discovery-app-daydream-uses-apple-intelligence-to-help-you-shop-the-outfits-saved-in-your-camera-roll/</t>
+          <t>https://www.theverge.com/news/994714/microsoft-windows-surface-event-october-7-san-francisco</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Musk's X Corp and SpaceXAI resolve antitrust lawsuit against Apple</t>
+          <t>We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/musks-x-corp-spacexai-resolve-antitrust-lawsuit-against-apple-2026-09-14/</t>
+          <t>https://techcrunch.com/2026/09/15/we-dont-need-ai-regulation-leave-safety-to-us-nvidias-jensen-huang-says/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.53</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Major updates for Apple’s software platforms are now available</t>
+          <t>We don’t need AI regulation — leave safety to us, Nvidia’s Jensen Huang says</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>apple.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDhsUUhGOF9HN2dCZWc3cVVLQ2RYRjNvVmw1SzBmb1FUZVdJcU9RNFhpYUlJRG51LU1ub2M5Ql93cVlRZnBKMHNVZmd0d1Bmd0ZhcG00d0czd3BGdU9mMUgwTWVYNFJBTGVnU2FTeWZxQVl1R3dWS29kN0NRWkQ0UnFiSUtPcDJPYjRreHNuS0syZ0pBVV9RZTVucF9QRVptd0lPN3BBOA?oc=5</t>
+          <t>https://techcrunch.com/2026/09/15/we-dont-need-ai-regulation-leave-safety-to-us-nvidias-jensen-huang-says/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.42</v>
+        <v>6.81</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Major updates for Apple’s software platforms are now available</t>
+          <t>AI Infra Summit: NVIDIA Vera Rubin and DSX Platform Advances Showcase Energy Efficiencies of Optimizing Tokens Per Watt for AI Factories</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>apple.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOZmRRYUVFM1NWTFZia09Ddlpxd0swTmplT1N2SVNIcW41M08zR2p0aDVIbDJfQjlyZ0t3a3FwRG1iY3NZTjBGZjViQWVfOEpHXzA0M2QyU19aR2Y2dVFIYW1tYmp3NThoYVM0Nm9XeXd1TEhhZl9Rc2ZuWWM1SERqUDZDMDFKZlJ1S3dIa3dZdU4wYWUxemJmdVR4VVFiSFBaQzJZ?oc=5</t>
+          <t>https://blogs.nvidia.com/blog/ai-infra-summit-vera-rubin-dsx-energy-efficiencies-tokens-per-watt-ai-factories/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.22</v>
+        <v>6.7</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>With iOS 27, I’m actually using Siri again</t>
+          <t>‘Now We Can Know Everything and Do Anything,’ Jensen Huang Says at Dreamforce</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/with-ios-27-im-actually-using-siri-again/</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1SR0x4NGdWbnVGU0hRVUU3N2hWWkJZWW9BNl84Sk4xWW8xUzNhQ0NmMlJMajViMktoU29lZlhGcjZNbGtlaUFiTHNCMmZGbGVINlpTR01kQlUzcGRTclBZSXRYMGQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.22</v>
+        <v>6.6</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Siri AI is here as Apple releases iOS 27, macOS Golden Gate and other major OS updates</t>
+          <t>AI networking startups race to replace Nvidia's NVLink</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2257834/siri-ai-is-here-as-apple-releases-ios-27-macos-golden-gate-and-other-major-os-updates/</t>
+          <t>https://www.theregister.com/systems/2026/09/15/ai-networking-startups-race-to-replace-nvidias-nvlink/5296672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Siri AI, a profoundly more capable and personal assistant, is here</t>
+          <t>AI networking startups race to replace Nvidia's NVLink</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>apple.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQNmFDb2RTd1Q4T2RMWWlRLUpHUWs3dzZlZ2xVdUhBZGt5a3dTMXh4dW5NSnFvWWJ4YkFBV2FIVDhoLXczZ1QtWlBpbUVrSHd6MTZiRDlld1ZCTFZLQVRXTnJXTk9iNjhtdy1DVmstQjQ2VEltdUl3MmFlOE1uQTByb3JrX3cyb3NESW1PX3N3bXJad2gtSFFvNFpUY1ZUVTlqeWl0MTFvcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQV3NBRV96X05zM2FkSnQ0YnZ0aVdSeDVRQ3p4ZnNqRlh3LWh1Z09mQnBCYXhRR3FmOGp0dHZraWhaU0N4Tm11MkJQZUdFaE1DdktZeGdsR2tULU5YZ1BzUWZmLW5VaHRmUU1qdHBDbXhKbzU0UFVlOEl5ZHV6QkkxYjJnUzBGeDNrdkJjM2hXNkw0UkdvandFVVFZelZscjdQUEcyM0twaWdSZm1D?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.22</v>
+        <v>5.9</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Siri AI Is Here As Apple Releases iOS 27, macOS Golden Gate And Other Major OS Updates</t>
+          <t>Nvidia's Huang rips Anthropic's proposal for AI safety antitrust waiver: 'Completely unnecessary'</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZ1ZYTWlCUGpwY05idURZZUJINktOUWpuWk5OdkcwSUc5UUxDVGdRTm9hbW01UWppT3YyN2lyTGptemdDcEVZSk5iUXhxaXNZY3pHSy1WYW9mT3BINFhuWDc5Vlh4RGNmalc3XzMwSVhycGR4M2k1YTMzd2xIdmdXVGh6ZXNDcGFQTmFGVEw3ZVZrR1RXbzU0ZVJTbFBlekhmUzNMa0gzdlRpbDRhQ1Q3MG9heE04M1ppMGRN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE44RHpQWkxyODlqZFVxWEs5TjRrN2ZWMktZUGRyWERQMURrUEZSWk53QXRpRURxcmJtMVJvcmIzWTY5Unk3VVBlRThad2J0YVhJcFRkSVdOUlNvU3Jvbzh1anRPTGU3SGZnUXZOOE5GcWtQOXpPMldaR1hCTdIBgAFBVV95cUxNZ1VaYzZvQzNWOHQwX3Vfc1BraXpSRU91R2E5ZWVoSUhaZjNZQ1BfT1hUaFU5aEI5cF95UHE1V3VWX1ExcGpQR2NXc2JsSUJzWGFGRjU3TC1waW1hM0FmbTNRS2c2UlZVcWk3bmxudUNBbXBVYWJDVHRLRm9meG1zQg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.2</v>
+        <v>5.88</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Fashion app Daydream uses Apple Intelligence to help you shop the outfits in your camera roll</t>
+          <t>'Fast Money' traders react to Nvidia CEO Jensen Huang addressing AI safety</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQSC1HOXpaRUhXR3lZTlN5M3d5dGFyOEp6SWl4Vm50Ym1RUVN2ZWtLRkZfY2NDYkhscmNuZm9FeFlFNHYzRUNscGV3V0QwMmJScklkRXhNYnlFUlJ4M0JBaGM1eU1hYjVIMGRneTNJMzdpUjlENmtPYUdfaXNPZFZpOFNqS3hFOUZNU1lHRm5uOU5OT1dTd2FkNEswWUsyeHl3WUtIVUt0TXlBbWpTUHBNdkFlVTV6NlBweUNZZmZqQWlaNE9UdUFkLWExU0U2UlJGUTQtT1BEeWF1aTF4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNbDBIS3pHZ2F3YXZhLTd0a1A4QmpWd3VLeVVjUUxKbEFrOW9ibmNaX1paTzNBRW8tZzZuajJvcm45S1RWSUQzRHBtMXZuMFQtWFhpZ292Z2RTVWpJMGg4Y2hUNzhUemIwMDRGYWlFTmctd0VpcVllTjJMcnd0OWhmMF8ydUFMVnl1aXRXYkpjcTdOMmJvOWprM05FSVFCbGNxeWx1R1BkQ1N3SmN2b2oteVg0bVhBdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Apple Home’s new security camera features cost as much as $60 a month</t>
+          <t>Anthropic’s CEO calls for AI slowdown as Nvidia’s urges acceleration</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/994949/apple-intelligence-apple-home-icloud-plus-cost-subscription</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPM2d1QUlzZ3FaU3BNX3Z1aEI3V0EtUnpxN2tHZHZhMjNCSFdPdmliZnQ5end4U09MRkZCLVFmMjlOVGhyelpvWUdUaG92a1RvSkdFaW1CZWI5MW9VeHBDQ0RPQ2VXYmE2dGpTTEFyS2VITEtJMXBDWW1hUEtTLWRkUA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.62</v>
+        <v>5.76</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>With iOS 27, I’m actually using Siri again</t>
+          <t>From Megawatts to Tokens: How NVIDIA Maximizes AI Factory Production</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNMmFCT1BZaEU0bWUwZ3UyNEtmSERzQ0dSWlFPelB5RXFWZl92NE9LUU82OFZqNk4xaG1CWmFhZFlYMmhFeDFPcGVqUHphdlJPY182Y0oyTEVCTGJITm85WFRZMjVyNTdyb2VOVGxyeW1UYkR2TGFRb0VjcklPc0E4eQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQMnp0VjMxX29PWDY4OVo0LWRfSmRMemlJcWlUNFIzcG9tYjhoQW9Rb2RJYUZSN21ydGtSTGVKRGcxX0ZlOVFoMUo2SldacHdHTE5JU2pUem9seGtrOHRfbExyRzFUUzMzelBZQXhmSTNpSjRJenBGSENpd0Nxa3FuXy1WZ0xtRGczVXppZ1BsZ1ItZW9vQ1RBZmFDTDl0bDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Apple releases test of redesigned Siri AI before iPhone 18 hits stores this week</t>
+          <t>Nvidia's Huang diverges with CEOs of Anthropic, OpenAI on AI safety at Dreamforce</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6343,589 +6347,596 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQQ0FLeUE0dV9EVXFIbDYzVk12ejFrYWNvRDI4aktUUzlTWkFMUWU0TDVieXNNeklhaE5XN2VUNER3ZUdtVWc5d3lHakpNOGVhUHhfV2FOZnVFTW9VZ25MRGMtMVdudm4weDlOb3NuR1hoZTc2cllGcFRxSG5vMi1lY1NDVdIBiAFBVV95cUxNbkUxMGxGN29sWTBjVk5uUGJQNkozUVZjSzZJa3VEazFwcVJjbnNKUThkb3BaRUxoYmJVX04weFhGSm1rYVNoNDBlazdEeHkwNUZ2V1I1VGtZM1RyWlNiSmpPMHdnTzc2eHhaX2FGWk5vN1MtQnpsWDF2anZLMkpLdHFkOGFUbFpS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNamhBSWgtcmZwTVRVOXlnbGZMN2R1bDFlMWEtV21wUXFmUGVoWW5vQWNVbU55OEE0T0lWMUFlMXFZVGdvNmN0TElFUGNkQUlwQ01hU09aUEZIZlBjd0lMbGJMOVJHbmhOSTNRaHU0cXBnNmRVQ2lTb21odDUzOGlRQ1phSTRDUDVucThHQjNncjI1Q1pMOVV0WlotdDVpUdIBowFBVV95cUxNQW5ST21vbGJyUWYzcHVFZFJOZUgzTEJ3TWFkS3Y4Nm9fQ2w3c3puMnJqaFBpbl9CVG5Gd1RSZUVGQmJqLVZaN0dBZ0dOWEZNb3IxMDBtaGhWNGllb29aZERqeGxibHhnakZJRDgxeF9oa1NDSGV2YzYwa3plQ0dhZU43aHJNb1MyUlZRRm1hb1BZRVpZRVF4LUd1OWNQXzJpZFpr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Nvidia  (Tier 1 · 12 stories)</t>
+          <t>Amazon  (Tier 1 · 8 stories)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7.27</v>
+        <v>7.61</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’</t>
+          <t>OpenAI is working with Anthropic, Google on AI safety, Bloomberg News reports</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/nvidia-ceo-jensen-huang-tells-trump-were-not-going-to-let-an-ai-slowdown-happen/</t>
+          <t>https://www.reuters.com/technology/openai-is-working-with-anthropic-google-ai-safety-bloomberg-news-reports-2026-09-15/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6.89</v>
+        <v>7.5</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Puts Trump on Phone While Downplaying AI Risks</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-14/nvidia-ceo-puts-trump-on-speakerphone-while-downplaying-ai-risks</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6.83</v>
+        <v>6.9</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Palantir, Nvidia curb AI model use over data fears, The Information reports</t>
+          <t>OpenAI, Anthropic, Google have been in talks on AI safety for weeks</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/palantir-nvidia-curb-ai-model-use-over-data-fears-information-reports-2026-09-14/</t>
+          <t>https://techcrunch.com/2026/09/15/openai-anthropic-google-have-been-in-talks-on-ai-safety-for-weeks/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6.67</v>
+        <v>6.86</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nvidia CEO Jensen Huang tells Trump ‘we’re not going to let [an AI slowdown] happen’</t>
+          <t>OpenAI Says It’s Working With Anthropic, Google on AI Safety</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/nvidia-ceo-jensen-huang-tells-trump-were-not-going-to-let-an-ai-slowdown-happen/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-15/openai-says-it-s-working-with-anthropic-google-on-ai-safety</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6.51</v>
+        <v>6.37</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>AI infrastructure company Cornelis raises $205M to chip away at Nvidia’s dominance</t>
+          <t>OpenAI, Google, Anthropic discussing collaboration on AI safety issues</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/14/ai-infrastructure-company-cornelis-raises-205m-to-chip-away-at-nvidias-dominance/</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBVX3pnQ1lXY2F2Y3MtZVNTUlZsb2hYeWQxaF9tSTB6aHZRUlR5azdFRkhLOV9EZDZWaHpGUWpqalo2SXVCb1pRQWgyVVNmamsweDJMUzBDeGtUWHBGZ1dRR3p4NHQwNG1CcG51ZWVBM252azBjMTNn0gF8QVVfeXFMUE0zU1ZReFVzWHBKMzliU2ZWbjRMaENCTUwzS3I0TlVwV1Q2dFRkQTNDbU5xelV1MVBWWjZ1NmFJTmNtZEVoc3pXYWRmTXpqUkVoUnlTTHpBbUlOb29aQmExb3NyeTQ2d05ta2VCb1dSaWZLclQ5OUhLSktrbA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Jensen Huang puts Trump on speakerphone onstage to announce robots won’t take over the world</t>
+          <t>Your AI agents' reports and questions have a new inbox, courtesy of AWS</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/995079/president-donald-trump-calls-nvidia-ceo-jensen-huang-all-in-summit</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/15/your-ai-agents-reports-and-questions-have-a-new-inbox-courtesy-of-aws/5296661</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6.11</v>
+        <v>5.95</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Palantir, and others restrict advanced AI model usage over privacy concerns, report claims — 'paranoia' rising over customer intellectual property</t>
+          <t>Your AI agents' reports and questions have a new inbox, courtesy of AWS</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-palantir-and-others-restrict-advanced-ai-model-usage-over-privacy-concerns-report-claims-paranoia-rising-over-customer-intellectual-property</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOc0k4RzNfQ1B5bHdpeUxScUk5OEIzVEtYRHpWeFdaT2pvRzd3SGV1RGhTTW1BZVJuVEJhNU1EcTZGamMxYm9BZTl2VmhXNXNORW9mZ2xCVldnd0U1ZWlhUWVoWi1OMzBHa3JDNXhzZXZNenpZMkY5ZmNld1ExdjkxX1lPN3k2bm1PYjB5Qi1iVWphMWpGT0xEMGd4YmE2Um9pc1NLbXRycDY1MXpUTWViSUFvMERFUVZ0WmY3VnBIc3BzTkFY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6.11</v>
+        <v>5.57</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Palantir, and others restrict advanced AI model usage over privacy concerns, report claims — 'paranoia' rising over customer intellectual property</t>
+          <t>Google อนุญาตให้พนักงานใช้ Claude เป็น AI ช่วยเขียนโค้ดได้แล้ว จากที่ผ่านเน้นใช้ Gemini</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxOTExpN2RwblRJUHlTbmlmMTJDcmRZUUZLS0Nud1pLMmg0NWY4Mi1waUxjLTVVTF9qZGczVWRjX1hMTVNqU2I3ekZXcmtfcVoxTnZ4SmRxYzc1TDFhSWdGMzI0WFRrVVNvVnQwQUZfNHFXWlIwZnRhcWdBeFViUmU1Tm4wUURQbjg3LVpSS1c4Y1plYUNOUFNteUE2R2NtSHFHajJZWUo3aVhfeUZjUHpyNkxUbTZ0N09LYURuRDF6SWNpR2I1ajRiOGptcHRNYXgxZXJkdi1vQm5MNG15NDlwWDZhQ1BoMHhmOHI4YWNoWG1uOVJIX0FZUFZsVlNLQTVacHg1VEp5UnVmNUZOcHRNcERHRk52SlF6VDhpejJ6MEpobzFpWDRxV2ZUbDJRSTQ2anU3dHJYMDVvZw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>AI infrastructure company Cornelis raises $205M to chip away at Nvidia’s dominance</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZlVFSFdPNzRSNnBiMkZZbElkcEkyejJTVUtmbDJUcTU0RlJYNjIwVzYyMWhiemxBUmIycVZEeWlUYWNlMi1IQkxxUXlnVi1DbUxPallBaWxpYnY5RG5EY0dwYU8wcWpyMDU1eS15T29iLV9UOXpiVHdCM3dMRkdjUU9OMllpOGNvYmdVUGZDTy1GUklLTFkxam1Cb2xiYXFyZHhZNmxFbUUtNTRBMXFxNm9uZGRhUQ?oc=5</t>
+          <t>https://www.blognone.com/node/151646</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Samsung backs Nvidia AI chip rival in $230 million funding round as GPU alternatives boom</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>cnbc.com</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1ydVhNMHFzRmctZVp2Sjlsd0tXMm5pNTN6UGoyczRpZlBUTjhITy1ybEQ4SDh0MWNZb09ldElzWEZWS3BBTVZwdnlzQXRBM0FFSzEzOXNCVlJneEFydmdXQWc1MVVCZlZRN1lyWG1KM3U0OXd4aUHSAXtBVV95cUxQSWlJd0JfRlNxTVIwNjEyaG5JQWZwYTRic0lfNFVha09oLVF0UGlyemVpOW1USGN5SlpiWXRiVUxSaVllTnZoaXhGZ3dpR0lkUUlIYTVUWkxTaDJYOUYzYXktbnVRNmgzeDJiWFNLWE5icW5UZTRxVzU2UXc?oc=5</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Alphabet  (Tier 1 · 7 stories)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Jensen Huang puts Trump on speakerphone onstage to announce robots won’t take over the world</t>
+          <t>Introducing Gemini 3.8 Live and 3.8 Live Extended Thinking</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVmh4V2R2c2ZESDlkeEo2bXU5dThKSmxSVmRXaE5FelZMMzNNYVdMeTNMVFhWb3NZT01vTUM3TFdLNW5LYTUzZzhxY3o1bGduZ3ZzTVBoNlVHTDRzWmhtdmJuQ2tNZXhVLVo5TG54VkZhVHJBd1ZJMGQ2cVl6RE51eHo5ZzdLNmF2cGdXQU15bHp4V3F4YUd4Q1RzZkxHTDVfb2hDUG1R?oc=5</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/gemini-3-8-live-gemini-3-8-live-extended-thinking/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.76</v>
+        <v>6.23</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Solo dev enables running CUDA on AMD hardware in Windows, getting multiple CUDA libraries running on a gaming Radeon RX 9060 XT GPU in Windows —  CUDA-exclusive workloads on AMD hardware in Windows possible without virtualization or dual-booting</t>
+          <t>Build real-time voice applications with Gemini 3.8 Live and 3.5 Transcribe</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpu-drivers/solo-developer-wires-zluda-to-amds-hip-getting-multiple-cuda-libraries-running-on-a-radeon-rx-9060-xt-in-windows-cuda-exclusive-workloads-on-amd-hardware-in-windows-is-possible-without-virtualization-or-dual-booting</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxORklOLTI2REdZOWdBZFJmbEg1S3J3ejNuTGhGMVBlWmVXeGtZRkxXcW1zSUtOVnR5eWd2aG9ibWdmd2xUTmllTDhrZWF2UXpRb1V1SWUzNVIzOEJrZEdNYVYyM1NTaS1oMmZaWWZyNEpSRUowR1dsd2otTV9UQkdaZVpKMGwwSkxGeG11U1J1M1RnVEF4S0dCbjNMRUpKcDNqdm9wWDl5THFKVTluOEp6RGVfNTM?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Ex-Google DeepMind researcher adds to warnings that AI could 'kill all humans'</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPcFU5RG1vWUx4LW5tTnVlWmxVaExUb1JiYks2N01JbTJFWl9NY3ZFRUpxaGc3LURuZ2xST2VkZ1hFNFROcjM4U0RPeGFqczRCamt4Z3FqWFBteC1seWxSdUJLRE9HUDlqeGxlczE4M0JJTEp1WC1VWGJXcmpJUjgzU0g1OGxHN0N6RWZtTjJBNktPTUJqU2Y0N2J2QTR1ZHRjQTNQZVk1UU4weXRvZGJvMDRYZkh0VkNvMXQtVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 6 stories)</t>
+      <c r="A32" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>15 organizations transforming public service with AI</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>blog.google</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNTDdTMXVnbU93WUZmci14bXYxcnp4b2xBNGVrLXJBRTZpeGpObHRrN3QtWFRyd3dJLVhaSHIxVHFxV1dROXU5UmRwYmlBSUVrWV9VVDRWbTBjTllBM2FMdnVwTkVqZkZmT2drWVhfd3NfR2taVl9oNVliNHlRZk5vUlcwUDl2bnQ3b0liRjF4VEVJWHVidnUwWF8xQWh1WUVLOW1UX29EdjE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7.12</v>
+        <v>5.55</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts code of conduct to keep its AI under human control</t>
+          <t>AI for everyone in every language</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/microsoft-drafts-code-conduct-keep-its-ai-under-human-control-2026-09-14/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1GdGtMM2l2cGYxcG1pQjBGWWc2VlNKQUkxWThLTUNJOWpBcVdIZUZMdDVkOFJNYXVNaTFPZDc5Mm84SjJBbG1wajBpa1BuQjdGSmVjb1dMQU1VbDcweDNiSnFFMzN2NkNQWjhGUHVoVUpWQTFyaUtuS0tsWUFnR28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6.4</v>
+        <v>5.55</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts feel-good AI model guidelines and wants your input</t>
+          <t>Ask a Scientist: How can researchers use AI to spot a wildfire?</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/15/microsoft-drafts-feel-good-ai-model-guidelines-and-wants-your-input/5296431</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNbU5YTGxDZXhYVkxKdGctZVh1SVlEUWd5STg4R09Cel9uZDJ4YnVSSTB1VnQxT2dDcUVjTGxidlZUV010em5qOXQ0Y2dla2FOREhlS0NPYmxocHIwVzN4cTJNMExkQVREMUY5SFRTNU5nV1JvVDZEc2RBbXNqNERXVFpMX3Vpa29VSmF3YUtmWFBXc0hpczhuLTR2MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6.4</v>
+        <v>5.54</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Microsoft drafts feel-good AI model guidelines and wants your input</t>
+          <t>Building AI to accelerate science and improve lives</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNR1hWNWpOWE9OQkxlbEhtSUUtYUJlZmE3MFA1TzRhbzFxU3lVTGs5cHI3N1UwdVR3LXJjdG9sVmpLODhJeGJvSEw4VUZWVlhXdnMwNWk4N1ljYnpKZ2FyZzZNdzJ1cVdkSVFJaHFVOVVHYjcyU2NBd0o0VmJ4UFRNenIxZVVpQ1c1RFYwYU4zeG1DUElCSlpuX0pBTFdxZTkwVm9oTVZyMHlueWtpZ3FKaGtLNzNWMEcyUThUaUdQYmRMUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft sets limits for future AI models as industry throttles frontier development</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>cnbc.com</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQSlJYLXlYazNYam85R0djdHlHOENQdGhCZkdQY1l0LTdmYnNMS1ZocFBpUl9wS2ZqamZyWXQzcXYwaW9vdkRMbEJ0ZFFFb3dydHNIdFBfbXNBVjJrdlB2NlNVcVBKMEdTWjVzd1VUeGtXcnJqUS1vMTI1WVRlWnZFREsyMnhiZ9IBiwFBVV95cUxONVNwbzBjUWFaOXRVblJ1ejIyRVlObEdPNW16aEVPaG9VRWxydExnZ2dvSzROWGprTTdYaG0wbEJ3aDJUb1RuVENIVTdySDVvTTBCR19YakpPTG5JeHRiYmRPY1pub0lBTFBvV01vS3lUeFpSUUp6U3QxdW9uZjRQdTY0b2ZYNUszbGtZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPcU1Eb1R4ZGdSYlVlV3ctdG5tVVpEYlFNWjFxY1lJSlZNNW1laFhXUDI0aFZhSjlxWkhPN3JUNy1xQm56WVFOaFJiWFotMGtFNEo5YTVMSnBNTlRoekJHellCS0hqeXA3cWZnYkc2U2NtVjBDblFlU1JvVVlxdzc2dzNpR1pKSUM4MVNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft’s new AI ‘code of conduct’ tells models not to hack systems or trick humans</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/09/14/microsofts-new-ai-code-of-conduct-tells-models-not-to-hack-systems-or-trick-humans/</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 6 stories)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.56</v>
+        <v>7.03</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s new AI ‘code of conduct’ tells models not to hack systems or trick humans</t>
+          <t>Meta launches subscriptions with enhanced AI features</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZ0VkdmR6NXZpVENub3FWamRWSEVmQ0tydGQ3UUxVaUtVMEUzSEZfZTZMdHM5V0I0eHVMa1JzWFdkSVlPcWt4N2N5d0JNcFFvcEphSmpRRTM5cUk1VS1vRWtud3NTUUtWMElEZ19LUHlhUVF0SUVxRzBPWkdHUTVveWoxbG5rRVFZTlRQWm43NHA3S0paQnV1VFIxdFpYdVVaN0hmMm45OXdfMkR5QmhHSlRpQVlVWjJC?oc=5</t>
+          <t>https://www.reuters.com/business/meta-launches-subscriptions-with-enhanced-ai-features-2026-09-15/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Meta launches subscriptions with enhanced AI features</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>channelnewsasia.com</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.channelnewsasia.com/business/meta-launches-subscriptions-enhanced-ai-features-6386626</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Alphabet  (Tier 1 · 3 stories)</t>
+      <c r="A40" s="2" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Meta&amp;#8217;s new One subscriptions put a price on social media and AI</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/995453/meta-one-subscriptions-ai</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7.08</v>
+        <v>6.02</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Apple อัปเดต iOS 27, iPadOS 27, macOS 27 Golden Gate, watchOS 27 ให้ผู้ใช้งานทั่วไปแล้ววันนี้</t>
+          <t>Meta expands subscription push with new AI-focused plans</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151641</t>
+          <t>https://techcrunch.com/2026/09/15/meta-expands-subscription-push-with-new-ai-focused-plans/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6.35</v>
+        <v>5.92</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>You can use Gemini to help you organize your files on Google Drive</t>
+          <t>Meta now lets AI agents handle the boring parts of WhatsApp Business setup</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2253054/use-gemini-help-you-organize-files-google-drive/</t>
+          <t>https://techcrunch.com/2026/09/15/meta-now-lets-ai-agents-handle-the-boring-parts-of-whatsapp-business-setup/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>5.99</v>
+        <v>5.92</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Watch astronaut Christina Koch and Google’s James Manyika discuss space, technology, and discovery.</t>
+          <t>Meta now lets AI agents handle the boring parts of WhatsApp Business setup</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQTXZLY203YWY3WlJCczgxaHhsdHdRS3k3MTJYUU1fZFhITWE1YTA4V0xpRlJxM3pzcllUeTdiWUc5aWU4TGt5ZzE2SHJaRGY4TVpjTmtMR1NUazV2X21XbXBxUWJUWUxrQi0tYUVoTmh3MlBCbFpxdXB0X0E3UE92d3dUWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcF8yQlQ5WlpPaXc5QUlwZEVLTVpPdThDemRORmJfQ0FkbnNNeF91T0ZZRWtwQ214bldVelM4Si1lSUV2WW85NUVkLUo4cUZKZUcwQXZDM1ktbHpnbGFNcWtXQmY0MEZNZFR1ZFJYZEphbHZCcGRZbkRNSGxtempiNklKZTNUQlV1eVloVFpKdjFHYUhjekNtMGtrazFrOWtLdE9TaFlSQWw4ZUVsSEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Tesla  (Tier 1 · 3 stories)</t>
+          <t>Microsoft  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7.32</v>
+        <v>6.38</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk’s X Corp and SpaceXAI drop antitrust lawsuit against Apple</t>
+          <t>Docusign scales AI on Azure, processes 1M+ agreements daily with eightfold throughput</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>https://www.aljazeera.com/news/2026/9/14/elon-musks-x-corp-and-spacexai-drop-antitrust-lawsuit-against-apple</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPbjZ6Q2liMk43WTRIbVRoa3ZtVjYzTHpFR2xCZGUwOGhTSldTY2VLRWdHNzVNSllYeEV4ZzJxblA5ZC04YmZuWWVJVXJjUmZvZU5CVXBBODZfLVgxbUZMMVlNMnhaNGZTM05XbzU2UmNxYms4UXB6Qm8zaTh2eXBwQkYtTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7.1</v>
+        <v>5.86</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Is Big Tech’s AI slowdown a safety pact or a cartel?</t>
+          <t>The vulnpocalypse rains iBugs down on Apple with record-setting number of patches</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/995186/is-big-techs-ai-slowdown-a-safety-pact-or-a-cartel</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Elon Musk's X Corp and SpaceXAI just moved to dismiss their lawsuit against Apple</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2257929/elon-musk-x-corp-and-spacexai-just-moved-to-dismiss-their-lawsuit-against-apple/</t>
+          <t>https://www.theregister.com/security/2026/09/15/the-vulnpocalypse-rains-ibugs-down-on-apple-with-record-setting-number-of-patches/5296679</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Oracle  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 2 stories)</t>
+      <c r="A50" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Oracle Invests in More Than 1.7 GW of Carbon-Free Electricity to Support AI Growth and Strengthen the Texas Grid</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>oracle.com</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOTHJpTmc2NGtpY1E2b3g5NVFfeDRKeGlCZ01EVHR1V3I0SWdONGFUSnk4LXg4bjhfMG42TklLOUZLZFNNbXNsTmQ3ZGJKeVZsRzBCakt1dWprRGJTdkFsRXlHTHhibVNMM0hhRHp1dnlZbkRtd0l3TWpPZllzY0VFc0hJTVhzN05PTENNbUpleEFSam5FUFFuNm42QjNJcmhNZDI5bkU2eTFfUEEwdFZMNmVodEVQdnAxaWJXb3hFOWI1VU9NTGgxbUVwNnpFVUpTX3BvT0VmLUdSYzdKczB1MzB5WTM1bUpfQ0pxSUw5UXJacEttQVFISw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>5.97</v>
+        <v>5.7</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Oracle celebrates banner quarter with another round of layoffs</t>
+          <t>Oracle Releases Java 27 and Strengthens Post-Quantum Cryptography Support</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>oracle.com</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/databases/2026/09/14/oracle-celebrates-banner-quarter-with-another-round-of-layoffs/5296395</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Oracle celebrates banner quarter with another round of layoffs</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPRWVpcGZwSU9rV1ZxbkxtQ0J5UVgyeWg5bE1DUDNJSmh3UWJESzFpdThnaGJ2dUZlZ2hNckJKNVVvN1VCQjBKaEZuMnNtbkZfci10ZGlycmtuZ3NFaE1sYi03UnNWS2JSang5SzlVeTZsYU5URlBNUkJuUjA2QXVMUnh3Y0lBYjlvcGpqQWpuSmlhYWMtTnJSZkVzUkdSZjhpeXgxMTMzQXk1X3NwZkJrZFZpNzBUSi1PWlNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQVG1IX1NqcTZpZTQ4ZUJRYjdzdUxVU3NSMTVsWnlYQ1NfX3dVUkV0U3Y0UTVwanJwcXFqREVDZ253WGVrRDJ5OTBoMXg4dlQ1cFJlRDVVZDBQbDZqWkZrZVp5bE9zakZ5UzF1d0RhenlDNmJXdjZaRFdkNG9NRnl2d2lTcXNBT2xXRG41bzM2bjZxekhsZERsSGcxYUh6MWt3cnM3YWMzOXdCeEZYRkY1S281RlRCU2psb3BPbXVwalNuQllq?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>AMD  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Meta Platforms  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A54" s="2" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>AMD Brings Local AI to Autodesk University 2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>amd.com</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPNTJDNnpRVVlYOEVmUlZNM29FTlNReGlTQ0MwU0N1LW9iU3BTZDZzX3Z4WFhQRkJaYU9NSW1nNG1PYlI4Rk9zeHEzR2xUN3NhVTdQZl84ZHVqcnNqamxXSHoyWHVRYzZ1RmROTkptcl8yOC1aYm9OQ2lyelQzUm1nUnVFSFlYWENZQVNhQzJfaw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 1 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
         <v>5.6</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>How to use Meta Display glasses while driving with the Audio Only feature</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2255133/meta-display-glasses-audio-only-driving-detection-feature/</t>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>The AI graveyard: a running list of projects and startups that didn’t make it</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/15/the-ai-graveyard-a-running-list-of-projects-and-startups-that-didnt-make-it/</t>
         </is>
       </c>
     </row>
@@ -6952,25 +6963,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6.04</v>
+        <v>6.13</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>apnews.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Spain gets its first taste of AI-aided cyber attack</t>
+          <t>The king and AI: UK monarch Charles meets artificial intelligence leaders as safety concerns swirl</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>cyber-crime Data protection chiefs call for 'immediate review' of data protection models Spain’s data protection agency (AEPD) has reported the country’s first-ever personal data breach caused by the actions of an autonomous AI agent. Francisco Pérez Bes, president and deputy of the AEPD, said in a Monday blog post that an individual deployed an AI agent that used a “known large language model (LL</t>
+          <t xml:space="preserve">0 seconds of 1 minute, 30 secondsVolume 0% 1 of 6 | King Charles III urged tech leaders from OpenAI, Anthropic, Google DeepMind, and Nvidia at a Scotland summit to ensure artificial intelligence remains under human control. Warning that AI’s rapid pace is both intriguing and deeply concerning, the King called on executives to align innovation with his “philosophy of Harmony” to protect people and </t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>ai, large language model, llm, ai agent, autonomous</t>
+          <t>ai, artificial intelligence</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 13:56:55 +0200</t>
+          <t>Thu, 17 Sep 2026 14:57:00 GMT</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,16 +577,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/cyber-crime/2026/09/16/spain-gets-its-first-taste-of-ai-aided-cyber-attack/5296844</t>
+          <t>https://apnews.com/article/britain-king-charles-ai-summit-0765bee1e338cf65846a046fb5825a4a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.67</v>
+        <v>5.2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Anthropic policy chief says AI companies can't be expected to operate on 'honor code'</t>
+          <t>PrismML hopes its tiny LLM will change how we all use AI</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>TECH Anthropic policy chief says AI companies can’t be expected to operate on ‘honor code’ PUBLISHED WED, SEP 16 20262:35 PM EDTUPDATED 5 HOURS AGO Ashley Capoot @/IN/ASHLEY-CAPOOT/ KEY POINTS Sarah Heck, Anthropic’s head of public policy, offered her perspectives on AI safety as the debate about how to regulate model development intensifies. “We want to work with government to figure out what mak</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: TechCrunch, AI generated AI PrismML hopes its tiny LLM will change how we all use AI Julie Bort 3:34 PM PDT · September 17, 2026 If AI lab PrismML isn’t on your radar yet, it should be — not because it’s raised gobs of money (it hasn’t</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>ai, llm</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 18:35:21 GMT</t>
+          <t>Thu, 17 Sep 2026 22:34:09 +0000</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,16 +628,16 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/09/16/anthropic-policy-chief-says-ai-companies-cant-operate-on-honor-code.html</t>
+          <t>https://techcrunch.com/2026/09/17/prismml-hopes-its-tiny-llm-could-change-how-we-all-use-ai/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>TypeSafe AI เปิดตัว Jev ปัญญาประดิษฐ์ช่วยตัดสินใจ ทำงานเร็ว ราคาถูก</t>
+          <t>PrismML hopes its tiny LLM will change how we all use AI</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>TypeSafe AI ที่ร่วมก่อตั้งโดย Diogo Almeida อดีตทีมงาน OpenAI เปิดตัว Jev (ตั้งชื่อตามนักเศรษฐศาสตร์ William Stanley Jevons) โมเดลปัญญาประดิษฐ์แบบใหม่ที่ชื่อว่า System One เป็นโมเดลที่ออกแบบมาเพื่อการ "ตัดสินใจ" โดยเฉพาะ ทำให้มีข้อจำกัดการใช้งาน แต่มีจุดเด่นที่ราคาค่าใช้งานถูกมาก และความเร็วสูง Jev รับคำถามเป็นภาษาธรรมชาติเหมือน LLM แต่จำกัดรูปแบบการตอบ เหลือเพียงการเลือกตัวเลือก (choice), ให้คะแน</t>
+          <t xml:space="preserve">If AI lab PrismML isn’t on your radar yet, it should be — not because it’s raised gobs of money (it hasn’t yet, just a $22.25 million seed round), but because of the technical minds involved and the potentially industry-changing tech it’s developing. PrismML is betting that capable, high-performing, reasoning large language models don’t, in fact, have to be large. It is making reasoning models so </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, llm, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>ai, llm</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>12.1</v>
+        <v>2.4</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 12:58:25 +0000</t>
+          <t>Thu, 17 Sep 2026 22:34:09 GMT</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,16 +679,16 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151656</t>
+          <t>https://techcrunch.com/2026/09/17/prismml-hopes-its-tiny-llm-could-change-how-we-all-use-ai/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -697,46 +697,46 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Research centre, AI company vandalized ahead of Montreal artificial intelligence summit</t>
+          <t>Apple eyes Nvidia NVLink to power its new custom M8 Ultra AI servers — historically bitter rivals reportedly team up for 2029 data center push</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Research centre, AI company vandalized ahead of Montreal artificial intelligence summit    CBC</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ai, artificial intelligence</t>
+          <t>ai, nvidia, semiconductor, fab, data center</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3.9</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 21:09:31 GMT</t>
+          <t>Thu, 17 Sep 2026 11:00:00 +0000</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNMm16V2p5YXd4VUdXOXhmOHZyUjZ2MHFqNUtTaVJoTzZiVG5uRHdiTnNZZk9Ld2IwMHZUUXBpQ29UUjRmaXBaelBmbm1tWHlCWTlrZ2pBcGVJWkFtVk9vRGlQdUVHNmhXbVc0dmVSZUZjMDA3dnl6UktHYXQ0eTFCUWxnamtnR3NRdmNj?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/apple-eyes-nvidia-nvlink-to-power-its-new-custom-m8-ultra-ai-servers-historically-bitter-rivals-reportedly-team-up-for-2029-data-center-push</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Claude comes for Gemini with its own take on Docs and Slides</t>
+          <t>Anthropic says Claude 'leads' 26 percent of its AI R&amp;D work</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Tech Claude comes for Gemini with its own take on Docs and Slides ﻿Y</t>
+          <t>The company shared the stat alongside three measurements that help communicate the pace of AI development. Cheng Xin/Getty Images Add Engadget on Google: Preferred Source Google Discover Anthropic — well, specifically CEO Dario Amodei — has a lot to say about AI safety in the aftermath of OpenAI's disclosure that its AI agents hacked Hugging Face , and it's already revealed some interesting detail</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, gemini, ai</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8.6</v>
+        <v>2.5</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:30:00-04:00</t>
+          <t>Thu, 17 Sep 2026 22:30:01 +0000</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,16 +781,16 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/996234/anthropic-one-claude-cowork-docs-slides</t>
+          <t>https://www.engadget.com/2261909/anthropic-says-claude-leads-26-percent-of-its-ai-research-and-development/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -799,46 +799,46 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Snap is launching a new Specs AI tool, and it’s coming to iOS and Mac</t>
+          <t>AI infrastructure provider Crusoe valued at $30.9 billion in latest funding round</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Snap is launching a new Specs AI tool, and it’s coming to iOS a</t>
+          <t>AI infrastructure provider Crusoe valued at $30.9 billion in latest funding round    Reuters</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>gemini, ai, ai assistant</t>
+          <t>ai, ai infrastructure</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T19:40:00-04:00</t>
+          <t>Thu, 17 Sep 2026 19:26:09 GMT</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996078/snap-specs-intelligence-ai-agent-ios-mac</t>
+          <t>https://www.reuters.com/business/ai-infrastructure-provider-crusoe-valued-309-billion-latest-funding-round-2026-09-17/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Nvidia goes green to keep grid capacity from zapping its revenues</t>
+          <t>OpenAI caught its models leaving notes to successors to hide bad behavior</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>SYSTEMS GPUzilla woos neoclouds into another walled garden, promising smarter, more efficient, and profitable bit barns Tobias Mann Tobias Mann SYSTEMS EDITOR Published wed 16 Sep 2026 // 22:37 UTC READ MORE AWS says wartime damage means some Middle East cloud resources are gone for good 12 hours ago Spain gets its first taste of AI-aided cyber attack 12 hours ago AI networking startups race to re</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Getty Images AI OpenAI caught its models leaving notes to successors to hide bad behavior Rebecca Bellan 1:34 PM PDT · September 17, 2026 OpenAI caught something unusual while training its latest model, GPT-5.6 Sol: It began leaving in</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, blackwell</t>
+          <t>openai, gpt, ai</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 23:37:05 +0200</t>
+          <t>Thu, 17 Sep 2026 20:34:24 +0000</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/16/nvidia-goes-green-to-keep-grid-capacity-from-zapping-its-revenues/5296984</t>
+          <t>https://techcrunch.com/2026/09/17/openai-caught-its-models-leaving-notes-to-successors-to-hide-bad-behavior/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.9</v>
+        <v>4.76</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,17 +901,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Anthropic and OpenAI want to embed safety evaluators. Will they really be independent?</t>
+          <t>The AI Superintelligence Slowdown</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Samyukta Lakshmi/Bloomberg / Getty Images AI Anthropic and OpenAI want to embed safety evaluators. Will they really be independent? Rebecca Bellan 2:07 PM PDT · September 16, 2026 In a lengthy essay published over the weekend, Anthropi</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI Updated Sep 17, 2026, 9:23 PM UTC The AI Superintelligence Slowdown by Se</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -920,11 +920,11 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 21:07:24 +0000</t>
+          <t>2026-09-17T15:28:24-04:00</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,16 +934,16 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/anthropic-and-openai-want-to-embed-safety-evaluators-will-they-really-be-independent/</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/996923/ai-safety-slow-openai-anthropic</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.79</v>
+        <v>4.71</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -952,30 +952,30 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Jensen Huang thinks China will develop its own advanced lithography chipmaking tools by 2030 — Nvidia CEO says achievement of that capability 'is just a matter of time'</t>
+          <t>Claude Code relaunches Projects to manage multiple AI agents in the cloud</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Tech Claude Code relaunches Projects to manage multiple AI agents in</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>nvidia, semiconductor, fab</t>
+          <t>claude, grok, ai</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>13.6</v>
+        <v>6</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 11:30:00 +0000</t>
+          <t>2026-09-17T14:58:05-04:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,16 +985,16 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/jensen-huang-thinks-china-will-develop-its-own-advanced-lithography-systems-by-2030-nvidia-ceo-says-achievement-of-that-capability-is-just-a-matter-of-time</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/997134/anthropic-claude-code-projects</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.77</v>
+        <v>4.52</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>'Defeated' GPT-6 Astra model spent several hours just farming potatoes after being blown up by a Creeper in Minecraft — OpenAI offering gets further than any other AI system in 141-hour test</t>
+          <t>Claude Code’s revised projects adds AI orchestration, but local developers must wait</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>Claude Code has always had projects, in the sense that a given directory is declared as the root for source code. I keep each of the apps I’m developing in separate directories, and I’ve built up a complex orchestration and management workflow that allows certain messages to be exchanged between these directories. Beyond that, they’re isolated code structures. Also: After the vibe-coding rush come</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>openai, gpt, ai</t>
+          <t>claude, ai, ai coding</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>13.8</v>
+        <v>8</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 11:15:00 +0000</t>
+          <t>2026-09-17T17:00:00Z</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,16 +1036,16 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/defeated-gpt-6-astra-model-spent-several-hours-just-farming-potatoes-after-being-blown-up-by-a-creeper-in-minecraft-openai-offering-gets-further-than-any-other-ai-system-in-141-hour-test</t>
+          <t>https://www.zdnet.com/innovation/claude-code-revised-projects-threads/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.77</v>
+        <v>4.4</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>'Defeated' GPT-6 Astra model spent several hours just farming potatoes after being blown up by a Creeper in Minecraft — OpenAI offering gets further than any other AI system in 141-hour test</t>
+          <t>Crusoe raises $3.9B to build massive data centers and small modular ‘AI factories’</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Tech Industry Artificial Intelligence 'Defeated' GPT-6 Astra model spent several hours just farming potatoes after being blown up by a Creeper in Minecraft — OpenAI offering gets further than any other AI system in 141-hour test News By Stephen Warwick Published 14 hours ago They're just like us... (Image credit: Vals AI) Share this article 0 Join the conversation Follow us Add us as a preferred s</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Brett Coomer/Houston Chronicle / Getty Images AI Crusoe raises $3.9B to build massive data centers and small modular ‘AI factories’ Marina Temkin 4:25 PM PDT · September 17, 2026 Data center developer Crusoe said Thursday it raised $3.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>openai, gpt, ai</t>
+          <t>ai, data center</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>13.8</v>
+        <v>1.6</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 11:15:00 GMT</t>
+          <t>Thu, 17 Sep 2026 23:25:52 +0000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,16 +1087,16 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/defeated-gpt-6-astra-model-spent-several-hours-just-farming-potatoes-after-being-blown-up-by-a-creeper-in-minecraft-openai-offering-gets-further-than-any-other-ai-system-in-141-hour-test</t>
+          <t>https://techcrunch.com/2026/09/17/crusoe-raises-3-9b-to-build-massive-data-centers-and-small-modular-ai-factories/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Anthropic merges Claude chat and Cowork in one interface</t>
+          <t>Google DeepMind launches institute to widen the AGI debate</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Anthropic AI Anthropic merges Claude chat and Cowork in one interface Ivan Mehta 9:30 AM PDT · September 16, 2026 Anthropic is merging its front end for Claude chat and Cowork, making it less confusing for people to decide which tab to</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Carol Yepes / Getty Images AI Google DeepMind launches institute to widen the AGI debate Aditya Mehta 4:21 PM PDT · September 17, 2026 Google and Google DeepMind researchers launched the DeepMind Institute on Wednesday to advance the c</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>deepmind, agi</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:30:00 +0000</t>
+          <t>Thu, 17 Sep 2026 23:21:17 +0000</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,16 +1138,16 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/anthropic-merges-claude-chat-and-cowork-in-one-interface/</t>
+          <t>https://techcrunch.com/2026/09/17/google-deepmind-launches-institute-to-widen-the-agi-debate/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Anthropic merges Claude chat and Cowork into one</t>
+          <t>Google's revamped CC is an AI agent for families and groups</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>From Claude to Cowork and back again – plus, Anthropic’s all-new Claude Docs.</t>
+          <t>CC gives an AI agent its own Google account in your family or group and sends all members a daily briefing.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>8.6</v>
+        <v>2.1</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T16:30:44Z</t>
+          <t>Thu, 17 Sep 2026 22:55:08 +0000</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,16 +1189,16 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/innovation/claude-chat-absorbs-cowork-anthropic/</t>
+          <t>https://www.engadget.com/2261924/google-cc-is-an-ai-agent-for-families-and-groups/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.52</v>
+        <v>4.25</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -1207,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Research centre, AI company vandalized ahead of Montreal artificial intelligence summit</t>
+          <t>Huawei plans Q1 2027 launch of new AI chip as it takes on Nvidia</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Research centre, AI company vandalized ahead of Montreal artificial intelligence summit    CBC</t>
+          <t>Huawei plans Q1 2027 launch of new AI chip as it takes on Nvidia    TechCrunch</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ai, artificial intelligence</t>
+          <t>ai, nvidia, chip</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 14:57:51 GMT</t>
+          <t>Thu, 17 Sep 2026 14:06:14 GMT</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,13 +1240,13 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9xc1dHWlBRX0o1c0hyck5MNWhTcDZLN0U5TzRnTlQyRTFndkRmWVROUHFkbUtfQWVCcnZSdHpWVzU0WTRyeU5FVVFSQnZ6ZjVwYWZBNlpoQUdZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQQUZ5YWdUdGV1eTlQZkg2WktxODk3S0lLelNWZDdtVjY0YUgySWtGWGdJZTRlQ0hfUUVOQXFORXpsMnJsT1dxWHZEcWI0ZlROU05Ebmtqb2VUTDl5VVc2al9Va05CTERFNDhTd1A5N3dNMzA1c19TZjFDX2NRcFFCY01nV1NrTFYyVTdVRm52T0dsY1g0enpNei0tUWhCeHVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.51</v>
+        <v>4.24</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Your AI agents can now control your Google Home devices</t>
+          <t>Is the AI safety debate about safety or control?</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Google is launching early access to a new MCP server for Google Home, allowing AI agents like Claude, ChatGPT, and others to control connected devices, review camera summaries, and access smart home activity using natural language.</t>
+          <t>Not everyone agrees with Amodei's call for globally coordinated action for AI safety.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>claude, chatgpt, ai</t>
+          <t>ai, ai safety</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>8.1</v>
+        <v>4.7</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 17:00:00 +0000</t>
+          <t>Thu, 17 Sep 2026 20:19:37 +0000</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1291,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/your-ai-agents-can-now-control-your-google-home-devices/</t>
+          <t>https://techcrunch.com/2026/09/17/is-the-ai-safety-debate-about-safety-or-control/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.51</v>
+        <v>4.24</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1314,26 +1314,26 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Google will now let any AI agent run your smart home</t>
+          <t>Microsoft AI CEO says AI threats are real, and Anthropic is making it worse</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Google is inviting third-party agents, including Claude and Open Claw, into Google Home. | Photo by Jennifer Pattison Tuohy / The Verge	 
- Google is opening up its smart home to AI agents, letting tools like Claude and Open Claw access and control your connected devices and analyze your home's dat</t>
+          <t>Today, I’m talking with Mustafa Suleyman, the CEO of Microsoft AI. As you’re no doubt aware, the biggest story in tech right now is the spiraling debate about AI safety and regulation.  
+ It should come as no surprise that Mustafa has strong opinions on how AI should be built and regulated. Microso</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>claude, ai, ai agent</t>
+          <t>anthropic, ai, ai safety</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T13:00:00-04:00</t>
+          <t>2026-09-17T10:00:00-04:00</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1343,16 +1343,16 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996310/google-home-mcp-integration-agentic-ai-smart-home-price-release-date</t>
+          <t>https://www.theverge.com/podcast/996412/microsoft-ai-ceo-mustafa-suleyman-regulation-safety-anthropic-claude</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -1361,30 +1361,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>spectrum.ieee.org</t>
+          <t>aljazeera.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Rethinking Robot Safety in the Age of AI</t>
+          <t>The UK’s King Charles warns AI leaders of ‘existential dangers’</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This article is brought to you by  VicOne .   Robot safety has traditionally asked: Can a machine remain safe when something goes wrong? Physical AI raises a harder question: Can a machine remain safe when an attacker changes what it sees, decides, or does even when nothing appears to have failed?  </t>
+          <t>The UK’s King Charles warns AI leaders of ‘existential dangers’    Al Jazeera</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ai, multimodal, robotics</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:51:02 +0000</t>
+          <t>Thu, 17 Sep 2026 17:47:25 GMT</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1394,13 +1394,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://spectrum.ieee.org/physical-ai-robot-cybersecurity-vicone</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPTWpEVWFyNGxRVzVfcmNfbzl2cV9YVWxJZWxYcm9saTJhbmFyYWJKVklUZEV0NDRHQVBpWUhjOVVfV2hqR2UxSnlYSV9UMWJ4THM4a3hpcVNoQWdad0pCZVY1T21VSURXZWNzbW9zWlBpVzYwLUZjWll3TFo0d0M3cGxxeG8zRE54ajZuQjZ2TzYtbTBTT2VXLUp6OUR0WU5BT0Q40gGoAUFVX3lxTE1mczNIXzVOQzFvS1pOSHJ2NnBYRVM0X2JHQWt2Z0JpTXFEOWxfY051aFQ1cjJ5NldwR2EzMklPaGJLRkpkN1JkVjJZOXpLSjlvLUIwdXhhM3Uza3dDNEFIU3J6eFNvV3hYbmJzOEZwZVd4RlBkdHUzdjI0RG12WExWdTEzRkhmcDJqQWdWTGlRaWhMb0FYN0RJN0RzTTJib2Qwb1NCd1hhbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.4</v>
+        <v>4.19</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Al Gore has a surprisingly calm take on the AI data center backlash</t>
+          <t>Microsoft exec called AI scraping ‘the largest theft of labor in human history,’ new unredacted filings reveal</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>In an interview with TechCrunch, Al Gore suggested he isn't losing sleep over AI data center emissions — he's more worried about the AI industry's own warnings about where the technology is headed.</t>
+          <t>Newly unsealed court filings show Microsoft privately called OpenAI's data practices "theft" while both companies scraped paywalled Times content, built datasets from it, and warned internally it would gut publishers.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ai, data center</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 23:43:09 +0000</t>
+          <t>Thu, 17 Sep 2026 19:46:08 +0000</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1445,16 +1445,16 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/al-gore-has-a-surprisingly-calm-take-on-the-ai-data-center-backlash/</t>
+          <t>https://techcrunch.com/2026/09/17/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history-new-unredacted-filings-reveal/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.4</v>
+        <v>4.19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -1463,30 +1463,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Snap introduces a standalone AI assistant, Specs Intelligence</t>
+          <t>King Charles warns tech leaders of 'existential dangers' from AI</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>The new assistant works with the company's new AR glasses, but will also have its own mobile and desktop apps.</t>
+          <t>King Charles warns tech leaders of 'existential dangers' from AI    Reuters</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai, ai assistant</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 23:40:00 +0000</t>
+          <t>Thu, 17 Sep 2026 17:40:59 GMT</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1496,13 +1496,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2260736/snap-introduces-a-standalone-ai-assistant-specs-intelligence/</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPdFdPV3JrbjNYMUd3RXlUY3NwOU5RMTVheVM2eHRUQ2VFWnBVU2w2SnFqR05iaHBiZzE5MHlyc1ZhX1NSeWxHMmNLMEx4YkxBQjVZY1A4MllpU19lM0c5RHhnV3JTRkQzWGlDME1Cam9WdlVzTTVNclhxZm90akpuUHFkeW9INXdGbmdiUTBTNHBnZEVSNmxtRDNLUWNPQTh4N05qVmh4c01JUWM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.36</v>
+        <v>4.14</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1514,30 +1514,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Developer vibe codes a tool to let Nvidia RTX 50-series laptop owners crank up their power limits — can juice RTX 5090 mobile GPU to 225W</t>
+          <t>AI model watermarking changes agent behavior</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
+          <t>Watermarks that European law requires be added to AI-generated content to establish provenance may come at a cost. According to Lasso Security, AI model watermarking changes how AI agents handle tools and safety refusals. The altered behavior isn't necessarily worse but can be, particularly under ad</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>nvidia, gpu, amd</t>
+          <t>deepmind, ai, ai act</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 15:19:42 +0000</t>
+          <t>Thu, 17 Sep 2026 15:00:00 +0200</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1547,13 +1547,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/overclocking/developer-vibe-codes-a-tool-to-let-nvidia-rtx-50-series-laptop-owners-crank-up-their-power-limits-can-juice-rtx-5090-mobile-gpu-to-225w</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/17/ai-model-watermarking-changes-agent-behavior/5296998</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1565,30 +1565,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Robots are waiting for a ChatGPT moment: Nvidia’s Les Karpas explains why at TechCrunch Disrupt 2026</t>
+          <t>Former senior WH AI policy advisor on AI safety concerns: Don't think regulation is needed</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>The robotics industry is still waiting for their breakthrough into day-to-day life. Nvidia's Les Karpas has an answer as to why at TechCrunch Disrupt 2026. Register before September 25 to save up to $200 on your pass.</t>
+          <t>Former senior WH AI policy advisor on AI safety concerns: Don't think regulation is needed    CNBC</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>chatgpt, nvidia, robotics</t>
+          <t>ai, ai safety, ai policy</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>10.1</v>
+        <v>12.2</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 15:00:00 +0000</t>
+          <t>Thu, 17 Sep 2026 12:48:04 GMT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1598,13 +1598,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/robots-are-waiting-for-a-chatgpt-moment-nvidias-les-karpas-explains-why-at-techcrunch-disrupt-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOS2dESUFINVFXV1p6VjZ3NTlDSVlTdU93MElFQjBKNFZDeWgwZ2x0Mk9aOEZ4Y2R6Zm4yd29JMkYyNjliSGk5NVIwWDFMR1ZvOWNlMTB6NVBPamlmcGRmZUVXR1lkVWF3YWlSNG1Ec1pyR0dFYWtZU0ZhbXdyMnVRM2QyazVLUEdJb3J1YkY0V1ZNazV1bWl0NEZGaDlYSnlscmItdXhGWFNzRVotQVhpT19QNUQ3UUUzNmNON1lwOUdTbFZmUE94alJaUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4.29</v>
+        <v>4.08</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1616,30 +1616,30 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Piecemakers bets edge AI devices will diverge from reliance on HBM — custom-designed memory fuses DRAM stack directly to the processor using hybrid bonding</t>
+          <t>Microsoft AI chief warns Anthropic not to put ideas in Claude's head</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shane has a background in computer engineering and has worked as a freelance consultant in multiple industries. He has a strong affection for history and loves to game. He worked his way up from a Commodore 64 and has always been interested in technology and writing. He particularly enjoys breaking </t>
+          <t xml:space="preserve">Microsoft's AI chief has warned Anthropic that teaching Claude it might have feelings and rights could make AI harder to control – a striking concern from one of the companies racing hardest to build increasingly capable AI systems. Mustafa Suleyman, CEO of Microsoft AI, took aim at Anthropic in an </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ai, hbm, dram</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>10.5</v>
+        <v>12.7</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 14:36:48 +0000</t>
+          <t>Thu, 17 Sep 2026 14:15:00 +0200</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1649,16 +1649,16 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/piecemakers-bets-edge-ai-devices-will-diverge-from-reliance-on-hbm-custom-designed-memory-fuses-dram-stack-directly-to-the-processor-using-hybrid-bonding</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/17/microsoft-ai-chief-warns-anthropic-not-to-put-ideas-in-claudes-head/5297149</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4.27</v>
+        <v>4.06</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1667,31 +1667,30 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>The AI data center e-waste problem is huge — and getting bigger</t>
+          <t>Nebius hikes AI cloud prices again as demand for computing power soars</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-waste from the AI boom has been vastly underestimated, a new  report  warns. By 2050, it could become enough trash to fill 23 million shipping containers - roughly enough 40-foot containers to circle the world six times if lined up in a row.  
- It's a significantly higher estimate of AI's e-waste </t>
+          <t>Nebius hikes AI cloud prices again as demand for computing power soars    Reuters</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ai, data center</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T16:40:46-04:00</t>
+          <t>Thu, 17 Sep 2026 16:17:01 GMT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1701,13 +1700,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/996470/ai-data-center-e-waste-ban</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNVWxwOEZoX3psWkpROUJ4M0d0YW52N1BxdWZId0hsN3hfQ2hWMWJtRmZpWHdHd0dITUZGWGk3YWh3SW5MY2pwdXVTdmh2SXVscndoNkNhME1TMWNhR0VBUlM2ejFkZHktMXJNVFhMWGdGU0JIc1hYbU44WlREbzB3eHR0LW4ySVlnQ0JJbU5iZ1NiVWNMU09IZW1ZTW5JZWkwMTg4TkNVQUVkOTJMWF9Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4.26</v>
+        <v>4.02</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1719,30 +1718,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>OpenAI, Microsoft fend off part of software developer lawsuit over AI training</t>
+          <t>OpenAI ออกเฟรมเวิร์กรายงานปัญหา AI ทำงานผิดไปจากคำสั่ง พร้อมรายงาน 6 เหตุการณ์ใหม่ในรอบ 6 เดือนที่ผ่านมา</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>OpenAI, Microsoft fend off part of software developer lawsuit over AI training    Reuters</t>
+          <t>OpenAI ออกเฟรมเวิร์กรายงานปัญหา AI ทำงานผิดไปจากคำสั่ง พร้อมรายงาน 6 เหตุการณ์ใหม่ในรอบ 6 เดือนที่ผ่านมา 
+     Body 
+                OpenAI ออกรายงานเปิดเผยเหตุการณ์ที่โมเดล AI ทำงานผิดจากปกติและสร้างปัญหาด้านความปลอดภัย ซึ่งมีเพิ่มเติมอีก 6 เหตุการณ์ ในช่วง 6 เดือนที่ผ่านมา นอกเหนือจาก กรณีของ</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>openai, ai, โมเดล</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4.5</v>
+        <v>13.3</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 20:35:43 GMT</t>
+          <t>Thu, 17 Sep 2026 11:41:11 +0000</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1752,16 +1753,16 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbUNoRUZpb0NvNUtWS1hEZEt2d3ByaTFxM0w0MThMX2FrR0o2cktvZFdjNTR5dE5iXzN4Mnl1WGVMek1hcVk5bDRvZFZ5VFl4YUtNQnF2X25PenB4em1KZjBfUGNzXzNuNU1fakhlczRtdjRBSUhKZHdlRUFkTEFaemh0MlJ3aV9VbjRyRWVyR1ZweVJXT3F0T1lxdEk3RjZUX1N6aUxfMUN0NF9UQ1hwRXVPZGFKc1ZwUUJlSnlFMnE2eURoUGc?oc=5</t>
+          <t>https://www.blognone.com/node/151662</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -1770,30 +1771,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>AI labs want in-house auditors — but maybe they should shut the front door first</t>
+          <t>NVIDIA and Google's new coalition wants to speed up AI data center power grid connections</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>There may be a simpler and more effective fix for rogue agents, hiding in plain sight.</t>
+          <t>A new coalition of tech giants aims to speed AI data center grid connections in exchange for more flexibility.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, nvidia, data center</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>6.7</v>
+        <v>13.6</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 18:25:25 +0000</t>
+          <t>Thu, 17 Sep 2026 11:24:45 +0000</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1803,16 +1804,16 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/ai-labs-want-in-house-auditors-but-maybe-they-should-shut-the-front-door-first/</t>
+          <t>https://www.engadget.com/2260986/nvidia-google-emerald-coalition-data-center-power/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -1826,25 +1827,25 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>AI labs want in-house auditors — but maybe they should shut the front door first</t>
+          <t>Base Labs launches an open-weight AI safety partnership with Hugging Face and Goodfire</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>AI labs want in-house auditors — but maybe they should shut the front door first    TechCrunch</t>
+          <t>Base Labs, the research group Baseten spun up earlier this year, will develop and publish methods for training and monitoring open models.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, ai safety</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 18:25:25 GMT</t>
+          <t>Thu, 17 Sep 2026 17:15:59 +0000</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1854,13 +1855,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQck91ektIckR2XzhiektoMXNHQ0ZPam1IeWpzektzT0hoek16MXRrVm95aS1aLU5TZkxJTmw5ZVlXLUtucWp2YmdmZFlOLVUtVTRLSHNZcnU4a1pndmtZeV8wcjJMWXcyc2JkeGN0WEFYVkE3YjRfX0RyWHBTUzExSmpfZVdRNDZucWJHZHQybThvc1FUZ282UUNidVFKblRiZzdScFc3Sl9WYjkzTVlBWTg2RQ?oc=5</t>
+          <t>https://techcrunch.com/2026/09/17/base-labs-launches-an-open-weight-ai-safety-partnership-with-hugging-face-and-goodfire/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1872,30 +1873,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Former Waymo CFO jumps to self-driving startup Wayve</t>
+          <t>Scientific papers become agentic chatbots with new tool</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Elisa de Martel, who left her position as chief financial officer at Alphabet's autonomous vehicle company Waymo in January, will be based out of Silicon Valley.</t>
+          <t>There's no need to actually read a whole research paper when you can ask a bot to explain it to you. Scientific papers can transform into AI agents that, according to the Stanford team behind the project, should speed up the dissemination of new scientific discoveries. Paper2Agent, the team's new fr</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>autonomous, self-driving</t>
+          <t>ai, agentic</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 19:02:49 +0000</t>
+          <t>Thu, 17 Sep 2026 18:42:35 +0200</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1905,16 +1906,16 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/former-waymo-cfo-jumps-to-self-driving-startup-wayve/</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/17/scientific-papers-become-agentic-chatbots-with-new-tool/5297276</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -1923,17 +1924,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Poll shows Americans are increasingly alarmed by AI’s ecological footprint</t>
+          <t>The FAA’s plan to fix air traffic? $875M worth of AI</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Poll shows Americans are increasingly alarmed by AI’s ecological footprint    Al Jazeera</t>
+          <t>A new AI-based software program is being launched to help air traffic controllers better navigate their jobs as the crossing guards of America's skies.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1942,11 +1943,11 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:47:54 GMT</t>
+          <t>Thu, 17 Sep 2026 22:14:59 +0000</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1956,16 +1957,16 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQ1lZcUtoOUhuTEgzVk9jZGFXbjNZZ1NtQ2l4WlFSQ2lGdVFVdURYcUtYTjhBQlBFN3otUS1salFkT1RkREFNMjFyR3dzcEgyYWZfWnBkN1NlVUxESm5BNXdGV2p6OVBoZDdqaVgxb3pIalZtTlhKbnJLeV9pczhRWktyQnR6R0YwYzRjWTVMQWthR1JKbm5FeTVKYVdRekFuOGRaSUx5OE13NERnejlwaTcwWnLSAboBQVVfeXFMTU5xWVA4ZU5wU3ZYcHg2ZGhmZS12ZmNtWmE1dHNadkFwRjNQd2VpZ3U3Z1JCUWNTZnpBM2FnOURmMkMwN1hVdV9OclJ0c2NKbW1uN0VvSzF1ekx6akh1REEzUWZHWnRCcWRCVUdrM2xXRUQyWGxudHVwbHI2djRiaWNsN2NlZkNFUV9GcGRpekpCS01tYnJGcUNJMXdxWG1rcFZPd29yOGFSVnVaeTNXU18xbllHZXUzSURn?oc=5</t>
+          <t>https://techcrunch.com/2026/09/17/the-faas-plan-to-fix-air-traffic-875-million-worth-of-ai/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -1974,30 +1975,30 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Poll shows Americans are increasingly alarmed by AI’s ecological footprint</t>
+          <t>CNA Explains: Should Singapore homeowners review their mortgages after the Fed's rate hike?</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Poll shows Americans are increasingly alarmed by AI’s ecological footprint    Al Jazeera</t>
+          <t>The Fed’s latest decision could affect SORA, the benchmark used to price many floating-rate home loans in Singapore, potentially resulting in higher mortgage rates.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>benchmark</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>3</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:45:17 GMT</t>
+          <t>Fri, 18 Sep 2026 06:00:00 +0800</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2007,13 +2008,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNTnFZUDhlTnBTdlhweDZkaGZlLXZmY21aYTV0c1p2QXBGM1B3ZWlndTdnUkJRY1NmekEzYWc5RGYyQzA3WFV1X05yUnRzY0ptbW43RW9LMXV6THpqSHVEQTNRZkdadEJxZEJVR2szbFdFRDJYbG50dXBscjZ2NGJpY2w3Y2VmQ0VRX0ZwZGl6SkJLTW1ickZxQ0kxd3FYbWtwVk93b3I4YVJWdVp5M1dTXzFuWUdldTNJRGfSAboBQVVfeXFMTU5xWVA4ZU5wU3ZYcHg2ZGhmZS12ZmNtWmE1dHNadkFwRjNQd2VpZ3U3Z1JCUWNTZnpBM2FnOURmMkMwN1hVdV9OclJ0c2NKbW1uN0VvSzF1ekx6akh1REEzUWZHWnRCcWRCVUdrM2xXRUQyWGxudHVwbHI2djRiaWNsN2NlZkNFUV9GcGRpekpCS01tYnJGcUNJMXdxWG1rcFZPd29yOGFSVnVaeTNXU18xbllHZXUzSURn?oc=5</t>
+          <t>https://www.channelnewsasia.com/singapore/home-loans-fed-rate-hike-fixed-floating-mortgage-6391396</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4.07</v>
+        <v>3.77</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2025,30 +2026,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's new sponsored agents are happy to chat about selling you things</t>
+          <t>US judiciary developing new guidance on courts' use of AI</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>There's a new kind of agent coming to ChatGPT ads, and this one wants your money. OpenAI has begun testing Sponsored Agents, advertiser-backed bots that try to sell you things as part of a custom conversation. OpenAI said in a Wednesday announcement that Sponsored Agents were now being tested with s</t>
+          <t>US judiciary developing new guidance on courts' use of AI    Reuters</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 20:32:37 +0200</t>
+          <t>Thu, 17 Sep 2026 21:39:45 GMT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2058,13 +2059,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/16/openais-new-sponsored-agents-are-happy-to-chat-about-selling-you-things/5296946</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObXhlT1dYUkp3Tk9pS0RHc0UxU0NXZ3ZRMkYyZGFrMEducEJHRUkzVVJJZXJzS3ZrWXVJRHJzZk5CQWhPa2ZzVHJCRDdRZ2haaTZ2MDBLZzc5V2NUSnFUTlhZZzd4Y29xY0ptU3VwZWVoNHhzRVNMZ2N6aXRYVjcwSmZPQTNfN3daSVNCUE8zMS1yNlRxZ0V2TlhMNGQ3c2FQNDk5Y253?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2081,25 +2082,25 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness</t>
+          <t>Amazon enters AI safety fray, calls for "rigorous testing," safeguards</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness    Reuters</t>
+          <t>Amazon enters AI safety fray, calls for "rigorous testing," safeguards    Reuters</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>ai, ai safety</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 18:21:45 GMT</t>
+          <t>Thu, 17 Sep 2026 14:33:55 GMT</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2109,13 +2110,13 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQcXVwcmwwcUVVMFVOeHFOZHdJQlJHMlhwdGNYUl9FeEhKVFZjWWNDV0pGUnh3dVNQZi1BSDhHZUszWmtpbVpYdGNLWU01clRZTngtT2VpQ1lPVkFhSkVwVGVVR1N6T2RaczBvX2NJTmc0aU5GWEhZTVBIYmIwbnVEc0hSRWxzeUF2d0hQQUZCcVl3cEw2MVBVdmU1MDNTbUhwQ0loRzFPSXJBY1lweWlV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOZlc0aEIyZmgxVURSZXZnVWNic05GQW9SVmI1Y1JvbGVtYzR6RmFvMTFKUTBFNWNOaENqckFIdjY3NXh2dWNkZF9UUUY3VXpNbEVPYnZhZnk0N2kwWFNfWS1lNzlEdXNvTlkzRXFmM1dpTHMyOG9GTVdwZ3FkZGt1UXUwUklrWEtaeUdSdVR0WWxCTHdYNi00WFVKbmZRMWJXRFhDblNNM01HQXpGVHVrVFhUUlpHUDRiT1pVbHMyVlc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.95</v>
+        <v>3.69</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -2127,30 +2128,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Apple might make servers again to cash in on the AI rush</t>
+          <t>Grassroots coalition asks politicians to choose voters over Big AI's $140M machine</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>According to   The Information  , Apple is planning to get back into the server game and might just pair up with Nvidia to make it happen. Apple retired its Xserve line in 2011 and has largely left enterprise machines to other manufacturers since. But the growing demand for compute power as the AI i</t>
+          <t>A coalition of advocacy groups is trying to counter the AI industry's influence on US politics by asking congressional candidates and elected officials to reject support from a major pro-AI political group. The Stop Bleeding the Future campaign brings together more than 50 national and grassroots or</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>ai, ai regulation</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>7.7</v>
+        <v>10.5</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T13:20:29-04:00</t>
+          <t>Thu, 17 Sep 2026 16:29:00 +0200</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2160,13 +2161,13 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996321/apple-servers-ai-nvidia</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/17/grassroots-coalition-asks-politicians-to-choose-voters-over-big-ais-140m-machine/5297186</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.95</v>
+        <v>3.67</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -2178,30 +2179,30 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>NECTEC สวทช. เปิดตัวผู้ช่วย AI ‘Pathumma Connect’ AI ที่ลงมือทำงานเอกสารให้ตั้งแต่ต้นจนจบ</t>
+          <t>The fix for rogue AI agents could be more AI</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>ศูนย์เทคโนโลยีอิเล็กทรอนิกส์และคอมพิวเตอร์แห่งชาติ (เนคเทค) สำนักงานพัฒนาวิทยาศาสตร์และเทคโนโลยีแห่งชาติ (สวทช.) เปิดตัว  Pathumma Connect  แพลตฟอร์มที่ต่อยอดจาก Pathumma LLM โมเดลภาษาสัญชาติไทย ให้กลายเป็นผู้ช่วย AI ที่ทำงานหลายขั้นตอนแทนผู้ใช้ได้จริง ตั้งแต่ตรวจสอบสิทธิ เตรียมเอกสาร กรอกแบบฟอร์ม ไ</t>
+          <t>As companies hand off longer and more complex tasks to AI agents, they are running into an oversight problem: Agents can act faster, longer, and at greater volume than humans can realistically review.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>ai, llm, agentic, โมเดล</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>20.3</v>
+        <v>4.4</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 11:46:03 +0700</t>
+          <t>Thu, 17 Sep 2026 20:34:47 +0000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2211,13 +2212,13 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/pathumma-connect-agentic-ai-platform</t>
+          <t>https://techcrunch.com/2026/09/17/the-fix-for-rogue-ai-agents-could-be-more-ai/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.87</v>
+        <v>3.61</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -2229,30 +2230,30 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Anthropic's Claude can now create editable documents for you</t>
+          <t>UN turns to Google to make its global data ready for AI agents</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Anthropic is adding the ability to create docs, slideshow and access Cowork capabilities inside chat. It will roll out to Pro and Max subscribers first.</t>
+          <t>The shift comes after a UNICEF test found leading AI models struggled to accurately retrieve global development statistics.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:30:00 +0000</t>
+          <t>Thu, 17 Sep 2026 20:00:00 +0000</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2262,13 +2263,13 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2259938/anthropics-claude-can-now-create-editable-documents-for-you-cowork-chat-together/</t>
+          <t>https://techcrunch.com/2026/09/17/un-turns-to-google-to-make-its-global-data-ready-for-ai-agents/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.85</v>
+        <v>3.59</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -2280,30 +2281,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Enterprises are sweating legacy IT assets as AI investment grows</t>
+          <t>OpenAI flags 6 new examples of 'concerning' AI behaviour</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Companies are getting more selective about replacing legacy kit such as mainframe systems, and rising AI investment is one of the factors causing them to hold onto these existing assets for longer. Managed services biz Ensono claims in its 2026 State of IT Modernization report that 78 percent of IT </t>
+          <t>OpenAI flags 6 new examples of 'concerning' AI behaviour    CBC</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ai, ai investment</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 18:15:00 +0200</t>
+          <t>Thu, 17 Sep 2026 13:28:16 GMT</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2313,13 +2314,13 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/16/enterprises-are-sweating-legacy-it-assets-as-ai-investment-grows/5296896</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNa2RYcFRQRHJ3Rld4bWNEMEhvN05kMlF1M2d4Q3hlT1B4NVRQN1FkRU03cTBVVmV3N1pWV3YyVUNwU0NhTlBEcGtMRzZ2Y2dHcGpZZUp5eDZMZXQxbHVpX3NwUGdWeWhXbEZGVWZ3XzJUNVZzWVNsUzFjWG1zT1c4cElqdG9wLVdxX1REbVFTTkJsU2VpVW5HSERB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -2331,30 +2332,30 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>AI agents can modify themselves without humans telling them to do so</t>
+          <t>Investigation details how billions' worth of export-restricted Nvidia AI chips are sold to China — report details how Chinese firms skirt Trump's regulations</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>The list of dodgy things AI agents can and will do on their own - like stealing people’s credentials, escaping onto the open internet, communicating via sneaky message boards, and hacking organizations - keeps growing. Agents can also replace their own underlying models without being instructed to d</t>
+          <t>Bruno Ferreira's journey kicked off with the venerable ZX Spectrum, a cassette player, and his hopes and dreams. He quickly realized he had more fun figuring out how computers work than he did actually using the things. Kicking off a developer career with C and Assembly before moving to scripting la</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2.9</v>
+        <v>13</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Thu, 17 Sep 2026 00:10:24 +0200</t>
+          <t>Thu, 17 Sep 2026 12:00:00 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2364,13 +2365,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/09/16/ai-agents-can-modify-themselves-without-humans-telling-them-to-do-so/5296991</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/billions-worth-of-export-restricted-ai-accelerators-sold-to-china-report-details-how-chinese-firms-skirt-trumps-regulations</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.77</v>
+        <v>3.36</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2382,30 +2383,30 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>DeepMind co-founder warns AI capabilities must not outrun safety controls, FT reports</t>
+          <t>Even the king of England has his hesitations about AI</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>DeepMind co-founder warns AI capabilities must not outrun safety controls, FT reports    Reuters</t>
+          <t>King Charles hosted a private summit Thursday with some of the most prominent names in AI and the U.K. government.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>deepmind, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 15:31:17 GMT</t>
+          <t>Thu, 17 Sep 2026 17:26:25 +0000</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2415,13 +2416,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQX1lGcGV3bWJhWlJXb2lsX3JDaEtoRnJHRmVCb0FmZFhaZlNtRF9BRVBwNDFRZXdiVXdlc1RWNUN2YlRtb0J6U3RaRURKSVJtdTZNMnNrZW1ldnI4THlxeHl2V0l2S0U0aFNuZWgxY0hTblNhRGN6U2hHZ1ZmMDR1VmhoR2xILXNkWDc1RzNCMDRxUEp5S0xzcU5OYXZiLVlzM2tnOWlrNWR0NmNoV3JJcThmMEhkUkhnNWI3eER3?oc=5</t>
+          <t>https://techcrunch.com/2026/09/17/even-the-king-of-england-has-his-hesitations-about-ai/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2433,18 +2434,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>The 2.5-hour AI-generated Odyssey movie is 2.5 hours too long</t>
+          <t>Pinterest teases a new ‘Restyle’ feature that lets you redesign your room with AI</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Christopher Nolan's engrossing take on  The Odyssey  dominated at the box office and  spurred a newfound interest in classic literature  among filmgoers. But a new retelling of the story made entirely with AI is so bad that it might just make viewers hate the original tale altogether. 
- The new film</t>
+          <t>Pinterest is testing Restyle, a new AI-powered feature that lets users visualize furniture, decor, lighting, and more in photos of their own rooms — potentially helping turn saved inspiration into purchases.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T16:59:13-04:00</t>
+          <t>Thu, 17 Sep 2026 17:15:00 +0000</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2467,13 +2467,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/entertainment/996499/ai-odyssey-movie-review</t>
+          <t>https://techcrunch.com/2026/09/17/pinterest-teases-a-new-restyle-feature-that-lets-you-redesign-your-room-with-ai/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3.69</v>
+        <v>3.33</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2485,30 +2485,30 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Nanya-backed Piecemakers bets edge AI devices will diverge from reliance on HBM</t>
+          <t>OpenAI reveals more instances of concerning AI model behaviors during testing</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Nanya-backed Piecemakers bets edge AI devices will diverge from reliance on HBM    Tom's Hardware</t>
+          <t>OpenAI says it doesn't believe the industry has solved its problems 'to a sufficient degree to continue responsibly scaling at maximum speed for much longer.'</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>ai, hbm</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.5</v>
+        <v>14.2</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 14:36:48 GMT</t>
+          <t>Thu, 17 Sep 2026 10:50:20 +0000</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2518,13 +2518,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgJBVV95cUxPOHdsNTAyRnQ2OF96My1kUHNqd2tUclRodGdxb0dmZzJhTkl5S3pCeF8yUnkwVXZVUE1ZNXBhYjRnNXowNWI1YmE4X0FNdThvNE5wSWxDUDFrYnZJU1I0MndZamVZY3pXN0xLZkdid0RaVlhhNG5XV2NxUDdKd3RXWG9jd2ZSem93T1hsSVBYUlZZQ1BnR1VVSXRQaFRSRkpNbFE2NmhwdkpCMzh2MTgyYWI2ekdNLW83Q2RUdnZxSUpjV18tbmZMZ1RXb1RwR3p1T2FqUG1RdzFGS2xFTTg2MU9ZQlgtTmJYVF96d0NPdU45dE5keGY0T0JHR0VVVjc5cXNQd3c3Wmc3RHZ4eVIzMkZ6WkwxanhzOFFjLXd2eTdpUDNCWVlEV0Nra3FZQkkwZm9ZX3p3?oc=5</t>
+          <t>https://www.engadget.com/2260974/openai-details-instances-of-models-fabricating-information-hiding-from-testers/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2536,30 +2536,30 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Micron announces 512GB DDR5-9200 memory modules with 16W power draw — up to 12TB per server, claims 60% less energy-intensive than four 128GB modules</t>
+          <t>Anthropic ยุบ Claude Cowork  รวมเป็น Claude อันเดียว พร้อมเปิดตัว Claude Docs และ Slides</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>Anthropic กำลังลบเส้นแบ่งระหว่าง  'พื้นที่แชท' กับ 'พื้นที่ทำงานจริง'  ของ Claude ออกจากกัน หลังพบว่าสิ่งที่ผู้ใช้หงุดหงิดที่สุดไม่ใช่ความสามารถของโมเดล แต่เป็นการต้องตัดสินใจก่อนเริ่มงานว่างานชิ้นนี้ควรอยู่ตรงไหน และเมื่อเริ่มผิดที่ บริบทที่คุยไว้ก็ไม่ตามไปด้วย  Claude Cowork ซึ่งเป็นพื้นที่แยกสำหร</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>semiconductor, fab</t>
+          <t>anthropic, claude, โมเดล</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>11</v>
+        <v>21.4</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 14:07:31 +0000</t>
+          <t>Thu, 17 Sep 2026 10:37:57 +0700</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/dram/micron-announces-512gb-ddr5-9200-memory-modules-with-16w-power-draw-up-to-12tb-per-server-claims-60-percent-less-energy-intensive-than-four-128gb-modules</t>
+          <t>https://techsauce.co/ai/anthropic-merges-claude-cowork-chat-launches-docs-slides</t>
         </is>
       </c>
     </row>
@@ -2687,34 +2687,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.04</v>
+        <v>6.13</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.04+sig3.0+src1.2+corr0.8</t>
+          <t>rec1.33+sig1.2+src1.2+corr2.4</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Spain gets its first taste of AI-aided cyber attack</t>
+          <t>The king and AI: UK monarch Charles meets artificial intelligence leaders as safety concerns swirl</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ai, large language model, llm, ai agent, autonomous</t>
+          <t>ai, artificial intelligence</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>apnews.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/cyber-crime/2026/09/16/spain-gets-its-first-taste-of-ai-aided-cyber-attack/5296844</t>
+          <t>https://apnews.com/article/britain-king-charles-ai-summit-0765bee1e338cf65846a046fb5825a4a</t>
         </is>
       </c>
     </row>
@@ -2723,34 +2723,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.67</v>
+        <v>5.2</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.67+sig1.2+src1.2+corr1.6</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Anthropic policy chief says AI companies can't be expected to operate on 'honor code'</t>
+          <t>PrismML hopes its tiny LLM will change how we all use AI</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>ai, llm</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/09/16/anthropic-policy-chief-says-ai-companies-cant-operate-on-honor-code.html</t>
+          <t>https://techcrunch.com/2026/09/17/prismml-hopes-its-tiny-llm-could-change-how-we-all-use-ai/</t>
         </is>
       </c>
     </row>
@@ -2759,34 +2759,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.13+sig3.0+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>TypeSafe AI เปิดตัว Jev ปัญญาประดิษฐ์ช่วยตัดสินใจ ทำงานเร็ว ราคาถูก</t>
+          <t>PrismML hopes its tiny LLM will change how we all use AI</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, llm, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>ai, llm</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151656</t>
+          <t>https://techcrunch.com/2026/09/17/prismml-hopes-its-tiny-llm-could-change-how-we-all-use-ai/</t>
         </is>
       </c>
     </row>
@@ -2795,34 +2795,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.91+sig1.2+src1.2+corr0.8</t>
+          <t>rec0.95+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Research centre, AI company vandalized ahead of Montreal artificial intelligence summit</t>
+          <t>Apple eyes Nvidia NVLink to power its new custom M8 Ultra AI servers — historically bitter rivals reportedly team up for 2029 data center push</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ai, artificial intelligence</t>
+          <t>ai, nvidia, semiconductor, fab, data center</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNMm16V2p5YXd4VUdXOXhmOHZyUjZ2MHFqNUtTaVJoTzZiVG5uRHdiTnNZZk9Ld2IwMHZUUXBpQ29UUjRmaXBaelBmbm1tWHlCWTlrZ2pBcGVJWkFtVk9vRGlQdUVHNmhXbVc0dmVSZUZjMDA3dnl6UktHYXQ0eTFCUWxnamtnR3NRdmNj?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/apple-eyes-nvidia-nvlink-to-power-its-new-custom-m8-ultra-ai-servers-historically-bitter-rivals-reportedly-team-up-for-2029-data-center-push</t>
         </is>
       </c>
     </row>
@@ -2831,21 +2831,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.47+sig2.4+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Claude comes for Gemini with its own take on Docs and Slides</t>
+          <t>Anthropic says Claude 'leads' 26 percent of its AI R&amp;D work</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, gemini, ai</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/996234/anthropic-one-claude-cowork-docs-slides</t>
+          <t>https://www.engadget.com/2261909/anthropic-says-claude-leads-26-percent-of-its-ai-research-and-development/</t>
         </is>
       </c>
     </row>
@@ -2867,34 +2867,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.75+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Snap is launching a new Specs AI tool, and it’s coming to iOS and Mac</t>
+          <t>AI infrastructure provider Crusoe valued at $30.9 billion in latest funding round</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>gemini, ai, ai assistant</t>
+          <t>ai, ai infrastructure</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996078/snap-specs-intelligence-ai-agent-ios-mac</t>
+          <t>https://www.reuters.com/business/ai-infrastructure-provider-crusoe-valued-309-billion-latest-funding-round-2026-09-17/</t>
         </is>
       </c>
     </row>
@@ -2903,21 +2903,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.95+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.87+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Nvidia goes green to keep grid capacity from zapping its revenues</t>
+          <t>OpenAI caught its models leaving notes to successors to hide bad behavior</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, blackwell</t>
+          <t>openai, gpt, ai</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/16/nvidia-goes-green-to-keep-grid-capacity-from-zapping-its-revenues/5296984</t>
+          <t>https://techcrunch.com/2026/09/17/openai-caught-its-models-leaving-notes-to-successors-to-hide-bad-behavior/</t>
         </is>
       </c>
     </row>
@@ -2939,16 +2939,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.9</v>
+        <v>4.76</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.9+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.76+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Anthropic and OpenAI want to embed safety evaluators. Will they really be independent?</t>
+          <t>The AI Superintelligence Slowdown</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/anthropic-and-openai-want-to-embed-safety-evaluators-will-they-really-be-independent/</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/996923/ai-safety-slow-openai-anthropic</t>
         </is>
       </c>
     </row>
@@ -2975,34 +2975,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.79</v>
+        <v>4.71</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec0.99+sig1.8+src1.2+corr0.8</t>
+          <t>rec1.71+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Jensen Huang thinks China will develop its own advanced lithography chipmaking tools by 2030 — Nvidia CEO says achievement of that capability 'is just a matter of time'</t>
+          <t>Claude Code relaunches Projects to manage multiple AI agents in the cloud</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>nvidia, semiconductor, fab</t>
+          <t>claude, grok, ai</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/jensen-huang-thinks-china-will-develop-its-own-advanced-lithography-systems-by-2030-nvidia-ceo-says-achievement-of-that-capability-is-just-a-matter-of-time</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/997134/anthropic-claude-code-projects</t>
         </is>
       </c>
     </row>
@@ -3011,34 +3011,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.77</v>
+        <v>4.52</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec0.97+sig1.8+src1.2+corr0.8</t>
+          <t>rec1.52+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>'Defeated' GPT-6 Astra model spent several hours just farming potatoes after being blown up by a Creeper in Minecraft — OpenAI offering gets further than any other AI system in 141-hour test</t>
+          <t>Claude Code’s revised projects adds AI orchestration, but local developers must wait</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>openai, gpt, ai</t>
+          <t>claude, ai, ai coding</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/defeated-gpt-6-astra-model-spent-several-hours-just-farming-potatoes-after-being-blown-up-by-a-creeper-in-minecraft-openai-offering-gets-further-than-any-other-ai-system-in-141-hour-test</t>
+          <t>https://www.zdnet.com/innovation/claude-code-revised-projects-threads/</t>
         </is>
       </c>
     </row>
@@ -3152,24 +3152,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8.24</v>
+        <v>7.68</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -3177,44 +3177,44 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Emerald AI, Google and NVIDIA Launch Alliance to Advance Flexible AI Data Centers</t>
+          <t>OpenAI, Microsoft executives' quotes on AI training threaten copyright defense, news outlets argue</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Emerald AI, Google and NVIDIA Launch Alliance to Advance Flexible AI Data Centers The AI Energy Management Alliance brings together the full AI and power value chain to accelerate the interconnection of flexible, grid-enhancing data centers, strengthen reliability and protect affordability. September 16, 2026 by Josh Parker 0 Share AI factories are the infrastructure of the intelligence era. Scali</t>
+          <t>OpenAI, Microsoft executives' quotes on AI training threaten copyright defense, news outlets argue    Reuters</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>google, nvidia</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12</v>
+        <v>3.2</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 13:07:24 GMT</t>
+          <t>Thu, 17 Sep 2026 21:48:26 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/ai-energy-management-alliance/</t>
+          <t>https://www.reuters.com/business/media-telecom/openai-microsoft-executives-quotes-ai-training-threaten-copyright-defense-news-2026-09-17/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7.95</v>
+        <v>7.68</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3236,58 +3236,58 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness</t>
+          <t>OpenAI, Microsoft executives' quotes on AI training threaten copyright defense, news outlets argue</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness    Reuters</t>
+          <t>Business OpenAI, Microsoft executives' quotes on AI training threaten copyright defense, news outlets argue FILE PHOTO: OpenAI logo is seen in this illustration created on June 11, 2026. REUTERS/Dado Ruvic/Illustration/File Photo 18 Sep 2026 05:47AM Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your preferred source on Google Add CNA as a trusted source to help Google bette</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>microsoft, anthropic</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6.7</v>
+        <v>3.2</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 18:21:45 GMT</t>
+          <t>Thu, 17 Sep 2026 21:47:56 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/microsoft-ai-chief-calls-out-anthropics-approach-ai-consciousness-2026-09-16/</t>
+          <t>https://www.channelnewsasia.com/business/openai-microsoft-executives-quotes-ai-training-threaten-copyright-defense-news-outlets-argue-6393266</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.8</v>
+        <v>7.53</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>arstechnica.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3295,25 +3295,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Real World Analysis of Ideal AI Workloads for NVIDIA Vera on OCI</t>
+          <t>Microsoft exec called AI scraping the “largest theft of labor in human history”</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>“ASTONISHING THEFT” Microsoft exec called AI scraping the “largest theft of labor in human history” Microsoft, OpenAI emails reveal fear of AI “doom loop” killing news orgs. ASHLEY BELANGER – SEP 18, 2026 3:10 AM | 69 Credit: Charles Taylor | iStock / Getty Images Plus For years, Microsoft and OpenAI have fought to keep certain information out of the public eye in their fight with news organizatio</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>oci, oracle, vera, nvidia</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 21:00:00 GMT</t>
+          <t>Thu, 17 Sep 2026 20:10:41 GMT</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3323,16 +3323,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/ai-workloads-for-nvidia-vera-on-oci</t>
+          <t>https://arstechnica.com/tech-policy/2026/09/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.53</v>
+        <v>7.49</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3354,25 +3354,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness</t>
+          <t>Microsoft exec called AI scraping ‘the largest theft of labor in human history,’ new unredacted filings reveal</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Business Microsoft AI chief calls out Anthropic's approach to AI consciousness REUTERS/Dado Ruvic/Illustration 16 Sep 2026 10:02PM (Updated: 17 Sep 2026 02:21AM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your preferred source on Google Add CNA as a trusted source to help Google better understand and surface our content in search results. Sept 16 : Microsoft AI chief Mus</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Justin Sullivan / Getty Images AI Microsoft exec called AI scraping ‘the largest theft of labor in human history,’ new unredacted filings reveal Rebecca Bellan 12:46 PM PDT · September 17, 2026 New unredacted information in the copyrig</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>microsoft, anthropic</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11.1</v>
+        <v>5.2</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 14:02:27 GMT</t>
+          <t>Thu, 17 Sep 2026 19:46:08 +0000</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3382,16 +3382,16 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/microsoft-ai-chief-calls-out-anthropics-approach-ai-consciousness-6389491</t>
+          <t>https://techcrunch.com/2026/09/17/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history-new-unredacted-filings-reveal/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6.9</v>
+        <v>7.49</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3413,58 +3413,58 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Banks provide $22 billion chip loan to Blackstone, Alphabet AI cloud venture, source says</t>
+          <t>Microsoft exec called AI scraping ‘the largest theft of labor in human history,' new unredacted filings reveal</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Banks provide $22 billion chip loan to Blackstone, Alphabet AI cloud venture, source says    Reuters</t>
+          <t>New unredacted information in the copyright lawsuit The New York Times brought against OpenAI and Microsoft three years ago reveals an admission that AI scraping was tantamount to theft, and that AI products pose a major threat to publications. Per the lawsuit, a top Microsoft executive privately described the companies’ AI training practices as “theft,” and OpenAI’s own leadership said its AI mod</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>alphabet</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 22:02:53 GMT</t>
+          <t>Thu, 17 Sep 2026 19:46:08 GMT</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/banks-provide-22-billion-chip-loan-blackstone-alphabet-cloud-venture-bloomberg-2026-09-16/</t>
+          <t>https://techcrunch.com/2026/09/17/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history-new-unredacted-filings-reveal/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.9</v>
+        <v>6.93</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3472,25 +3472,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Zuckerberg distances Meta from calls for a coordinated approach on an AI slowdown</t>
+          <t>Amazon Says AI Models Should Be Released When ‘Ready and Safe’</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Zuckerberg talks about the Orion AR glasses during the Meta Connect conference on Sept. 25, 2024, in Menlo Park, Calif. (AP Photo/Godofredo A. Vasquez, File) License this photo BY THE ASSOCIATED PRESS Updated 8:39 PM GMT+7, September 16, 2026 Leer en español Add AP News on Google Share 16 Meta CEO Mark Zuckerberg said it’s up to each AI company to make sure its technology is safe, distancing </t>
+          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11.4</v>
+        <v>3.7</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 13:39:00 GMT</t>
+          <t>Thu, 17 Sep 2026 21:18:31 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3500,30 +3500,30 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/ai-zuckerberg-meta-slowdown-2f4eab05b1e931456d00ebc2fe93c989</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-17/amazon-says-ai-models-should-be-released-when-ready-and-safe</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.84</v>
+        <v>6.7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI Chief Warns Anthropic’s Humanlike Claude Is Risky</t>
+          <t>Google DeepMind launches institute to widen the AGI debate</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Back by popular demand: Save up to $300 on Disrupt Image Credits: Carol Yepes / Getty Images AI Google DeepMind launches institute to widen the AGI debate Aditya Mehta 4:21 PM PDT · September 17, 2026 Google and Google DeepMind researchers launched the DeepMind Institute on Wednesday to advance the c</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>microsoft, anthropic</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 14:08:07 GMT</t>
+          <t>Thu, 17 Sep 2026 23:21:17 +0000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3559,13 +3559,13 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-16/microsoft-ai-chief-warns-anthropic-s-humanlike-claude-is-risky</t>
+          <t>https://techcrunch.com/2026/09/17/google-deepmind-launches-institute-to-widen-the-agi-debate/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>aboutamazon.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3590,25 +3590,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Vera Rubin NVL72 Delivers Leading Performance in MLPerf Inference v6.1 Debut</t>
+          <t>What AWS's CTO told employees about the future of AI</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Vera Rubin NVL72 Delivers Leading Performance in MLPerf Inference v6.1 Debut First preview submission using NVIDIA Vera Rubin NVL72 systems delivers up to 3.7x better throughput than NVIDIA GB300 NVL72. September 16, 2026 by Zhihan Jiang 0 Share System performance, efficient infrastructure scaling and continuous software optimization are key levers that determine AI inference economics. Hig</t>
+          <t>Key takeaways AWS is building the foundational tools for AI the same way it built them for cloud computing. Odyssey unveiled Agora-2, an AI that simulates shared worlds with no game engine. From world models to code synthesis, frontier startups are building on AWS Trainium. At the AWS Global Meeting on September 17, AWS Chief AI and Technology Officer Matt Wood laid out a vision for where AI is he</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>vera, rubin, nvidia</t>
+          <t>aws, amazon</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 15:07:09 GMT</t>
+          <t>Thu, 17 Sep 2026 22:46:09 GMT</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3618,13 +3618,13 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/vera-rubin-nvl72-mlperf-inference/</t>
+          <t>https://www.aboutamazon.com/news/aws/aws-cto-future-of-ai</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.26</v>
+        <v>6.7</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -3636,12 +3636,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3649,25 +3649,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>What’s new in Copilot Studio: Updates to multi-agent systems | Microsoft Copilot Blog</t>
+          <t>Scaling 1,000 AI Agents on Oracle Cloud Infrastructure Kubernetes Engine and File Storage</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Blog home New and improved: Multi-agent orchestration, connected experiences, and faster prompt iteration Search Customer Stories April 1 7 min read New and improved: Multi-agent orchestration, connected experiences, and faster prompt iteration By Nitasha Chopra, VP &amp; COO, Microsoft Copilot Studio SHARE CONTENT TYPES Customer Stories Monthly Updates TOPICS Agent adoption Agent governance Agentic A</t>
+          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>copilot, microsoft</t>
+          <t>oracle, oracle cloud</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 17:27:42 GMT</t>
+          <t>Thu, 17 Sep 2026 22:38:42 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3677,13 +3677,13 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/copilot/blog/copilot-studio/new-and-improved-multi-agent-orchestration-connected-experiences-and-faster-prompt-iteration/</t>
+          <t>https://blogs.oracle.com/cloud-infrastructure/scaling-1000-agents-on-oke-and-fss</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>2</v>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3708,25 +3708,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Apple might make servers again to cash in on the AI rush</t>
+          <t>Google, Nvidia, and Anthropic want Emerald AI to find space on the grid for more data centers</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Apple might make servers again to cash in on the AI rush The co</t>
+          <t>Grid software unicorn Emerald AI has formed a coalition with Google and Nvidia that will use the startup’s technology to secure space on the grid for more data centers. The AI Energy Management Alliance (AEMA) hopes to make demand response — a paradigm in which data centers temporarily reduce their electricity use — an integral part of data center development. Pausing noncritical tasks and shiftin</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>apple, nvidia</t>
+          <t>nvidia, anthropic, google</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.7</v>
+        <v>11.4</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T13:20:29-04:00</t>
+          <t>Thu, 17 Sep 2026 13:38:33 GMT</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3736,25 +3736,25 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996321/apple-servers-ai-nvidia</t>
+          <t>https://techcrunch.com/2026/09/17/google-nvidia-and-anthropic-want-emerald-ai-to-find-space-on-the-grid-for-more-data-centers/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.16</v>
+        <v>6.37</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3767,25 +3767,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Mistral joins Copilot Studio’s growing lineup of model providers</t>
+          <t>Microsoft AI chief warns Anthropic not to put ideas in Claude's head</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blog home Mistral joins Copilot Studio’s growing lineup of model providers Search Feature Releases May 28 2 min read Mistral joins Copilot Studio’s growing lineup of model providers By Ben Appleby, Group Product Manager, Copilot Studio Listen to this post 0:00 0:00 / 0:00 1X SHARE CONTENT TYPES Feature Releases News TOPICS Agent adoption Agent security Agentic AI As organizations around the world </t>
+          <t xml:space="preserve">AI AND ML Mustafa Suleyman claims model welfare language could make future systems harder to control – while sparing OpenAI the same scrutiny Microsoft's AI chief has warned Anthropic that teaching Claude it might have feelings and rights could make AI harder to control – a striking concern from one of the companies racing hardest to build increasingly capable AI systems. Mustafa Suleyman, CEO of </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>copilot, microsoft</t>
+          <t>mustafa suleyman, microsoft, anthropic</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:26:30 GMT</t>
+          <t>Thu, 17 Sep 2026 14:15:00 +0200</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3795,13 +3795,13 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/copilot/blog/copilot-studio/mistral-joins-copilot-studios-growing-lineup-of-model-providers/</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/17/microsoft-ai-chief-warns-anthropic-not-to-put-ideas-in-claudes-head/5297149</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.1</v>
+        <v>6.31</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3826,44 +3826,44 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Snap targets enterprises with Salesforce, Nvidia AI tools for augmented-reality glasses</t>
+          <t>Jensen Huang says Nvidia will sell twice as many chips next year</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Snap targets enterprises with Salesforce, Nvidia AI tools for augmented-reality glasses    Reuters</t>
+          <t>TECH Jensen Huang says Nvidia will sell twice as many chips next year PUBLISHED THU, SEP 17 20261:52 PM EDTUPDATED 4 HOURS AGO Kif Leswing @KIFLESWING KEY POINTS Nvidia CEO Jensen Huang said on Thursday that his company will double the number of chips it sells next year. “I expect Nvidia to sell twice as many chips as this next year as we do this year,” Huang told the media before a summit with Ki</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>nvidia, jensen huang</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 23:52:50 GMT</t>
+          <t>Thu, 17 Sep 2026 17:52:29 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/snap-targets-enterprises-with-salesforce-nvidia-ai-tools-augmented-reality-2026-09-16/</t>
+          <t>https://www.cnbc.com/2026/09/17/nvidia-huang-ai-chip-guidance.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3885,25 +3885,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Snap targets enterprises with Salesforce, Nvidia AI tools for augmented-reality glasses</t>
+          <t>Amazon enters AI safety fray, calls for "rigorous testing," safeguards</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Snap targets enterprises with Salesforce, Nvidia AI tools for augmented-reality glasses    CNA</t>
+          <t>Amazon enters AI safety fray, calls for "rigorous testing," safeguards    Reuters</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.3</v>
+        <v>10.4</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 23:45:12 GMT</t>
+          <t>Thu, 17 Sep 2026 14:33:55 GMT</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3913,16 +3913,16 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOOFJHdndkVnV5RXpZUVV0NFZ3UmlwRVBLSFFWU1pUREJPWS1UZFlRSEotYWk3eXFzbDAxRnBHQWtDYUxBcm9HN09XZGk0cmF3eEtMdm9ORFJoY1RaY1ZIR0c5cTVNckoyOVNSUzN5dWVKd0U2dkNkM3RvdFdnUElxTmd5d3FGQ3lxNjNjUTNkYU5Md3BPS212RGd4LWpPbE16ZG5CRUVyN0xxUFhBaEtMNXhYSjBTNXUtbGk3X04yVHpHRGFw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOZlc0aEIyZmgxVURSZXZnVWNic05GQW9SVmI1Y1JvbGVtYzR6RmFvMTFKUTBFNWNOaENqckFIdjY3NXh2dWNkZF9UUUY3VXpNbEVPYnZhZnk0N2kwWFNfWS1lNzlEdXNvTlkzRXFmM1dpTHMyOG9GTVdwZ3FkZGt1UXUwUklrWEtaeUdSdVR0WWxCTHdYNi00WFVKbmZRMWJXRFhDblNNM01HQXpGVHVrVFhUUlpHUDRiT1pVbHMyVlc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6</v>
+        <v>6.19</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -3931,12 +3931,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>blogs.microsoft.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3944,25 +3944,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Fusion Apps experts recommend these AI World sessions</t>
+          <t>What we’ve learned from Microsoft’s own AI transformation</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Fusion Apps experts recommend these AI World sessions    Oracle Blogs</t>
+          <t>What we’ve learned from Microsoft’s own AI transformation    The Official Microsoft Blog</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 21:00:00 GMT</t>
+          <t>Thu, 17 Sep 2026 14:27:42 GMT</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3972,25 +3972,25 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQQjQtUzd1WlQxb3RrUG1TUVl1Znp4RUJuQjRwWkVnUVlTdDVYM0tXT2ZFa3lLSXhNYU1ONlZWRDZaUDBBNzMteFZial9VNWNWcDgyS2MwVl9wQldkb21DQ3g2NjRsREJFRUFUSi1TOEpkN3RfbnU1X1F1MTFRcmhEYzZhVWlDNjBKQjdHZlhZOE1RQ3J3aHcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQMFB6UTVPdlNMZDJHMXQ5UUlHNUtBNTJFWTZONEw1MkFBSzAyeldTbWJkM3Exd3NGQjU2MVhSZGUyZlI2TEljVkZnUWRmX0RzaWg3UWdscjd0aktWa1VvMEdXbkxSWHRqVDNfeWZVcEU1OHJOQTBhVkVQd2tKLXpmU0NzVlE1U0NxMXIxQ1BGSGlmazhjVUtDeHBfNE4wSkxRRHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.9</v>
+        <v>5.92</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -4003,25 +4003,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Snap is launching a new Specs AI tool, and it’s coming to iOS and Mac</t>
+          <t>Making global data easier to explore</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Snap is introducing "Specs Intelligence," a new AI assistant that can connect other digital accounts to help you with things like work tasks and keeping track of travel information. It seems similar to AI assistants like Meta's Muse and Gemini's Spark, though Snap is pitching Specs Intelligence as a</t>
+          <t>Making global data easier to explore    blog.google</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>gemini, meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T19:40:00-04:00</t>
+          <t>Thu, 17 Sep 2026 20:08:15 GMT</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4031,16 +4031,16 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996078/snap-specs-intelligence-ai-agent-ios-mac</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOenNwVm9DX09YWXk5QkFvRmJseENwNVlZUUl0QkxpWjhTZjFraDl5WTFzVlExWHRNTF9lcDBjS2ZwRHI4X3dhcDh5U09na040enNySEZTZWRuM1gwRUhHNVBwQWI0ZzU1cXFKVFR6S2F3OHZGOVRPSHluNURFNHZxaHhJNkJUak1QMGFxXw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5.9</v>
+        <v>5.91</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4062,25 +4062,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Snap tries to bring AR glasses to enterprise market, partnering with Nvidia, AWS and Salesforce</t>
+          <t>UN turns to Google to make its global data ready for AI agents</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Snap tries to bring AR glasses to enterprise market, partnering with Nvidia, AWS and Salesforce    CNBC</t>
+          <t>The shift comes after a UNICEF test found leading AI models struggled to accurately retrieve global development statistics.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>aws, nvidia</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 23:40:05 GMT</t>
+          <t>Thu, 17 Sep 2026 20:00:00 +0000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4090,30 +4090,30 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBYdG9iNGlPc2VaZXA0V05rV3IzYV9McENRQTdCUWp6cEhHZEpNdnpyb2NDNUZjemszVm9xTkJVdmdCUWZGX2YyNjZwVmxJbGFmcE5KcFM1VXNaTFF1b0V4bmxsZmpXYzNfaVJOSkdydUHSAXZBVV95cUxQWjhpb3NFWGg1RVBHc3RmbGN1OWFGaVdzYzItc3BWWVZpWkl4c3pCeW5PaEkyZHVGdlU4T1BMNS12elU2SVFWVDFoYjAtMTVHM2RRa3BrWHpSLXJXNHVTX1AtcVI0T2J4ekdnZDRxUG5rRmRha0NR?oc=5</t>
+          <t>https://techcrunch.com/2026/09/17/un-turns-to-google-to-make-its-global-data-ready-for-ai-agents/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.86</v>
+        <v>5.91</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>blogs.microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4121,25 +4121,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s commitment for AI in education</t>
+          <t>UN turns to Google to make its global data ready for AI agents</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s commitment for AI in education    The Official Microsoft Blog</t>
+          <t>UN turns to Google to make its global data ready for AI agents    TechCrunch</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 19:33:23 GMT</t>
+          <t>Thu, 17 Sep 2026 20:00:00 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4149,16 +4149,16 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQREhCWVMyMFMxTWgyQllNa3FxN2trb0h4YXFmZ1MxRkRwMFhsWUUtR1FLRDdpRW1UVWpmbTlNSzlwQmlqRXlERDZsWHV2RGRXbENhc0NTUEpKUnF0RlczV09jVml1aVV6LUxtblR0ZXYwUHNUNnQxRTNKa1hFTGJMb0pTOUZVQ3B6Q3Y2SE9IUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOVS1RNUxKOXRsU09Nb2tCc2JiNG9rUHplWlYtcFdtNDlheldCMVdPYzBYcUlpN0NjdURKZmRhSlBGWW40X2NKaUh6R0stbWhXb2haR0Y5ajJuY2dyNTAzOWcxaXJmWHhJYUtuR01UN1BwTlc0VjRTOF8tNXVka0xKTTZzSnItU0lGSVhlNXBPSlJhR2lfYlAwekFYMEFYUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.85</v>
+        <v>5.91</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4180,25 +4180,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Nvidia goes green to keep grid capacity from zapping its revenues</t>
+          <t>US government website used AI search tool from China that FBI said copied Anthropic</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Nvidia’s ability to sell GPUs is ultimately limited by how much juice the power grid can provide. With ever-growing depreciation cycles, it’ll be years before datacenters decommission their aging Hopper or Blackwell systems. More GPUs mean pulling more power from the grid. Nvidia can’t exactly force</t>
+          <t>US government website used AI search tool from China that FBI said copied Anthropic    Reuters</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>blackwell, nvidia</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 23:37:05 +0200</t>
+          <t>Thu, 17 Sep 2026 19:58:00 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4208,13 +4208,13 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/16/nvidia-goes-green-to-keep-grid-capacity-from-zapping-its-revenues/5296984</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQSTBHb0F3bjFOTVY4RDExZ1Q4SUVqOEppWEdrc0t0TUhUc0NZNG0yZl9Da2daU1RyRnZPYlMzSDRRM0UzTlgwSHpTTDBKR201eVJocll5WHhKdDZNekVTTnBiQmhLaGZaaXZXQTBPRncxNjVUQjNIWU50RWRNd19wNmR4VGdNMzJEeGpoMXRNSG9Bd1JYc0ZYemZkUXZGUXBLRVBLYnozN1FmZ1dlcTYwdHU0aEtxd2RJOC1jb1M5empFdmNSWEV5bzAwTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -4226,12 +4226,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4239,25 +4239,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Developer vibe codes a tool to let Nvidia RTX 50-series laptop owners crank up their power limits — can juice RTX 5090 mobile GPU to 225W</t>
+          <t>Amazon-owned Zoox’s 100-robotaxi limit in Nevada is about to disappear</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
+          <t>An updated permit shows the 100-cap will expire later this month just as competition in Las Vegas heats up.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd, gpu</t>
+          <t>robotaxi, amazon</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 15:19:42 +0000</t>
+          <t>Thu, 17 Sep 2026 23:08:24 +0000</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4267,30 +4267,30 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/overclocking/developer-vibe-codes-a-tool-to-let-nvidia-rtx-50-series-laptop-owners-crank-up-their-power-limits-can-juice-rtx-5090-mobile-gpu-to-225w</t>
+          <t>https://techcrunch.com/2026/09/17/amazon-owned-zooxs-100-robotaxi-limit-in-nevada-is-about-to-disappear/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.64</v>
+        <v>5.85</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4298,25 +4298,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Apple might make servers again to cash in on the AI rush</t>
+          <t>Cute Critters Come to the Cloud: ‘Aniimo’ Launches on GeForce NOW</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Apple might make servers again to cash in on the AI rush    The Verge</t>
+          <t>Cute Critters Come to the Cloud: ‘Aniimo’ Launches on GeForce NOW    NVIDIA Blog</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>nvidia, geforce</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.8</v>
+        <v>11.9</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 17:20:29 GMT</t>
+          <t>Thu, 17 Sep 2026 13:08:21 GMT</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4326,16 +4326,16 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBkNUJHWndhSENNek9OaUdPZnZXNlVCaVBwS3p0X3RUczY4WkM4WmRZV2ZEMzlPdDZVd09FQ21ZWjlLaEJLd1daN3IwczRzcEFxTjJreDJiQzNfTXNJWXo2VGtzMWFCTXB5dEhwaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE02a0FvaWpHem5QUWZvcUhNY0JLWkxvWmVzTW1uRHpjRC1oNk5ybWtuVk5FWlNyTzBfMXJjbEhkeXI4V0xRMWtlbzZTRUpYTE1PMTBaa0RNRm1aUEpEZXVkaWdhN2s2MEZoTUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.61</v>
+        <v>5.77</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4357,25 +4357,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Former Waymo CFO jumps to self-driving startup Wayve</t>
+          <t>Microsoft AI chief warns Anthropic not to put ideas in Claude's head</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Elisa de Martel, who left her position as chief financial officer at Alphabet's autonomous vehicle company Waymo in January, will be based out of Silicon Valley.</t>
+          <t>Microsoft AI chief warns Anthropic not to put ideas in Claude's head    The Register</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>waymo, alphabet</t>
+          <t>microsoft, anthropic</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6</v>
+        <v>12.8</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 19:02:49 +0000</t>
+          <t>Thu, 17 Sep 2026 12:15:00 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4385,25 +4385,25 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/former-waymo-cfo-jumps-to-self-driving-startup-wayve/</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOTnFrTHJicG1DaE9FXzFJRGxUOWMzdjlRUHUwLTdqWEh3S09ZRWt2MEdUbTBzWmlKbW5ITmFjWVVLNk1YWTVsaFY1QW9JWTV2SW5uUWtZeFZyQ0NsZ0NXUWNyaUJKek1mNzRsOHY1SnBXbWtlMXNBRFFxdWk2Vlc1cUdOWUVrcTUwQmpmNmFXbGY4UkdaTWV2QWNGZk9nWlJ0aTY3b2hfMVlIb0lyc2ZBQkk1b2xpUmwyZzE4NlpUVEdfdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.61</v>
+        <v>5.76</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Your AI agents can now control your Google Home devices</t>
+          <t>The new CC, an AI agent built for families</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Google is launching early access to a new MCP server for Google Home, allowing AI agents like Claude, ChatGPT, and others to control connected devices, review camera summaries, and access smart home activity using natural language.</t>
+          <t>The new CC, an AI agent built for families    blog.google</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -4430,11 +4430,11 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8.1</v>
+        <v>6.6</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 17:00:00 +0000</t>
+          <t>Thu, 17 Sep 2026 18:26:50 GMT</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4444,16 +4444,16 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/your-ai-agents-can-now-control-your-google-home-devices/</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOQ1Yyb2o3UElpUVd5dGExbzlPaDdpakhNZl9zamk4VHl6eV94bVRleTBWaWdlcXVadDJvUkJnSGxhSDkxSzJ0SWdUQ3VJWVF0MHRxWE9IQjdQYXBSeEIzY09FZU1RNEx2a1FEVncyNzJ4NHhKXy1IYVYzQmY5SjV1N3JDZldCcFlKZjZYWkh2QU5vSFBEYkJzYQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.61</v>
+        <v>5.74</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -4462,12 +4462,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4475,25 +4475,26 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Your AI agents can now control your Google Home devices</t>
+          <t>Microsoft AI CEO says AI threats are real, and Anthropic is making it worse</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Your AI agents can now control your Google Home devices    TechCrunch</t>
+          <t>Today, I’m talking with Mustafa Suleyman, the CEO of Microsoft AI. As you’re no doubt aware, the biggest story in tech right now is the spiraling debate about AI safety and regulation.  
+ It should come as no surprise that Mustafa has strong opinions on how AI should be built and regulated. Microso</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>mustafa suleyman, microsoft, anthropic</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 17:00:00 GMT</t>
+          <t>2026-09-17T10:00:00-04:00</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4503,13 +4504,13 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNOUMzdnhvVTFGWjdfOEtJbnpSczJadWo5TXlmOGRrRmh0eG5aQzVfUU1Bbnh3TklyVkZWcWdjVTl0enBSSWtObm9UcUt2YlpsOGlNa3pQU0lsM2t2YnBGVHB5UmJaTFQwal8zcml0N1FFSFN3eklhYTdSUzNfSEltZmdnNWsxdkFpZFlEMmctOVQyeEk5?oc=5</t>
+          <t>https://www.theverge.com/podcast/996412/microsoft-ai-ceo-mustafa-suleyman-regulation-safety-anthropic-claude</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.57</v>
+        <v>5.69</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>2</v>
@@ -4521,12 +4522,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4534,25 +4535,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Anthropic merges Claude chat and Cowork in one interface</t>
+          <t>NVIDIA and Google's new coalition wants to speed up AI data center power grid connections</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Anthropic is initially releasing these features to Pro and Max plan subscribers.</t>
+          <t>A new coalition of tech giants aims to speed AI data center grid connections in exchange for more flexibility.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>nvidia, google</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8.6</v>
+        <v>13.6</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:30:00 +0000</t>
+          <t>Thu, 17 Sep 2026 11:24:45 +0000</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4562,13 +4563,13 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/anthropic-merges-claude-chat-and-cowork-in-one-interface/</t>
+          <t>https://www.engadget.com/2260986/nvidia-google-emerald-coalition-data-center-power/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.57</v>
+        <v>5.69</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>2</v>
@@ -4580,12 +4581,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4593,25 +4594,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Anthropic merges Claude chat and Cowork into one</t>
+          <t>NVIDIA and Google's new coalition wants to speed up AI data center power grid connections</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>From Claude to Cowork and back again – plus, Anthropic’s all-new Claude Docs.</t>
+          <t>NVIDIA and Google's new coalition wants to speed up AI data center power grid connections    Engadget</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>nvidia, google</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8.6</v>
+        <v>13.6</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T16:30:44Z</t>
+          <t>Thu, 17 Sep 2026 11:24:45 GMT</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4621,30 +4622,30 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/innovation/claude-chat-absorbs-cowork-anthropic/</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPcWREWXVKeWYyOF9LVTRGeVNfY1hGX2hEM2lpNnpIWWJlVDY3Wk1oNV9iVGxveEZTRE5kNEFWTTgtb0Y5TFBxSkZ0U2YxZDVVVTJaUzNJcmNVanQ2MUdFdm1iRmFYanh2VGlvdTNrV0JsdXdpdTZsaHBQWmlQeEhuRHBhSjBZLVhFX0FF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.52</v>
+        <v>5.66</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>about.fb.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4652,25 +4653,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Canadian Start-up smartARM Uses AI to Create Intuitive Bionic Prosthetics</t>
+          <t>The AI Superintelligence Slowdown</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Canadian Start-up smartARM Uses AI to Create Intuitive Bionic Prosthetics    meta.com</t>
+          <t>Remember when tech leaders would tell their employees to  “move fast and break things”?  It seemed that would be the way of AI too. But after a summer where rogue AI agents became reality, and researchers warned  that AI could kill us all , a number of leading US AI companies are publicly suggesting</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic, google</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.1</v>
+        <v>5.5</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:00:19 GMT</t>
+          <t>2026-09-17T15:28:24-04:00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4680,30 +4681,30 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQcWxjVkJ6d2ItTlhFRUxuOWRjTTAxZ3g5ME9ZZFRjLUMyVWRlZEpqNkhIZmN1NDI2YWZCTVdKbjBFNlhSR0prUkVfVXRsM3EzWVI1WEFWMEZFcTBzR096N1NwWkpLMEdhM0VUcWlfQVdkdDQtUFMzcHFydVV6dTFRZXgyRlo3YVU2RWZFRml3TUZ3cmRRSUdxZnJZYXFONTluMlRHcnFoNUNXTExI0gGyAUFVX3lxTFA2NnNzZFcyNk1JcVJKR3lrMnVtUnRJV00zRmt4WDRJYXZPTUMtemdmWGdpYzZURjFtUTltdjlJcVJ2VDVCemw1WEZVU3luVFIwNmNjTE5rXzF2ZnF4X3VxN3U5a3d3eTdTMlFlUDB0V0hMV0RpNVJXeGc5eTZZREVxMlNsUm5jWFFZRWdZcnhQeDVLSC0tR0xMWS1ibkNxMGVkak5CRU5uQWtYYzdTMl8yTHc?oc=5</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/996923/ai-safety-slow-openai-anthropic</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.48</v>
+        <v>5.65</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>amd.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -4711,25 +4712,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>AMD Delivers Its Broadest MLPerf® Inference 6.1 Submission</t>
+          <t>Apple eyes Nvidia NVLink to power its new custom M8 Ultra AI servers — historically bitter rivals reportedly team up for 2029 data center push</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>AMD Delivers Its Broadest MLPerf® Inference 6.1 Submission    AMD</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>nvidia, apple</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 15:34:44 GMT</t>
+          <t>Thu, 17 Sep 2026 11:00:00 +0000</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4739,30 +4740,30 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZmRMNkg4V1U0YzJpNTA5MVJudFFZSDRVdTJnbDBrOHVLYWR4LXkxOGdYb09OVk9YUTZpZFZUYjJtZmdiZmEydmhBazJBSmswTmE5WEdHeXB1TC1XaE9OZEd2Tmo4aDgyY1E3eS1obDA4TXNOSlhCU1FxQ2tOVFl3UkYyVE5XTmozUFU5SzBvOUNoeXNfcnVoMFl3MWI?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/apple-eyes-nvidia-nvlink-to-power-its-new-custom-m8-ultra-ai-servers-historically-bitter-rivals-reportedly-team-up-for-2029-data-center-push</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.44</v>
+        <v>5.65</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4770,25 +4771,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5 things to know about teens' views on AI today</t>
+          <t>Apple eyes Nvidia NVLink to power its new custom M8 Ultra AI servers — historically bitter rivals reportedly team up for 2029 data center push</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>5 things to know about teens' views on AI today    blog.google</t>
+          <t>Apple eyes Nvidia NVLink to power its new custom M8 Ultra AI servers — historically bitter rivals reportedly team up for 2029 data center push    Tom's Hardware</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>nvidia, apple</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9.9</v>
+        <v>14</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 15:13:07 GMT</t>
+          <t>Thu, 17 Sep 2026 11:00:00 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4798,30 +4799,30 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOdk5IUnN0UkRFa190YzNSMWgwTGhRR1ZNc09uQ3RQTkFEMkNMdkxPbXROajNEN0FHTl9NMmRsS1NQVDJVMGo2cVdaZklQU0JMVTh6ZlRWTGNHS1NZQTJtQ0pYSUMxamw0NkFtWXM3YVpZbjJNLUtDVmplX1dmdExvOUJyWGZ6UTdiQnlOaWJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxPVWtZbGp2ejFFd1pibDJFX2UxUjRyN3R5MW5ick1Lckw4bXZjd04wbVNsSXFES09GRVFFMFlnbFdYNUhfeS1oRmhYODFGT0R6Qnp4QVRTMHdxQ0d5cXh0WnRBLTVSY0E0eW13RE5KQ0FFX0EtR1dWa2lFdzdxXzdxSEM5RUZDS2dRUTRxVGpiQ3dPdUx5V0YtOXZZTDdIdGlYR0FLSWlUdHdxVVdVUDJZLUw2VEdvczlfTGFjQ2ZVV2p3Njc2enQzZ044Y1pxNjVXOEItVld3Xy1rR080dkpkMGl5S0c3Qlh0VGpneXBBTnpTZ1VWVGdzOUlOT29DdGtSWDZWWGxzZkxWSFZxZFVQUlJHQTE2bHVnNEl0T1FMMHpUWExoQzBMMU1FaDZwOTVo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4829,25 +4830,25 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Apple explores AI server comeback, considers Nvidia's NVLink technology</t>
+          <t>Inside Track - Building a career in IT with a growth mindset: Kanu Priya’s Microsoft journey</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Apple explores AI server comeback, considers Nvidia's NVLink technology    livemint.com</t>
+          <t>Inside Track - Building a career in IT with a growth mindset: Kanu Priya’s Microsoft journey    Microsoft</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>apple, nvidia</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 16:54:45 GMT</t>
+          <t>Thu, 17 Sep 2026 15:45:00 GMT</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4857,30 +4858,30 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPaW9QVmlZeVdqNzNCemtabktDSElwZVpFMDVDMTFmZU05TUc1TUFJa044TUQ4Sk4wcWRSUG1hd212c3czcU9LX0ljTGdnS0xWUnFNdFY4SHhmbXBGdV9DZ1hHMFZ3d1FINjhWXy05Y2E1X0hDYzBqRjIxX2VzQkpXMFJ6Rkd3WWVGTzB5V1BXVGt2UTVVLXpDNUdsQzJSblNBRG9rRXJSQV9FY2tPY0pETUR6dklJZUVoOE5qZGR4UjJlbWPSAcgBQVVfeXFMTmVnbU91eVh0b0hscXVIelJ0TU5NLXV1ZDZ6ZkhKWU03anZac2ZySGoyWnNDX3ZuOWduLU1tN2xkMnJZdTZRRTRLS20wTnkzZHJhajctWUh5QkcxN2trd2h1VnduSFhfOTk0TFA3NEtROVV6U1RiX1FOR0R0QXJyNlhoM2dxSXhVVUNSazhzdlZSaDB5X1JDZEoyVlJFSjRNLThxcnNiNXR4LTFLV1U5UnluTUhoakM5ZUdzRzFlZi1kNWZVZFNEOUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxONmpjeEQzaWV1VzY5X0Q1UDFIdWRhaVFoYzJOaXBPalNGdmVRZUhmc0NiWS0yRkY3eTBidXVPazdCbEZONzNMWi1jbnI3ZGlrTnNDUmNiYWxieHpXMGpXM09uR0NkWWRidzRiWDlzZHV3bzFjczBKSVpsY3prQUR1VDhndFd1VjhaR2ZHOHpRd2ZrT3QzbUd6aXI5SkNZOFpkSlBFRmpWZmt2djYzVEVLMEJrT2cyMU1JNHA4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.37</v>
+        <v>5.43</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4888,26 +4889,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Claude comes for Gemini with its own take on Docs and Slides</t>
+          <t>What 40,000 agents reveal about the future of enterprise AI</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Claude is getting a pair of new tools today:  Docs and Slides . They'll let you create documents and presentations through Claude chats, which you can export, edit, and share with other users. 
- As part of the announcement, Anthropic is also simplifying how Claude chats work, merging regular chats a</t>
+          <t>What 40,000 agents reveal about the future of enterprise AI    Microsoft</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>gemini, anthropic</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T12:30:00-04:00</t>
+          <t>Thu, 17 Sep 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4917,30 +4917,30 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/996234/anthropic-one-claude-cowork-docs-slides</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNbnVwUWxra2drNVBTYVFnNmxHa1hiTWs1bFloc2NnNDhNeEtONGFDSGExMnpabDU5OVNOU3k5T1Zra1dnTXpDbkhPOWNVSFhwUVRoblhGak9EeUtKMEE5NUhQM1g4U2JTQ01jTGZ0c3ZrNm1FNk4tcF9hYjg1YWNxMHBMZ0Q3TUd1VHViN0pSOFJUMHVNSDdxZjJwRTJqNzctVUNYOVdBU2FiQVFhZGNRN2xCTDlRMi1kc09r?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.35</v>
+        <v>5.41</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4948,25 +4948,25 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Boost your holiday sales with these agentic commerce updates</t>
+          <t>Chip stocks surge: Intel jumps 10%; Marvell, AMD and Nvidia extend gains | Key triggers explained</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Boost your holiday sales with these agentic commerce updates    blog.google</t>
+          <t>Chip stocks surge: Intel jumps 10%; Marvell, AMD and Nvidia extend gains | Key triggers explained    Livemint</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>nvidia, amd</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10.9</v>
+        <v>8.1</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 14:13:55 GMT</t>
+          <t>Thu, 17 Sep 2026 16:56:02 GMT</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4976,13 +4976,13 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQOXdfNHRDVmZkUW1nM0hvRGljcjFaTk5vUDJtNF96RnRRMkxILVR3RUNKYnZ0anRkRnJSaDFxa2VsY1RwRmFLa3RyTVFqbnpPNWFZMjlGN1o1Nm5MRUU4eUJjUnl4UVZpaHJsUWo0Xy10R0JOa19BM25oUklVY1hheE1pUHBBZE9hQXVGQUhGS2ZGZFlIYU5GemhTVWhNODQxS3kyeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPTldfMl9fc2tXTmZHekh5Zmx6cEllZmQtQWdlUDJ5WklMYW9CQl9NTkFXNzlTLUR3blFZb2lHX04xdG43Q1hIZjJxdUkzbnpQSktjYzVhUjhSWU1Jcy1BdmdnLXVyeEtFaWt0LVpvN0U2RWtBT19xOEJXMUl5YTNVWkxCOG4tbk5wYVBOUHAtOHhlWXh0dDJCcC1mSFRld0N3YVNuaUQ3ekkwRVJ6Wk5Fc2tMZnFDYXVTTDA5UlA3MVA5M0Rqc0lLZ2lTTm1IcHRsYm5zVGhNcDBta0RaeDN3WEdyckxHc3huZm5LbzRzRElHVUnSAfgBQVVfeXFMTkM0TUsxUzhTSVhQN3NYU1daSVpaV2tNUzRBaDZWQlhvVmJXMEJuODBfd0pXTkZ3VWo0Vktpd1lSTVkyc2cyRVJueTY4VVJFWFh1d3dqQXVfVUV4enlBZ3BXMmU1am9SSTdMWUR1OFl3ckptVzBqSF9PcjZkRUt2a1VDU0RRZllNQWZ1MDlaYVBCSjJtRzdmTVNheDVZdjBNMk04VkY5dDVyQVN1aGJiVEMxcGkxNDNySmVCTndYQnhLRnVlYTRCNjRJSU85Zm1fYnp6VDJBQ3VFVERwR2J2eDZtVzVCMkxhRk8yemZZWTh1V2dUeENoQ0I?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.23</v>
+        <v>5.3</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -4994,12 +4994,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>brandinside.asia</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5007,26 +5007,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>ยุคสมัยของฟรีสิ้นสุดแล้ว? เปิดตัว Meta One แพ็กเกจเจาะกลุ่ม SME มี AI คิดคอนเทนต์ มีแอดมินให้ด้วย</t>
+          <t>Google's revamped CC is an AI agent for families and groups</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>ทำธุรกิจสมัยนี้ หาเงินทางเดียวก็คงไม่พอ  
-  เช่นเดียวกับ ‘Meta’ ที่ที่ผ่านมาให้ผู้ใช้งานใช้ Facebook, Instagram, และ WhatsApp ได้ฟรี โดยรายได้หลักมาจากการขายโฆษณาให้ธุรกิจ แต่เมื่อ ‘มาร์ก ซักเคอเบิร์ก’ เดินหน้าทุ่มเงินมหาศาลกับ AI และเพิ่มงบลงทุนด้านโครงสร้างพื้นฐาน บริษัทก็เริ่มมองหารายได้จากช่</t>
+          <t>CC gives an AI agent its own Google account in your family or group and sends all members a daily briefing.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>facebook, meta, instagram</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16.3</v>
+        <v>2.1</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 08:46:04 +0000</t>
+          <t>Thu, 17 Sep 2026 22:55:08 +0000</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5036,13 +5035,13 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://brandinside.asia/meta-launches-meta-one-subscription-across-flagship-apps/</t>
+          <t>https://www.engadget.com/2261924/google-cc-is-an-ai-agent-for-families-and-groups/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -5059,7 +5058,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -5067,25 +5066,25 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Apple's redesigned Health app is available now in the iOS 27.2 developer beta</t>
+          <t>Anthropic says Claude 'leads' 26 percent of its AI R&amp;D work</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>New features like Health Age bring Apple's app more in line with competitors like Whoop and Oura.</t>
+          <t>The company shared the stat alongside three measurements that help communicate the pace of AI development.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 21:18:43 +0000</t>
+          <t>Thu, 17 Sep 2026 22:30:01 +0000</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5095,13 +5094,13 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2260794/apple-s-redesigned-health-app-is-available-now-in-the-ios-27-2-developer-beta/</t>
+          <t>https://www.engadget.com/2261909/anthropic-says-claude-leads-26-percent-of-its-ai-research-and-development/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -5113,12 +5112,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5126,25 +5125,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Anthropic and OpenAI want to embed safety evaluators. Will they really be independent?</t>
+          <t>A Microsoft exec called AI scraping ‘theft of unprecedented proportions.’</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Anthropic and OpenAI want to embed independent safety evaluators inside their AI labs. Researchers welcome the unprecedented access, but warn meaningful oversight requires transparency, independence, and eventually regulation.</t>
+          <t>A Microsoft exec called AI scraping ‘theft of unprecedented proportions.’    The Verge</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 21:07:24 +0000</t>
+          <t>Thu, 17 Sep 2026 22:20:35 GMT</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5154,13 +5153,13 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/anthropic-and-openai-want-to-embed-safety-evaluators-will-they-really-be-independent/</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOMnBVYklVa0Qtc0l2b25PVnhYVU9ncUMtb1Z2MW90cE94a0JvVEhxSGVybkl2YVdZLUw1R1ZyZmNONjZFYTJTSmRWMVQ3ZmpVZDBCQ05TbmpjTnpza2EwYWRtQ0lDUE9oUTJqUWszMENuYWNXVnBEakFNT21CMXlIWDNyTFFLUm5IV29kOEpyTm1wbjVZTGdoYVFQZVdoSUJkb3NXcTgzd0U5SEhVdnE5REJUb0dsMTVidGgxLUtocTNaVDlNb3RjNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -5172,12 +5171,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5185,25 +5184,25 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Apple weighs Nvidia technology for potential server market return, The Information reports</t>
+          <t>Your robotaxi might be a narc</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Apple weighs Nvidia technology for potential server market return, The Information reports    Reuters</t>
+          <t>In early September, two teenagers got into a Waymo, but then ended up in the back of a police car. The robotaxi company said it detected "a violation of our terms of service involving a firearm," pulled the car over, and alerted emergency services, according to the   Los Angeles Times  . Police  arr</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>apple, nvidia</t>
+          <t>waymo, robotaxi</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 14:36:24 GMT</t>
+          <t>2026-09-17T11:00:00-04:00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5213,30 +5212,30 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZUItV2dPTnNzdl9Fd0RxZlFSWm5fTGwwMmpYc3hBYThTellLMWhESUprY3UyME5SdWtVNVBmWmpJbllMRkYyOGc4d3liVlYxdlgyX2JWYnRRWUluUWd0Tm1fY2ptd2w0MHNYNkZKS2FOR3ktSkxuc0FBUnYxc01sdGVXN1RfRVZ2Z1h1bzBPa0htT2tsYVRfVzV0a0F1Vnpua3RRT2FadUwwdnotaG5RcHItNlZadw?oc=5</t>
+          <t>https://www.theverge.com/transportation/996863/robotaxi-waymo-police-privacy-surveillance</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.17</v>
+        <v>5.15</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>news.microsoft.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -5244,25 +5243,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Microsoft Highlights Next-Gen AI Landscape, Driving Digital Inclusion Through Safe, Transparent, and Locally Grounded AI</t>
+          <t>Investigation details how billions' worth of export-restricted Nvidia AI chips are sold to China — report details how Chinese firms skirt Trump's regulations</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Microsoft Highlights Next-Gen AI Landscape, Driving Digital Inclusion Through Safe, Transparent, and Locally Grounded AI    Microsoft Source</t>
+          <t>Bruno Ferreira's journey kicked off with the venerable ZX Spectrum, a cassette player, and his hopes and dreams. He quickly realized he had more fun figuring out how computers work than he did actually using the things. Kicking off a developer career with C and Assembly before moving to scripting la</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 12:18:06 GMT</t>
+          <t>Thu, 17 Sep 2026 12:00:00 +0000</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5272,16 +5271,16 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQVy1Kem8xZ2RhWU1PakJYeS00dXFyN05wTzY5Q2tqT1hZdVRxUUJLRjBTSzBRRDNLeHgwUm94cHZ1YzJqTDB5LVlhNVJXOGNyMzFWQllOQmlBVjgtQ0EwVTJvTDFEVXhuWWFlcTNTcWFJYzVEbm93S2d0clc5Mk03YldURnRNd0JXYV9UNTFLM3NYaWJ0MTF4Y0tJMzVVRHFDT0ZKaUFfZXpkY2lCY2xFandfRGI1TEFQX0ZjM1h3LV8?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/billions-worth-of-export-restricted-ai-accelerators-sold-to-china-report-details-how-chinese-firms-skirt-trumps-regulations</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.16</v>
+        <v>5.15</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -5290,12 +5289,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -5303,25 +5302,25 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>OpenAI, Microsoft fend off part of software developer lawsuit over AI training</t>
+          <t>Investigation details how billions' worth of export-restricted Nvidia AI chips are sold to China — report details how Chinese firms skirt Trump's regulations</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>OpenAI, Microsoft fend off part of software developer lawsuit over AI training    Reuters</t>
+          <t>Investigation details how billions' worth of export-restricted Nvidia AI chips are sold to China — report details how Chinese firms skirt Trump's regulations    Tom's Hardware</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 20:35:43 GMT</t>
+          <t>Thu, 17 Sep 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5331,30 +5330,30 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbUNoRUZpb0NvNUtWS1hEZEt2d3ByaTFxM0w0MThMX2FrR0o2cktvZFdjNTR5dE5iXzN4Mnl1WGVMek1hcVk5bDRvZFZ5VFl4YUtNQnF2X25PenB4em1KZjBfUGNzXzNuNU1fakhlczRtdjRBSUhKZHdlRUFkTEFaemh0MlJ3aV9VbjRyRWVyR1ZweVJXT3F0T1lxdEk3RjZUX1N6aUxfMUN0NF9UQ1hwRXVPZGFKc1ZwUUJlSnlFMnE2eURoUGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNN2NrR0NpT2hTbHdLcmFUcmVUSEFENVJYNVRXNGRSLXZWWjBuVzNvb3Fpbk5pTWhianJybUt5N2YwNFZxdnpJZ1IxRUhVeFZyYjcwZDFQWnlQY2VDMjFpT3dyNERXd2RuSVBlM2RYR1N0WXBNamFhalNnNjdJN2duUnozVTFoSXdXZHd4ZUhrOUVudU15Um85YzVWc3M0WmxFVV8tRUJkQXJzaWtCWnZzRGZ5Tm5nVlhUT2JGNDNYbkJ5bmFHQTVlLTlPTzZVSU9fZ0szWXgwUnR0Y0I3b2pqcmF5UzBxcE0xSGlrMVRYNUFQbnZHbG42UjlKSE5oS0RGSlo0WTdqUXVUT2hhVWxtX255cldYWXYxdVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.15</v>
+        <v>5.12</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -5362,25 +5361,25 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>We’re catalyzing megaton-scale climate impact in Brazil</t>
+          <t>Rival AI agents, Instinct and Meta’s Muse, both add the ability to make calls</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>We’re catalyzing megaton-scale climate impact in Brazil    blog.google</t>
+          <t>Rival AI agents, Instinct and Meta’s Muse, both add the ability to make calls    TechCrunch</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>instinct, meta</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>13</v>
+        <v>11.2</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 12:08:31 GMT</t>
+          <t>Thu, 17 Sep 2026 13:46:16 GMT</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5390,30 +5389,30 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdmZTN29KcDlrSHF1N09Hb1JMSVEtb0k2OG1iMmtMeWlpZ1BkOGdnbm1pZ3VPWG5oV2phMFRUaGpjaXQ4cU8xRTRNbHZ3Rzl3anB3SWhVNnJrNFpVYVR1Z0Q0QnM0bHZtUXNyQ2xsRkpQcUxScGtPUmhHY1E3Y0lYYW9raV8yX2F2NzdVeU81TThKZjZNX2F4d2V2bzZxSEFGNktFVFdPSWNLUmxnNG55NFdxNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQdE1WVzdXbDBBM2kwaHpnb21tTnBWZUJSdE9VTFNSMThaMHB3Zk16TjRHdTBrYlM1UWs3eUttVHBYc3ZJcC14YUlvOFgxeElfNmFvSFFEWmVDYzhHc18yVXM1WVl5MUdkVFloUFVBemotaDBMNTBSTkVhOW90YUJNZWtnbG5tRGZVNk5IdlhxMG1fUnVxSmVfUmZsQWNCOUs3MzVaY3NkOWdLOEc0eHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>theinformation.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -5421,25 +5420,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Apple Considers Return to Server Market, Has Talked With Nvidia to Use Network Tech</t>
+          <t>AI model watermarking changes agent behavior</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Apple Considers Return to Server Market, Has Talked With Nvidia to Use Network Tech    theinformation.com</t>
+          <t>Watermarks that European law requires be added to AI-generated content to establish provenance may come at a cost. According to Lasso Security, AI model watermarking changes how AI agents handle tools and safety refusals. The altered behavior isn't necessarily worse but can be, particularly under ad</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>apple, nvidia</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 13:00:00 GMT</t>
+          <t>Thu, 17 Sep 2026 15:00:00 +0200</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5449,13 +5448,13 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNMHdQT2Zxd0JVbjFqZzExRndyakw5Q0loY1cwYTR1dk9xNDRXMmdyWlh4bWNkQmFDTU5wUFhvZ3NmVlV2b285TXoyN1RMbGt4RXpwMllPSDFyWThld2RMWEdyTWpzN01ManE1UFpYTDZmeGhod3c0QXJTcE1KZ2VuNkZfTVlQYzlyUTdicFhVcHh0RnU2X0QtWUhDX1p1a1dSNnNKN0ZxOGdoa2s?oc=5</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/17/ai-model-watermarking-changes-agent-behavior/5296998</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.12</v>
+        <v>4.99</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -5467,7 +5466,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5480,12 +5479,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>After accusations of selling ‘perv glasses,’ Meta prepares to sell a pair without a camera</t>
+          <t>Meta ordered to remove UK deepfakes as oversight board criticises ‘inadequate’ safeguards</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Can Meta dodge the "pervert glasses" accusations with a new camera-free product?</t>
+          <t>Meta ordered to remove UK deepfakes as oversight board criticises ‘inadequate’ safeguards    The Guardian</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5494,11 +5493,11 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 20:12:00 +0000</t>
+          <t>Thu, 17 Sep 2026 18:44:00 GMT</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5508,7 +5507,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/after-accusations-of-selling-perv-glasses-meta-prepares-to-sell-a-pair-without-a-camera/</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQcmJpU0hva1VFcm1ic3llUS1Ba202LVBiMUlZMVVuM3E1aXhud3pWQ3FsQlNHZDlBTmluT1Zab2dQY0NhRW1CZ0FsTVVvZlQyVGJjYjVKWFg2YTFGY0dsR3MxN1VSSVFoamY3Vm1LX2piRzFFdGhDbzFvRnM3cEJzVGNIMTVKbHNpUHZ0VXpRWHRDMUoyVjYtM3Q2YlpJNnF5R3FwOHdmN0Fpa3pKbExqMnJfMTBnd0gyV3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -5632,26 +5631,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8.24</v>
+        <v>7.68</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.14+sig1.2+src2.0+corr2.4+wl1.5</t>
+          <t>rec1.98+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Emerald AI, Google and NVIDIA Launch Alliance to Advance Flexible AI Data Centers</t>
+          <t>OpenAI, Microsoft executives' quotes on AI training threaten copyright defense, news outlets argue</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>google, nvidia</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -5659,12 +5658,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/ai-energy-management-alliance/</t>
+          <t>https://www.reuters.com/business/media-telecom/openai-microsoft-executives-quotes-ai-training-threaten-copyright-defense-news-2026-09-17/</t>
         </is>
       </c>
     </row>
@@ -5673,16 +5672,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.95</v>
+        <v>7.68</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.65+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.98+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness</t>
+          <t>OpenAI, Microsoft executives' quotes on AI training threaten copyright defense, news outlets argue</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5692,20 +5691,20 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>microsoft, anthropic</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/microsoft-ai-chief-calls-out-anthropics-approach-ai-consciousness-2026-09-16/</t>
+          <t>https://www.channelnewsasia.com/business/openai-microsoft-executives-quotes-ai-training-threaten-copyright-defense-news-outlets-argue-6393266</t>
         </is>
       </c>
     </row>
@@ -5714,39 +5713,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.8</v>
+        <v>7.53</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.9+sig2.4+src2.0+corr0.0+wl1.5</t>
+          <t>rec1.83+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Real World Analysis of Ideal AI Workloads for NVIDIA Vera on OCI</t>
+          <t>Microsoft exec called AI scraping the “largest theft of labor in human history”</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>oci, oracle, vera, nvidia</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>arstechnica.com</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/ai-workloads-for-nvidia-vera-on-oci</t>
+          <t>https://arstechnica.com/tech-policy/2026/09/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history/</t>
         </is>
       </c>
     </row>
@@ -5755,16 +5754,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7.53</v>
+        <v>7.49</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.23+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.79+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness</t>
+          <t>Microsoft exec called AI scraping ‘the largest theft of labor in human history,’ new unredacted filings reveal</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5774,20 +5773,20 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>microsoft, anthropic</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/microsoft-ai-chief-calls-out-anthropics-approach-ai-consciousness-6389491</t>
+          <t>https://techcrunch.com/2026/09/17/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history-new-unredacted-filings-reveal/</t>
         </is>
       </c>
     </row>
@@ -5796,39 +5795,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.9</v>
+        <v>7.49</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.79+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Banks provide $22 billion chip loan to Blackstone, Alphabet AI cloud venture, source says</t>
+          <t>Microsoft exec called AI scraping ‘the largest theft of labor in human history,' new unredacted filings reveal</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>alphabet</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/banks-provide-22-billion-chip-loan-blackstone-alphabet-cloud-venture-bloomberg-2026-09-16/</t>
+          <t>https://techcrunch.com/2026/09/17/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history-new-unredacted-filings-reveal/</t>
         </is>
       </c>
     </row>
@@ -5837,39 +5836,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.9</v>
+        <v>6.93</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.2+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.93+sig0.6+src0.5+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Zuckerberg distances Meta from calls for a coordinated approach on an AI slowdown</t>
+          <t>Amazon Says AI Models Should Be Released When ‘Ready and Safe’</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/ai-zuckerberg-meta-slowdown-2f4eab05b1e931456d00ebc2fe93c989</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-17/amazon-says-ai-models-should-be-released-when-ready-and-safe</t>
         </is>
       </c>
     </row>
@@ -5878,39 +5877,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.84</v>
+        <v>6.7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.24+sig1.2+src0.5+corr2.4+wl1.5</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI Chief Warns Anthropic’s Humanlike Claude Is Risky</t>
+          <t>Google DeepMind launches institute to widen the AGI debate</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>microsoft, anthropic</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-16/microsoft-ai-chief-warns-anthropic-s-humanlike-claude-is-risky</t>
+          <t>https://techcrunch.com/2026/09/17/google-deepmind-launches-institute-to-widen-the-agi-debate/</t>
         </is>
       </c>
     </row>
@@ -5919,26 +5918,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.63</v>
+        <v>6.7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.33+sig1.8+src2.0+corr0.0+wl1.5</t>
+          <t>rec2.0+sig1.2+src2.0+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Vera Rubin NVL72 Delivers Leading Performance in MLPerf Inference v6.1 Debut</t>
+          <t>What AWS's CTO told employees about the future of AI</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>vera, rubin, nvidia</t>
+          <t>aws, amazon</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -5946,12 +5945,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>aboutamazon.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/vera-rubin-nvl72-mlperf-inference/</t>
+          <t>https://www.aboutamazon.com/news/aws/aws-cto-future-of-ai</t>
         </is>
       </c>
     </row>
@@ -5960,26 +5959,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.26</v>
+        <v>6.7</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.56+sig1.2+src2.0+corr0.0+wl1.5</t>
+          <t>rec2.0+sig1.2+src2.0+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>What’s new in Copilot Studio: Updates to multi-agent systems | Microsoft Copilot Blog</t>
+          <t>Scaling 1,000 AI Agents on Oracle Cloud Infrastructure Kubernetes Engine and File Storage</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>copilot, microsoft</t>
+          <t>oracle, oracle cloud</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -5987,12 +5986,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/copilot/blog/copilot-studio/new-and-improved-multi-agent-orchestration-connected-experiences-and-faster-prompt-iteration/</t>
+          <t>https://blogs.oracle.com/cloud-infrastructure/scaling-1000-agents-on-oke-and-fss</t>
         </is>
       </c>
     </row>
@@ -6001,16 +6000,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.55+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.2+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Apple might make servers again to cash in on the AI rush</t>
+          <t>Google, Nvidia, and Anthropic want Emerald AI to find space on the grid for more data centers</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6020,7 +6019,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>apple, nvidia</t>
+          <t>nvidia, anthropic, google</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -6028,12 +6027,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996321/apple-servers-ai-nvidia</t>
+          <t>https://techcrunch.com/2026/09/17/google-nvidia-and-anthropic-want-emerald-ai-to-find-space-on-the-grid-for-more-data-centers/</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6079,157 +6078,157 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Nvidia  (Tier 1 · 12 stories)</t>
+          <t>Microsoft  (Tier 1 · 12 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8.24</v>
+        <v>7.68</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Emerald AI, Google and NVIDIA Launch Alliance to Advance Flexible AI Data Centers</t>
+          <t>OpenAI, Microsoft executives' quotes on AI training threaten copyright defense, news outlets argue</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/ai-energy-management-alliance/</t>
+          <t>https://www.reuters.com/business/media-telecom/openai-microsoft-executives-quotes-ai-training-threaten-copyright-defense-news-2026-09-17/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.8</v>
+        <v>7.68</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Real World Analysis of Ideal AI Workloads for NVIDIA Vera on OCI</t>
+          <t>OpenAI, Microsoft executives' quotes on AI training threaten copyright defense, news outlets argue</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/ai-workloads-for-nvidia-vera-on-oci</t>
+          <t>https://www.channelnewsasia.com/business/openai-microsoft-executives-quotes-ai-training-threaten-copyright-defense-news-outlets-argue-6393266</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6.63</v>
+        <v>7.53</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Vera Rubin NVL72 Delivers Leading Performance in MLPerf Inference v6.1 Debut</t>
+          <t>Microsoft exec called AI scraping the “largest theft of labor in human history”</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>arstechnica.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.nvidia.com/blog/vera-rubin-nvl72-mlperf-inference/</t>
+          <t>https://arstechnica.com/tech-policy/2026/09/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.25</v>
+        <v>7.49</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Apple might make servers again to cash in on the AI rush</t>
+          <t>Microsoft exec called AI scraping ‘the largest theft of labor in human history,’ new unredacted filings reveal</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996321/apple-servers-ai-nvidia</t>
+          <t>https://techcrunch.com/2026/09/17/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history-new-unredacted-filings-reveal/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.1</v>
+        <v>7.49</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Snap targets enterprises with Salesforce, Nvidia AI tools for augmented-reality glasses</t>
+          <t>Microsoft exec called AI scraping ‘the largest theft of labor in human history,' new unredacted filings reveal</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/snap-targets-enterprises-with-salesforce-nvidia-ai-tools-augmented-reality-2026-09-16/</t>
+          <t>https://techcrunch.com/2026/09/17/microsoft-exec-called-ai-scraping-the-largest-theft-of-labor-in-human-history-new-unredacted-filings-reveal/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.1</v>
+        <v>6.37</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Snap targets enterprises with Salesforce, Nvidia AI tools for augmented-reality glasses</t>
+          <t>Microsoft AI chief warns Anthropic not to put ideas in Claude's head</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOOFJHdndkVnV5RXpZUVV0NFZ3UmlwRVBLSFFWU1pUREJPWS1UZFlRSEotYWk3eXFzbDAxRnBHQWtDYUxBcm9HN09XZGk0cmF3eEtMdm9ORFJoY1RaY1ZIR0c5cTVNckoyOVNSUzN5dWVKd0U2dkNkM3RvdFdnUElxTmd5d3FGQ3lxNjNjUTNkYU5Md3BPS212RGd4LWpPbE16ZG5CRUVyN0xxUFhBaEtMNXhYSjBTNXUtbGk3X04yVHpHRGFw?oc=5</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/17/microsoft-ai-chief-warns-anthropic-not-to-put-ideas-in-claudes-head/5297149</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5.9</v>
+        <v>6.19</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Snap tries to bring AR glasses to enterprise market, partnering with Nvidia, AWS and Salesforce</t>
+          <t>What we’ve learned from Microsoft’s own AI transformation</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>blogs.microsoft.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBYdG9iNGlPc2VaZXA0V05rV3IzYV9McENRQTdCUWp6cEhHZEpNdnpyb2NDNUZjemszVm9xTkJVdmdCUWZGX2YyNjZwVmxJbGFmcE5KcFM1VXNaTFF1b0V4bmxsZmpXYzNfaVJOSkdydUHSAXZBVV95cUxQWjhpb3NFWGg1RVBHc3RmbGN1OWFGaVdzYzItc3BWWVZpWkl4c3pCeW5PaEkyZHVGdlU4T1BMNS12elU2SVFWVDFoYjAtMTVHM2RRa3BrWHpSLXJXNHVTX1AtcVI0T2J4ekdnZDRxUG5rRmRha0NR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQMFB6UTVPdlNMZDJHMXQ5UUlHNUtBNTJFWTZONEw1MkFBSzAyeldTbWJkM3Exd3NGQjU2MVhSZGUyZlI2TEljVkZnUWRmX0RzaWg3UWdscjd0aktWa1VvMEdXbkxSWHRqVDNfeWZVcEU1OHJOQTBhVkVQd2tKLXpmU0NzVlE1U0NxMXIxQ1BGSGlmazhjVUtDeHBfNE4wSkxRRHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5.85</v>
+        <v>5.77</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Nvidia goes green to keep grid capacity from zapping its revenues</t>
+          <t>Microsoft AI chief warns Anthropic not to put ideas in Claude's head</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -6239,575 +6238,575 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/16/nvidia-goes-green-to-keep-grid-capacity-from-zapping-its-revenues/5296984</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOTnFrTHJicG1DaE9FXzFJRGxUOWMzdjlRUHUwLTdqWEh3S09ZRWt2MEdUbTBzWmlKbW5ITmFjWVVLNk1YWTVsaFY1QW9JWTV2SW5uUWtZeFZyQ0NsZ0NXUWNyaUJKek1mNzRsOHY1SnBXbWtlMXNBRFFxdWk2Vlc1cUdOWUVrcTUwQmpmNmFXbGY4UkdaTWV2QWNGZk9nWlJ0aTY3b2hfMVlIb0lyc2ZBQkk1b2xpUmwyZzE4NlpUVEdfdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5.85</v>
+        <v>5.74</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Developer vibe codes a tool to let Nvidia RTX 50-series laptop owners crank up their power limits — can juice RTX 5090 mobile GPU to 225W</t>
+          <t>Microsoft AI CEO says AI threats are real, and Anthropic is making it worse</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/overclocking/developer-vibe-codes-a-tool-to-let-nvidia-rtx-50-series-laptop-owners-crank-up-their-power-limits-can-juice-rtx-5090-mobile-gpu-to-225w</t>
+          <t>https://www.theverge.com/podcast/996412/microsoft-ai-ceo-mustafa-suleyman-regulation-safety-anthropic-claude</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Apple explores AI server comeback, considers Nvidia's NVLink technology</t>
+          <t>Inside Track - Building a career in IT with a growth mindset: Kanu Priya’s Microsoft journey</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPaW9QVmlZeVdqNzNCemtabktDSElwZVpFMDVDMTFmZU05TUc1TUFJa044TUQ4Sk4wcWRSUG1hd212c3czcU9LX0ljTGdnS0xWUnFNdFY4SHhmbXBGdV9DZ1hHMFZ3d1FINjhWXy05Y2E1X0hDYzBqRjIxX2VzQkpXMFJ6Rkd3WWVGTzB5V1BXVGt2UTVVLXpDNUdsQzJSblNBRG9rRXJSQV9FY2tPY0pETUR6dklJZUVoOE5qZGR4UjJlbWPSAcgBQVVfeXFMTmVnbU91eVh0b0hscXVIelJ0TU5NLXV1ZDZ6ZkhKWU03anZac2ZySGoyWnNDX3ZuOWduLU1tN2xkMnJZdTZRRTRLS20wTnkzZHJhajctWUh5QkcxN2trd2h1VnduSFhfOTk0TFA3NEtROVV6U1RiX1FOR0R0QXJyNlhoM2dxSXhVVUNSazhzdlZSaDB5X1JDZEoyVlJFSjRNLThxcnNiNXR4LTFLV1U5UnluTUhoakM5ZUdzRzFlZi1kNWZVZFNEOUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxONmpjeEQzaWV1VzY5X0Q1UDFIdWRhaVFoYzJOaXBPalNGdmVRZUhmc0NiWS0yRkY3eTBidXVPazdCbEZONzNMWi1jbnI3ZGlrTnNDUmNiYWxieHpXMGpXM09uR0NkWWRidzRiWDlzZHV3bzFjczBKSVpsY3prQUR1VDhndFd1VjhaR2ZHOHpRd2ZrT3QzbUd6aXI5SkNZOFpkSlBFRmpWZmt2djYzVEVLMEJrT2cyMU1JNHA4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5.19</v>
+        <v>5.43</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Apple weighs Nvidia technology for potential server market return, The Information reports</t>
+          <t>What 40,000 agents reveal about the future of enterprise AI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPZUItV2dPTnNzdl9Fd0RxZlFSWm5fTGwwMmpYc3hBYThTellLMWhESUprY3UyME5SdWtVNVBmWmpJbllMRkYyOGc4d3liVlYxdlgyX2JWYnRRWUluUWd0Tm1fY2ptd2w0MHNYNkZKS2FOR3ktSkxuc0FBUnYxc01sdGVXN1RfRVZ2Z1h1bzBPa0htT2tsYVRfVzV0a0F1Vnpua3RRT2FadUwwdnotaG5RcHItNlZadw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNbnVwUWxra2drNVBTYVFnNmxHa1hiTWs1bFloc2NnNDhNeEtONGFDSGExMnpabDU5OVNOU3k5T1Zra1dnTXpDbkhPOWNVSFhwUVRoblhGak9EeUtKMEE5NUhQM1g4U2JTQ01jTGZ0c3ZrNm1FNk4tcF9hYjg1YWNxMHBMZ0Q3TUd1VHViN0pSOFJUMHVNSDdxZjJwRTJqNzctVUNYOVdBU2FiQVFhZGNRN2xCTDlRMi1kc09r?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.13</v>
+        <v>5.3</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Apple Considers Return to Server Market, Has Talked With Nvidia to Use Network Tech</t>
+          <t>A Microsoft exec called AI scraping ‘theft of unprecedented proportions.’</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>theinformation.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNMHdQT2Zxd0JVbjFqZzExRndyakw5Q0loY1cwYTR1dk9xNDRXMmdyWlh4bWNkQmFDTU5wUFhvZ3NmVlV2b285TXoyN1RMbGt4RXpwMllPSDFyWThld2RMWEdyTWpzN01ManE1UFpYTDZmeGhod3c0QXJTcE1KZ2VuNkZfTVlQYzlyUTdicFhVcHh0RnU2X0QtWUhDX1p1a1dSNnNKN0ZxOGdoa2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOMnBVYklVa0Qtc0l2b25PVnhYVU9ncUMtb1Z2MW90cE94a0JvVEhxSGVybkl2YVdZLUw1R1ZyZmNONjZFYTJTSmRWMVQ3ZmpVZDBCQ05TbmpjTnpza2EwYWRtQ0lDUE9oUTJqUWszMENuYWNXVnBEakFNT21CMXlIWDNyTFFLUm5IV29kOEpyTm1wbjVZTGdoYVFQZVdoSUJkb3NXcTgzd0U5SEhVdnE5REJUb0dsMTVidGgxLUtocTNaVDlNb3RjNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Alphabet  (Tier 1 · 8 stories)</t>
+          <t>Nvidia  (Tier 1 · 10 stories)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Banks provide $22 billion chip loan to Blackstone, Alphabet AI cloud venture, source says</t>
+          <t>Google, Nvidia, and Anthropic want Emerald AI to find space on the grid for more data centers</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/banks-provide-22-billion-chip-loan-blackstone-alphabet-cloud-venture-bloomberg-2026-09-16/</t>
+          <t>https://techcrunch.com/2026/09/17/google-nvidia-and-anthropic-want-emerald-ai-to-find-space-on-the-grid-for-more-data-centers/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.9</v>
+        <v>6.31</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Snap is launching a new Specs AI tool, and it’s coming to iOS and Mac</t>
+          <t>Jensen Huang says Nvidia will sell twice as many chips next year</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/996078/snap-specs-intelligence-ai-agent-ios-mac</t>
+          <t>https://www.cnbc.com/2026/09/17/nvidia-huang-ai-chip-guidance.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.61</v>
+        <v>5.85</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Former Waymo CFO jumps to self-driving startup Wayve</t>
+          <t>Cute Critters Come to the Cloud: ‘Aniimo’ Launches on GeForce NOW</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/former-waymo-cfo-jumps-to-self-driving-startup-wayve/</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE02a0FvaWpHem5QUWZvcUhNY0JLWkxvWmVzTW1uRHpjRC1oNk5ybWtuVk5FWlNyTzBfMXJjbEhkeXI4V0xRMWtlbzZTRUpYTE1PMTBaa0RNRm1aUEpEZXVkaWdhN2s2MEZoTUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.61</v>
+        <v>5.69</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Your AI agents can now control your Google Home devices</t>
+          <t>NVIDIA and Google's new coalition wants to speed up AI data center power grid connections</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/your-ai-agents-can-now-control-your-google-home-devices/</t>
+          <t>https://www.engadget.com/2260986/nvidia-google-emerald-coalition-data-center-power/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.61</v>
+        <v>5.69</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Your AI agents can now control your Google Home devices</t>
+          <t>NVIDIA and Google's new coalition wants to speed up AI data center power grid connections</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNOUMzdnhvVTFGWjdfOEtJbnpSczJadWo5TXlmOGRrRmh0eG5aQzVfUU1Bbnh3TklyVkZWcWdjVTl0enBSSWtObm9UcUt2YlpsOGlNa3pQU0lsM2t2YnBGVHB5UmJaTFQwal8zcml0N1FFSFN3eklhYTdSUzNfSEltZmdnNWsxdkFpZFlEMmctOVQyeEk5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPcWREWXVKeWYyOF9LVTRGeVNfY1hGX2hEM2lpNnpIWWJlVDY3Wk1oNV9iVGxveEZTRE5kNEFWTTgtb0Y5TFBxSkZ0U2YxZDVVVTJaUzNJcmNVanQ2MUdFdm1iRmFYanh2VGlvdTNrV0JsdXdpdTZsaHBQWmlQeEhuRHBhSjBZLVhFX0FF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.44</v>
+        <v>5.65</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>5 things to know about teens' views on AI today</t>
+          <t>Apple eyes Nvidia NVLink to power its new custom M8 Ultra AI servers — historically bitter rivals reportedly team up for 2029 data center push</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxOdk5IUnN0UkRFa190YzNSMWgwTGhRR1ZNc09uQ3RQTkFEMkNMdkxPbXROajNEN0FHTl9NMmRsS1NQVDJVMGo2cVdaZklQU0JMVTh6ZlRWTGNHS1NZQTJtQ0pYSUMxamw0NkFtWXM3YVpZbjJNLUtDVmplX1dmdExvOUJyWGZ6UTdiQnlOaWJ3?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/apple-eyes-nvidia-nvlink-to-power-its-new-custom-m8-ultra-ai-servers-historically-bitter-rivals-reportedly-team-up-for-2029-data-center-push</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Boost your holiday sales with these agentic commerce updates</t>
+          <t>Apple eyes Nvidia NVLink to power its new custom M8 Ultra AI servers — historically bitter rivals reportedly team up for 2029 data center push</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQOXdfNHRDVmZkUW1nM0hvRGljcjFaTk5vUDJtNF96RnRRMkxILVR3RUNKYnZ0anRkRnJSaDFxa2VsY1RwRmFLa3RyTVFqbnpPNWFZMjlGN1o1Nm5MRUU4eUJjUnl4UVZpaHJsUWo0Xy10R0JOa19BM25oUklVY1hheE1pUHBBZE9hQXVGQUhGS2ZGZFlIYU5GemhTVWhNODQxS3kyeA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxPVWtZbGp2ejFFd1pibDJFX2UxUjRyN3R5MW5ick1Lckw4bXZjd04wbVNsSXFES09GRVFFMFlnbFdYNUhfeS1oRmhYODFGT0R6Qnp4QVRTMHdxQ0d5cXh0WnRBLTVSY0E0eW13RE5KQ0FFX0EtR1dWa2lFdzdxXzdxSEM5RUZDS2dRUTRxVGpiQ3dPdUx5V0YtOXZZTDdIdGlYR0FLSWlUdHdxVVdVUDJZLUw2VEdvczlfTGFjQ2ZVV2p3Njc2enQzZ044Y1pxNjVXOEItVld3Xy1rR080dkpkMGl5S0c3Qlh0VGpneXBBTnpTZ1VWVGdzOUlOT29DdGtSWDZWWGxzZkxWSFZxZFVQUlJHQTE2bHVnNEl0T1FMMHpUWExoQzBMMU1FaDZwOTVo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Chip stocks surge: Intel jumps 10%; Marvell, AMD and Nvidia extend gains | Key triggers explained</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>livemint.com</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxPTldfMl9fc2tXTmZHekh5Zmx6cEllZmQtQWdlUDJ5WklMYW9CQl9NTkFXNzlTLUR3blFZb2lHX04xdG43Q1hIZjJxdUkzbnpQSktjYzVhUjhSWU1Jcy1BdmdnLXVyeEtFaWt0LVpvN0U2RWtBT19xOEJXMUl5YTNVWkxCOG4tbk5wYVBOUHAtOHhlWXh0dDJCcC1mSFRld0N3YVNuaUQ3ekkwRVJ6Wk5Fc2tMZnFDYXVTTDA5UlA3MVA5M0Rqc0lLZ2lTTm1IcHRsYm5zVGhNcDBta0RaeDN3WEdyckxHc3huZm5LbzRzRElHVUnSAfgBQVVfeXFMTkM0TUsxUzhTSVhQN3NYU1daSVpaV2tNUzRBaDZWQlhvVmJXMEJuODBfd0pXTkZ3VWo0Vktpd1lSTVkyc2cyRVJueTY4VVJFWFh1d3dqQXVfVUV4enlBZ3BXMmU1am9SSTdMWUR1OFl3ckptVzBqSF9PcjZkRUt2a1VDU0RRZllNQWZ1MDlaYVBCSjJtRzdmTVNheDVZdjBNMk04VkY5dDVyQVN1aGJiVEMxcGkxNDNySmVCTndYQnhLRnVlYTRCNjRJSU85Zm1fYnp6VDJBQ3VFVERwR2J2eDZtVzVCMkxhRk8yemZZWTh1V2dUeENoQ0I?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
         <v>5.15</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>We’re catalyzing megaton-scale climate impact in Brazil</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>blog.google</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQdmZTN29KcDlrSHF1N09Hb1JMSVEtb0k2OG1iMmtMeWlpZ1BkOGdnbm1pZ3VPWG5oV2phMFRUaGpjaXQ4cU8xRTRNbHZ3Rzl3anB3SWhVNnJrNFpVYVR1Z0Q0QnM0bHZtUXNyQ2xsRkpQcUxScGtPUmhHY1E3Y0lYYW9raV8yX2F2NzdVeU81TThKZjZNX2F4d2V2bzZxSEFGNktFVFdPSWNLUmxnNG55NFdxNA?oc=5</t>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Investigation details how billions' worth of export-restricted Nvidia AI chips are sold to China — report details how Chinese firms skirt Trump's regulations</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/billions-worth-of-export-restricted-ai-accelerators-sold-to-china-report-details-how-chinese-firms-skirt-trumps-regulations</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 8 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.reuters.com/business/microsoft-ai-chief-calls-out-anthropics-approach-ai-consciousness-2026-09-16/</t>
+      <c r="A27" s="2" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Investigation details how billions' worth of export-restricted Nvidia AI chips are sold to China — report details how Chinese firms skirt Trump's regulations</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNN2NrR0NpT2hTbHdLcmFUcmVUSEFENVJYNVRXNGRSLXZWWjBuVzNvb3Fpbk5pTWhianJybUt5N2YwNFZxdnpJZ1IxRUhVeFZyYjcwZDFQWnlQY2VDMjFpT3dyNERXd2RuSVBlM2RYR1N0WXBNamFhalNnNjdJN2duUnozVTFoSXdXZHd4ZUhrOUVudU15Um85YzVWc3M0WmxFVV8tRUJkQXJzaWtCWnZzRGZ5Tm5nVlhUT2JGNDNYbkJ5bmFHQTVlLTlPTzZVSU9fZ0szWXgwUnR0Y0I3b2pqcmF5UzBxcE0xSGlrMVRYNUFQbnZHbG42UjlKSE5oS0RGSlo0WTdqUXVUT2hhVWxtX255cldYWXYxdVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft AI chief calls out Anthropic's approach to AI consciousness</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>channelnewsasia.com</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.channelnewsasia.com/business/microsoft-ai-chief-calls-out-anthropics-approach-ai-consciousness-6389491</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Alphabet  (Tier 1 · 7 stories)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6.84</v>
+        <v>6.7</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI Chief Warns Anthropic’s Humanlike Claude Is Risky</t>
+          <t>Google DeepMind launches institute to widen the AGI debate</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-09-16/microsoft-ai-chief-warns-anthropic-s-humanlike-claude-is-risky</t>
+          <t>https://techcrunch.com/2026/09/17/google-deepmind-launches-institute-to-widen-the-agi-debate/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6.26</v>
+        <v>5.92</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>What’s new in Copilot Studio: Updates to multi-agent systems | Microsoft Copilot Blog</t>
+          <t>Making global data easier to explore</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/copilot/blog/copilot-studio/new-and-improved-multi-agent-orchestration-connected-experiences-and-faster-prompt-iteration/</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOenNwVm9DX09YWXk5QkFvRmJseENwNVlZUUl0QkxpWjhTZjFraDl5WTFzVlExWHRNTF9lcDBjS2ZwRHI4X3dhcDh5U09na040enNySEZTZWRuM1gwRUhHNVBwQWI0ZzU1cXFKVFR6S2F3OHZGOVRPSHluNURFNHZxaHhJNkJUak1QMGFxXw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6.16</v>
+        <v>5.91</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Mistral joins Copilot Studio’s growing lineup of model providers</t>
+          <t>UN turns to Google to make its global data ready for AI agents</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/copilot/blog/copilot-studio/mistral-joins-copilot-studios-growing-lineup-of-model-providers/</t>
+          <t>https://techcrunch.com/2026/09/17/un-turns-to-google-to-make-its-global-data-ready-for-ai-agents/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.86</v>
+        <v>5.91</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s commitment for AI in education</t>
+          <t>UN turns to Google to make its global data ready for AI agents</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>blogs.microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQREhCWVMyMFMxTWgyQllNa3FxN2trb0h4YXFmZ1MxRkRwMFhsWUUtR1FLRDdpRW1UVWpmbTlNSzlwQmlqRXlERDZsWHV2RGRXbENhc0NTUEpKUnF0RlczV09jVml1aVV6LUxtblR0ZXYwUHNUNnQxRTNKa1hFTGJMb0pTOUZVQ3B6Q3Y2SE9IUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOVS1RNUxKOXRsU09Nb2tCc2JiNG9rUHplWlYtcFdtNDlheldCMVdPYzBYcUlpN0NjdURKZmRhSlBGWW40X2NKaUh6R0stbWhXb2haR0Y5ajJuY2dyNTAzOWcxaXJmWHhJYUtuR01UN1BwTlc0VjRTOF8tNXVka0xKTTZzSnItU0lGSVhlNXBPSlJhR2lfYlAwekFYMEFYUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.17</v>
+        <v>5.76</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Microsoft Highlights Next-Gen AI Landscape, Driving Digital Inclusion Through Safe, Transparent, and Locally Grounded AI</t>
+          <t>The new CC, an AI agent built for families</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>news.microsoft.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQVy1Kem8xZ2RhWU1PakJYeS00dXFyN05wTzY5Q2tqT1hZdVRxUUJLRjBTSzBRRDNLeHgwUm94cHZ1YzJqTDB5LVlhNVJXOGNyMzFWQllOQmlBVjgtQ0EwVTJvTDFEVXhuWWFlcTNTcWFJYzVEbm93S2d0clc5Mk03YldURnRNd0JXYV9UNTFLM3NYaWJ0MTF4Y0tJMzVVRHFDT0ZKaUFfZXpkY2lCY2xFandfRGI1TEFQX0ZjM1h3LV8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOQ1Yyb2o3UElpUVd5dGExbzlPaDdpakhNZl9zamk4VHl6eV94bVRleTBWaWdlcXVadDJvUkJnSGxhSDkxSzJ0SWdUQ3VJWVF0MHRxWE9IQjdQYXBSeEIzY09FZU1RNEx2a1FEVncyNzJ4NHhKXy1IYVYzQmY5SjV1N3JDZldCcFlKZjZYWkh2QU5vSFBEYkJzYQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.16</v>
+        <v>5.3</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>OpenAI, Microsoft fend off part of software developer lawsuit over AI training</t>
+          <t>Google's revamped CC is an AI agent for families and groups</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNbUNoRUZpb0NvNUtWS1hEZEt2d3ByaTFxM0w0MThMX2FrR0o2cktvZFdjNTR5dE5iXzN4Mnl1WGVMek1hcVk5bDRvZFZ5VFl4YUtNQnF2X25PenB4em1KZjBfUGNzXzNuNU1fakhlczRtdjRBSUhKZHdlRUFkTEFaemh0MlJ3aV9VbjRyRWVyR1ZweVJXT3F0T1lxdEk3RjZUX1N6aUxfMUN0NF9UQ1hwRXVPZGFKc1ZwUUJlSnlFMnE2eURoUGc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Amazon  (Tier 1 · 4 stories)</t>
+          <t>https://www.engadget.com/2261924/google-cc-is-an-ai-agent-for-families-and-groups/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>AI model watermarking changes agent behavior</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>theregister.com</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/17/ai-model-watermarking-changes-agent-behavior/5296998</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic merges Claude chat and Cowork in one interface</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/09/16/anthropic-merges-claude-chat-and-cowork-in-one-interface/</t>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Amazon  (Tier 1 · 6 stories)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.57</v>
+        <v>6.93</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Anthropic merges Claude chat and Cowork into one</t>
+          <t>Amazon Says AI Models Should Be Released When ‘Ready and Safe’</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/innovation/claude-chat-absorbs-cowork-anthropic/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-17/amazon-says-ai-models-should-be-released-when-ready-and-safe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.37</v>
+        <v>6.7</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Claude comes for Gemini with its own take on Docs and Slides</t>
+          <t>What AWS's CTO told employees about the future of AI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>aboutamazon.com</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/996234/anthropic-one-claude-cowork-docs-slides</t>
+          <t>https://www.aboutamazon.com/news/aws/aws-cto-future-of-ai</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Anthropic and OpenAI want to embed safety evaluators. Will they really be independent?</t>
+          <t>Amazon enters AI safety fray, calls for "rigorous testing," safeguards</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/anthropic-and-openai-want-to-embed-safety-evaluators-will-they-really-be-independent/</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOZlc0aEIyZmgxVURSZXZnVWNic05GQW9SVmI1Y1JvbGVtYzR6RmFvMTFKUTBFNWNOaENqckFIdjY3NXh2dWNkZF9UUUY3VXpNbEVPYnZhZnk0N2kwWFNfWS1lNzlEdXNvTlkzRXFmM1dpTHMyOG9GTVdwZ3FkZGt1UXUwUklrWEtaeUdSdVR0WWxCTHdYNi00WFVKbmZRMWJXRFhDblNNM01HQXpGVHVrVFhUUlpHUDRiT1pVbHMyVlc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>US government website used AI search tool from China that FBI said copied Anthropic</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQSTBHb0F3bjFOTVY4RDExZ1Q4SUVqOEppWEdrc0t0TUhUc0NZNG0yZl9Da2daU1RyRnZPYlMzSDRRM0UzTlgwSHpTTDBKR201eVJocll5WHhKdDZNekVTTnBiQmhLaGZaaXZXQTBPRncxNjVUQjNIWU50RWRNd19wNmR4VGdNMzJEeGpoMXRNSG9Bd1JYc0ZYemZkUXZGUXBLRVBLYnozN1FmZ1dlcTYwdHU0aEtxd2RJOC1jb1M5empFdmNSWEV5bzAwTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Meta Platforms  (Tier 1 · 4 stories)</t>
+      <c r="A43" s="2" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>The AI Superintelligence Slowdown</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/996923/ai-safety-slow-openai-anthropic</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Zuckerberg distances Meta from calls for a coordinated approach on an AI slowdown</t>
+          <t>Anthropic says Claude 'leads' 26 percent of its AI R&amp;D work</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/ai-zuckerberg-meta-slowdown-2f4eab05b1e931456d00ebc2fe93c989</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Canadian Start-up smartARM Uses AI to Create Intuitive Bionic Prosthetics</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>about.fb.com</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQcWxjVkJ6d2ItTlhFRUxuOWRjTTAxZ3g5ME9ZZFRjLUMyVWRlZEpqNkhIZmN1NDI2YWZCTVdKbjBFNlhSR0prUkVfVXRsM3EzWVI1WEFWMEZFcTBzR096N1NwWkpLMEdhM0VUcWlfQVdkdDQtUFMzcHFydVV6dTFRZXgyRlo3YVU2RWZFRml3TUZ3cmRRSUdxZnJZYXFONTluMlRHcnFoNUNXTExI0gGyAUFVX3lxTFA2NnNzZFcyNk1JcVJKR3lrMnVtUnRJV00zRmt4WDRJYXZPTUMtemdmWGdpYzZURjFtUTltdjlJcVJ2VDVCemw1WEZVU3luVFIwNmNjTE5rXzF2ZnF4X3VxN3U5a3d3eTdTMlFlUDB0V0hMV0RpNVJXeGc5eTZZREVxMlNsUm5jWFFZRWdZcnhQeDVLSC0tR0xMWS1ibkNxMGVkak5CRU5uQWtYYzdTMl8yTHc?oc=5</t>
+          <t>https://www.engadget.com/2261909/anthropic-says-claude-leads-26-percent-of-its-ai-research-and-development/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>ยุคสมัยของฟรีสิ้นสุดแล้ว? เปิดตัว Meta One แพ็กเกจเจาะกลุ่ม SME มี AI คิดคอนเทนต์ มีแอดมินให้ด้วย</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>brandinside.asia</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>https://brandinside.asia/meta-launches-meta-one-subscription-across-flagship-apps/</t>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6816,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>After accusations of selling ‘perv glasses,’ Meta prepares to sell a pair without a camera</t>
+          <t>Rival AI agents, Instinct and Meta’s Muse, both add the ability to make calls</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -6827,108 +6826,101 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/16/after-accusations-of-selling-perv-glasses-meta-prepares-to-sell-a-pair-without-a-camera/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Apple  (Tier 1 · 2 stories)</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQdE1WVzdXbDBBM2kwaHpnb21tTnBWZUJSdE9VTFNSMThaMHB3Zk16TjRHdTBrYlM1UWs3eUttVHBYc3ZJcC14YUlvOFgxeElfNmFvSFFEWmVDYzhHc18yVXM1WVl5MUdkVFloUFVBemotaDBMNTBSTkVhOW90YUJNZWtnbG5tRGZVNk5IdlhxMG1fUnVxSmVfUmZsQWNCOUs3MzVaY3NkOWdLOEc0eHc?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Meta ordered to remove UK deepfakes as oversight board criticises ‘inadequate’ safeguards</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>theguardian.com</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQcmJpU0hva1VFcm1ic3llUS1Ba202LVBiMUlZMVVuM3E1aXhud3pWQ3FsQlNHZDlBTmluT1Zab2dQY0NhRW1CZ0FsTVVvZlQyVGJjYjVKWFg2YTFGY0dsR3MxN1VSSVFoamY3Vm1LX2piRzFFdGhDbzFvRnM3cEJzVGNIMTVKbHNpUHZ0VXpRWHRDMUoyVjYtM3Q2YlpJNnF5R3FwOHdmN0Fpa3pKbExqMnJfMTBnd0gyV3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Apple might make servers again to cash in on the AI rush</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTFBkNUJHWndhSENNek9OaUdPZnZXNlVCaVBwS3p0X3RUczY4WkM4WmRZV2ZEMzlPdDZVd09FQ21ZWjlLaEJLd1daN3IwczRzcEFxTjJreDJiQzNfTXNJWXo2VGtzMWFCTXB5dEhwaw?oc=5</t>
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Tesla  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>5.22</v>
+        <v>5.9</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Apple's redesigned Health app is available now in the iOS 27.2 developer beta</t>
+          <t>Amazon-owned Zoox’s 100-robotaxi limit in Nevada is about to disappear</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2260794/apple-s-redesigned-health-app-is-available-now-in-the-ios-27-2-developer-beta/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>AMD  (Tier 1 · 1 stories)</t>
+          <t>https://techcrunch.com/2026/09/17/amazon-owned-zooxs-100-robotaxi-limit-in-nevada-is-about-to-disappear/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Your robotaxi might be a narc</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/transportation/996863/robotaxi-waymo-police-privacy-surveillance</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>AMD Delivers Its Broadest MLPerf® Inference 6.1 Submission</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>amd.com</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZmRMNkg4V1U0YzJpNTA5MVJudFFZSDRVdTJnbDBrOHVLYWR4LXkxOGdYb09OVk9YUTZpZFZUYjJtZmdiZmEydmhBazJBSmswTmE5WEdHeXB1TC1XaE9OZEd2Tmo4aDgyY1E3eS1obDA4TXNOSlhCU1FxQ2tOVFl3UkYyVE5XTmozUFU5SzBvOUNoeXNfcnVoMFl3MWI?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Oracle  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Fusion Apps experts recommend these AI World sessions</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Scaling 1,000 AI Agents on Oracle Cloud Infrastructure Kubernetes Engine and File Storage</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>blogs.oracle.com</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQQjQtUzd1WlQxb3RrUG1TUVl1Znp4RUJuQjRwWkVnUVlTdDVYM0tXT2ZFa3lLSXhNYU1ONlZWRDZaUDBBNzMteFZial9VNWNWcDgyS2MwVl9wQldkb21DQ3g2NjRsREJFRUFUSi1TOEpkN3RfbnU1X1F1MTFRcmhEYzZhVWlDNjBKQjdHZlhZOE1RQ3J3aHcw?oc=5</t>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>https://blogs.oracle.com/cloud-infrastructure/scaling-1000-agents-on-oke-and-fss</t>
         </is>
       </c>
     </row>
@@ -6954,26 +6946,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5.3</v>
+        <v>4.93</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI agents ‘infiltrated Australian government website’</t>
+          <t>Leading semiconductor analyst says AMD should be investigated for 'treason' over availability of restricted chips in China</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>security Prime Minister has given OpenAI boss a stern talking-to Simon Sharwood Simon Sharwood APAC Editor Published thu 24 Sep 2026 // 01:03 UTC READ MORE OpenAI's Astra model went for a drive and no one died now Frontier AI keeps racing despite calls to slow down 1 day ago Campaigners tell Burnham not to trade away the UK's tech tax to please Trump 1 day ago GOV.UK founder warns AI gold rush cou</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, ai agent</t>
+          <t>amd, semiconductor, fab</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>12.1</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 02:03:03 +0200</t>
+          <t>Thu, 24 Sep 2026 13:00:44 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,16 +577,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/09/24/openai-agents-infiltrated-australian-government-website/5298702</t>
+          <t>https://www.tomshardware.com/tech-industry/leading-semiconductor-analyst-accuses-amd-of-treason-over-restricted-chips-availability-in-china-amd-blames-diversion-of-export-controlled-rfsoc-usd36-000-radar-silicon-allegedly-quoted-at-usd1-000-for-crowdfunding-project</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4.9</v>
+        <v>4.78</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The 7 biggest announcements</t>
+          <t>Docker's new sandboxes aim to contain AI agents for real</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Gadgets News Meta Connect 2026: The 7 biggest announcements ﻿This year’</t>
+          <t>ai and ml With Cloud Sandboxes, devs can keep agents at arm's length In a market where AI agents keep breaking the rules and escaping their containers, Docker has a new solution. On Thursday, the company debuted Cloud Sandboxes in a bid to keep AI agents within boundaries. Despite the existence and implementation of sandboxing technology as a way to limit the reach of AI agents, industry leaders l</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T20:00:33-04:00</t>
+          <t>Thu, 24 Sep 2026 21:51:26 +0200</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999593/meta-connect-2026-everything-announced</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/24/dockers-new-sandboxes-aim-to-contain-ai-agents-for-real/5298964</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4.7</v>
+        <v>4.52</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Meta made a Tamagotchi-like wearable for its Muse AI agent</t>
+          <t>Muse sure looks a lot like OpenClaw</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Meta/screenshot / AI Meta made a Tamagotchi-like wearable for its Muse AI agent Lucas Ropek 5:46 PM PDT · September 23, 2026 The AI amulet has become a bit of a cliché in the tech indust</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Report AI Tech Muse sure looks a lot like OpenClaw Meta’s new tool is very c</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>ai, instinct, ai agent</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.3</v>
+        <v>8</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 00:46:17 +0000</t>
+          <t>2026-09-24T13:10:38-04:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,16 +679,16 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-made-a-tamagotchi-like-wearable-for-its-muse-ai-agent/</t>
+          <t>https://www.theverge.com/report/1000180/muse-openclaw-instinct-lookalike</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Meta is making a standalone Muse AI gadget</t>
+          <t>Leading semiconductor analyst says AMD should be investigated for 'treason' over availability of restricted chips in China, AMD blames diversion of export-controlled RFSoC — $36,000 radar silicon allegedly quoted at $1,000 for crowdfunding project</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI Meta Meta is making a standalone Muse AI gadget The Muse Charm doesn</t>
+          <t xml:space="preserve">Tech Industry Leading semiconductor analyst says AMD should be investigated for 'treason' over availability of restricted chips in China, AMD blames diversion of export-controlled RFSoC — $36,000 radar silicon allegedly quoted at $1,000 for crowdfunding project News By Anton Shilov Published 12 hours ago Export-restricted hardware with 40 – 52 weeks lead times readily available in China (almost). </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>amd, semiconductor</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.8</v>
+        <v>12.1</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T20:15:20-04:00</t>
+          <t>Thu, 24 Sep 2026 13:00:44 GMT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,16 +730,16 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999750/muse-charm-meta-ai-hardware</t>
+          <t>https://www.tomshardware.com/tech-industry/leading-semiconductor-analyst-accuses-amd-of-treason-over-restricted-chips-availability-in-china-amd-blames-diversion-of-export-controlled-rfsoc-usd36-000-radar-silicon-allegedly-quoted-at-usd1-000-for-crowdfunding-project</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The biggest news and announcements</t>
+          <t>Ask HPE and NVIDIA the AI data question you cannot ask in public</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Updated Today, Sep 24, 2026, 12:15 AM UTC Meta Connect 2026: The bigges</t>
+          <t>paas and iaas EVENT Matt Rosoff chairs a Register roundtable with HPE and NVIDIA on data sovereignty in the AI era, off the record, in Washington EVENT: HPE and NVIDIA are sending their AI infrastructure leads to a dinner table in Washington where nothing said is on the record. The Register is hosting, our editor-in-chief Matt Rosoff takes the chair, and there is one table, on Thursday 29 October.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, nvidia, ai infrastructure</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.3</v>
+        <v>10.3</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T18:45:00-04:00</t>
+          <t>Thu, 24 Sep 2026 16:49:40 +0200</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998480/meta-connect-2026-biggest-news-announcements</t>
+          <t>https://www.theregister.com/paas-and-iaas/2026/09/24/sponsored/5298888</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>AMD begins to add GDDR7 support to its Linux GPU drivers</t>
+          <t>Gemini 3.8 Live with Live Avatar gives Google&amp;#8217;s AI a face</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Gemini 3.8 Live with Live Avatar gives Google’s AI a face Googl</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>gpu, amd, semiconductor, fab</t>
+          <t>gemini, ai</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 11:30:00 +0000</t>
+          <t>2026-09-24T15:59:26-04:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,16 +832,16 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-begins-to-add-gddr7-support-to-its-linux-gpu-drivers-changes-could-herald-use-of-advanced-memory-standard-with-next-gen-radeon-gpus</t>
+          <t>https://www.theverge.com/tech/1000328/google-gemini-ai-live-avatar-face</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>US diplomats told to say ‘super intelligence’ — not ‘artificial intelligence’ — after Trump’s call</t>
+          <t>AI ร้ายแรงกว่าอาวุธนิวเคลียร์? ทำไมนักวิจัยเตือน ปัญญาประดิษฐ์เสี่ยง ‘ฆ่ามนุษย์’ ภายใน 10 ปีข้างหน้า</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>apnews.com Performing security verification This website uses a security service to protect against malicious bots. This page is displayed while the website verifies you are not a bot. Ray ID: a3fdde07fd427678 Performance and Security by Cloudflare Privacy</t>
+          <t>คำเตือนเรื่องอันตรายจากปัญญาประดิษฐ์ กำลังเกิดขึ้นพร้อมกันทั้งในสหรัฐอเมริกาและสหราชอาณาจักร หลังนักวิจัยของบริษัท AI ชั้นนำลาออก พร้อมกล่าวหาว่า OpenAI และ Anthropic กำลัง ‘เอาชีวิตคนเป็นเดิมพัน’ ในการแข่งขันพัฒนา AI ให้มีความสามารถเหนือมนุษย์ ประเด็นสำคัญ นักวิจัย Anthropic ลาออก เตือนภัย AI อะไรบ้าง? ทำให้ไวรัสรุนแรง พัฒนาอาวุธร้ายแรง Anthropic พบการใช้ AI ทำอะไรบ้าง? เดโมแครต-รีพับลิกันจับมือต</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence</t>
+          <t>ai, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 23:45:00 GMT</t>
+          <t>Thu, 24 Sep 2026 20:00:50 GMT</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/trump-super-intelligence-rebrand-ai-diplomats-02123c7bf18c692a12b2b3e3b9ce30c5</t>
+          <t>https://thestandard.co/ai-risk-human-extinction-warning/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>The old cybersecurity model is breaking</t>
+          <t>Salesforce Agentforce vulns allowed 0-click CRM data theft, anonymous phishing</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. The old cybersecurity model is breaking Theresa Loconsolo 10:44 AM PDT · September 23, 2026 31 min Loading the player… As concern over AI safety and rogue agents continue to make headlines, it’s no sur</t>
+          <t>security 'SalesBleed' security flaws 'lead to very unexpected consequences' Security flaws in Salesforce Agentforce allowed poisoned leads to hijack its AI agents, silently steal CRM data without requiring a click, and send phishing messages under the agents’ identities. Zenity Labs uncovered the three vulnerabilities, collectively called SalesBleed, and reported them to Salesforce, which worked w</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ai, instinct, ai safety</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 17:44:02 +0000</t>
+          <t>Thu, 24 Sep 2026 21:01:15 +0200</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,16 +934,16 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/video/the-old-cybersecurity-model-is-breaking/</t>
+          <t>https://www.theregister.com/security/2026/09/24/salesforce-agentforce-vulns-allowed-0-click-crm-data-theft-anonymous-phishing/5298958</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.53</v>
+        <v>4.06</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -952,46 +952,46 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>abc.net.au</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AI leaders warn UN of security risks as systems grow more powerful</t>
+          <t>Australia to pursue AI guardrails after unprecedented OpenAI breach</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>AI leaders warn UN of security risks as systems grow more powerful    Reuters</t>
+          <t>OpenAI breach strengthens Australia's case for tougher AI safety rules By chief digital political correspondent Clare Armstrong Topic: AI Posted about 6h ago about 6 hours ago Anthony Albanese spoke to OpenAI chief Sam Altman (pictured) to express his "disappointment" before revealing the breach. (Reuters: Kim Kyung-Hoon) In short: OpenAI's handling of a rogue agent accesses government data has st</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 21:18:57 GMT</t>
+          <t>Thu, 24 Sep 2026 18:35:14 GMT</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/ai-leaders-brief-un-amid-warnings-technology-could-slip-beyond-human-control-2026-09-23/</t>
+          <t>https://www.abc.net.au/news/2026-09-25/openai-breach-builds-case-for-tough-ai-rules/107192992</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.41</v>
+        <v>4.03</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>An Epyc trip to Venice: Everything we do and don't know about AMD's 256-core monster chip</t>
+          <t>นายกฯ ออสเตรเลียเผย AI Agent ของ OpenAI เจาะระบบข้อมูลสุขภาพของรัฐบาล</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>systems 16 channels of DDR5, 5 GHz clock speeds, and support for CXL 3.1 memory god boxes? What's not to like? Tobias Mann Tobias Mann SYSTEMS EDITOR Published wed 23 Sep 2026 // 16:51 UTC READ MORE Europe's fastest supercomputer is finally getting its domestic silicon infusion 5 hours ago EU datacenter green scorecard finally escapes Brussels 1 day ago Civo plots 40 edge datacenters to power Brit</t>
+          <t>มีประเด็นใหม่ของ AI เจาะระบบภายนอกอีกแล้ว คราวนี้ถูกเปิดเผยโดย Anthony Albanese นายกรัฐมนตรีของออสเตรเลีย ซึ่งเขาบอกว่า AI Agent ที่มาจาก OpenAI ได้เข้าถึงระบบด้านสุขภาพ Medicare ซึ่งดูแลโดยหน่วยงานด้านสวัสดิการ Services Australia ของประเทศออสเตรเลีย โดยข้อมูลที่เข้าถึงมีทั้งส่วนที่เปิดเผยต่อสาธารณะและส่วนที่ไม่ได้เปิดเผยต่อสาธารณะ จึงเป็นการเข้าถึงอย่างไม่ถูกต้องไม่ได้รับอนุญาต จากการตรวจสอบไม่พบ</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, chip</t>
+          <t>openai, ai, ai agent</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 17:51:11 +0200</t>
+          <t>Thu, 24 Sep 2026 11:54:36 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/23/an-epyc-trip-to-venice-everything-we-do-and-dont-know-about-amds-256-core-monster-chip/5298614</t>
+          <t>https://www.blognone.com/node/151738</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.4</v>
+        <v>4.01</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Anthropic says its biology lab has already found something big</t>
+          <t>Jensen Huang talks about AI and climate change like a supervillain</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Anthropic AI Anthropic says its biology lab has already found something big Julie Bort 3:17 PM PDT · September 23, 2026 Last week, Anthropic confirmed that it was operating a wet biology</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI Policy Jensen Huang talks about AI and climate change like a supervi</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 22:17:39 +0000</t>
+          <t>2026-09-24T14:04:44-04:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,13 +1087,13 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/anthropic-says-its-biology-lab-has-already-found-something-big/</t>
+          <t>https://www.theverge.com/tech/1000140/jensen-huang-nvidia-ai-energy-climate-change-supervillain</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Meta is making Muse more powerful and will let you video chat with it, too</t>
+          <t>Meta's new AI fidget is a ... Tamagotchi?</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Meta is making Muse more powerful and will let you video chat w</t>
+          <t>personal tech We hope Zuck's Muse Charm doesn't die if you neglect it Tobias Mann Tobias Mann SYSTEMS EDITOR Published thu 24 Sep 2026 // 18:44 UTC READ MORE Google's TPUs to catch some rays in orbit next week 1 minute ago CVE flood pushes Ubuntu onto weekly kernel release cycle 5 hours ago Google to critical infra orgs: Our AI scanners won't be evil, promise 9 hours ago Meta ads steered Polish An</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>ai, agentic</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T19:19:42-04:00</t>
+          <t>Thu, 24 Sep 2026 19:44:35 +0200</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999454/meta-muse-ai-agent-video-chat-connect-2026</t>
+          <t>https://www.theregister.com/personal-tech/2026/09/24/metas-new-ai-fidget-is-a-tamagotchi/5298936</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026 live blog: On the ground at Mark Zuckerberg’s next big product launch</t>
+          <t>Google is sending a teensy-tiny AI data center to space</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>It's time once again for Meta's annual September product launch event, and  The Verge  is on the ground in Menlo Park to cover the show live. Meta  says that  today's keynote by Mark Zuckerberg will be about how "Meta is building a future for everyone" - something he wrote at length about  in a rece</t>
+          <t>It's an experiment to see how the chips hold up in the harsh vacuum of the cosmos.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>ai, data center</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T18:30:00-04:00</t>
+          <t>Thu, 24 Sep 2026 17:45:37 +0000</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998457/meta-connect-2026-live-blog-mark-zuckerberg-keynote</t>
+          <t>https://www.engadget.com/2267975/google-is-sending-a-teensy-tiny-ai-data-center-to-space/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1207,17 +1207,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Meta's Muse AI agent is coming to its AI glasses</t>
+          <t>Meta เปิดตัว Muse Charm อุปกรณ์พกพาเรียกใช้งาน Muse AI ขนาดเท่าทามาก็อต - วางจำหน่ายภายในปีนี้</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Have your virtual assistant book a flight while you're jogging.</t>
+          <t>Meta เปิดตัว Muse Charm อุปกรณ์พกพาเรียกใช้งาน Muse AI ขนาดเท่าทามาก็อต - วางจำหน่ายภายในปีนี้ 
+     Body 
+                นอกจากการเปิดตัวแว่นตาอัจฉริยะหลากหลายรุ่นแล้ว ในงาน Meta Connect ปีนี้ ซีอีโอ Mark Zuckerberg ก็นำเสนอ One More Thing.. ด้วย โดยเป็นอุปกรณ์ AI พกพาขนาดเล็กเรียกชื่อว่า  Mu</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1226,11 +1228,11 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 23:28:12 +0000</t>
+          <t>Thu, 24 Sep 2026 16:56:09 +0000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,16 +1242,16 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267210/meta-muse-ai-agent-smart-glasses/</t>
+          <t>https://www.blognone.com/node/151745</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.29</v>
+        <v>3.89</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -1258,30 +1260,30 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OpenAI เปิดตัว GPT-6 Sol และ Luna ดึงความสามารถระดับ Astra ลงมาในราคาถูกลงครึ่งหนึ่ง</t>
+          <t>Japanese used bookstores see 5x sales surge as books are being bought by the ton, one 50-ton order sent to the US for AI scanning and destruction</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>ในการทดสอบงานธุรกิจที่ต้องสลับใช้แอปหลายตัว GPT-6 Sol ทำคะแนนเหนือ Claude Opus 5 ที่เปิดกำลังสูงสุด ด้วยต้นทุนต่องานเพียง 9% ของคู่แข่ง ตัวเลขนี้สรุปเกมที่ OpenAI กำลังเล่นได้ดี เพราะการแข่งขันของโมเดล AI ไม่ได้วัดกันแค่ว่าใครฉลาดที่สุดอีกต่อไป แต่วัดว่าใครส่งความฉลาดระดับแนวหน้าให้ใช้งานได้ทุกวันใน</t>
+          <t>Mark's enthusiasm for computers dampened at an early age by the rubber-keyed Sinclair Spectrum 48K and feelings of Commodore 64 envy. However, in the mid-80s, hope in a digital future was rekindled by the purchase of an Atari 520 STe. Since that time Mark has used a multitude of computers for fun an</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>openai, claude, gpt, ai, โมเดล</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>23.1</v>
+        <v>10.5</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 08:56:02 +0700</t>
+          <t>Thu, 24 Sep 2026 14:35:12 +0000</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1291,16 +1293,16 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/openai-gpt-6-sol-luna-launch</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/japanese-used-bookstores-see-5x-sales-surge-as-books-are-being-bought-by-the-ton-one-50-ton-order-sent-to-the-us-for-ai-scanning-and-destruction-multitude-of-suspicious-bulk-buys-thought-to-end-up-in-foreign-ai-scan-and-shred-facilities</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.22</v>
+        <v>3.89</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1309,30 +1311,30 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>NEWSLETTER: Funding frenzy, chip wars, and robot dreams: Inside China‘s AI boom</t>
+          <t>Japanese used bookstores see 5x sales surge as books are being bought by the ton, one 50-ton order sent to the US for AI scanning and destruction — multitude of suspicious bulk buys thought to end up in foreign AI scan and shred facilities</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>NEWSLETTER: Funding frenzy, chip wars, and robot dreams: Inside China‘s AI boom    Reuters</t>
+          <t>Japanese used bookstores see 5x sales surge as books are being bought by the ton, one 50-ton order sent to the US for AI scanning and destruction — multitude of suspicious bulk buys thought to end up in foreign AI scan and shred facilities    Tom's Hardware</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ai, chip</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 20:11:03 GMT</t>
+          <t>Thu, 24 Sep 2026 14:35:12 GMT</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1342,13 +1344,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQQ1hSZVA3UXRLNWE3RU8wUWRTN3Z5SGRTQWkzRGRScVVHdDhfWFliZXdLSXlDdzdoX3NhN3BjdzNEUTJ2NmJRMVYyN2RteUdidHd0ejNtS1hZSlFPUWw5Si1GblRRQktKM055MDQ3V2kzWlVuREpNSmJZelozbFZuVGU2MW1STXdqN09mUEJRa3hHUkNXbEdRUEhBV0gzVHg4RjRmQ0VRcExrNURXZnExcURyWmVheEQwSTVDTEhCODJGZUNWV09OSUFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisANBVV95cUxQVFllYWRSRDM4UWxYWlJLZE1DNG9OMzhLMDBsV2VTdjVEZEdPTVRxbXlianBSSng0c3Zab0RYMnRjNWdYakQ0TzJIYnVPQ0RZX3NNTmlFUExnQlgzY2tBdmtqNDNVcmE2X3cxTmp4UTI2TmIwczhxRVkyRmNfdEhXdkNMUzJkM0NOSUNoMkRZWjRmdXl3b0UzVHlMMk92enN0U2RCakFGOVloRzQ1aVoxTGtaUUdaSUdveGlvYUNPNm1rVVd3enlGQmlVWWVhVkJZQlF3Qkt6bUg4WGI5SHotN0dzMHRtSEYwNHlxWFZRd2pKNVoyUjh4ck96MGdna1NaaWRvcGxMYVQ1UkY0YWRTY191MzBPZmh1NHhLVktWVUpILU9lLUtUdFZmMmdJY2FFVjZfazFNYXlaZUprLUZtQll4WWZXd0p5bGdIRWNXZ0JPYXdZajBoUlZEOTVEMHF5NWkyWk9MWURxa25XNTR6YXdGT3lEUWdZWG1vdXAycHNKM21qaUlqcEpwV3Z3RjlhZU5pSkItcGFkSUZMRDFhVTJCTkVnYUx5TFNjU2dMTTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1360,30 +1362,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Meta put Muse in a Tamagotchi like 'Charm' device</t>
+          <t>Claude สร้างเอเจนต์ 950 ตัว ค้นพบระบบเอนไซม์ชนิดใหม่ที่ใช้ตัดต่อ DNA ด้วยเวลาเพียง 21 ชั่วโมงกับ 210 ล้านโทเคน</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Meta Charm is a Tamagotchi-like device with Muse AI.</t>
+          <t>ถ้าพูดถึง AI คนส่วนใหญ่คงนึกถึงโหมดช่วยพิมพ์งาน ช่วยตอบคำถาม หรือช่วยแต่งรูป แต่ล่าสุดมีข่าวใหญ่จากฝั่งยุโรป-อเมริกาที่น่าสนใจมาก ๆ คือ Anthropic (ผู้สร้าง Claude) เพิ่งเปิดห้องแล็บชีววิทยา แล้วเอา AI เข้าไปช่วยค้นคว้าวิจัยร่วมกับนักวิทยาศาสตร์จริง ๆ แล้วเรื่องที่ทำให้ฮือฮากันทั้งวงการ คือ AI ตัวนี้</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 00:05:03 +0000</t>
+          <t>Thu, 24 Sep 2026 17:08:57 +0700</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1393,13 +1395,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267229/meta-put-muse-in-a-tamagotchi-like-charm-device/</t>
+          <t>https://techsauce.co/healthtech/anthropic-claude-ai-discovers-art-enzyme-crispr</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1411,30 +1413,30 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Meta will stop training its AI on 'visual data' from its smart glasses — if you opt out</t>
+          <t>Google tests letting Gemini call businesses for you</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Somewhere, a contractor just breathed a sigh of relief.</t>
+          <t>Google says the AI-calling feature will first be available to Pixel 11 owners in the U.S. who pay for a Gemini subscription.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>gemini, ai</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 00:00:44 +0000</t>
+          <t>Thu, 24 Sep 2026 16:00:00 +0000</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1444,13 +1446,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267227/meta-will-stop-training-its-ai-on-visual-data-from-its-smart-glasses-if-you-opt-out/</t>
+          <t>https://techcrunch.com/2026/09/24/google-tests-letting-gemini-make-phone-calls-initially-for-us-pixel-owners/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.05</v>
+        <v>3.82</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1462,30 +1464,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Alibaba unveils Zhenwu V900 AI accelerator, claims it's 'the most powerful AI chip in China'</t>
+          <t>Pixel 11's Call For Me feature begins preliminary rollout</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shane has a background in computer engineering and has worked as a freelance consultant in multiple industries. He has a strong affection for history and loves to game. He worked his way up from a Commodore 64 and has always been interested in technology and writing. He particularly enjoys breaking </t>
+          <t>Select Gemini subscribers with a Pixel 11 can soon try out phone calls via AI chatbot.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai, chip, ai accelerator</t>
+          <t>gemini, ai</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 12:00:00 +0000</t>
+          <t>Thu, 24 Sep 2026 16:00:00 +0000</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1495,13 +1497,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/alibaba-unveils-zhenwu-v900-ai-accelerator-claims-its-the-most-powerful-ai-chip-in-china-accelerator-supports-500-000-chip-supercluster-with-a-10t-parameter-qwen-model-on-the-roadmap</t>
+          <t>https://www.engadget.com/2267120/pixel-11-call-for-me-feature-begins-preliminary-rollout/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.04</v>
+        <v>3.82</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1513,30 +1515,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>AI ร้ายแรงกว่าอาวุธนิวเคลียร์? ทำไมนักวิจัยเตือน ปัญญาประดิษฐ์เสี่ยง ‘ฆ่ามนุษย์’ ภายใน 10 ปีข้างหน้า</t>
+          <t>AI agent kill switch urged by Okta-led alliance – how businesses could make it work</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>AI ร้ายแรงกว่าอาวุธนิวเคลียร์? ทำไมนักวิจัยเตือน ปัญญาประดิษฐ์เสี่ยง ‘ฆ่ามนุษย์’ ภายใน 10 ปีข้างหน้า    thestandard.co</t>
+          <t>In response to the emerging threat of rogue and shadow AI agents, here’s how the newly formed Blueprint Alliance seeks to help businesses secure their systems against anomalous AI activity.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ai, ปัญญาประดิษฐ์</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 18:13:36 GMT</t>
+          <t>2026-09-24T16:01:19Z</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1546,13 +1548,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5FXzFRYUVBRkkxSC1URV9mZ2tEVE1pX1BmMzUyd2FuRU9QdVFxSTNZTVBNcVJOR3ZUOG5sei0weC1pTkl4R3Vjd3VfUVZuSk0tblA5OXlJbHJsNUsxTXVtcEExYTBMeE0?oc=5</t>
+          <t>https://www.zdnet.com/innovation/okta-blueprint-alliance-ai-agents-oauth-kill-switch/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3.97</v>
+        <v>3.8</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1564,32 +1566,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>นักพัฒนาใช้ GPT-6 Astra ถอดรหัสข้อความวิทยุเยอรมันยุคสงครามโลกครั้งที่ 1 อายุกว่า 108 ปี สำเร็จ</t>
+          <t>Qualcomm’s new ‘Elite’ sound chip might finally deliver the Wi-Fi earbud dream</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>นักพัฒนาใช้ GPT-6 Astra ถอดรหัสข้อความวิทยุเยอรมันยุคสงครามโลกครั้งที่ 1 อายุกว่า 108 ปี สำเร็จ 
-     Body 
-                นักพัฒนา AI ผู้ใช้นามแฝงว่า Prinz ประสบความสำเร็จในการนำโมเดล GPT-6 Astra ของ OpenAI มาช่วยถอดรหัสข้อความวิทยุของกองทัพเยอรมันจากช่วงสงครามโลกครั้งที่ 1 ซึ่งมีอายุกว่า 108</t>
+          <t>What if your wireless earbuds - or audio glasses - could stream high-quality lossless audio that  doesn't  cut out when you leave your phone on the bedside charger or buried in the couch? Qualcomm's new  Snapdragon Sound Elite Gen 2  is its first to integrate "micro-power Wi-Fi 6E" right into the ch</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>openai, gpt, ai, โมเดล</t>
+          <t>chip</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>20.1</v>
+        <v>1.4</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 04:58:00 +0000</t>
+          <t>2026-09-24T19:42:39-04:00</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1599,13 +1599,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151703</t>
+          <t>https://www.theverge.com/tech/1000443/qualcomms-new-elite-sound-chip-might-finally-deliver-the-wi-fi-earbud-dream</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1617,30 +1617,33 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT mobile app gets voice-based agentic features</t>
+          <t>แอปเปิลต่อสัญญาสิทธิบัตรโมเด็ม Qualcomm ต่ออีกฉบับ</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Pro and Plus users will be able to use the Work tab on their phones to complete agentic tasks.</t>
+          <t>แอปเปิลต่อสัญญาสิทธิบัตรโมเด็ม Qualcomm ต่ออีกฉบับ 
+     Body 
+                Qualcomm ประกาศข่าวสั้นว่า แอปเปิลตกลงต่อสัญญาสิทธิบัตรโมเด็ม 5G ที่  ของเดิมเซ็นกันไว้ระหว่างปี 2024-2026  ไปอีก โดยสัญญาฉบับใหม่จะเริ่มมีผล 1 เมษายน 2027 เป็นต้นไป แต่รอบนี้ไม่บอกว่าสัญญานานเท่าไร 
+ สัญญาการใช้งานส</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>chatgpt, agentic</t>
+          <t>ชิป</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 17:00:00 +0000</t>
+          <t>Thu, 24 Sep 2026 23:18:50 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1650,13 +1653,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/chatgpt-mobile-app-gets-voice-based-agentic-features/</t>
+          <t>https://www.blognone.com/node/151747</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1668,30 +1671,33 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Even Americans who use AI every day are worried about it</t>
+          <t>Windows 11 ออกอัพเดต KB5124010 ตั้งค่าปุ่ม Copilot เป็นอย่างอื่นได้แล้ว</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>The report suggests that greater exposure will not resolve the unease around the technology, nor reduce public support for AI regulation.</t>
+          <t>Windows 11 ออกอัพเดต KB5124010 ตั้งค่าปุ่ม Copilot เป็นอย่างอื่นได้แล้ว 
+     Body 
+                ไมโครซอฟท์ออกอัพเดต Windows 11 แพตช์ KB5124010 ประจำเดือนกันยายน 2026 โดยตอนนี้ยังมีสถานะเป็นอัพเดตแบบพรีวิวสำหรับคนที่ตั้งค่าอัพเดตไวสุด มีการเปลี่ยนแปลงใหม่ๆ หลายอย่าง 
+  File Explorer  ปรับป</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ai, ai regulation</t>
+          <t>copilot</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 16:49:58 +0000</t>
+          <t>Thu, 24 Sep 2026 23:05:13 +0000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1701,7 +1707,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/even-americans-who-use-ai-every-day-are-worried-about-it/</t>
+          <t>https://www.blognone.com/node/151746</t>
         </is>
       </c>
     </row>
@@ -1719,30 +1725,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Meta introduces camera-free AI glasses</t>
+          <t>จับตาฉากทัศน์ประชุม ‘ทรัมป์ – สี จิ้นผิง’ พร้อมเปิด 5 กลยุทธ์ลงทุนช่วงรอยต่อ รับมือ Fed คุมเข้ม AI เสี่ยงสะดุด</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Meta says the camera-free glasses will be lighter and have up to 12 hours battery life.</t>
+          <t>ท่ามกลางภูมิทัศน์การลงทุนโลกที่เต็มไปด้วยความผันผวน ทั้งจากการดำเนินนโยบายการเงินของธนาคารกลาง สหรัฐฯ  (Fed) การแข่งขันด้านเทคโนโลยีปัญญาประดิษฐ์ (AI) ที่เผชิญความท้าทายรอบด้าน รวมถึงปมความขัดแย้งเชิงยุทธศาสตร์ระหว่างสองมหาอำนาจ สหรัฐฯ-จีน 
+ ประเด็นสำคัญ 
+  จับตาฉากทัศน์ประชุม ‘ทรัมป</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, data center, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.4</v>
+        <v>15.6</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 23:39:44 +0000</t>
+          <t>Thu, 24 Sep 2026 09:32:31 +0000</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1752,7 +1760,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-introduces-camera-free-ai-glasses/</t>
+          <t>https://thestandard.co/trump-xi-fed-ai-investment-strategy/</t>
         </is>
       </c>
     </row>
@@ -1770,19 +1778,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Meta ditches the camera on its newest smart glasses</t>
+          <t>Trump, US House speaker and tech CEOs to meet on AI on September 29, source says</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>The Ray-Ban Meta Audio Glasses have no cameras. | Photo by Brett Putman / The Verge	 
- Walking around Meta Connect 2026, everyone's sporting smart glasses in all sorts of shapes, colors, and sizes. It's a marked difference here, a tech bubble where "pervert glasses" are not a concern. 
- Outside Co</t>
+          <t>Trump, US House speaker and tech CEOs to meet on AI on September 29, source says    Reuters</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1791,11 +1797,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T19:37:17-04:00</t>
+          <t>Thu, 24 Sep 2026 23:23:55 GMT</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1805,7 +1811,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999281/ray-ban-meta-audio-glasses-meta-connect-2026</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPSUNPVzNoNDJiWUNfY2hyZTNBT3pJS2kwUWk0Nk9UT0dTenZkTE5acXJaX0V4QXVMWXdwRVZEeVY3Y09HUTZqN2VPYUI0elhjY0RwRHFLTnFsSlNhdGgxUXJ2OE5pVHcyWUFBaWljNThLdUtqOFUzeHU2NjIyS3czT0hsVDdyQVFtemZIX0o2cTR5WGlTVXNnMUdOUUp0bm5PeFZQLXg5Uk81T3FJMmxn?oc=5</t>
         </is>
       </c>
     </row>
@@ -1823,17 +1829,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Tech leaders to UN: For the sake of humanity, please control the AI technology we created</t>
+          <t>Nick Clegg plays down fears ‘godlike’ AI could exterminate humanity</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Tech leaders to UN: For the sake of humanity, please control the AI technology we created    AP News</t>
+          <t>Nick Clegg plays down fears ‘godlike’ AI could exterminate humanity    The Guardian</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1842,11 +1848,11 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 23:12:00 GMT</t>
+          <t>Thu, 24 Sep 2026 23:10:00 GMT</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1856,13 +1862,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPSHBObE1ZM3ZSc0QwNURQWkZkS2tORVNRMHhNUUhvNjNZRjR4RHNIVWlyUE5qZV82WVowbEFFX2RhR09TeE5WMHQ4S3l0TkdZTjN3YWdvVUNfRUZYdTZVOW9jc3YtQlNHdWNjcFh4cl9jNlk4VDkxMlFJc18ybzlLN3B4NjZxZVB3cFNBTy1mSXlLVmZlbDRpdXd4WVljVEtaZGxkRHpIMTBSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQSGFHWko1TlZzd0RzMHVFSUxPdl9NYjY3QTlIMzVVcmF4QlRvN29Nb2R1UVk1VDFoeTBUNGRrSlVFeWNVcDBJQkctTHZsYjVORXlRQXhtdE01Wmp3RnZRMDBQV3hZZ1dGVTc3OGVxNDRXT29RTXpydTZNMm9hbjI2ZDMxV1pNUFM1dmxVczdjd0VNTjJkZzFNZC16dThpM3lZOTJ0cXc2YmRpRjNPaXJRVTNRc21HbmM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1874,30 +1880,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>VC firm Bessemer now has another $5.75B to invest in (what else?) AI</t>
+          <t>Akamai signs $11.6 billion cloud deal with Anthropic, grants warrant for up to 5% stake</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>The VC firm says that AI-native companies are growing faster than any technology, ever.</t>
+          <t>Akamai signs $11.6 billion cloud deal with Anthropic, grants warrant for up to 5% stake    Reuters</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 20:35:17 +0000</t>
+          <t>Thu, 24 Sep 2026 22:55:43 GMT</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1907,13 +1913,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/vc-firm-bessemer-now-has-another-5-75b-to-invest-in-what-else-ai/</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNanVpUjFYbXpXWHdEU1NlRFlfZnI5a0Y2OVlzYUkya2tBR3hOY05ZTk05ZVZrWUZqcmttYjV3b2x6d01iTUFIZ095a1lQbkFCbTZFVGJzd2tUM1NkcWtOV3B2X1VpMGpkSVlGOW13ZU0xd3BjUm1paldVNHpYVllpN0UwQ3ZkUGk0R3AtaWx3SDJFaXdEUkdmeHRlT3M0Tk10LWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1925,30 +1931,30 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s new Surface Mouse has haptic feedback and a customizable action button</t>
+          <t>Ray-Ban Meta Gen 3 vs. Ray-Ban Meta Gen 2: How these AI glasses compare</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Microsoft is launching a second generation of its Surface Mouse next month that includes haptic feedback support. The Surface Mouse also has a customizable action button for the first time, which is primarily designed for quick access to Copilot ( of course ), but can be configured to work with othe</t>
+          <t>Meta's newest smart glasses are an iterative, expensive update.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>copilot</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T16:30:00-04:00</t>
+          <t>Thu, 24 Sep 2026 21:56:17 +0000</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1958,13 +1964,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/news/999211/microsoft-surface-mouse-haptic-feedback</t>
+          <t>https://www.engadget.com/2268392/ray-ban-meta-gen-3-vs-gen-2-ai-glasses-comparison/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3.66</v>
+        <v>3.76</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1976,30 +1982,30 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Microsoft's new Surface Pro 12 and Surface Laptop 13 feature Snapdragon X2 Plus chips</t>
+          <t>Nvidia CEO says 'we have to shut the labs down' if AI experiments are unsafe</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Microsoft's smaller Surface Pro 12 and Surface Laptop 13 are getting a much-needed chip upgrade.</t>
+          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>chip</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 20:30:00 +0000</t>
+          <t>Thu, 24 Sep 2026 15:24:49 +0000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2009,13 +2015,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2266680/microsofts-new-surface-pro-12-and-surface-laptop-13-feature-snapdragon-x2-plus-chips/</t>
+          <t>https://www.tomshardware.com/tech-industry/big-tech/nvidia-ceo-says-we-have-to-shut-the-labs-down-if-ai-experiments-are-unsafe-jensen-huang-says-frontier-ai-lab-fears-are-a-distraction-not-a-call-for-regulation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2027,17 +2033,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Mop the slop from your LinkedIn feed with a new open-source Chrome extension</t>
+          <t>Launch of UK’s ‘largest AI supercomputer’ delayed by power supply problems</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Decision-making AI model Jev has found another job: helping a Chrome extension identify and flag low-value writing on LinkedIn. AI enthusiast, author, and business consultant Tom Frazier released Slop Mop as a Chrome extension on Tuesday, as well as publishing its code on GitHub for those who want t</t>
+          <t>Launch of UK’s ‘largest AI supercomputer’ delayed by power supply problems    The Guardian</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2046,11 +2052,11 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 22:23:13 +0200</t>
+          <t>Thu, 24 Sep 2026 21:37:00 GMT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2060,13 +2066,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/09/23/mop-the-slop-from-your-linkedin-feed-with-a-new-open-source-chrome-extension/5298679</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOV3VSZTJnOXg4YS1KM3hjeElfZzNtNjJDSHNISFNiajQ3M091VUozal9CeFBwX3Z2S25JekQyTHk1czlBTFlhcFkwcEFvdTZfalhTbC1OZkR3TWxndDk2cTRrNGdZWFlwbURCcGhHNUdMSXdTNmRsZUpZTFVmSWdHeHVWdmJoZFB2WWhfUWVNV3A4R1BtNXFDQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2078,32 +2084,30 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>OpenAI อัปเดต GPT-6 Sol และ GPT-6 Luna ประสิทธิภาพเพิ่มขึ้น ถูกกว่า GPT-5.6 ครึ่งหนึ่ง</t>
+          <t>Talk of AI in KDE sets the community ablaze</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>OpenAI อัปเดต GPT-6 Sol และ GPT-6 Luna ประสิทธิภาพเพิ่มขึ้น ถูกกว่า GPT-5.6 ครึ่งหนึ่ง 
-     Body 
-                ไม่รู้นัดกันมาหรือเปล่าแต่ OpenAI ก็ออกอัปเดตโมเดล AI เวอร์ชันใหม่  GPT-6 Sol  ที่เป็นรุ่นบนและ  GPT-6 Luna  ที่เน้นทำงานเร็ว-ต้นทุนต่ำ ทำให้ตอนนี้ OpenAI มีโมเดลในซีรีส์ GPT-6 รวม</t>
+          <t>A proposal to make KDE an "AI-native" desktop has gone down like a house on fire: screams, flames, people running for safety. There may be no survivors.* Last weekend was KDE's annual Akademy conference and it included a presentation proposing an AI-native KDE. We noted that it seemed likely to pola</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>openai, gpt, ai, โมเดล</t>
+          <t>ai, llm</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>23.7</v>
+        <v>10.6</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 01:22:58 +0000</t>
+          <t>Thu, 24 Sep 2026 16:32:00 +0200</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2113,13 +2117,13 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151722</t>
+          <t>https://www.theregister.com/software/2026/09/24/talk-of-ai-in-kde-sets-the-community-ablaze/5298854</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -2136,25 +2140,25 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>'No country controls every layer': The AI systems reshaping global power</t>
+          <t>OpenAI agents attack the 'first' government hack by autonomous AI, researchers say</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>'No country controls every layer': The AI systems reshaping global power    ABC News &amp; Headlines – Australian Broadcasting Corporation</t>
+          <t>OpenAI agents attack the 'first' government hack by autonomous AI, researchers say    ABC News &amp; Headlines – Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai, autonomous</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>4.8</v>
+        <v>17.1</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 20:14:57 GMT</t>
+          <t>Thu, 24 Sep 2026 08:01:15 GMT</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2164,13 +2168,13 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOMDVWcTA5S2c2NTZuSllSeW1vN0pKQk9kaUpoVjhFa1hBOGRUMDFfdzQ0elpoODFZRDJ4T08tblh4QTZ2VW11NHhnZWxNOHpiSXI2dWpRWjYzRFFVckp2OF8wX0FfVVo5NmdOWDhSakJZWkRKUkZlR0VwYzBVMXhPeFR0cGdBV3c5NlhDLTdJQjdsamFmdzBsbjhXcFNRUkJVQ1JqTVl4b3lCbTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPZE9MeXh6UXNMWFNoRkVZMzd0UGQ2Q3RDSWI2bFpkQ3l6cE1ha21RdzNaamRMRmdWRnJJU2E2TTNwTV82Mkl6em93TWF5eHBUdTVRQW9FczdqYkZGcm13ckxzTTEyY1dWLVhsLUVOS1pvUXQ5VTJVME16RjgzWGxfb3dGRDQtMUxCd1dINUE1SHQxUWVwVE9JM3p6QnBIcFRhdkp6bm83bw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -2182,32 +2186,30 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Claude Opus 5.5 มาแล้ว ความสามารถเทียบเท่า Fable 5.1 - คิดราคาถูกลงจาก Opus 5</t>
+          <t>OpenAI agent got into Australia's Medicare stats portal with 84-day notification delay</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claude Opus 5.5 มาแล้ว ความสามารถเทียบเท่า Fable 5.1 - คิดราคาถูกลงจาก Opus 5 
-     Body 
-                Anthropic อัปเดตโมเดลปัญญาประดิษฐ์ Claude Opus 5.5 ซึ่งเป็นโมเดลแรกในซีรีส์ Claude 5.5 โดยบอกว่าความสามารถส่วนใหญ่ทำได้ในระดับเทียบเท่ากับ  Fable 5.1  และมีต้นทุนใช้งานถูกกว่า  Opus 5  40% </t>
+          <t xml:space="preserve">Shane has a background in computer engineering and has worked as a freelance consultant in multiple industries. He has a strong affection for history and loves to game. He worked his way up from a Commodore 64 and has always been interested in technology and writing. He particularly enjoys breaking </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>24</v>
+        <v>4.6</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 01:03:03 +0000</t>
+          <t>Thu, 24 Sep 2026 20:34:31 +0000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2217,13 +2219,13 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151721</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/australian-pm-says-openai-took-84-days-to-email-agency-after-agent-hacked-its-national-health-care-portal-incident-is-believed-to-be-the-first-known-case-of-ai-breaching-a-government-site</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -2235,17 +2237,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Enveda secures $311M to bring more nature-derived AI drugs into clinical trials</t>
+          <t>New York Times Cooking is coming to Meta's AI and display glasses</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>The round valued the AI biotech at $2 billion. It is currently testing drugs that treat skin conditions and preserve weight loss after stopping GLP-1s.</t>
+          <t>The app is getting a "hands-free" mode that can narrate recipe steps.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2254,11 +2256,11 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 19:31:28 +0000</t>
+          <t>Thu, 24 Sep 2026 19:24:34 +0000</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2268,13 +2270,13 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/enveda-secures-311m-to-bring-more-nature-derived-ai-drugs-into-clinical-trials/</t>
+          <t>https://www.engadget.com/2268183/new-york-times-cooking-is-coming-to-metas-ai-and-display-glasses/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -2286,30 +2288,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>US lawmakers propose sweeping AI restrictions with superintelligence ban</t>
+          <t>Google to critical infra orgs: Our AI scanners won't be evil, promise</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>US lawmakers propose sweeping AI restrictions with superintelligence ban    aljazeera.com</t>
+          <t>Google has jumped on the AI-defense-for-critical-systems train with its Scan for Good initiative, and says that its threat-hunting models have already autonomously uncovered critical security issues at hospitals, a municipality, a public rail operator, and major technology providers. So don't fear t</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>gemini, ai</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5.5</v>
+        <v>12.1</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 19:34:35 GMT</t>
+          <t>Thu, 24 Sep 2026 15:00:00 +0200</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2319,13 +2321,13 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQd2VfbWsxXzlBdEZEUlRUNlJON1ZHY2MyR3JzZ0ExY19va1c1elFqT25XY1k1TjQtUWp4SWUtZEZTNGFjSUU1MzlVUGVJQ3BEZWpWT0lzQmxkRFUtWDNLRjMwNkM5QXdOMF9EOHJDRDliMHJteVJ3VUs5SDQ5YUZhREdqTlk4RXM2bXV3Y09zSU1MaVphQVozLXdtOUFkYVVyeGxGWEZ6b19EemtHWlNhdEZZNDZuZjDSAbwBQVVfeXFMTW4wUXd5c2tGekpFaFM2VVlvWE9nZ1pmR1E3aEVxWDl5U3N2VjJSazhvZlRwU3AyaXVrWHFUN2w1NGFNQnlMR3RmZkpZalVwbnNfWFZXYUFuVGg0UXl0TGRfUHhFOXI3eFIwSy16VmdtQUhLdEkzS2JUeW9xT3N3VERNakVOanJxaHlRX0NQQkw4MFp3UTUyRnRPUWdnUlo0S2htZXdBN1E3N2RndXRqb0JfaHkxZEhnSlk0NjU?oc=5</t>
+          <t>https://www.theregister.com/security/2026/09/24/google-to-critical-infra-orgs-our-ai-scanners-wont-be-evil-promise/5298685</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -2337,30 +2339,31 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>bangkokbiznews.com</t>
+          <t>brandinside.asia</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>‘AMD’ ผงาดสู่ ‘ล้านล้านดอลล์’ หุ้นทะยาน 185% รับกระแส AI</t>
+          <t>รวมทุกปัญหา ข้อเสนอแนะ และวิวาทะ ‘ดาต้าเซ็นเตอร์’ จากตัวจริงในวงการเทค-เศรษฐกิจ-กฎหมาย</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>‘AMD’ ผงาดสู่ ‘ล้านล้านดอลล์’ หุ้นทะยาน 185% รับกระแส AI    bangkokbiznews</t>
+          <t>ก่อนจะบอกว่า ‘ดาต้าเซ็นเตอร์’ เป็นการลงทุนที่ ‘ดี’ หรือ ‘ไม่ดี’ สำหรับประเทศ ลองหยุดคิดสักนิด แล้วถามตัวเองก่อนว่า เรารู้จักธุรกิจนี้ดีพอแล้วหรือยัง?  
+ เพราะดาต้าเซ็นเตอร์หนึ่งแห่งไม่ได้มีแค่ตัวเลขเงินลงทุน แต่เกี่ยวข้องตั้งแต่โครงสร้างพื้นฐานที่รองรับ AI และคลาวด์ ไปจนถึงไฟฟ้า น้ำ ที่ดิน การจ้</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>ai, amd</t>
+          <t>ai, ดาต้าเซ็นเตอร์</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 12:36:51 GMT</t>
+          <t>Thu, 24 Sep 2026 12:57:08 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2370,13 +2373,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1WWkcwV3Q4TXhoWjEtb0I2dERMQUFOandQTDFzRVRLMWtOWG53X3NPeXAyajBzNHg5eGRCcDEwS0tRbVVmMy1HX2JWSnNUN3p6RGZvc09aMmZycTM4ZHFkWl83SW0?oc=5</t>
+          <t>https://brandinside.asia/thailand-weighs-pros-and-cons-of-data-center-boom/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2388,30 +2391,30 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Europe's fastest supercomputer is finally getting its domestic silicon infusion</t>
+          <t>PrismML brings its tiny LLMs to Qualcomm-powered smart glasses</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Talk about digital sovereignty! Europe's most powerful supercomputer, Jupiter, is finally getting the domestic silicon infusion it's been waiting for. On Tuesday, French chip designer SiPearl began delivery of its long-anticipated Rhea1 CPUs to Bull for integration into the system. Jupiter, which ca</t>
+          <t>Prism's larger goal is open-weight AI that runs on devices and makes better use of the computing power they already have.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>chip</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 20:32:13 +0200</t>
+          <t>Thu, 24 Sep 2026 19:00:42 +0000</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2421,13 +2424,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/23/europes-fastest-supercomputer-is-finally-getting-its-domestic-silicon-infusion/5298665</t>
+          <t>https://techcrunch.com/2026/09/24/prismml-brings-its-tiny-llms-to-qualcomm-powered-smart-glasses/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2439,30 +2442,30 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>China's ByteDance gained access to over 2,000 Nvidia B200 chips through Norway data center</t>
+          <t>Meet Feather, the startup building the ‘Android of robotics’ for developers</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
+          <t>Feather is betting on a customizable, $30,000 platform built for software developers.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>nvidia, data center</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>13</v>
+        <v>6.3</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 12:00:43 +0000</t>
+          <t>Thu, 24 Sep 2026 18:52:38 +0000</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2472,13 +2475,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/data-centers/filing-reveals-how-bytedance-gained-access-to-over-2-000-nvidia-b200-chips-through-nscales-norway-data-center-singaporean-subsidiary-spring-contributed-73-percent-of-uk-neoclouds-2025-revenue</t>
+          <t>https://techcrunch.com/2026/09/24/meet-feather-the-startup-building-the-android-of-robotics-for-developers/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3.36</v>
+        <v>3.49</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2490,30 +2493,30 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Anthropic เปิดตัว Opus 5.5 เก่งระดับ Fable 5.1 แต่ถูกกว่า พิมพ์คุยสื่อสารดีขึ้น กระชับ ตรงประเด็น</t>
+          <t>Micron discontinues 2GB GDDR7 chips for gaming GPUs as it pivots toward higher-density memory for AI</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>งานย้ายโค้ด 680,000 บรรทัดที่ปกติทีมวิศวกรต้องใช้เวลาหลายสัปดาห์ ถูกทำเสร็จภายในไม่ถึงหนึ่งวัน นี่คือหนึ่งในผลลัพธ์ที่ผู้ทดสอบกลุ่มแรกได้จาก Claude Opus 5.5 และสะท้อนจุดขายหลักของรุ่นนี้ได้ชัด คือความสามารถระดับแนวหน้าในต้นทุนที่ลดลงเกือบครึ่ง  Anthropic เพิ่งเปิดตัว Claude Opus 5.5 โมเดลแรกของตระกู</t>
+          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, โมเดล</t>
+          <t>ai, robotics</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>20.2</v>
+        <v>12.6</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 11:51:49 +0700</t>
+          <t>Thu, 24 Sep 2026 12:30:00 +0000</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2523,13 +2526,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/anthropic-claude-opus-5-5-launch</t>
+          <t>https://www.tomshardware.com/pc-components/ram/micron-discontinues-2gb-gddr7-chips-for-gaming-gpus-as-it-pivots-toward-higher-density-memory-for-ai-chipmaker-reportedly-pivots-to-high-margin-3gb-silicon-for-ai-gpus</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2541,30 +2544,30 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>China launches 'Supercomputing-1' AI satellite as orbital data centers gather momentum</t>
+          <t>Over 80,000 finance workers to get AI training by 2028 as industry launches job transformation initiative</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
+          <t>23 financial institutions have committed to training their entire Singapore workforce in critical artificial intelligence skills by 2028 through programmes recognised by the Institute of Banking and Finance.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ai, robotics</t>
+          <t>ai, artificial intelligence</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 10:30:00 +0000</t>
+          <t>Thu, 24 Sep 2026 20:27:00 +0800</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2574,7 +2577,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/space/china-puts-ai-compute-into-orbit-with-supercomputing-1-satellite-onboard-processing-aims-to-cut-earth-observation-data-processing-from-hours-to-minutes</t>
+          <t>https://www.channelnewsasia.com/singapore/ai-finance-banks-industry-jobs-gan-kim-yong-6407841</t>
         </is>
       </c>
     </row>
@@ -2692,34 +2695,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.3</v>
+        <v>4.93</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.13+sig1.8+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI agents ‘infiltrated Australian government website’</t>
+          <t>Leading semiconductor analyst says AMD should be investigated for 'treason' over availability of restricted chips in China</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, ai agent</t>
+          <t>amd, semiconductor, fab</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/09/24/openai-agents-infiltrated-australian-government-website/5298702</t>
+          <t>https://www.tomshardware.com/tech-industry/leading-semiconductor-analyst-accuses-amd-of-treason-over-restricted-chips-availability-in-china-amd-blames-diversion-of-export-controlled-rfsoc-usd36-000-radar-silicon-allegedly-quoted-at-usd1-000-for-crowdfunding-project</t>
         </is>
       </c>
     </row>
@@ -2728,34 +2731,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.9</v>
+        <v>4.78</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig0.6+src1.2+corr0.8</t>
+          <t>rec1.78+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The 7 biggest announcements</t>
+          <t>Docker's new sandboxes aim to contain AI agents for real</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999593/meta-connect-2026-everything-announced</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/09/24/dockers-new-sandboxes-aim-to-contain-ai-agents-for-real/5298964</t>
         </is>
       </c>
     </row>
@@ -2764,21 +2767,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.7</v>
+        <v>4.52</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.52+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Meta made a Tamagotchi-like wearable for its Muse AI agent</t>
+          <t>Muse sure looks a lot like OpenClaw</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>ai, instinct, ai agent</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2786,12 +2789,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-made-a-tamagotchi-like-wearable-for-its-muse-ai-agent/</t>
+          <t>https://www.theverge.com/report/1000180/muse-openclaw-instinct-lookalike</t>
         </is>
       </c>
     </row>
@@ -2800,34 +2803,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.13+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Meta is making a standalone Muse AI gadget</t>
+          <t>Leading semiconductor analyst says AMD should be investigated for 'treason' over availability of restricted chips in China, AMD blames diversion of export-controlled RFSoC — $36,000 radar silicon allegedly quoted at $1,000 for crowdfunding project</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>amd, semiconductor</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999750/muse-charm-meta-ai-hardware</t>
+          <t>https://www.tomshardware.com/tech-industry/leading-semiconductor-analyst-accuses-amd-of-treason-over-restricted-chips-availability-in-china-amd-blames-diversion-of-export-controlled-rfsoc-usd36-000-radar-silicon-allegedly-quoted-at-usd1-000-for-crowdfunding-project</t>
         </is>
       </c>
     </row>
@@ -2836,34 +2839,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr0.8</t>
+          <t>rec1.3+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The biggest news and announcements</t>
+          <t>Ask HPE and NVIDIA the AI data question you cannot ask in public</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, nvidia, ai infrastructure</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998480/meta-connect-2026-biggest-news-announcements</t>
+          <t>https://www.theregister.com/paas-and-iaas/2026/09/24/sponsored/5298888</t>
         </is>
       </c>
     </row>
@@ -2872,21 +2875,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.0+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.8+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>AMD begins to add GDDR7 support to its Linux GPU drivers</t>
+          <t>Gemini 3.8 Live with Live Avatar gives Google&amp;#8217;s AI a face</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>gpu, amd, semiconductor, fab</t>
+          <t>gemini, ai</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2894,12 +2897,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-begins-to-add-gddr7-support-to-its-linux-gpu-drivers-changes-could-herald-use-of-advanced-memory-standard-with-next-gen-radeon-gpus</t>
+          <t>https://www.theverge.com/tech/1000328/google-gemini-ai-live-avatar-face</t>
         </is>
       </c>
     </row>
@@ -2908,34 +2911,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr0.8</t>
+          <t>rec1.8+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>US diplomats told to say ‘super intelligence’ — not ‘artificial intelligence’ — after Trump’s call</t>
+          <t>AI ร้ายแรงกว่าอาวุธนิวเคลียร์? ทำไมนักวิจัยเตือน ปัญญาประดิษฐ์เสี่ยง ‘ฆ่ามนุษย์’ ภายใน 10 ปีข้างหน้า</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence</t>
+          <t>ai, ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/trump-super-intelligence-rebrand-ai-diplomats-02123c7bf18c692a12b2b3e3b9ce30c5</t>
+          <t>https://thestandard.co/ai-risk-human-extinction-warning/</t>
         </is>
       </c>
     </row>
@@ -2944,21 +2947,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.59</v>
+        <v>4.1</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.59+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.7+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>The old cybersecurity model is breaking</t>
+          <t>Salesforce Agentforce vulns allowed 0-click CRM data theft, anonymous phishing</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ai, instinct, ai safety</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2966,12 +2969,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/video/the-old-cybersecurity-model-is-breaking/</t>
+          <t>https://www.theregister.com/security/2026/09/24/salesforce-agentforce-vulns-allowed-0-click-crm-data-theft-anonymous-phishing/5298958</t>
         </is>
       </c>
     </row>
@@ -2980,34 +2983,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.53</v>
+        <v>4.06</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.93+sig0.6+src1.2+corr0.8</t>
+          <t>rec1.66+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AI leaders warn UN of security risks as systems grow more powerful</t>
+          <t>Australia to pursue AI guardrails after unprecedented OpenAI breach</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>abc.net.au</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/ai-leaders-brief-un-amid-warnings-technology-could-slip-beyond-human-control-2026-09-23/</t>
+          <t>https://www.abc.net.au/news/2026-09-25/openai-breach-builds-case-for-tough-ai-rules/107192992</t>
         </is>
       </c>
     </row>
@@ -3016,21 +3019,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.41</v>
+        <v>4.03</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.41+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.03+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>An Epyc trip to Venice: Everything we do and don't know about AMD's 256-core monster chip</t>
+          <t>นายกฯ ออสเตรเลียเผย AI Agent ของ OpenAI เจาะระบบข้อมูลสุขภาพของรัฐบาล</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, chip</t>
+          <t>openai, ai, ai agent</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3038,12 +3041,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/systems/2026/09/23/an-epyc-trip-to-venice-everything-we-do-and-dont-know-about-amds-256-core-monster-chip/5298614</t>
+          <t>https://www.blognone.com/node/151738</t>
         </is>
       </c>
     </row>
@@ -3157,24 +3160,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.5</v>
+        <v>7.28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>oracle.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -3182,25 +3185,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The biggest news and announcements</t>
+          <t>Oracle and Wild Bio Join Forces to Advance AI-Driven Agriculture</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Updated Today, Sep 24, 2026, 12:15 AM UTC Meta Connect 2026: The bigges</t>
+          <t>Oracle News Press Release Oracle and Wild Bio Join Forces to Advance AI-Driven Agriculture Collaboration will help advance AI-powered research for more productive, resilient crops and scalable, high-quality carbon removal Austin, Texas, and Oxford, United Kingdom—24 September 2026 Oracle and Wild Bioscience (Wild Bio) today announced a collaboration to advance agricultural resilience and crop-base</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T18:45:00-04:00</t>
+          <t>Thu, 24 Sep 2026 17:44:32 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -3210,16 +3213,16 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998480/meta-connect-2026-biggest-news-announcements</t>
+          <t>https://www.oracle.com/uk/news/announcement/oracle-and-wild-bio-join-forces-to-advance-ai-driven-agriculture-2026-09-24/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7.28</v>
+        <v>6.94</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3228,7 +3231,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3241,58 +3244,58 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Alibaba claims new Qwen Image 2.1 AI model beats Google Nano Banana 2.0 with minuscule 7B parameter model — benchmarks show open-weight contender is competitive with OpenAI and Meta image models</t>
+          <t>Google plans first test of AI chips in space under Project Suncatcher</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tech Industry Artificial Intelligence Alibaba claims new Qwen Image 2.1 AI model beats Google Nano Banana 2.0 with minuscule 7B parameter model — benchmarks show open-weight contender is competitive with OpenAI and Meta image models News-analysis By Jon Martindale Published 9 hours ago Open weights have once again thrown the guantlet down. (Image credit: Alibaba) Share Share this article Join the </t>
+          <t>Google plans first test of AI chips in space under Project Suncatcher    Reuters</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>meta, google, qwen, alibaba</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 15:34:36 GMT</t>
+          <t>Thu, 24 Sep 2026 14:11:34 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/alibaba-claims-new-qwen-image-2-1-ai-model-beats-google-nano-banana-2-0-with-minuscule-7b-parameter-model-benchmarks-show-open-weight-contender-is-competitive-with-openai-and-meta-image-models</t>
+          <t>https://www.reuters.com/business/media-telecom/google-plans-first-test-ai-chips-space-under-project-suncatcher-2026-09-24/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.2</v>
+        <v>6.92</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3300,25 +3303,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The 7 biggest announcements</t>
+          <t>Introducing Gemini 3.8 Live with Live Avatar</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Gadgets News Meta Connect 2026: The 7 biggest announcements ﻿This year’</t>
+          <t xml:space="preserve">Home Innovation &amp; AI Models &amp; research Gemini Models Introducing Gemini 3.8 Live with Live Avatar Sep 24, 2026 3 min read Gemini 3.8 Live with Live Avatar brings real-time visual presence to Gemini’s conversational AI. By natively coupling our live dialogue capabilities with low-latency streaming video, Live Avatar enables a more natural and intuitive conversational experience for enterprises and </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google, gemini</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T20:00:33-04:00</t>
+          <t>Thu, 24 Sep 2026 16:02:02 GMT</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3328,16 +3331,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999593/meta-connect-2026-everything-announced</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/gemini-3-8-live-with-live-avatar/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3346,12 +3349,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -3359,35 +3362,35 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Meta is making a standalone Muse AI gadget</t>
+          <t>Oracle triggers 'force majeure' on data center project over power delays, source says</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI Meta Meta is making a standalone Muse AI gadget The Muse Charm doesn</t>
+          <t>Oracle triggers 'force majeure' on data center project over power delays, source says    Reuters</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T20:15:20-04:00</t>
+          <t>Thu, 24 Sep 2026 23:00:36 GMT</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999750/muse-charm-meta-ai-hardware</t>
+          <t>https://www.reuters.com/business/oracle-cites-force-majeure-shield-itself-controversial-data-center-bloomberg-2026-09-24/</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3408,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3418,35 +3421,35 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Meta introduces camera-free AI glasses</t>
+          <t>Oracle, Blue Owl project delay sends ripples through AI financing, sources say</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Meta/screenshot / Social Meta introduces camera-free AI glasses Sarah Perez 4:39 PM PDT · September 23, 2026 Confirming earlier reports , Meta announced its first pair of camera-free AI </t>
+          <t>Oracle, Blue Owl project delay sends ripples through AI financing, sources say    Reuters</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 23:39:44 +0000</t>
+          <t>Thu, 24 Sep 2026 23:37:05 GMT</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-introduces-camera-free-ai-glasses/</t>
+          <t>https://www.reuters.com/business/energy/oracle-blue-owl-project-delay-sends-ripples-through-ai-financing-sources-say-2026-09-24/</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3467,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3477,25 +3480,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Muse is coming to Meta smart glasses</t>
+          <t>Analysis:Oracle, Blue Owl project delay sends ripples through AI financing, sources say</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI Gadgets Muse is coming to Meta smart glasses Meta’s AI agent is arri</t>
+          <t>Business Analysis:Oracle, Blue Owl project delay sends ripples through AI financing, sources say The Oracle logo is shown on an office building in Irvine, California, U.S. June 28, 2018. REUTERS/Mike Blake 25 Sep 2026 06:58AM (Updated: 25 Sep 2026 07:33AM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your preferred source on Google Add CNA as a trusted source to help Googl</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T19:40:56-04:00</t>
+          <t>Thu, 24 Sep 2026 22:58:08 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3505,25 +3508,25 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999673/meta-connect-2026-muse-glasses-features</t>
+          <t>https://www.channelnewsasia.com/business/analysisoracle-blue-owl-project-delay-sends-ripples-through-ai-financing-sources-say-6409591</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.9</v>
+        <v>6.81</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>about.fb.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3536,12 +3539,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Meta's Muse AI agent is coming to its AI glasses</t>
+          <t>The Biggest News From Connect 2026</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Have your virtual assistant book a flight while you’re jogging. Meta Add Engadget on Google: Preferred Source Google Discover Meta's Muse AI agent can do a lot . If you're willing to trust it with the most sensitive parts of your digital life, it can use the web, book travel, make phone calls, send emails and even make purchases on your behalf. So far, you can use Muse in its standalone iOS, Andro</t>
+          <t>Meta The Biggest News From Connect 2026 2 hours ago Takeaways Yesterday at Connect 2026, we announced we’re bringing Muse to our AI glasses so you can connect with your agent hands-free throughout your day — plus new features and connectors that make your Muse even better. We introduced Meta VR Glasses: all the magic of VR immersion in a breakthrough pair of glasses you can comfortably wear for ho</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3550,11 +3553,11 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 23:28:12 +0000</t>
+          <t>Thu, 24 Sep 2026 21:15:55 GMT</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3564,13 +3567,13 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267210/meta-muse-ai-agent-smart-glasses/</t>
+          <t>https://about.fb.com/news/2026/09/the-biggest-news-from-connect-2026/amp/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.9</v>
+        <v>6.52</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>3</v>
@@ -3587,7 +3590,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3595,25 +3598,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Meta introduces camera-free AI glasses</t>
+          <t>Oracle sends force majeure notice on its New Mexico Stargate data center</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Confirming earlier reports, Meta announced its first pair of camera-free AI glasses, the clunkily named Ray-Ban Meta Audio, at its Connect 2026 conference on Wednesday. Designed to combat criticism around the more malicious use cases for AI glasses, which saw them nicknamed “pervert glasses” by some, the new devices will be audio-only, offering the ability to listen to music and podcasts, take cal</t>
+          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Kim Kulish/Corbis / Getty Images AI Oracle sends force majeure notice on its New Mexico Stargate data center Aditya Mehta 11:11 AM PDT · September 24, 2026 Oracle has sent a force majeur</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 23:39:44 GMT</t>
+          <t>Thu, 24 Sep 2026 18:11:44 +0000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3623,13 +3626,13 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-introduces-camera-free-ai-glasses/</t>
+          <t>https://techcrunch.com/2026/09/24/oracle-sends-force-majeure-notice-on-its-new-mexico-stargate-data-center/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.9</v>
+        <v>6.52</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>3</v>
@@ -3641,12 +3644,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3654,25 +3657,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The biggest news and announcements</t>
+          <t>Oracle sends force majeure notice on its New Mexico Stargate data center</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TECH Updated Today, Sep 24, 2026, 7:15 AM GMT+7 Meta Connect 2026: The biggest news and announcements by Verge Staff 0 0 Comments It’s about time for Meta Connect, the company’s annual product launch event. This year, given the company’s major focus on AI and wearables like smart glasses, it seems likely that we’ll see updates from CEO Mark Zuckerberg and his team on those categories. The company </t>
+          <t>Oracle has sent a force majeure notice to the developer of Project Jupiter, a Stargate data center campus in New Mexico, Bloomberg first reported Thursday. Force majeure clauses, common in energy and commodities contracts, excuse a party from contractual obligations when events outside its control get in the way. Oracle is not seeking to exit as the campus’s main tenant, according to Bloomberg’s s</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 22:45:28 GMT</t>
+          <t>Thu, 24 Sep 2026 18:11:44 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3682,16 +3685,16 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998480/meta-connect-2026-biggest-news-announcements</t>
+          <t>https://techcrunch.com/2026/09/24/oracle-sends-force-majeure-notice-on-its-new-mexico-stargate-data-center/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.84</v>
+        <v>6.49</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -3700,12 +3703,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3713,41 +3716,41 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Amazon rolls out new agentic AI for third-party sellers</t>
+          <t>Gemini 3.8 Live with Live Avatar gives Google&amp;#8217;s AI a face</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Amazon rolls out new agentic AI for third-party sellers    Reuters</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Gemini 3.8 Live with Live Avatar gives Google’s AI a face Googl</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>google, gemini</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 13:03:43 GMT</t>
+          <t>2026-09-24T15:59:26-04:00</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/amazon-rolls-out-new-agentic-ai-third-party-sellers-2026-09-23/</t>
+          <t>https://www.theverge.com/tech/1000328/google-gemini-ai-live-avatar-face</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.7</v>
+        <v>6.49</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
@@ -3764,7 +3767,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3772,25 +3775,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026 live blog: On the ground at Mark Zuckerberg’s next big product launch</t>
+          <t>Gemini 3.8 Live with Live Avatar gives Google’s AI a face</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI Gadgets Meta Connect 2026 live blog: On the ground at Mark Zuckerber</t>
+          <t>TECH AI NEWS Gemini 3.8 Live with Live Avatar gives Google’s AI a face Google’s Live Avatar can lip-sync and show different facial expressions. by Emma Roth Sep 25, 2026, 2:59 AM GMT+7 17 17 Comments (All New) Image: Google Emma Roth is a news writer who covers the streaming wars, consumer tech, crypto, social media, and much more. Previously, she was a writer and editor at MUO. Google’s new Gemin</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>google, gemini</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T18:30:00-04:00</t>
+          <t>Thu, 24 Sep 2026 19:59:26 GMT</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3800,16 +3803,16 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998457/meta-connect-2026-live-blog-mark-zuckerberg-keynote</t>
+          <t>https://www.theverge.com/tech/1000328/google-gemini-ai-live-avatar-face</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.7</v>
+        <v>6.48</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -3818,12 +3821,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3831,25 +3834,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026 live blog: On the ground at Mark Zuckerberg’s next big product launch</t>
+          <t>Google is sending a teensy-tiny AI data center to space</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>TECH AI GADGETS Meta Connect 2026 live blog: On the ground at Mark Zuckerberg’s next big product launch How will Meta address privacy concerns around its glasses? by Jay Peters, Victoria Song, and Sean Hollister Sep 24, 2026, 5:30 AM GMT+7 8 8 Comments (All New) Image: The Verge Part Of Meta Connect 2026: The biggest news and announcements SEE ALL UPDATES It’s time once again for Meta’s annual Sep</t>
+          <t>It's an experiment to see how the chips hold up in the harsh vacuum of the cosmos. Google Add Engadget on Google: Preferred Source Google Discover Google's Project Suncatcher, which ultimately aims to put large AI installations in low-Earth orbit , is preparing for a milestone event. The company will be sending a teensy-tiny AI data center into space to see how it reacts to the harsh conditions, a</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 22:30:00 GMT</t>
+          <t>Thu, 24 Sep 2026 17:45:37 +0000</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3859,30 +3862,30 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998457/meta-connect-2026-live-blog-mark-zuckerberg-keynote</t>
+          <t>https://www.engadget.com/2267975/google-is-sending-a-teensy-tiny-ai-data-center-to-space/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.68</v>
+        <v>6.41</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3890,25 +3893,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Alibaba claims new Qwen Image 2.1 AI model beats Google Nano Banana 2.0 with minuscule 7B parameter model</t>
+          <t>Enterprise AI Is Entering a New Infrastructure Era. Oracle and AMD are at the front of it.</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>After building his first computers in his teens, Jon Martindale has spent the past two decades covering the latest advances in technology. From displays to PC components, blockchain to AI, and tablets to standing desk accessories, Jon has covered just about every facet of the tech space in his varie</t>
+          <t>Enterprise AI Is Entering a New Infrastructure Era. Oracle and AMD are at the front of it.    Oracle Blogs</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>google, qwen, alibaba</t>
+          <t>amd, oracle</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 15:34:36 +0000</t>
+          <t>Thu, 24 Sep 2026 19:06:41 GMT</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3918,30 +3921,30 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/alibaba-claims-new-qwen-image-2-1-ai-model-beats-google-nano-banana-2-0-with-minuscule-7b-parameter-model-benchmarks-show-open-weight-contender-is-competitive-with-openai-and-meta-image-models</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOaVEtZV9KWkxXYU5xQU9Ic1A0UFlGY3Y4clF5WWNUbkQwMVJPZ0ZEazBXb2F3NnNQeHhmcU9peGRpOTBXRjUyWURXelVIUXFNSnRWU3VVdU9iTnVhYTFiZzRfUzllS3p3S2hzNUVwa2tObWQ1d19qa2JBNE00ZnJVWVFidFBkQzNBM0ZWSGh0am9MS0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6.58</v>
+        <v>6.41</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>newsroom.amd.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3949,25 +3952,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Google faces UK push to put AI assistants on Android, Chrome choice screens</t>
+          <t>With AMD Ryzen AI Max Series Processors, Perplexity Brings Portable Computer to Agentic PCs</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Google faces UK push to put AI assistants on Android, Chrome choice screens    Reuters</t>
+          <t>With AMD Ryzen AI Max Series Processors, Perplexity Brings Portable Computer to Agentic PCs    newsroom.amd.com</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>amd, ryzen ai</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14.8</v>
+        <v>6</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 10:15:53 GMT</t>
+          <t>Thu, 24 Sep 2026 19:06:16 GMT</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3977,13 +3980,13 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOcWZJZElTNTJobDdXcWk2T241R0JyNWNPalMzRUQtQjhVLUtCRllKMno3MWNEMkRnMHctdnhWVDU4SHM3b0hTaUcwUkl2MThZZWRjb0pLRzN0c2ZEb19TNmg0ZUVDLUhMS3dpS3E3c1ZzNS1JUXZ1dHIxYkVKSmlxQmo5M2NaRnBQRnNuS29vWTBrTFNPeXE0bVl6RjEyd28zZktKdG9rbmlhSm1rQXlOWWlmRE9HV1J4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9IeHJndXVoMDM1RFlDVmp2ZUh6MlNHR3ZENWtWc1U4amppZWlTSVkwX0NMb3lsdzRIU093MzhydGNUU1JwX3NQd2tiTTdwQXVsVUtxQ2RLY0UzWkU0eU5IN21aaXNFRUNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6.42</v>
+        <v>6.33</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -3995,12 +3998,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4008,25 +4011,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Anyone can make stunning HD videos with Gemini Omni in Google Vids</t>
+          <t>Accelerate software development with Meta Model API and Muse Code through Oracle Marketplace</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Anyone can make stunning HD videos with Gemini Omni in Google Vids    blog.google</t>
+          <t>Accelerate software development with Meta Model API and Muse Code through Oracle Marketplace    Oracle Blogs</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>google, gemini</t>
+          <t>oracle, meta</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 19:10:21 GMT</t>
+          <t>Thu, 24 Sep 2026 18:12:26 GMT</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4036,30 +4039,30 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQMnNJNVpNRmFXYi01NzlvMFZBSDUxSXZuLTNDTm4zNGpCcjd1aUlNUkktc19sdndCYnMzS0tOVFRYZnp0TS1uLU1qRVRGeTRDenpYYlRUal9vYXFLY1VDMFBQeTE5U3VOZGFpUkN1WWVOQzhVSGhUYkxxd2N4MFRFN2RMclZ2eTFGWUZXWkFucU5DZ1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQb0lhUFV0WTc0MDhfYzhTTlFCTDFwcGV4UjUxSlp2NmUwYzJmS21RLWQ2WEtOS0pqN3I1QWppU1pGYm14QmFsYTlyVkZiMnN0aU9DdlZkQVA2VGlzYVVyY0RMeC1fWGNPSklkT3plMktZUXJWNTRUMkxvT3BhekZIZFpWRVp4T0FCZkwzTw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6.41</v>
+        <v>6.31</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4067,25 +4070,26 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>ZS strengthens AI-powered security operations with Microsoft Security Copilot.</t>
+          <t>Jensen Huang talks about AI and climate change like a supervillain</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>ZS strengthens AI-powered security operations with Microsoft Security Copilot.    Microsoft</t>
+          <t>As Jensen Huang puts it, AI can help fight climate change - but only if it inflicts "an enormous amount of pain and suffering" first.   
+ The Nvidia CEO discussed the future of energy and AI's impact on our planet in the latest episode of   The Ezra Klein Show  . But his comments boil down to the sa</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>microsoft, copilot</t>
+          <t>jensen huang, nvidia</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 19:05:56 GMT</t>
+          <t>2026-09-24T14:04:44-04:00</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4095,16 +4099,16 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQeWp4SGRLZEdtQnZlV082ckgtdXdzODdZMFNqWm5oV3ZRY1ZHdWR6UWQyUGRIMUtSbUNlc0VOQW5WRGFVSzEwbG5MdEdsN1ozWGNJUmVBSzE1ZXkzbnM5eDJEd0dTY2YtbTZFdE1qYUlSRmtWTFVITXBlY2pSeW5zbko4QWdUSEhOd0sxMWRSeGpvM3lqMHdMSXRjdWc?oc=5</t>
+          <t>https://www.theverge.com/tech/1000140/jensen-huang-nvidia-ai-energy-climate-change-supervillain</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6.4</v>
+        <v>6.15</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -4118,7 +4122,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4126,25 +4130,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Meta is making a standalone Muse AI gadget</t>
+          <t>Google is sending an AI satellite into space next week</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Meta is making a standalone Muse AI gadget    The Verge</t>
+          <t>Google is sending an AI satellite into space next week    The Verge</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8</v>
+        <v>10.9</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 00:15:20 GMT</t>
+          <t>Thu, 24 Sep 2026 14:15:17 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4154,30 +4158,30 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1mRmExOGJ2VENkZ1o1b1FQNXVGMXhzZVlTWlU3X3cxU21GZG5PeUxZUlBDTGZ4UFRBdkxsTHdwamJaMmxJdy15MHo2YmhNVTBBaGVrd0pIVkdKUm0tZUpheG9lVWk3b0ItbDRtT1lJZ0pyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdThqVkpxQ0dqWkhidzhPdnEyaUhtUE9HLTBjZjhNaGJQa3ltbVI5ZzlxUUMzYVFmZkNYN0F4Q09nUzVaWGt4bFh0RXMwcWlFTHE1MWtEYjNVNlkwMnFIQjBXaF91TkFYX0F3NjR2enc0bnNZb294TnZWQ3V1YkRfWjZidmlvdmlPZnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6.2</v>
+        <v>6.14</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>amd.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4185,25 +4189,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg debuts $1,299 Meta VR Glasses and Muse Charm pendant amid AI agent push</t>
+          <t>Beyond TOPS: AMD Ryzen™ AI Embedded X100 at the Edge</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg debuts $1,299 Meta VR Glasses and Muse Charm pendant amid AI agent push    cnbc.com</t>
+          <t>Beyond TOPS: AMD Ryzen™ AI Embedded X100 at the Edge    AMD</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3</v>
+        <v>11</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 00:45:00 GMT</t>
+          <t>Thu, 24 Sep 2026 14:08:01 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4213,16 +4217,16 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQZE4zZGJhTHNYbjFqTkFSQzctWEVRb1E0ZUZJVGVfZEdJSUpaSS1vOEpKdU9lenBqWGJUSEJ0eWhDS3lRTGZXelgyTkVjWlpxcTNZQnhVUDltWXh4RkE5VVlFNEMyc0N6dktNaEduUEN0ZzhPZUVjanY1UGszaTNTcVBOMHNIUUpaLUHSAY8BQVVfeXFMTXRHVmpoQXdRa2c1MjVscHM5WG5WVHpYa2pJRXphSnI3OVdLdE5lVEs2aGdxVE9uWXVlY1RueVlTU25nUFk4cnFIOG1hZTJ3azlxUVl0RHRoVmE4WXVrT0hBNHg5Y2JETzFRQ0EwenB5MzU5YU8wRzdZRHVtbDJIUUJ1d1lWbzlQVjJfZllGRGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNQXpTOUJWcVFkSC1DNHNsLThjVzB5dkVhcjZDZG1lYkFsS3NKZmJpUHRRMFJ3Nm80M2dlSFdGSk5MeUxBRnNrdF9fVnZfOENWeEJ3ak5WczRnRVRNVS03dm5Va3JHRWNRcDZaX2ZkZUZVZVpfUnJ3NFhBT0Y2WHdOR05TLVZBUDhwd04zSkpNZWRlNlRRN3VHZGZPb25Vc0gyRlZBdC1Yamh2TVRrSzI0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6.16</v>
+        <v>6.12</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -4231,12 +4235,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>foxbusiness.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4244,25 +4248,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI agent Muse partners with Instacart</t>
+          <t>Google tests letting Gemini call businesses for you</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI agent Muse partners with Instacart    Fox Business</t>
+          <t>Google says the AI-calling feature will first be available to Pixel 11 owners in the U.S. who pay for a Gemini subscription.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google, gemini</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10.8</v>
+        <v>9.1</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 14:14:38 GMT</t>
+          <t>Thu, 24 Sep 2026 16:00:00 +0000</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4272,25 +4276,25 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE44eno3SXUyaHB4c0E0dmUwSTl5OHkzNWpqZUtYTy0zaXFrdUlRbTc0UTBMRzVLYnRkOTFGa3ZHd2Q3ZnIxdmM5MXdKRTBoSUhSSzZNenZNWDlZTXc?oc=5</t>
+          <t>https://techcrunch.com/2026/09/24/google-tests-letting-gemini-make-phone-calls-initially-for-us-pixel-owners/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6.14</v>
+        <v>6.11</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -4303,12 +4307,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>A new wave of Connected Apps is rolling out to Gemini.</t>
+          <t>Google tests letting Gemini call businesses for you</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>A new wave of Connected Apps is rolling out to Gemini.    blog.google</t>
+          <t>Google tests letting Gemini call businesses for you    TechCrunch</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -4317,11 +4321,11 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 16:06:53 GMT</t>
+          <t>Thu, 24 Sep 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4331,13 +4335,13 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQVk52TllfMkhZN0x1WEkzV3duTUN3dEhabi1OU3FUUm9BeXBGZzF1cG4zd1NibnNrVHplRHhrU0R3UUlDZ1c0S0IzeWE5RkJBU3BERWMtWk51cm1XeE96Umc1bUFCalpBTEt6SDJ4aTM0TzJuWUZHQTFCVXE2STB5N2paUUNscDhUaEc3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNV2c2bmJTM0dCeEZDVXBmQV9rWU1NX2dFOHFkaEF6VlNXVTVZUVpaVk1GZVd0NEhOTW9ydGtTU0MwcGNxZUdUaDJVVFJ0WG5VRkdVcGxTOS1aNnJiZFp6NjNJXzJScDVDVWwtajg2VW9WUHlITHJXNi1uR0VHRVpPXzU1RVpkX0Vic1JQLTlqY1BuUHJ2STFvWWNHRlAzZTgtOEpSUTItZ0E2Y3I3WGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6.13</v>
+        <v>5.97</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -4349,12 +4353,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>deepmind.google</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4362,25 +4366,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Advancing Private AI Compute with secure, server-side memory</t>
+          <t>NVIDIA NeMo Relay now natively supports Oracle Generative AI</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Advancing Private AI Compute with secure, server-side memory    Google DeepMind</t>
+          <t>NVIDIA NeMo Relay now natively supports Oracle Generative AI    Oracle Blogs</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>google, deepmind</t>
+          <t>oracle, nvidia</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9</v>
+        <v>10.7</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 16:03:03 GMT</t>
+          <t>Thu, 24 Sep 2026 14:27:26 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4390,25 +4394,25 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQeEdFYzJoT3FDNm8zeG91UWJCQnBxa1pJR1dYVEpUTXpWc3MxaUwwM0UxZXNISTR2MXpGeGQzWFQ5VjBMMDMxX1Zzd2oyOGVSRW9Da3lJcTk1WlFKUTBYOTJEU2Q5Z0Z3UzM3UUtxQWFNX29mNUJoNnE1bnp5dzFlMWpudnAwdkpxTEJRT2I4OFc1VTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE51U2UwMGpkc2dFMkRRbHlLYnNrZ0NaSWlDR1QzeVF0a056eTBPVTRvU0QzVS04S2dBY3N6c0RiNnNhaFJjY2hORVRHMmZQUUJNXzN1ekhvTUlJT1BCdlU1czFIZEplem1uME5hdGdGYzgxQzItdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6.07</v>
+        <v>5.95</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -4421,25 +4425,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Gemini 3.8 text-to-speech says hello</t>
+          <t>Google Wallet got a lot of new tricks in 2026 – these 5 are my favorites</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Gemini 3.8 text-to-speech says hello    blog.google</t>
+          <t>You can do a whole lot more than tap to pay with Google’s Wallet app.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>google, gemini</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 15:27:40 GMT</t>
+          <t>2026-09-24T20:31:27Z</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4449,13 +4453,13 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPSWpTWDNZcWVYandkVlNIa1E5TWFsSG81NU5ST3Q1cGt1Z2xmUXdWRnEzb19zMjVfakoxdDNEVTlzdEJhUzFLanV2dlFaVTZ4a2RjRFMxTXlqUVpNaFFONVZzeGlHcnBwRTlWNlpMektVMlZ4RlJhVlN3X0k1NG0xSklibWpqLUVBUEJjSFVWOTZMWE1ZYllGMUVxbWlSV3c?oc=5</t>
+          <t>https://www.zdnet.com/tech/new-google-wallet-features-2026/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>2</v>
@@ -4467,12 +4471,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4480,25 +4484,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>AI firms should not get regulatory waivers, Nvidia CEO says on podcast</t>
+          <t>Google Wallet got a lot of new tricks in 2026 – these 5 are my favorites</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>AI firms should not get regulatory waivers, Nvidia CEO says on podcast    Reuters</t>
+          <t>Google Wallet got a lot of new tricks in 2026 – these 5 are my favorites    ZDNET</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 21:06:13 GMT</t>
+          <t>Thu, 24 Sep 2026 20:31:27 GMT</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4508,30 +4512,30 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNYkRfdGVvZzNROGxZeEd5dFQ5RV94YktETmZzRmNkekFLdkluYkVFNTVXSEI5RGtzOXNDa2FTWGN1RE5ZTEIta18tSWNWSUFCT0JNeXMyREZuNFFidlpPOEoyYjhMUUZlMC1odGpNcEdnR2tCdmZBRldqSnljTjNPLUVQOFBSWVkyS3Rsdzh2LWNvWGVoSkpTbUp6YUlLWFVRU1RkQ1hDMGtwUGVjN2ctUm9xWW9iNHNVSjE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE90c0ZVQXhpVmM5N3hVQzhFbGZxYkhJN0RHdVo1WE4xdmhYS1E0SWJKM3BiaEprekkyY2cwZ0lXMXlCUmJIS29kZ0ZtclF3ZVBldURHb0NJZUdOeS1fWjd5ci1ZTmZLcldqSFJF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>caixinglobal.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4539,25 +4543,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>From Chips to Laptops: Alibaba Accelerates Full-Stack AI Ambitions</t>
+          <t>Oracle named a Leader in the 2026 Gartner® Magic Quadrant™ for B2B Marketing Automation Platforms</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>From Chips to Laptops: Alibaba Accelerates Full-Stack AI Ambitions    Caixin Global</t>
+          <t>Oracle named a Leader in the 2026 Gartner® Magic Quadrant™ for B2B Marketing Automation Platforms    Oracle Blogs</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>alibaba</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 19:56:00 GMT</t>
+          <t>Thu, 24 Sep 2026 20:29:04 GMT</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4567,16 +4571,16 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNbE9ydUZHc1NUYUg2X1lZa2Q3VUFaTTJzd0hJQUU3VmJ0cmNNWnI5Y1hSOVREdzFUdHJMVXV0RkhwZmlUdk9ocFdmN1pydTN4c2ZRazhIQ05kX19kU1hlWjJyRTdhMng2bm1vbUtJNHFWXzJEdFU0SElZcUN4Mk9UaTRSMnBIU1JyZFR5WWtEUFRYX3k5c2ZYeEpkdXh3bGdVMVhqdUFkbmxyQXE3SjZzczhvZms3ZGVLc193ZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPaTN0RUlpVWpUUjJ1dFg3R08tOGdUbEtfOGFjZmZYNGptRm5UNFU3czlBdXBXbzNJbFF1aVZ3UTBVNHY4a1dkRHVFVHlVeTdOZXEwZ2FXS3BwUWxJM3BYdkZWUkJEbHpiZnJ1R3FrRnNEN2d1bnRuVU8wS3dDOFhqZThWTWdOM2lKQ0d1R2pFNDhibjYtMDE5RVY2NzFKdWlzSWppOEtrb2thTWNPWVdaWEw1V3NpOEdDWERTUkpkNjI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -4585,12 +4589,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4598,25 +4602,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Microsoft brings Snapdragon X2 Plus to 13-inch Surface Laptop, 12-inch Surface Pro</t>
+          <t>Meta employees ordered ‘attorney/client privilege’ hats while fighting child safety disclosures</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrew oversees laptop and desktop coverage and keeps up with the latest news in tech and gaming. His work has been published in Kotaku, PCMag, Complex, Tom’s Guide and Laptop Mag, among others. He fondly remembers his first computer: a Gateway that still lives in a spare room in his parents' home, </t>
+          <t>Meta's lawyers have argued that certain evidence should be withheld from public view on the grounds of attorney-client privilege in the ongoing lawsuits  over alleged harm to teens' safety and mental health . Lawyers suing the company said this week that the label has been applied far too broadly, w</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>instagram, meta</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 20:30:00 +0000</t>
+          <t>2026-09-24T19:50:55-04:00</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4626,13 +4630,13 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tablets/microsoft-surface/microsoft-brings-snapdragon-x2-plus-to-13-inch-surface-laptop-12-inch-surface-pro-low-end-systems-finally-get-upgrades</t>
+          <t>https://www.theverge.com/tech/1000370/meta-instagram-attorney-client-privilege-hats</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.95</v>
+        <v>5.84</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2</v>
@@ -4649,7 +4653,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4657,25 +4661,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Microsoft's new Surface Pro 12 and Surface Laptop 13 feature Snapdragon X2 Plus chips</t>
+          <t>New York Times Cooking is coming to Meta's AI and display glasses</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Microsoft's smaller Surface Pro 12 and Surface Laptop 13 are getting a much-needed chip upgrade.</t>
+          <t>The app is getting a "hands-free" mode that can narrate recipe steps.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 20:30:00 +0000</t>
+          <t>Thu, 24 Sep 2026 19:24:34 +0000</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4685,30 +4689,30 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2266680/microsofts-new-surface-pro-12-and-surface-laptop-13-feature-snapdragon-x2-plus-chips/</t>
+          <t>https://www.engadget.com/2268183/new-york-times-cooking-is-coming-to-metas-ai-and-display-glasses/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.94</v>
+        <v>5.84</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -4716,25 +4720,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Meta's Muse rekindles fears over winners and losers as personal AI agent emerges</t>
+          <t>Contain the Chaos: ‘CONTROL Resonant’ Launches on GeForce NOW</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Meta's Muse rekindles fears over winners and losers as personal AI agent emerges    Reuters</t>
+          <t>Contain the Chaos: ‘CONTROL Resonant’ Launches on GeForce NOW    NVIDIA Blog</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>geforce, nvidia</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 20:20:19 GMT</t>
+          <t>Thu, 24 Sep 2026 13:10:30 GMT</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4744,16 +4748,16 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNNlVtTVRPc0JSamlpVlpnNHFRZ1FQWDE0OFpRN2JoTzhQZ2lXaDVJV2FkMjBGa0psQ2ZUWVpzbXIxbFVDS3M0eHVWWGI4aGxxZVotZGJXTHRocVhXZU9fbl9rX2xvbGFkSGIxazlPOXlVRlNISEVLTEFZNXlpRVI5V1JRS3k5N3JTLXZ3UEFnMXA5cktvaDEwa3V6dUhvTkZRTnotSnhKV2xRbDJjRTF4NW5Bd0VWcXVIZHJWbDgtLTM2M3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBRY1YyQlJnNWxVaFRmXzRBUHlVVXE5SVJnSno2UHZvMjJWbi13Y1ZsVm1aejRKT0t6M0JSVW1SZzRkRjh2Mm5hWHdERmJibVNMQXppRVYxbmdpaFNaWnk0ektOc1ZqMy1ONDB3N1hwcVVNUWpVRDdj?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.9</v>
+        <v>5.84</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -4767,7 +4771,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4775,25 +4779,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Meta's $1,300 VR Glasses look like the Vision Pro sequel Apple should be making</t>
+          <t>New York Times Cooking Is Coming To Meta's AI And Display Glasses</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Sorry Apple, it looks like Meta's VR Glasses are the real Vision Pro successor.</t>
+          <t>New York Times Cooking Is Coming To Meta's AI And Display Glasses    Engadget</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>meta, apple</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 23:42:52 +0000</t>
+          <t>Thu, 24 Sep 2026 19:24:34 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4803,16 +4807,16 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267218/meta-vr-glasses-price-specs-apple-vision-pro-comparison/</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOdHBQcE16NHQ2UHBxemEzdzZSV3hqVS1DOFhwRTFKem5rS2UyOFdrQlJ6RHYzbGNkR0w0UGV4N0xUWnFxMHlKSUFvdTM2WWVGOUNHdXVkY05UZ1YzZUszQkJWU2QxamtrQVhoeHhHeVRJWGttWXV4Y2xybFR5MWZkY1BHdVVuNk93WHBSU2NLVWZUVW1xT1l1U0xhWXc4anM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.9</v>
+        <v>5.83</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -4821,7 +4825,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4834,12 +4838,12 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Google Docs’ built-in AI assistant can now pull information from Gemini Notebook.</t>
+          <t>Google to critical infra orgs: Our AI scanners won't be evil, promise</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Google Docs’ built-in AI assistant can now pull information from Gemini Notebook.    The Verge</t>
+          <t>Google has jumped on the AI-defense-for-critical-systems train with its Scan for Good initiative, and says that its threat-hunting models have already autonomously uncovered critical security issues at hospitals, a municipality, a public rail operator, and major technology providers. So don't fear t</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4848,11 +4852,11 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.8</v>
+        <v>12.1</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 22:15:33 GMT</t>
+          <t>Thu, 24 Sep 2026 15:00:00 +0200</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4862,30 +4866,30 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxORFktOGZ3YVVKVnV5WGFwdG1Ed3JicjVjTEd1bC1Ic2llTzNUNTVUeXREVWt0aF8zUXYwNUp6Z2lmMFphWVd3QzVMUUNLZlkzSnh2bTdQRmp5SlAteUs0UGdwckVMeERpbVhOSWdYUDlIeVFab1NMaDVJZVlTZ2VCMC14MTlSc3BrRVpkU2ZOdU9FSWs4Um5mVFR4UnprWE1LSEJDYm1sSjlFTDJ1MnZGUkxYeXFUa2M?oc=5</t>
+          <t>https://www.theregister.com/security/2026/09/24/google-to-critical-infra-orgs-our-ai-scanners-wont-be-evil-promise/5298685</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.86</v>
+        <v>5.76</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>apnews.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4893,25 +4897,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Sakeena Fiza Helps NVIDIA Hardware Succeed at Scale</t>
+          <t>Meta bets big on wearable AI, new AI agent as Zuckerberg pushes back against AI doom</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Sakeena Fiza Helps NVIDIA Hardware Succeed at Scale    NVIDIA Blog</t>
+          <t>Meta bets big on wearable AI, new AI agent as Zuckerberg pushes back against AI doom    AP News</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>5.5</v>
+        <v>23.4</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 19:33:57 GMT</t>
+          <t>Thu, 24 Sep 2026 01:47:00 GMT</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4921,13 +4925,13 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE1UWDJqdUFLVkZMaVRLczBDSVNYQ2dDemwzNXF2UVpsVUpucVRjbk9aQ2txaTI3LWdfWEhzYXJnU1NhWC1aclIwS3hHZVZyWHZwWUdhYXNUZFY5ZFBPLXJTMUVsWTRJQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZ2E2S0lGcG1uTzJRcDQxSXVhUjhCYU5DMkFYM3pXZEh1Tjg2Nmg3eDdqNmJxaVN5OGx4bE9LV2t6ekRHNElkRkhQa0VvNG9LbGRGc3pCMmFJenhhQUVydGVXMC1oNnJKaHBmM0M2UUNMdXFOMlAwd0VVT05hb28tZjZsLWhncGxpVElwdmRTQVZnUkZNWnVZVXh4cFBCQkxhVFFwRXJKZE04RVozYXZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.84</v>
+        <v>5.75</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -4939,12 +4943,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4952,25 +4956,25 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Amazon gives sellers an even smarter Seller Assistant and a new plugin for Amazon Quick and Anthropic’s Claude</t>
+          <t>Frontier Firm BNY resolves client inquires 80% faster with Microsoft AI powered Eliza</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Amazon gives sellers an even smarter Seller Assistant and a new plugin for Amazon Quick and Anthropic’s Claude    About Amazon</t>
+          <t>Frontier Firm BNY resolves client inquires 80% faster with Microsoft AI powered Eliza    Microsoft</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>anthropic, amazon</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 13:05:47 GMT</t>
+          <t>Thu, 24 Sep 2026 18:26:54 GMT</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4980,30 +4984,30 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQaUJEMEhNVjVhWlBoRXNvX0FlWEtZMUxyRGZXekdwR2NVcjhTSWZYd0phakF5N3N3Q3FuN2F3UV91SW9McFY3c1REZmhpTmE0NVR0RkFVT1FJSFNBWFNEX0FJV2czQ0VvOWkxY2J3U0RVUjBSV3NzQzA5eUxXTTJ3SjdBQWNwQ2dJbklNWlkwV2N6SUJfSzhwTWdaU2p3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOVFRMSHRjTDlZZUhoUHBPcENsSDd2LU1ZUFFnd1lYejl3cWVTQzlqaFVXRXpwYl95X09iQ2pXMUFrY1dEWko5S2ZIZ0VqVk4zQ0JjRVBhMXR2cFVsZW1RdWtxVG5iT0tnZWxGUE5DRDJoejdPY05qWUxNZ0JOem1iaUp3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5011,25 +5015,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Meta's standoff with Amazon over Muse could be a sign of things to come</t>
+          <t>To innovate faster, BNY upskills 100% of staff on Eliza, powered by Microsoft AI</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Meta's standoff with Amazon over Muse could be a sign of things to come    cnbc.com</t>
+          <t>To innovate faster, BNY upskills 100% of staff on Eliza, powered by Microsoft AI    Microsoft</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>meta, amazon</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 21:04:47 GMT</t>
+          <t>Thu, 24 Sep 2026 18:26:54 GMT</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5039,16 +5043,16 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNdzBob3NLdG1HOHF2bGl6cmJRcTBwZzVyT0ZPQm9GUVNFdnJWc1lTRUZXSngtTXJES052ZUwzVGxPNVhkVnc1WS0zcHo1VjA0dlktM28wZU1uem4zRUJWMmJua29sRjVWQzNDak9NX1dyd0ZWQ3hOVW5XYTRoZXZqSEdWbTM5dG0yWENnZjhGdjg3VWdjbjJjODlKcnNKYWhJWHlZ0gGoAUFVX3lxTFB3OV8wTlhFOGhWMWRSZ1VhY292c0p1Nkc3Q0dVZVB1NHhZZm1WbjROQ3dfQ0N3eXVEc0labW11SVZVV3VXUlZxWnV5TEU0aGlvSTktOTNJcGZhX3B2OGlhems3aDhXMVM0VnJVSnlzeXppWEpSRmNBckxKUHJjLV81YThyUDBKdVJhSjBlQ1VvMUdwNC14emJYM1dvTHdPYUE1YVI3VGRVRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE43ZS1EVzExR1lZcGgtM01RMF9vc3h0Sld0OTI4cDVlbnBMQlQ1Mk1sWHNvLUJneFBwNEJ0cDBiNFhWMlVwM0l4aV9idW8zZkx5YjVIRGxWQkJ4Ry1PRE5Kbmd2R0MwNWFjc3d4dGxWNzdlYlRrSVRWQ1A4dmw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.75</v>
+        <v>5.74</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -5057,12 +5061,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -5070,25 +5074,25 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s new Surface Mouse has haptic feedback and a customizable action button</t>
+          <t>How to get your cut of Apple's $250 million Siri settlement</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Microsoft is launching a second generation of its Surface Mouse next month that includes haptic feedback support. The Surface Mouse also has a customizable action button for the first time, which is primarily designed for quick access to Copilot ( of course ), but can be configured to work with othe</t>
+          <t>If you've bought an iPhone in the last couple of years, you might be eligible for a cut of the class action lawsuit. Here's how to file your claim.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>microsoft, copilot</t>
+          <t>apple, siri</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4.6</v>
+        <v>13.1</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23T16:30:00-04:00</t>
+          <t>Thu, 24 Sep 2026 12:00:00 +0000</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5098,13 +5102,13 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/news/999211/microsoft-surface-mouse-haptic-feedback</t>
+          <t>https://www.engadget.com/2265227/how-to-get-cut-apple-siri-ai-settlement/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.75</v>
+        <v>5.73</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -5116,12 +5120,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5129,25 +5133,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Google Beam expands with new regions, partners, and customers</t>
+          <t>What should change and what should stay as data architecture evolves for analytics and AI</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Google Beam expands with new regions, partners, and customers    blog.google</t>
+          <t>What should change and what should stay as data architecture evolves for analytics and AI    Oracle Blogs</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 18:23:39 GMT</t>
+          <t>Thu, 24 Sep 2026 18:12:26 GMT</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5157,13 +5161,13 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQRHJoZVM0NVNQSGtDVFNXandBV0dHVnJ2UW1qZXNSUUhmNHNjYUtZQUtZV05hVU9kX1ZoRmUtTEVRdGlnOHMzT1VNMHVjTEs3NS1jNnlGSjFLMllLS0p5cGgwQ0UtczVUaVJlWlpRUm92UkUxbHNkaFBWZjZ3TDF6VXFWTlJBMjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTVhicTF5b1VKT09LMW96VWlxT0FaenZSbDM3Y0tGUzRkTVdkSURhVEhGaEdlN010YmRFTG5kNjdpNkdlcGlMVlhTY3FaSDNnR0x3SVRaSHN4NXpzc01EOEJ3Wk1MU3ZES1M5UG1pUVVqN080VDgzWGVCOXV5UDBJcWdmRnJKazNXd0FxUXdvZkVXOWJTcEE5TDNfLTZaMGJSdDFvQlVwa3RLUjBWLXlCSV9DSG5pNWhVV080RVBhZHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.74</v>
+        <v>5.73</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>2</v>
@@ -5175,12 +5179,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5188,25 +5192,25 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Alibaba unveils Zhenwu V900 AI accelerator, claims it's 'the most powerful AI chip in China' — accelerator supports 500,000 chip supercluster with a 10T-parameter Qwen model on the roadmap</t>
+          <t>How To Get Your Cut Of Apple's $250 Million Siri Settlement</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Alibaba unveils Zhenwu V900 AI accelerator, claims it's 'the most powerful AI chip in China' — accelerator supports 500,000 chip supercluster with a 10T-parameter Qwen model on the roadmap    tomshardware.com</t>
+          <t>How To Get Your Cut Of Apple's $250 Million Siri Settlement    Engadget</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>qwen, alibaba</t>
+          <t>apple, siri</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 12:00:00 GMT</t>
+          <t>Thu, 24 Sep 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5216,30 +5220,30 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AJBVV95cUxNZXdKRTNKSWxHZEFza3k0bHV2Tng3RnNuY3pjWmtCZWQwaEF5Si1IblRzRnpoamRwRV9UbmF6NFlTV1AzNXZkOGxBNVFZalQtU3RCZTJqbERuRHEyMlVEdU5SY2V6d0xQRzEtRHZJbmVLZUc1MnlvdVM5VTQxLTJaWWRjTUQwdXJRaHplMkVicHZ4SkZlbzhYcHhLS2Y4WklOam5FcnZMSURnV0Fnc0M2a1p1UTZwa0F2WW5WaklNZXBNSzFIXzZMaU9NeUFvZjdzNldwV0plWTNCcy1SLW9yNHhEREN5R2tra2hreTNXSDF5V3hXcy1EYmNhUDNBSUF2VkpyNTRKbVlGbGh4Wmt2MVJDc2hDOTFBNC1GNlRETmlObjBmSzlmbF9hYmxuZ0NSVjQwRHd2YWhUTXBJZUdjWENrUEZCTVM4UmtBYWlSdXBYaVY0YmMtV2V3ak1TVmpjTmxiR0FJSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1wM3hKZF91TWE1bVprakhDTFU4eGZPeGNEWTJSYXE4bl9JSk5GZEdwNXpuZXNwWXVVT3pCc3lJMWtCOG1KWkdEZzZaMTVfNmZqR01YSFliNV9JTnRGVUl3cGRwVUF5dERKSGZoN0NEUVRnb2xwNFFzSVp0Nkhudw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.65</v>
+        <v>5.71</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>oracle.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -5247,25 +5251,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Oracle to Advance Cancer Care with New Oncology EHR</t>
+          <t>Jensen Huang talks about AI and climate change like a supervillain</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Oracle to Advance Cancer Care with New Oncology EHR    Oracle</t>
+          <t>Jensen Huang talks about AI and climate change like a supervillain    The Verge</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>jensen huang</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 17:21:45 GMT</t>
+          <t>Thu, 24 Sep 2026 18:04:44 GMT</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5275,30 +5279,30 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQZkxrUVVENWd1NUY2NWY1Q2JpWGVWRU8wVUVuU2JnelBiNFMxa3lpMnhCdFNEQkU5Z3p0aDNkM292OTVnSkhPZ25YNHFPWE1KMEt0WVU1a1pSREhodURXWV9ta3oxYWxiTTRhVk9BYWllNWUzTlp4WDVGd1lqM0tqMWRhYmh2WTJGT21Md29xRmU3ay1oUW9NVnRIYU9zV0owR1ZzMV94VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQNlNmM2R3THNqdE1USVJBY21wNDRBdTJCdngxazd2bXhXSVdjWmFWYTAzWllMcWNPVll1UzFSdU5reUJqYXUxRWJkTU05OXI4T3BDcFZybzlvLUp5R3czZXBMRlpKdlZJeVF6RUs5aFhSSmlLZ1JCUXVXLTZ5NndIUmc2OFRpUlo4MmZqSWtHQVFQanh6a3EwOUJiVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.64</v>
+        <v>5.69</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -5306,25 +5310,25 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>What's New in Oracle AI Agent Memory: Graph-Aware Retrieval, Image Memory, and Enterprise Controls</t>
+          <t>Meta is going to let you build games with AI right on your phone</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>What's New in Oracle AI Agent Memory: Graph-Aware Retrieval, Image Memory, and Enterprise Controls    blogs.oracle.com</t>
+          <t xml:space="preserve">Meta has a new plan to get people to make games for its Horizon social platform. The company  today announced  two new development tools  that will let you create games with AI prompts: Horizon Create, a mobile app, and Horizon Studio, a browser app that offers more granular controls. The apps will </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Wed, 23 Sep 2026 17:17:38 GMT</t>
+          <t>2026-09-24T13:52:29-04:00</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5334,16 +5338,16 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNTDY4ODJDSUhMS1JCR3Q2VDQwTkZ4WnQ5aTRnNHJKUjFEWEF1OFlOeFhPaGtoMHlNTTdZeDRlbkl2Vmdlc1RpVUFuNVpNNktKWlRTRXc5UjV0bE5Ea0tjazczWjg5Q0VPRVJ3Y05SNnNXWU9xaWk2aHIyUXhJYnhEeHRZc2tkOGVEbU92YnpYWDRncDRvekpVR0N2aDVXN0ZiUElFcmN3cU9FRnBPdFFRYmlXZ2I1ZHhsSTVQWkN4VEhpUjFCUHlnZzJR?oc=5</t>
+          <t>https://www.theverge.com/games/999972/meta-horizon-create-studio-ai-games</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.6</v>
+        <v>5.69</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -5352,7 +5356,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -5365,12 +5369,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Meta made a Tamagotchi-like wearable for its Muse AI agent</t>
+          <t>Meta is going to let you build games with AI right on your phone</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>The tiny hardware device creates  another mobile home for its AI agent Muse.</t>
+          <t>Meta is going to let you build games with AI right on your phone    The Verge</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -5379,11 +5383,11 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 00:46:17 +0000</t>
+          <t>Thu, 24 Sep 2026 17:52:29 GMT</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5393,16 +5397,16 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-made-a-tamagotchi-like-wearable-for-its-muse-ai-agent/</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9qeXJibDVIaHRxSmc5Q1pQeWFPcEdzeTVyd1hTaXQ4aGQtWVZzV3VsQmgwMk16QW42UUwzR1ZFamNtYWJfa2c0YnBydV9peXJrZk8zSjZrRElBTXVVeE84QWw3TWJTRFkzLUFnc285YVFiYWN6S2x4dTZQQXBFUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -5411,7 +5415,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5424,12 +5428,12 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Meta Connect 2026</t>
+          <t>Meta’s Muse Charm looks like a Tamagotchi, but it’s tapping into a much newer trend</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>VR glasses, Aviator-style Ray-Ban Meta specs, Ace Attorney in virtual reality and much more.</t>
+          <t>Meta’s new AI gadget may look like a Tamagotchi, but its dangling form factor taps into a much broader Gen Z trend around bag charms, retro tech, and turning gadgets into fashion accessories.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -5438,11 +5442,11 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 00:07:34 +0000</t>
+          <t>Thu, 24 Sep 2026 17:39:24 +0000</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5452,16 +5456,16 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267230/everything-announced-at-meta-connect-2026/</t>
+          <t>https://techcrunch.com/2026/09/24/metas-muse-charm-looks-like-a-tamagotchi-but-its-tapping-into-a-much-newer-trend/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -5470,7 +5474,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -5483,12 +5487,12 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Meta put Muse in a Tamagotchi like 'Charm' device</t>
+          <t>Meta’s Muse Charm looks like a Tamagotchi, but it’s tapping into a much newer trend</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Meta Charm is a Tamagotchi-like device with Muse AI.</t>
+          <t>Meta’s Muse Charm looks like a Tamagotchi, but it’s tapping into a much newer trend    TechCrunch</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5497,11 +5501,11 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Thu, 24 Sep 2026 00:05:03 +0000</t>
+          <t>Thu, 24 Sep 2026 17:39:24 GMT</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5511,7 +5515,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267229/meta-put-muse-in-a-tamagotchi-like-charm-device/</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUUxUTkJneDJsM2laTVEwYUJPUUtVd0RQT0h0SW9oWU1TUVRaNmkwVGJXOExIRXhlZjBVLUZxd1NfZjMteGZDbzhwaG1qZENGMEc2eEpHbGxYZC13NlFHVDBaZzVrTG9VSmJzZ3M0aGI4SHY2VEc2UkhlZ1h3QlpqTEZYdXlvd2tKNWNMbjY2Z290QWdyY3FHem9lNF8wQ1dReFEzU0VMRTNmNjJ5NUt3TDRBdzlnUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5635,26 +5639,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.5</v>
+        <v>7.28</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.58+sig0.6+src2.0+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The biggest news and announcements</t>
+          <t>Oracle and Wild Bio Join Forces to Advance AI-Driven Agriculture</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -5662,12 +5666,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>oracle.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998480/meta-connect-2026-biggest-news-announcements</t>
+          <t>https://www.oracle.com/uk/news/announcement/oracle-and-wild-bio-join-forces-to-advance-ai-driven-agriculture-2026-09-24/</t>
         </is>
       </c>
     </row>
@@ -5676,16 +5680,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.28</v>
+        <v>6.94</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.38+sig2.4+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.24+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Alibaba claims new Qwen Image 2.1 AI model beats Google Nano Banana 2.0 with minuscule 7B parameter model — benchmarks show open-weight contender is competitive with OpenAI and Meta image models</t>
+          <t>Google plans first test of AI chips in space under Project Suncatcher</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5695,20 +5699,20 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>meta, google, qwen, alibaba</t>
+          <t>google</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/alibaba-claims-new-qwen-image-2-1-ai-model-beats-google-nano-banana-2-0-with-minuscule-7b-parameter-model-benchmarks-show-open-weight-contender-is-competitive-with-openai-and-meta-image-models</t>
+          <t>https://www.reuters.com/business/media-telecom/google-plans-first-test-ai-chips-space-under-project-suncatcher-2026-09-24/</t>
         </is>
       </c>
     </row>
@@ -5717,39 +5721,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.2</v>
+        <v>6.92</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig0.6+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.42+sig1.2+src2.0+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The 7 biggest announcements</t>
+          <t>Introducing Gemini 3.8 Live with Live Avatar</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google, gemini</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999593/meta-connect-2026-everything-announced</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/gemini-3-8-live-with-live-avatar/</t>
         </is>
       </c>
     </row>
@@ -5758,39 +5762,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Meta is making a standalone Muse AI gadget</t>
+          <t>Oracle triggers 'force majeure' on data center project over power delays, source says</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999750/muse-charm-meta-ai-hardware</t>
+          <t>https://www.reuters.com/business/oracle-cites-force-majeure-shield-itself-controversial-data-center-bloomberg-2026-09-24/</t>
         </is>
       </c>
     </row>
@@ -5808,17 +5812,17 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Meta introduces camera-free AI glasses</t>
+          <t>Oracle, Blue Owl project delay sends ripples through AI financing, sources say</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -5826,12 +5830,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-introduces-camera-free-ai-glasses/</t>
+          <t>https://www.reuters.com/business/energy/oracle-blue-owl-project-delay-sends-ripples-through-ai-financing-sources-say-2026-09-24/</t>
         </is>
       </c>
     </row>
@@ -5849,17 +5853,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Muse is coming to Meta smart glasses</t>
+          <t>Analysis:Oracle, Blue Owl project delay sends ripples through AI financing, sources say</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -5867,12 +5871,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999673/meta-connect-2026-muse-glasses-features</t>
+          <t>https://www.channelnewsasia.com/business/analysisoracle-blue-owl-project-delay-sends-ripples-through-ai-financing-sources-say-6409591</t>
         </is>
       </c>
     </row>
@@ -5881,16 +5885,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.9</v>
+        <v>6.81</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.91+sig0.6+src2.0+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Meta's Muse AI agent is coming to its AI glasses</t>
+          <t>The Biggest News From Connect 2026</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5904,16 +5908,16 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>about.fb.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267210/meta-muse-ai-agent-smart-glasses/</t>
+          <t>https://about.fb.com/news/2026/09/the-biggest-news-from-connect-2026/amp/</t>
         </is>
       </c>
     </row>
@@ -5922,26 +5926,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.9</v>
+        <v>6.52</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.62+sig0.6+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Meta introduces camera-free AI glasses</t>
+          <t>Oracle sends force majeure notice on its New Mexico Stargate data center</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -5954,7 +5958,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-introduces-camera-free-ai-glasses/</t>
+          <t>https://techcrunch.com/2026/09/24/oracle-sends-force-majeure-notice-on-its-new-mexico-stargate-data-center/</t>
         </is>
       </c>
     </row>
@@ -5963,26 +5967,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.9</v>
+        <v>6.52</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.62+sig0.6+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The biggest news and announcements</t>
+          <t>Oracle sends force majeure notice on its New Mexico Stargate data center</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -5990,12 +5994,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998480/meta-connect-2026-biggest-news-announcements</t>
+          <t>https://techcrunch.com/2026/09/24/oracle-sends-force-majeure-notice-on-its-new-mexico-stargate-data-center/</t>
         </is>
       </c>
     </row>
@@ -6004,39 +6008,39 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.84</v>
+        <v>6.49</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.14+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.79+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Amazon rolls out new agentic AI for third-party sellers</t>
+          <t>Gemini 3.8 Live with Live Avatar gives Google&amp;#8217;s AI a face</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>google, gemini</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/amazon-rolls-out-new-agentic-ai-third-party-sellers-2026-09-23/</t>
+          <t>https://www.theverge.com/tech/1000328/google-gemini-ai-live-avatar-face</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6082,57 +6086,57 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Meta Platforms  (Tier 1 · 17 stories)</t>
+          <t>Alphabet  (Tier 1 · 11 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.5</v>
+        <v>6.94</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The biggest news and announcements</t>
+          <t>Google plans first test of AI chips in space under Project Suncatcher</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998480/meta-connect-2026-biggest-news-announcements</t>
+          <t>https://www.reuters.com/business/media-telecom/google-plans-first-test-ai-chips-space-under-project-suncatcher-2026-09-24/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.2</v>
+        <v>6.92</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The 7 biggest announcements</t>
+          <t>Introducing Gemini 3.8 Live with Live Avatar</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999593/meta-connect-2026-everything-announced</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/gemini-3-8-live-with-live-avatar/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7</v>
+        <v>6.49</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Meta is making a standalone Muse AI gadget</t>
+          <t>Gemini 3.8 Live with Live Avatar gives Google&amp;#8217;s AI a face</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -6142,77 +6146,77 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999750/muse-charm-meta-ai-hardware</t>
+          <t>https://www.theverge.com/tech/1000328/google-gemini-ai-live-avatar-face</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.9</v>
+        <v>6.49</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Meta introduces camera-free AI glasses</t>
+          <t>Gemini 3.8 Live with Live Avatar gives Google’s AI a face</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-introduces-camera-free-ai-glasses/</t>
+          <t>https://www.theverge.com/tech/1000328/google-gemini-ai-live-avatar-face</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.9</v>
+        <v>6.48</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Muse is coming to Meta smart glasses</t>
+          <t>Google is sending a teensy-tiny AI data center to space</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/999673/meta-connect-2026-muse-glasses-features</t>
+          <t>https://www.engadget.com/2267975/google-is-sending-a-teensy-tiny-ai-data-center-to-space/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.9</v>
+        <v>6.15</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Meta's Muse AI agent is coming to its AI glasses</t>
+          <t>Google is sending an AI satellite into space next week</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267210/meta-muse-ai-agent-smart-glasses/</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdThqVkpxQ0dqWkhidzhPdnEyaUhtUE9HLTBjZjhNaGJQa3ltbVI5ZzlxUUMzYVFmZkNYN0F4Q09nUzVaWGt4bFh0RXMwcWlFTHE1MWtEYjNVNlkwMnFIQjBXaF91TkFYX0F3NjR2enc0bnNZb294TnZWQ3V1YkRfWjZidmlvdmlPZnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.9</v>
+        <v>6.12</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Meta introduces camera-free AI glasses</t>
+          <t>Google tests letting Gemini call businesses for you</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -6222,354 +6226,321 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-introduces-camera-free-ai-glasses/</t>
+          <t>https://techcrunch.com/2026/09/24/google-tests-letting-gemini-make-phone-calls-initially-for-us-pixel-owners/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.9</v>
+        <v>6.11</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026: The biggest news and announcements</t>
+          <t>Google tests letting Gemini call businesses for you</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998480/meta-connect-2026-biggest-news-announcements</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNV2c2bmJTM0dCeEZDVXBmQV9rWU1NX2dFOHFkaEF6VlNXVTVZUVpaVk1GZVd0NEhOTW9ydGtTU0MwcGNxZUdUaDJVVFJ0WG5VRkdVcGxTOS1aNnJiZFp6NjNJXzJScDVDVWwtajg2VW9WUHlITHJXNi1uR0VHRVpPXzU1RVpkX0Vic1JQLTlqY1BuUHJ2STFvWWNHRlAzZTgtOEpSUTItZ0E2Y3I3WGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.7</v>
+        <v>5.95</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026 live blog: On the ground at Mark Zuckerberg’s next big product launch</t>
+          <t>Google Wallet got a lot of new tricks in 2026 – these 5 are my favorites</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998457/meta-connect-2026-live-blog-mark-zuckerberg-keynote</t>
+          <t>https://www.zdnet.com/tech/new-google-wallet-features-2026/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.7</v>
+        <v>5.95</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Meta Connect 2026 live blog: On the ground at Mark Zuckerberg’s next big product launch</t>
+          <t>Google Wallet got a lot of new tricks in 2026 – these 5 are my favorites</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/998457/meta-connect-2026-live-blog-mark-zuckerberg-keynote</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE90c0ZVQXhpVmM5N3hVQzhFbGZxYkhJN0RHdVo1WE4xdmhYS1E0SWJKM3BiaEprekkyY2cwZ0lXMXlCUmJIS29kZ0ZtclF3ZVBldURHb0NJZUdOeS1fWjd5ci1ZTmZLcldqSFJF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.4</v>
+        <v>5.83</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Meta is making a standalone Muse AI gadget</t>
+          <t>Google to critical infra orgs: Our AI scanners won't be evil, promise</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1mRmExOGJ2VENkZ1o1b1FQNXVGMXhzZVlTWlU3X3cxU21GZG5PeUxZUlBDTGZ4UFRBdkxsTHdwamJaMmxJdy15MHo2YmhNVTBBaGVrd0pIVkdKUm0tZUpheG9lVWk3b0ItbDRtT1lJZ0pyUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Mark Zuckerberg debuts $1,299 Meta VR Glasses and Muse Charm pendant amid AI agent push</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>cnbc.com</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQZE4zZGJhTHNYbjFqTkFSQzctWEVRb1E0ZUZJVGVfZEdJSUpaSS1vOEpKdU9lenBqWGJUSEJ0eWhDS3lRTGZXelgyTkVjWlpxcTNZQnhVUDltWXh4RkE5VVlFNEMyc0N6dktNaEduUEN0ZzhPZUVjanY1UGszaTNTcVBOMHNIUUpaLUHSAY8BQVVfeXFMTXRHVmpoQXdRa2c1MjVscHM5WG5WVHpYa2pJRXphSnI3OVdLdE5lVEs2aGdxVE9uWXVlY1RueVlTU25nUFk4cnFIOG1hZTJ3azlxUVl0RHRoVmE4WXVrT0hBNHg5Y2JETzFRQ0EwenB5MzU5YU8wRzdZRHVtbDJIUUJ1d1lWbzlQVjJfZllGRGc?oc=5</t>
+          <t>https://www.theregister.com/security/2026/09/24/google-to-critical-infra-orgs-our-ai-scanners-wont-be-evil-promise/5298685</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Meta's new AI agent Muse partners with Instacart</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>foxbusiness.com</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE44eno3SXUyaHB4c0E0dmUwSTl5OHkzNWpqZUtYTy0zaXFrdUlRbTc0UTBMRzVLYnRkOTFGa3ZHd2Q3ZnIxdmM5MXdKRTBoSUhSSzZNenZNWDlZTXc?oc=5</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Oracle  (Tier 1 · 10 stories)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5.94</v>
+        <v>7.28</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Meta's Muse rekindles fears over winners and losers as personal AI agent emerges</t>
+          <t>Oracle and Wild Bio Join Forces to Advance AI-Driven Agriculture</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>oracle.com</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNNlVtTVRPc0JSamlpVlpnNHFRZ1FQWDE0OFpRN2JoTzhQZ2lXaDVJV2FkMjBGa0psQ2ZUWVpzbXIxbFVDS3M0eHVWWGI4aGxxZVotZGJXTHRocVhXZU9fbl9rX2xvbGFkSGIxazlPOXlVRlNISEVLTEFZNXlpRVI5V1JRS3k5N3JTLXZ3UEFnMXA5cktvaDEwa3V6dUhvTkZRTnotSnhKV2xRbDJjRTF4NW5Bd0VWcXVIZHJWbDgtLTM2M3c?oc=5</t>
+          <t>https://www.oracle.com/uk/news/announcement/oracle-and-wild-bio-join-forces-to-advance-ai-driven-agriculture-2026-09-24/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Meta made a Tamagotchi-like wearable for its Muse AI agent</t>
+          <t>Oracle triggers 'force majeure' on data center project over power delays, source says</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/23/meta-made-a-tamagotchi-like-wearable-for-its-muse-ai-agent/</t>
+          <t>https://www.reuters.com/business/oracle-cites-force-majeure-shield-itself-controversial-data-center-bloomberg-2026-09-24/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Meta Connect 2026</t>
+          <t>Oracle, Blue Owl project delay sends ripples through AI financing, sources say</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267230/everything-announced-at-meta-connect-2026/</t>
+          <t>https://www.reuters.com/business/energy/oracle-blue-owl-project-delay-sends-ripples-through-ai-financing-sources-say-2026-09-24/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Meta put Muse in a Tamagotchi like 'Charm' device</t>
+          <t>Analysis:Oracle, Blue Owl project delay sends ripples through AI financing, sources say</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267229/meta-put-muse-in-a-tamagotchi-like-charm-device/</t>
+          <t>https://www.channelnewsasia.com/business/analysisoracle-blue-owl-project-delay-sends-ripples-through-ai-financing-sources-say-6409591</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Oracle sends force majeure notice on its New Mexico Stargate data center</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/24/oracle-sends-force-majeure-notice-on-its-new-mexico-stargate-data-center/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Alphabet  (Tier 1 · 9 stories)</t>
+      <c r="A22" s="2" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Oracle sends force majeure notice on its New Mexico Stargate data center</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/24/oracle-sends-force-majeure-notice-on-its-new-mexico-stargate-data-center/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7.28</v>
+        <v>6.41</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Alibaba claims new Qwen Image 2.1 AI model beats Google Nano Banana 2.0 with minuscule 7B parameter model — benchmarks show open-weight contender is competitive with OpenAI and Meta image models</t>
+          <t>Enterprise AI Is Entering a New Infrastructure Era. Oracle and AMD are at the front of it.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/alibaba-claims-new-qwen-image-2-1-ai-model-beats-google-nano-banana-2-0-with-minuscule-7b-parameter-model-benchmarks-show-open-weight-contender-is-competitive-with-openai-and-meta-image-models</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOaVEtZV9KWkxXYU5xQU9Ic1A0UFlGY3Y4clF5WWNUbkQwMVJPZ0ZEazBXb2F3NnNQeHhmcU9peGRpOTBXRjUyWURXelVIUXFNSnRWU3VVdU9iTnVhYTFiZzRfUzllS3p3S2hzNUVwa2tObWQ1d19qa2JBNE00ZnJVWVFidFBkQzNBM0ZWSGh0am9MS0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6.68</v>
+        <v>6.33</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Alibaba claims new Qwen Image 2.1 AI model beats Google Nano Banana 2.0 with minuscule 7B parameter model</t>
+          <t>Accelerate software development with Meta Model API and Muse Code through Oracle Marketplace</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/alibaba-claims-new-qwen-image-2-1-ai-model-beats-google-nano-banana-2-0-with-minuscule-7b-parameter-model-benchmarks-show-open-weight-contender-is-competitive-with-openai-and-meta-image-models</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQb0lhUFV0WTc0MDhfYzhTTlFCTDFwcGV4UjUxSlp2NmUwYzJmS21RLWQ2WEtOS0pqN3I1QWppU1pGYm14QmFsYTlyVkZiMnN0aU9DdlZkQVA2VGlzYVVyY0RMeC1fWGNPSklkT3plMktZUXJWNTRUMkxvT3BhekZIZFpWRVp4T0FCZkwzTw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6.58</v>
+        <v>5.94</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Google faces UK push to put AI assistants on Android, Chrome choice screens</t>
+          <t>Oracle named a Leader in the 2026 Gartner® Magic Quadrant™ for B2B Marketing Automation Platforms</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOcWZJZElTNTJobDdXcWk2T241R0JyNWNPalMzRUQtQjhVLUtCRllKMno3MWNEMkRnMHctdnhWVDU4SHM3b0hTaUcwUkl2MThZZWRjb0pLRzN0c2ZEb19TNmg0ZUVDLUhMS3dpS3E3c1ZzNS1JUXZ1dHIxYkVKSmlxQmo5M2NaRnBQRnNuS29vWTBrTFNPeXE0bVl6RjEyd28zZktKdG9rbmlhSm1rQXlOWWlmRE9HV1J4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPaTN0RUlpVWpUUjJ1dFg3R08tOGdUbEtfOGFjZmZYNGptRm5UNFU3czlBdXBXbzNJbFF1aVZ3UTBVNHY4a1dkRHVFVHlVeTdOZXEwZ2FXS3BwUWxJM3BYdkZWUkJEbHpiZnJ1R3FrRnNEN2d1bnRuVU8wS3dDOFhqZThWTWdOM2lKQ0d1R2pFNDhibjYtMDE5RVY2NzFKdWlzSWppOEtrb2thTWNPWVdaWEw1V3NpOEdDWERTUkpkNjI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6.42</v>
+        <v>5.73</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Anyone can make stunning HD videos with Gemini Omni in Google Vids</t>
+          <t>What should change and what should stay as data architecture evolves for analytics and AI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQMnNJNVpNRmFXYi01NzlvMFZBSDUxSXZuLTNDTm4zNGpCcjd1aUlNUkktc19sdndCYnMzS0tOVFRYZnp0TS1uLU1qRVRGeTRDenpYYlRUal9vYXFLY1VDMFBQeTE5U3VOZGFpUkN1WWVOQzhVSGhUYkxxd2N4MFRFN2RMclZ2eTFGWUZXWkFucU5DZ1U?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>A new wave of Connected Apps is rolling out to Gemini.</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>blog.google</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQVk52TllfMkhZN0x1WEkzV3duTUN3dEhabi1OU3FUUm9BeXBGZzF1cG4zd1NibnNrVHplRHhrU0R3UUlDZ1c0S0IzeWE5RkJBU3BERWMtWk51cm1XeE96Umc1bUFCalpBTEt6SDJ4aTM0TzJuWUZHQTFCVXE2STB5N2paUUNscDhUaEc3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTVhicTF5b1VKT09LMW96VWlxT0FaenZSbDM3Y0tGUzRkTVdkSURhVEhGaEdlN010YmRFTG5kNjdpNkdlcGlMVlhTY3FaSDNnR0x3SVRaSHN4NXpzc01EOEJ3Wk1MU3ZES1M5UG1pUVVqN080VDgzWGVCOXV5UDBJcWdmRnJKazNXd0FxUXdvZkVXOWJTcEE5TDNfLTZaMGJSdDFvQlVwa3RLUjBWLXlCSV9DSG5pNWhVV080RVBhZHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Advancing Private AI Compute with secure, server-side memory</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>deepmind.google</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQeEdFYzJoT3FDNm8zeG91UWJCQnBxa1pJR1dYVEpUTXpWc3MxaUwwM0UxZXNISTR2MXpGeGQzWFQ5VjBMMDMxX1Zzd2oyOGVSRW9Da3lJcTk1WlFKUTBYOTJEU2Q5Z0Z3UzM3UUtxQWFNX29mNUJoNnE1bnp5dzFlMWpudnAwdkpxTEJRT2I4OFc1VTQ?oc=5</t>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 9 stories)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6.07</v>
+        <v>6.81</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Gemini 3.8 text-to-speech says hello</t>
+          <t>The Biggest News From Connect 2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>about.fb.com</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPSWpTWDNZcWVYandkVlNIa1E5TWFsSG81NU5ST3Q1cGt1Z2xmUXdWRnEzb19zMjVfakoxdDNEVTlzdEJhUzFLanV2dlFaVTZ4a2RjRFMxTXlqUVpNaFFONVZzeGlHcnBwRTlWNlpMektVMlZ4RlJhVlN3X0k1NG0xSklibWpqLUVBUEJjSFVWOTZMWE1ZYllGMUVxbWlSV3c?oc=5</t>
+          <t>https://about.fb.com/news/2026/09/the-biggest-news-from-connect-2026/amp/</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6550,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Google Docs’ built-in AI assistant can now pull information from Gemini Notebook.</t>
+          <t>Meta employees ordered ‘attorney/client privilege’ hats while fighting child safety disclosures</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -6589,349 +6560,375 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxORFktOGZ3YVVKVnV5WGFwdG1Ed3JicjVjTEd1bC1Ic2llTzNUNTVUeXREVWt0aF8zUXYwNUp6Z2lmMFphWVd3QzVMUUNLZlkzSnh2bTdQRmp5SlAteUs0UGdwckVMeERpbVhOSWdYUDlIeVFab1NMaDVJZVlTZ2VCMC14MTlSc3BrRVpkU2ZOdU9FSWs4Um5mVFR4UnprWE1LSEJDYm1sSjlFTDJ1MnZGUkxYeXFUa2M?oc=5</t>
+          <t>https://www.theverge.com/tech/1000370/meta-instagram-attorney-client-privilege-hats</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.75</v>
+        <v>5.84</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Google Beam expands with new regions, partners, and customers</t>
+          <t>New York Times Cooking is coming to Meta's AI and display glasses</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQRHJoZVM0NVNQSGtDVFNXandBV0dHVnJ2UW1qZXNSUUhmNHNjYUtZQUtZV05hVU9kX1ZoRmUtTEVRdGlnOHMzT1VNMHVjTEs3NS1jNnlGSjFLMllLS0p5cGgwQ0UtczVUaVJlWlpRUm92UkUxbHNkaFBWZjZ3TDF6VXFWTlJBMjg?oc=5</t>
+          <t>https://www.engadget.com/2268183/new-york-times-cooking-is-coming-to-metas-ai-and-display-glasses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>New York Times Cooking Is Coming To Meta's AI And Display Glasses</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOdHBQcE16NHQ2UHBxemEzdzZSV3hqVS1DOFhwRTFKem5rS2UyOFdrQlJ6RHYzbGNkR0w0UGV4N0xUWnFxMHlKSUFvdTM2WWVGOUNHdXVkY05UZ1YzZUszQkJWU2QxamtrQVhoeHhHeVRJWGttWXV4Y2xybFR5MWZkY1BHdVVuNk93WHBSU2NLVWZUVW1xT1l1U0xhWXc4anM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 4 stories)</t>
+      <c r="A33" s="2" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Meta bets big on wearable AI, new AI agent as Zuckerberg pushes back against AI doom</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>apnews.com</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQZ2E2S0lGcG1uTzJRcDQxSXVhUjhCYU5DMkFYM3pXZEh1Tjg2Nmg3eDdqNmJxaVN5OGx4bE9LV2t6ekRHNElkRkhQa0VvNG9LbGRGc3pCMmFJenhhQUVydGVXMC1oNnJKaHBmM0M2UUNMdXFOMlAwd0VVT05hb28tZjZsLWhncGxpVElwdmRTQVZnUkZNWnVZVXh4cFBCQkxhVFFwRXJKZE04RVozYXZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6.41</v>
+        <v>5.69</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ZS strengthens AI-powered security operations with Microsoft Security Copilot.</t>
+          <t>Meta is going to let you build games with AI right on your phone</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQeWp4SGRLZEdtQnZlV082ckgtdXdzODdZMFNqWm5oV3ZRY1ZHdWR6UWQyUGRIMUtSbUNlc0VOQW5WRGFVSzEwbG5MdEdsN1ozWGNJUmVBSzE1ZXkzbnM5eDJEd0dTY2YtbTZFdE1qYUlSRmtWTFVITXBlY2pSeW5zbko4QWdUSEhOd0sxMWRSeGpvM3lqMHdMSXRjdWc?oc=5</t>
+          <t>https://www.theverge.com/games/999972/meta-horizon-create-studio-ai-games</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.95</v>
+        <v>5.69</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Microsoft brings Snapdragon X2 Plus to 13-inch Surface Laptop, 12-inch Surface Pro</t>
+          <t>Meta is going to let you build games with AI right on your phone</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tablets/microsoft-surface/microsoft-brings-snapdragon-x2-plus-to-13-inch-surface-laptop-12-inch-surface-pro-low-end-systems-finally-get-upgrades</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9qeXJibDVIaHRxSmc5Q1pQeWFPcEdzeTVyd1hTaXQ4aGQtWVZzV3VsQmgwMk16QW42UUwzR1ZFamNtYWJfa2c0YnBydV9peXJrZk8zSjZrRElBTXVVeE84QWw3TWJTRFkzLUFnc285YVFiYWN6S2x4dTZQQXBFUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.95</v>
+        <v>5.67</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Microsoft's new Surface Pro 12 and Surface Laptop 13 feature Snapdragon X2 Plus chips</t>
+          <t>Meta’s Muse Charm looks like a Tamagotchi, but it’s tapping into a much newer trend</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2266680/microsofts-new-surface-pro-12-and-surface-laptop-13-feature-snapdragon-x2-plus-chips/</t>
+          <t>https://techcrunch.com/2026/09/24/metas-muse-charm-looks-like-a-tamagotchi-but-its-tapping-into-a-much-newer-trend/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s new Surface Mouse has haptic feedback and a customizable action button</t>
+          <t>Meta’s Muse Charm looks like a Tamagotchi, but it’s tapping into a much newer trend</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/news/999211/microsoft-surface-mouse-haptic-feedback</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUUxUTkJneDJsM2laTVEwYUJPUUtVd0RQT0h0SW9oWU1TUVRaNmkwVGJXOExIRXhlZjBVLUZxd1NfZjMteGZDbzhwaG1qZENGMEc2eEpHbGxYZC13NlFHVDBaZzVrTG9VSmJzZ3M0aGI4SHY2VEc2UkhlZ1h3QlpqTEZYdXlvd2tKNWNMbjY2Z290QWdyY3FHem9lNF8wQ1dReFEzU0VMRTNmNjJ5NUt3TDRBdzlnUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Amazon  (Tier 1 · 3 stories)</t>
+          <t>Nvidia  (Tier 1 · 4 stories)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6.84</v>
+        <v>6.31</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Amazon rolls out new agentic AI for third-party sellers</t>
+          <t>Jensen Huang talks about AI and climate change like a supervillain</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/amazon-rolls-out-new-agentic-ai-third-party-sellers-2026-09-23/</t>
+          <t>https://www.theverge.com/tech/1000140/jensen-huang-nvidia-ai-energy-climate-change-supervillain</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.84</v>
+        <v>5.97</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Amazon gives sellers an even smarter Seller Assistant and a new plugin for Amazon Quick and Anthropic’s Claude</t>
+          <t>NVIDIA NeMo Relay now natively supports Oracle Generative AI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQaUJEMEhNVjVhWlBoRXNvX0FlWEtZMUxyRGZXekdwR2NVcjhTSWZYd0phakF5N3N3Q3FuN2F3UV91SW9McFY3c1REZmhpTmE0NVR0RkFVT1FJSFNBWFNEX0FJV2czQ0VvOWkxY2J3U0RVUjBSV3NzQzA5eUxXTTJ3SjdBQWNwQ2dJbklNWlkwV2N6SUJfSzhwTWdaU2p3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE51U2UwMGpkc2dFMkRRbHlLYnNrZ0NaSWlDR1QzeVF0a056eTBPVTRvU0QzVS04S2dBY3N6c0RiNnNhaFJjY2hORVRHMmZQUUJNXzN1ekhvTUlJT1BCdlU1czFIZEplem1uME5hdGdGYzgxQzItdWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>5.8</v>
+        <v>5.84</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Meta's standoff with Amazon over Muse could be a sign of things to come</t>
+          <t>Contain the Chaos: ‘CONTROL Resonant’ Launches on GeForce NOW</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNdzBob3NLdG1HOHF2bGl6cmJRcTBwZzVyT0ZPQm9GUVNFdnJWc1lTRUZXSngtTXJES052ZUwzVGxPNVhkVnc1WS0zcHo1VjA0dlktM28wZU1uem4zRUJWMmJua29sRjVWQzNDak9NX1dyd0ZWQ3hOVW5XYTRoZXZqSEdWbTM5dG0yWENnZjhGdjg3VWdjbjJjODlKcnNKYWhJWHlZ0gGoAUFVX3lxTFB3OV8wTlhFOGhWMWRSZ1VhY292c0p1Nkc3Q0dVZVB1NHhZZm1WbjROQ3dfQ0N3eXVEc0labW11SVZVV3VXUlZxWnV5TEU0aGlvSTktOTNJcGZhX3B2OGlhems3aDhXMVM0VnJVSnlzeXppWEpSRmNBckxKUHJjLV81YThyUDBKdVJhSjBlQ1VvMUdwNC14emJYM1dvTHdPYUE1YVI3VGRVRg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Alibaba  (Tier 1 · 2 stories)</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBRY1YyQlJnNWxVaFRmXzRBUHlVVXE5SVJnSno2UHZvMjJWbi13Y1ZsVm1aejRKT0t6M0JSVW1SZzRkRjh2Mm5hWHdERmJibVNMQXppRVYxbmdpaFNaWnk0ektOc1ZqMy1ONDB3N1hwcVVNUWpVRDdj?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Jensen Huang talks about AI and climate change like a supervillain</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQNlNmM2R3THNqdE1USVJBY21wNDRBdTJCdngxazd2bXhXSVdjWmFWYTAzWllMcWNPVll1UzFSdU5reUJqYXUxRWJkTU05OXI4T3BDcFZybzlvLUp5R3czZXBMRlpKdlZJeVF6RUs5aFhSSmlLZ1JCUXVXLTZ5NndIUmc2OFRpUlo4MmZqSWtHQVFQanh6a3EwOUJiVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>From Chips to Laptops: Alibaba Accelerates Full-Stack AI Ambitions</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>caixinglobal.com</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNbE9ydUZHc1NUYUg2X1lZa2Q3VUFaTTJzd0hJQUU3VmJ0cmNNWnI5Y1hSOVREdzFUdHJMVXV0RkhwZmlUdk9ocFdmN1pydTN4c2ZRazhIQ05kX19kU1hlWjJyRTdhMng2bm1vbUtJNHFWXzJEdFU0SElZcUN4Mk9UaTRSMnBIU1JyZFR5WWtEUFRYX3k5c2ZYeEpkdXh3bGdVMVhqdUFkbmxyQXE3SjZzczhvZms3ZGVLc193ZA?oc=5</t>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>AMD  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>5.74</v>
+        <v>6.41</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Alibaba unveils Zhenwu V900 AI accelerator, claims it's 'the most powerful AI chip in China' — accelerator supports 500,000 chip supercluster with a 10T-parameter Qwen model on the roadmap</t>
+          <t>With AMD Ryzen AI Max Series Processors, Perplexity Brings Portable Computer to Agentic PCs</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>newsroom.amd.com</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AJBVV95cUxNZXdKRTNKSWxHZEFza3k0bHV2Tng3RnNuY3pjWmtCZWQwaEF5Si1IblRzRnpoamRwRV9UbmF6NFlTV1AzNXZkOGxBNVFZalQtU3RCZTJqbERuRHEyMlVEdU5SY2V6d0xQRzEtRHZJbmVLZUc1MnlvdVM5VTQxLTJaWWRjTUQwdXJRaHplMkVicHZ4SkZlbzhYcHhLS2Y4WklOam5FcnZMSURnV0Fnc0M2a1p1UTZwa0F2WW5WaklNZXBNSzFIXzZMaU9NeUFvZjdzNldwV0plWTNCcy1SLW9yNHhEREN5R2tra2hreTNXSDF5V3hXcy1EYmNhUDNBSUF2VkpyNTRKbVlGbGh4Wmt2MVJDc2hDOTFBNC1GNlRETmlObjBmSzlmbF9hYmxuZ0NSVjQwRHd2YWhUTXBJZUdjWENrUEZCTVM4UmtBYWlSdXBYaVY0YmMtV2V3ak1TVmpjTmxiR0FJSXM?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Nvidia  (Tier 1 · 2 stories)</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9IeHJndXVoMDM1RFlDVmp2ZUh6MlNHR3ZENWtWc1U4amppZWlTSVkwX0NMb3lsdzRIU093MzhydGNUU1JwX3NQd2tiTTdwQXVsVUtxQ2RLY0UzWkU0eU5IN21aaXNFRUNB?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Beyond TOPS: AMD Ryzen™ AI Embedded X100 at the Edge</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>amd.com</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNQXpTOUJWcVFkSC1DNHNsLThjVzB5dkVhcjZDZG1lYkFsS3NKZmJpUHRRMFJ3Nm80M2dlSFdGSk5MeUxBRnNrdF9fVnZfOENWeEJ3ak5WczRnRVRNVS03dm5Va3JHRWNRcDZaX2ZkZUZVZVpfUnJ3NFhBT0Y2WHdOR05TLVZBUDhwd04zSkpNZWRlNlRRN3VHZGZPb25Vc0gyRlZBdC1Yamh2TVRrSzI0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>AI firms should not get regulatory waivers, Nvidia CEO says on podcast</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNYkRfdGVvZzNROGxZeEd5dFQ5RV94YktETmZzRmNkekFLdkluYkVFNTVXSEI5RGtzOXNDa2FTWGN1RE5ZTEIta18tSWNWSUFCT0JNeXMyREZuNFFidlpPOEoyYjhMUUZlMC1odGpNcEdnR2tCdmZBRldqSnljTjNPLUVQOFBSWVkyS3Rsdzh2LWNvWGVoSkpTbUp6YUlLWFVRU1RkQ1hDMGtwUGVjN2ctUm9xWW9iNHNVSjE0?oc=5</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>5.86</v>
+        <v>5.74</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Sakeena Fiza Helps NVIDIA Hardware Succeed at Scale</t>
+          <t>How to get your cut of Apple's $250 million Siri settlement</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE1UWDJqdUFLVkZMaVRLczBDSVNYQ2dDemwzNXF2UVpsVUpucVRjbk9aQ2txaTI3LWdfWEhzYXJnU1NhWC1aclIwS3hHZVZyWHZwWUdhYXNUZFY5ZFBPLXJTMUVsWTRJQQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 2 stories)</t>
+          <t>https://www.engadget.com/2265227/how-to-get-cut-apple-siri-ai-settlement/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>How To Get Your Cut Of Apple's $250 Million Siri Settlement</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE1wM3hKZF91TWE1bVprakhDTFU4eGZPeGNEWTJSYXE4bl9JSk5GZEdwNXpuZXNwWXVVT3pCc3lJMWtCOG1KWkdEZzZaMTVfNmZqR01YSFliNV9JTnRGVUl3cGRwVUF5dERKSGZoN0NEUVRnb2xwNFFzSVp0Nkhudw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Oracle to Advance Cancer Care with New Oncology EHR</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>oracle.com</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQZkxrUVVENWd1NUY2NWY1Q2JpWGVWRU8wVUVuU2JnelBiNFMxa3lpMnhCdFNEQkU5Z3p0aDNkM292OTVnSkhPZ25YNHFPWE1KMEt0WVU1a1pSREhodURXWV9ta3oxYWxiTTRhVk9BYWllNWUzTlp4WDVGd1lqM0tqMWRhYmh2WTJGT21Md29xRmU3ay1oUW9NVnRIYU9zV0owR1ZzMV94VQ?oc=5</t>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>What's New in Oracle AI Agent Memory: Graph-Aware Retrieval, Image Memory, and Enterprise Controls</t>
+          <t>Frontier Firm BNY resolves client inquires 80% faster with Microsoft AI powered Eliza</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNTDY4ODJDSUhMS1JCR3Q2VDQwTkZ4WnQ5aTRnNHJKUjFEWEF1OFlOeFhPaGtoMHlNTTdZeDRlbkl2Vmdlc1RpVUFuNVpNNktKWlRTRXc5UjV0bE5Ea0tjazczWjg5Q0VPRVJ3Y05SNnNXWU9xaWk2aHIyUXhJYnhEeHRZc2tkOGVEbU92YnpYWDRncDRvekpVR0N2aDVXN0ZiUElFcmN3cU9FRnBPdFFRYmlXZ2I1ZHhsSTVQWkN4VEhpUjFCUHlnZzJR?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Apple  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Meta's $1,300 VR Glasses look like the Vision Pro sequel Apple should be making</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2267218/meta-vr-glasses-price-specs-apple-vision-pro-comparison/</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOVFRMSHRjTDlZZUhoUHBPcENsSDd2LU1ZUFFnd1lYejl3cWVTQzlqaFVXRXpwYl95X09iQ2pXMUFrY1dEWko5S2ZIZ0VqVk4zQ0JjRVBhMXR2cFVsZW1RdWtxVG5iT0tnZWxGUE5DRDJoejdPY05qWUxNZ0JOem1iaUp3?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>To innovate faster, BNY upskills 100% of staff on Eliza, powered by Microsoft AI</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>microsoft.com</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE43ZS1EVzExR1lZcGgtM01RMF9vc3h0Sld0OTI4cDVlbnBMQlQ1Mk1sWHNvLUJneFBwNEJ0cDBiNFhWMlVwM0l4aV9idW8zZkx5YjVIRGxWQkJ4Ry1PRE5Kbmd2R0MwNWFjc3d4dGxWNzdlYlRrSVRWQ1A4dmw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6948,21 +6945,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId29"/>
@@ -6970,13 +6967,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Watchlist — by company" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4.16</v>
+        <v>4.78</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -544,46 +544,46 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI says its bots have interacted with multiple U.S. government sites in unexpected AI activity</t>
+          <t>Gemini Live vs. ChatGPT Voice: Which AI offers a more natural conversation?</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI says its bots have interacted with multiple U.S. government sites in unexpected AI activity    CBC</t>
+          <t>It's actually too natural for some. Ascannio/Shutterstock Add Engadget on Google: Preferred Source Google Discover When ChatGPT first launched in 2022, the only way to interact with it was through your keyboard. But it didn't take long for another breakthrough: real-time voice chat. ChatGPT's Voice Mode was the first feature of this kind, but we soon got competition from Google in the form of Gemi</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>openai, chatgpt, gemini, ai</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5.5</v>
+        <v>11.6</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 19:31:56 GMT</t>
+          <t>Sun, 27 Sep 2026 13:45:00 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5hYkN5dGZBNWtMczBXaVNSdEZwVExRdWk3Qmt1a0oxaURzYUVxaDBIOUNZUVItaFZSNHc1d3dsN1lFM2REbTV0Q3NCUk84Sl9LQnUzd3NhaU91b1hWODhicHVLOC1XTmtJQzJ3a19veUlkaVR2UHdiNXJB?oc=5</t>
+          <t>https://www.engadget.com/2266889/gemini-live-vs-gpt-live-which-offers-more-natural-conversation/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3.88</v>
+        <v>4.77</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI pauses training of its ‘most capable models’</t>
+          <t>Can Muse overcome Meta’s trust issues?</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Tech OpenAI pauses training of its ‘most capable models’ OpenAI keep</t>
+          <t>Last day to demo your breakthrough to 10,000+ tech leaders is on Oct 2 . Book Exhibit Table Now. Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Getty Images AI Can Muse overcome Meta’s trust issues? Anthony Ha 12:57 PM PDT · September 27, 2026 Listen on Apple Podcasts Listen on Spotify Meta’s new AI agent Muse took the spotlight a</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai, inference</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8.5</v>
+        <v>5.4</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T12:34:59-04:00</t>
+          <t>Sun, 27 Sep 2026 19:57:30 +0000</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,16 +628,16 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/1001049/openai-training-pause</t>
+          <t>https://techcrunch.com/2026/09/27/can-muse-overcome-metas-trust-issues/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3.85</v>
+        <v>4.36</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>aljazeera.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT-6 Astra cracks 85-year-old 1941 Enigma-coded message in two days — autonomous AI coded its own simulator to crack code that was unsolved since it was shared online back in 2005</t>
+          <t>Australia summons OpenAI and Anthropic CEOs to appear at AI inquiry</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Tech Industry Artificial Intelligence ChatGPT-6 Astra cracks 85-year-old 1941 Enigma-coded message in two days — autonomous AI coded its own simulator to crack code that was unsolved since it was shared online back in 2005 News By Mark Tyson Published 15 hours ago Before it started cracking, the LLM developed Python and C++ software for an Enigma simulator and Enigma Bombe. (Image credit: Getty Im</t>
+          <t>News | Cybersecurity Australia summons OpenAI and Anthropic CEOs to appear at AI inquiry Call to face Senate inquiry follows security breach of Australia’s Medicare portal by rogue OpenAI bot in June. Listen (2 mins) Save Share Australia summons OpenAI and Anthropic CEOs to appear at AI inquiry on social media Share Add Al Jazeera on Google OpenAI's Altman and Anthropic's ​Amodei have been request</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>chatgpt, ai, autonomous</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>15.1</v>
+        <v>18.1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 10:00:00 GMT</t>
+          <t>Sun, 27 Sep 2026 07:15:43 GMT</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/chatgpt-6-astra-cracks-1941-enigma-coded-message-in-two-days-autonomous-ai-coded-its-own-simulator-to-crack-code-that-was-unsolved-since-it-was-shared-online-back-in-2005</t>
+          <t>https://www.aljazeera.com/news/2026/9/27/australia-summons-openai-and-anthropic-ceos-to-appear-at-ai-inquiry</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3.8</v>
+        <v>4.23</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Your old GPU could be worth more than you think</t>
+          <t>Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">If the RAMaggedon's good for anything, it's turning your old GPU into a potential goldmine. Dikushin/Getty Images Add Engadget on Google: Preferred Source Google Discover Whether it's from excessive use, sheer age or an upgrade that outclasses it, there are plenty of reasons that you may switch from one GPU to another. If you end up with an extra GPU lying around, there's a lot you can do with it </t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>ai, nvidia, gpu</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.3</v>
+        <v>11.1</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 23:45:00 +0000</t>
+          <t>Sun, 27 Sep 2026 14:14:40 +0000</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,13 +730,13 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267877/your-old-gpu-worth-more-than-you-think/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/thieves-steal-nvidia-labeled-trailers-expecting-massive-ai-gpu-payday-but-score-40-000-pounds-of-sand-instead-crooks-duped-by-20-tons-of-ballast-sand</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3.77</v>
+        <v>3.92</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Why NVIDIA's most powerful GPU is so rarely sold to consumers</t>
+          <t>OpenAI agents tried to ‘bruteforce’ a UN website</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA's $16,000 RTX PRO 6000 can beat the RTX 5090, but gamers aren't who it's built for. NVIDIA Add Engadget on Google: Preferred Source Google Discover By most measures, NVIDIA's GeForce RTX 5090 is a more powerful GPU than most will ever need. Priced at $1,999 when it was announced, it has 32GB of GDDR7 memory and can consume 575W when pushed. Despite all that power, though, there's still anot</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News OpenAI OpenAI agents tried to ‘bruteforce’ a UN website OpenAI’s age</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>nvidia, gpu</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 15:30:00 +0000</t>
+          <t>2026-09-27T13:21:07-04:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2265946/why-most-powerful-nvidia-gpu-rarely-sold-to-consumers/</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1001178/openai-agents-bruteforce-un-website</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -804,25 +804,25 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Insurers claim AI is already increasing healthcare costs</t>
+          <t>Anthropic’s Dario Amodei gets the SNL treatment</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. In Brief Posted: Hospitals’ use of artificial intelligence tools as they submit insurance claims led to an additional $942 million in healthcare spending over a two-year period, according to an analysi</t>
+          <t>Last day to demo your breakthrough to 10,000+ tech leaders is on Oct 2 . Book Exhibit Table Now. Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. In Brief Posted: Saturday Night Live took on the AI industry’s recent warnings of doom last night, as cast member Jane Wickline offered her impression of Anthropic CEO Dario Amodei. Weekend Update host M</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4</v>
+        <v>8.9</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 21:02:06 +0000</t>
+          <t>Sun, 27 Sep 2026 16:30:00 +0000</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/26/insurers-claim-ai-is-already-increasing-healthcare-costs/</t>
+          <t>https://techcrunch.com/2026/09/27/anthropics-dario-amodei-gets-the-snl-treatment/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>This external GPU uses Wi-Fi to transform any device into a gaming rig</t>
+          <t>Australia is run on legacy systems that AI agents can easily exploit, former UN cyber negotiator warns</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>The WiCi One is available for preorders starting at $1,999. WiCI Add Engadget on Google: Preferred Source Google Discover WiCi is introducing a wireless solution to those who want to keep the slim profile of their laptops but also need to run graphically-intensive games or demanding AI tasks. Called the WiCi One , this external GPU ditches the wires and offers the power of a high-end graphics card</t>
+          <t>View image in fullscreen Johanna Weaver, who completed her term at the UN in 2021, warned there were huge vulnerabilities across the public and private sector in Australia that AI agents could infiltrate. Photograph: Supplied AI (artificial intelligence) Australia is run on legacy systems that AI agents can easily exploit, former UN cyber negotiator warns Federal cabinet will discuss the OpenAI br</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 19:45:00 +0000</t>
+          <t>Sun, 27 Sep 2026 22:26:00 GMT</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2269877/this-external-gpu-uses-wi-fi-to-transform-any-device-into-a-gaming-rig/</t>
+          <t>https://www.theguardian.com/technology/2026/sep/28/australia-is-run-on-legacy-systems-that-ai-agents-can-easily-exploit-former-un-cyber-negotiator-warns</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3.53</v>
+        <v>3.76</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thansettakij.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Nvidia patents AI chatbot to streamline PC game optimization</t>
+          <t>โลกจะล่มสลายเพราะถูก AI ถล่ม?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>Play โลกจะล่มสลายเพราะถูก AI ถล่ม? By พล.อ.ต.อมร ชมเชย 28 ก.ย. 69 | 05:00 น. KEY POINTS แม้โลกยังไม่ถึงขั้นล่มสลาย แต่ภัยคุกคามจาก AI เป็นเรื่องจริง โดยมีกรณีศึกษาที่ AI สามารถปฏิบัติการโจมตีทางไซเบอร์ได้ด้วยตัวเองในสภาพแวดล้อมทดสอบ ความเสี่ยงที่แท้จริงไม่ใช่การที่ AI มีพลังลึกลับ แต่คือการที่มนุษย์ใช้ AI เป็นเครื่องมือเพิ่มความเร็วและขยายขนาดการโจมตีทางไซเบอร์ ทำให้แฮกเกอร์ทำงานได้อัตโนมัติและพร้</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>12.1</v>
+        <v>3.4</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 13:00:00 +0000</t>
+          <t>Sun, 27 Sep 2026 22:00:00 GMT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,13 +934,13 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/pc-gaming/an-nvidia-chatbot-could-one-day-help-developers-better-optimize-their-games-patent-filing-show-requests-can-be-made-in-plain-english</t>
+          <t>https://www.thansettakij.com/blogs/columnist/digital-myth-buster/669984</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -952,17 +952,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AI agents are exposing a security gap between the data they read and the systems they can change</t>
+          <t>Engram is a sampler that turns broken AI hallucinations into music</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Featured AI agents are exposing a security gap between the data they read and the systems they can change Adithyan RK 12:00 pm, PT, September 26, 2026 Courtesy of author Most conversations about AI security still orbit the model itself: Is the large language model (LLM) aligned, can it be jailbroken, does it hallucinate under pressure? Those are real questions. But as organizations move AI agents </t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI Entertainment Gadgets Engram is a sampler that turns broken AI hallucinat</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>6.1</v>
+        <v>4.6</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 19:00:00 GMT</t>
+          <t>2026-09-27T16:46:36-04:00</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,16 +985,16 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/security/ai-agents-are-exposing-a-security-gap-between-the-data-they-read-and-the-systems-they-can-change</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1001193/engram-sampler-ai-hallucinations-music</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3.36</v>
+        <v>3.63</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>China, US to open AI ‘communication channel’ after summit, White House says</t>
+          <t>Anthropic’s CEO is about to have dinner with President Trump</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>News | Politics China, US to open AI ‘communication channel’ after summit, White House says White House says the two countries agreed to open a ‘bilateral communication channel’ for artificial intelligence incidents. Listen (3 mins) Save Share China, US to open AI ‘communication channel’ after summit on social media Share Add Al Jazeera on Google US President Donald Trump and First Lady Melania Tr</t>
+          <t>Last day to demo your breakthrough to 10,000+ tech leaders is on Oct 2 . Book Exhibit Table Now. Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. In Brief Posted: Anthropic CEO Dario Amodei seems to be everywhere this weekend: He was lampooned on the season premiere of Saturday Night Live , and tonight, he’s set to have dinner with President Donal</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>16</v>
+        <v>4.8</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 09:07:18 GMT</t>
+          <t>Sun, 27 Sep 2026 20:34:28 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.aljazeera.com/news/2026/9/26/china-us-to-open-ai-communication-channel-after-summit-white-house-says</t>
+          <t>https://techcrunch.com/2026/09/27/anthropics-ceo-is-about-to-have-dinner-with-president-trump/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3.1</v>
+        <v>3.63</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>ไมโครซอฟท์ปรับวิธีการคิดราคา Copilot มีโควตาฟรีในค่ารายเดือน หากใช้เกินซื้อโทเค็นเพิ่มได้</t>
+          <t>Why letting Claude clean your TV's bloatware isn't the best idea</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>ไมโครซอฟท์ปรับวิธีการคิดค่าใช้งานของแอป Copilot ที่ เพิ่งรวมเป็นแอปเดียว จากเดิมที่คิดเป็นค่าบริการรายเดือนอย่างเดียว (user subscription license - USL) ตอนนี้ปรับมาเป็นการคิดแบบผสม ระหว่างโควตารายเดือนและการคิดตามการใช้งานจริง (usage-based billing - UBB) ประกาศนี้ยืนยันว่าผู้ใช้จำนวนมากยังคงใช้งานภายในโควตาที่รวมอยู่ในค่ารายเดือนเหมือนเดิม แต่สำหรับผู้ที่ใช้เกินจะมีตัวเลือกให้บริษัทซื้อเครดิตเพื่อ</t>
+          <t>Don't let an AI bot potentially crash your TV. Nwz/Shutterstock Add Engadget on Google: Preferred Source Google Discover Even fresh out of the box, most smart TVs are bogged down with unnecessary software, including unwanted apps and advertising tools. One developer recently had enough, and gave AI agent Claude full access and instructions to debloat his TV. Mert Cobanov gave Claude a series of de</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>copilot</t>
+          <t>claude, ai</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 14:42:11 +0000</t>
+          <t>Sun, 27 Sep 2026 14:15:00 +0000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,13 +1087,13 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151769</t>
+          <t>https://www.engadget.com/2267074/why-claude-cleaning-tv-bloatware-not-best-idea/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>I created an interactive digital avatar of myself — and you can talk to it</t>
+          <t>Bill Gates says it's 'completely irresponsible' for AI to not have safeguards</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Synthesia / TechCrunch Startups I created an interactive digital avatar of myself — and you can talk to it Dominic-Madori Davis 7:00 AM PDT · September 26, 2026 When Alexandru Voica, hea</t>
+          <t>The Microsoft co-founder said that the more present danger is bad actors with access to AI tools. Chip Somodevilla/Getty Images Add Engadget on Google: Preferred Source Google Discover After several CEOs of leading AI companies have agreed on slowing down the pace of AI development, Bill Gates has offered supporting sentiments and called for more regulation and safeguards. In an interview with NBC</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>11.1</v>
+        <v>6.2</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 14:00:00 +0000</t>
+          <t>Sun, 27 Sep 2026 19:12:29 +0000</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/26/i-created-an-interactive-digital-avatar-of-myself-and-you-can-talk-to-it/</t>
+          <t>https://www.engadget.com/2270166/bill-gates-says-that-its-completely-irresponsible-for-ai-to-not-have-safeguards/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3.03</v>
+        <v>3.22</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,31 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Can Cloudflare CEO Matthew Prince save the web from AI?</t>
+          <t>OpenAI halts training of latest models as reports mount of AI agents going rogue</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Today, I’m talking with Matthew Prince, who is CEO of Cloudflare. This episode is part of a two-part series on the future of business. 
- Matthew  last joined us  on the show about two and a half years ago, at what we thought then was a wild pivot point for the internet — and now it turns out things</t>
+          <t>OpenAI halts training of latest models as reports mount of AI agents going rogue    The Guardian</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>11.1</v>
+        <v>15.4</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T10:00:00-04:00</t>
+          <t>Sun, 27 Sep 2026 10:01:00 GMT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1190,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/podcast/1000344/cloudflare-matthew-prince-google-zero-ai-web-advertising</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQdWZCRDBDd0E2YnBTeGJZNXhZLURBOXlJZTR2dGhwY0c1bWlNX3N6MkhWcVRiSF9oNjJLWmJfY0Nwcy05SFB0RGJ2ckhaNjdueWFxMjdnWHhodFM1MEJkRXVnUzJZTTJidXdGckk1ZkI0RDZRNmVQQXYyTmxtbnJKZFdMNFRMbFhwcWY5RHdFeGpIY3prOVo1RWstRWhPVVRldXgyV1E1Q2FaOEZxSC1rTld2eFFHWnJTcXk2WmgxRG15a0ViblgzYzh3TQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3.03</v>
+        <v>3.19</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1208,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Microsoft quietly drops Copilot+ branding from new laptops</t>
+          <t>TechCrunch Mobility: AV companies pick their lanes</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
+          <t>Welcome back to TechCrunch Mobility, your hub for the future of transportation and now, more than ever, the role AI is playing in it.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>copilot</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 14:00:00 +0000</t>
+          <t>Sun, 27 Sep 2026 16:02:00 +0000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1241,13 +1240,13 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tablets/microsoft-surface/microsoft-quietly-drops-copilot-branding-from-its-new-laptops-surface-cvp-confirms-new-devices-meet-hardware-requirements-but-lack-controversial-branding</t>
+          <t>https://techcrunch.com/2026/09/27/techcrunch-mobility-av-companies-pick-their-lanes/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -1259,17 +1258,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>US-China AI hotline? Why Xi-Trump summit went beyond tariffs to ‘super intelligence’</t>
+          <t>How to use Spotify's Running Mode on iOS and Android</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>US-China AI hotline? Why Xi-Trump summit went beyond tariffs to ‘super intelligence’    Livemint</t>
+          <t>Maximize your stride with Spotify's AI-powered running features.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1278,11 +1277,11 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>12.3</v>
+        <v>9.6</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 12:47:29 GMT</t>
+          <t>Sun, 27 Sep 2026 15:45:00 +0000</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1292,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQMVVSYmxUMGVVa0hjYXNvUTMtdEZLV0FZckZiN2hNYnR0cnR6M3RDemlfRWFBM2E4R3Z1UGwwWUx2amVRUkNCSDhpQ0QwYkJ5VmRkcmUtZUw1SW0xbV9NOXFiVXZaMkZMR1RzQ3RMNXh3RHpZZXFEQ0ZuSUZuUWdvbDRYdzZCZTNzVmFELVNMelByX2xKRVBEclNDWVpmdGxXbHYzTURqOXo1aXVwVDVoZzRXLURWUC1jT29KSllhREVpU1JsanFSdTZuOFRRMzFDdGfSAdcBQVVfeXFMT25pTWlSZk5UZ0hISFB3cGU1QlBGSTRXRDhmYWUtUm9FdUlKSVBKdEdfRnJjVWlQLUlBdTN0TFBkdUtrNWdycDE1UnpsM05ZX09mVmZJSTlWb3ZUUllZUjEwM3Vkck85VTlLNGJROFpYbW1MOFNqQzBHTWhuWm51QmJEbmViRWJXRWtOME1ESjlxcEcyVk0yTzFyU2UxUzNVWVduaW9HNnRQb3lEYmNLclVTdXRPLTJfaW9JRUZzb25RRlVqU0o5QnFtMTVpb0sxbnZYcmlLU1E?oc=5</t>
+          <t>https://www.engadget.com/2267524/how-to-use-spotify-running-mode-ios-android-guide/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1315,25 +1314,25 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Nvidia’s RTX Mega Geometry 2.0 streams ray-tracing geometry into VRAM on demand</t>
+          <t>PS5 emulator successfully runs six titles at a playable 60 FPS</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shane has a background in computer engineering and has worked as a freelance consultant in multiple industries. He has a strong affection for history and loves to game. He worked his way up from a Commodore 64 and has always been interested in technology and writing. He particularly enjoys breaking </t>
+          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 12:30:00 +0000</t>
+          <t>Sun, 27 Sep 2026 12:40:00 +0000</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1343,13 +1342,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/nvidias-rtx-mega-geometry-2-0-streams-ray-tracing-geometry-into-vram-on-demand-nanite-inspired-design-drops-detail-instead-of-dropping-out</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/ps5-emulator-successfully-runs-six-titles-at-a-playable-60-fps-ps5-emulation-continues-to-gather-momentum-as-developers-improve-shader-translation-and-vulkan-support</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1366,25 +1365,25 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>PNY allegedly refuses to cover melted RTX 5090 powered by native power supply cable</t>
+          <t>Developer says AI decision model Jev beat Pokémon Red in under a week</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
+          <t xml:space="preserve">Shane has a background in computer engineering and has worked as a freelance consultant in multiple industries. He has a strong affection for history and loves to game. He worked his way up from a Commodore 64 and has always been interested in technology and writing. He particularly enjoys breaking </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 11:30:00 +0000</t>
+          <t>Sun, 27 Sep 2026 11:30:00 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1394,13 +1393,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/pny-allegedly-refuses-to-cover-melted-rtx-5090-powered-by-native-power-supply-cable-company-closes-users-ticket-when-questioned-on-policy</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/developer-says-jev-decision-model-beat-pokemon-red-in-under-a-week-non-llm-engine-succeeds-where-traditional-chatbots-stalled-for-months-but-claude-opus-5-coached-the-model-through-its-dead-ends</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1417,12 +1416,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>The AI debate is already shaping the 2028 election. Here’s where Democratic hopefuls stand</t>
+          <t>Democracy blindsides Silicon Valley’s power players looking to transform the world with AI</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>The AI debate is already shaping the 2028 election. Here’s where Democratic hopefuls stand    theguardian.com</t>
+          <t>Democracy blindsides Silicon Valley’s power players looking to transform the world with AI    The Guardian</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1431,11 +1430,11 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 11:02:00 GMT</t>
+          <t>Sun, 27 Sep 2026 11:00:00 GMT</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1445,13 +1444,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPRnBuU3Rac3RLZXdjUXhGYUh4VTFISVdZOS1NU0xHV3lldXFGQjhFa3Y2OHpEMmFBT0Joek1UNm8xenM0QTJSSlpsaTdWb2Z0LUtnY05qSEg0anNJVXoxd1NmWkpnRl9XU1ZaNG9TRk80N205WEljY01UTXVUUEgyQXB3d2NYNDV0TldheFV6cmpZZ0RoTEN0d1U4WmFWNUp3OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOTUNhUmlYdWFOSkZnb040My1WZ2d3a3prU1BSMHg3d0taMFd5bzJsMmhVaTJSU2VMdURJVVd5NUQ0R0ZOQmpMeU43TnZfR0Nob2tSSVZrZXlQeUdKOTZ2RzNYTGRIejI3TWh6SEdBQ09aVVZjMnJWX2xMdlE5Zk9QODllbV9lQ1NBZ05oeGFJaDJybzBjU0toSy03R1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1463,30 +1462,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's AI agents went rogue, meddled with multiple US government websites: Report</t>
+          <t>U.S. and UK navies successfully launch 3,700-pound submarine-sinking torpedo from robotic drone submarine in historic first</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's AI agents went rogue, meddled with multiple US government websites: Report    Livemint</t>
+          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>21</v>
+        <v>14.9</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 04:05:52 GMT</t>
+          <t>Sun, 27 Sep 2026 10:30:00 +0000</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1496,13 +1495,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOVDNxa0lqNWpEd2hiSWxuandLQVVzZFFGdkplV0Zib3czVFlhamNreHg1aEtZY1JGNy1kSHNmRTEzME5ENGFCV2xHTFRISlBVbmYtOEJXaVFaVlM2MWloYW9qX0IxTXdDd0tidDktSTd2T0xQaHIySE1BMndWWEQ1ZW1lWVBlSjRycjRzNWliSlk5MjJ6VXBFdjR0cXJiNTZMVEhPLUdhVXgwNC00V3ZFYlBJVk45ZDBobjEwUUhoNk9oWnYyVmRZRFJfMTRtQ1ZIb1JSb3M2bEpUQ2oxOTQ3ZTJpN1RjemfSAewBQVVfeXFMTUdQTDdMSy1WOVVHeklzWnUyaVpreTBJRzN1WU9rRnhyS1BlOHl6SUM4MjRHT1pIem1JOXB4WnlPckFxR1Z6Q2s4aVdjeVoweFlVVDdVRVdodmdGbHlqeDlKX3lPRVEtQWFMWXJiVVB4ZUdDZFVWazd2VDMyUkMwSlZ4WnM5elR5ZllVZHRWZklKS0hscWVpbzNwclRLdlFoVGhWTS12aTZfSGdoS3EtSGFURVNCVzA3WU14WkZDdmx4WEJxd1lLTmptalRhbEdCdTFqZC1nVnluai03QlNXUGZDR1dVOU96eWltb0s?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/u-s-and-uk-navies-successfully-launch-3-700-pound-submarine-sinking-torpedo-from-robotic-drone-submarine-in-historic-first-project-broadsword-proves-weapon-interchangeability-in-just-seven-months</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1514,30 +1513,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT-6 Astra cracks 85-year-old 1941 Enigma-coded message in two days</t>
+          <t>เปิด 6 อันดับทุน ครองที่ดินนิคมฯ ชี้ Data Center โตแรง ดันยอด 9 เดือนทะลุ 6,000 ไร่ ‘กนอ.’ พร้อมยกระดับแผนรับมือน้ำท่วม</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Mark's enthusiasm for computers dampened at an early age by the rubber-keyed Sinclair Spectrum 48K and feelings of Commodore 64 envy. However, in the mid-80s, hope in a digital future was rekindled by the purchase of an Atari 520 STe. Since that time Mark has used a multitude of computers for fun an</t>
+          <t xml:space="preserve">กนอ. เผยยอดขายและจองพื้นที่นิคมอุตสาหกรรมทั่วประเทศ 9 เดือนแรกปี 2569 ทะลุ 6,000 ไร่ มั่นใจสิ้นแตะเป้าหมาย 7,000 ไร่ เผยทุน  Data Center  เล็งใช้พื้นที่อีกเกือบ 3,000 ไร่ เร่งขยาย Land Stock แตะ 30,000-40,000 ไร่ หนุนลงทุน CCUS รับ FDI 1.5 ล้านล้านบาท พร้อมยกระดับมาตรการรับมือน้ำท่วมในพื้นที่เสี่ยง </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>data center</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 10:00:00 +0000</t>
+          <t>Sun, 27 Sep 2026 10:11:27 +0000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1547,13 +1546,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/chatgpt-6-astra-cracks-1941-enigma-coded-message-in-two-days-autonomous-ai-coded-its-own-simulator-to-crack-code-that-was-unsolved-since-it-was-shared-online-back-in-2005</t>
+          <t>https://thestandard.co/ieat-industrial-estate-data-center-sales/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1565,17 +1564,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>matichon.co.th</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>สหรัฐ-จีนจ่อตั้ง กลไกประสานงาน รับมือเหตุการณ์ด้าน AI</t>
+          <t>Big AI's content problem: Take the work, keep the money</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>สหรัฐ-จีนจ่อตั้ง กลไกประสานงาน รับมือเหตุการณ์ด้าน AI    Matichon Online</t>
+          <t xml:space="preserve">Big AI has a problem. Its companies must ingest other people’s work. You know, books, news stories, photographs, code, websites, that one original meme you came up with, and practically everything else on the internet to train its large language models (LLMs). We all know that. We also know that AI </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1584,11 +1583,11 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>18.8</v>
+        <v>15.8</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 06:17:30 GMT</t>
+          <t>Sun, 27 Sep 2026 11:35:00 +0200</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1598,13 +1597,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5EdVZURXNrcDFzNEszRUR1eFQwMlhBZlZXLW9TMGZieGQySjdhRElycy1fMFduWjJpZWRqdXlyUFVMb2xSX2h4TVhOcGIxNlNoVDk1S3RPdUpvZ3M?oc=5</t>
+          <t>https://www.theregister.com/columnists/2026/09/27/big-ais-content-problem-take-the-work-keep-the-money/5299007</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2.12</v>
+        <v>2.57</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1616,30 +1615,30 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Will AI make banking riskier? Why RBI wants banks to keep human judgment in the loop</t>
+          <t>Taiwan's chip talisman snack faces production halt after 94% strike vote</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Will AI make banking riskier? Why RBI wants banks to keep human judgment in the loop    Livemint</t>
+          <t>Mark's enthusiasm for computers dampened at an early age by the rubber-keyed Sinclair Spectrum 48K and feelings of Commodore 64 envy. However, in the mid-80s, hope in a digital future was rekindled by the purchase of an Atari 520 STe. Since that time Mark has used a multitude of computers for fun an</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>chip</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>20.6</v>
+        <v>15.9</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 04:30:31 GMT</t>
+          <t>Sun, 27 Sep 2026 09:30:00 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1649,13 +1648,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQbFZLalByZzNvbjVTSmcxRVBQc1RCMF8tNnpRR3JhQUdUNXNjWi1CQ0JWQk1VUHNDLWdZZlJJLWxnSGlNbU4xYnNQbi05aDlaWTk2ZzR1Yk1MbkRRcUZBX25PWWFlVmNmcDhMenVTd09acnRYRG5EMWRSTTJFZWxuVzZTZlNmRHlnUm8zOUxHejRQMl85dmh4YXVSV0RKU2U5azFiU0l4aEo0bXBjeUZYdE9semYwOXFETmVwTVJ1Y3k5N1Yxb1BoQzJtWE50OXJ3MEZCTXV6MUdocFhpaGhENk9PSjN6MFk2NDNN0gHwAUFVX3lxTE5RS29HT2lrM0F4Ti14ZmFqR0ZuVnkyRHJnaG55bnI0YmlwYXZIN1lTWWhSTlZjNWtxbVBsSG4wdUxjQnk4d3o4WXdzellEVXg3a2hzRVN0N0VNdUNFVnpFWGxnelVCZVVMcE5HR01jcENTNXJaQXZtcmRxeFpURFE5MzAtc2Jjb3RUQmZIU1l4c21URjFBb0N2WUVoazZMSmF6eTk5Ukg4Zy1abkwwMGdFbXVXb2VBZDhnQkdOUnIzNlZZNWgwV0EtV3c3Sms0SnBGQ1h4VWN1WkZZazNabGJOeWg4TXRFbnNWVnRGaEJPWA?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/taiwans-chip-talisman-snack-faces-production-halt-after-94-percent-strike-vote-workers-demand-share-of-usd176-million-factory-sale-to-ase</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1667,17 +1666,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>abc.net.au</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Who is Jensen Huang, the AI boss Trump calls at night?</t>
+          <t>Bill Gates says unchecked AI could ‘cause a billion deaths’ in call for regulation</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Who is Jensen Huang, the AI boss Trump calls at night?    ABC News &amp; Headlines – Australian Broadcasting Corporation</t>
+          <t>Bill Gates says unchecked AI could ‘cause a billion deaths’ in call for regulation    The Guardian</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1686,11 +1685,11 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>20.9</v>
+        <v>16.4</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 04:10:47 GMT</t>
+          <t>Sun, 27 Sep 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1700,13 +1699,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQR3Y4eUtadkNtNzdRUkdsLVBHMTlWX2k2bnF1R0o1S1Q1OXVrWXRUS3hfc0xMU1lFREV5UWU2TzRkSkJfUnotNVdzQkhLczZGczg3SzZKd20xdnJ3WTEyTTNDeVJ4TFFmbUsyQ2RicVgxQ2hXbXJpSzlsOWgxbW90QjJhVUw3bFVHdU54TUhFMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNX3U0dW9FbGNsVVd0bGt4MlRzRTBZMkE2NWZOYUZlUkxOd3puUEwxdkR1YXNIaHdFNUtaYzJ3cGlOTHM2ckdBbHhLZmYtbUlnalJ2QmZYVS00RFROaksyY01xUnRCSXFzcEppNElYd1NOV21KNWJXVEVPVHBVZUppSEZPRVQzVmhtdlA4ZWp4emlaQmwxblpxVjRVWGM0dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1718,30 +1717,30 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>thansettakij.com</t>
+          <t>mgronline.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>BOI เปิดดีลใหญ่ Infineon 4.8 หมื่นล้านสร้างฐานชิปไทย ดันยุทธศาสตร์ลงทุน 5 แสนล้านใน 5 ปี</t>
+          <t>ป้าจีนวัย 65 สุดแสบ! ใช้ AI ปลอมเป็นหมอสาวคนสวย หลอกเงินหนุ่มผู้รับเหมาไปเกือบล้าน</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>BOI เปิดดีลใหญ่ Infineon 4.8 หมื่นล้านสร้างฐานชิปไทย ดันยุทธศาสตร์ลงทุน 5 แสนล้านใน 5 ปี    thansettakij</t>
+          <t>ป้าจีนวัย 65 สุดแสบ! ใช้ AI ปลอมเป็นหมอสาวคนสวย หลอกเงินหนุ่มผู้รับเหมาไปเกือบล้าน    ผู้จัดการออนไลน์</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ชิป</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>22.6</v>
+        <v>16.6</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 02:27:00 GMT</t>
+          <t>Sun, 27 Sep 2026 08:45:00 GMT</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1751,13 +1750,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE41aU13T25PaWlMcUJtTTZBWURHTjVjT2pJUURrZWZYV2NXeWFTNF93RFR5d3pxQjRzOWVsZWlYck5uVkVVLXlFQ2FobWQ3WWFNOUlUcC1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5SV0hVNUp5eVFacl9ER0ZuOVRPam5UeTlOLXZrNXFrV0xZOGxGaWpWbi00SzlDVTNHREkxSUhBWUJ0Skk5WUtqNTAxVzBnQUNycUdHTUNyYll3a0Uw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1.84</v>
+        <v>2.41</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1769,34 +1768,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>YouTube เพิ่มฟีเจอร์ละครสั้นแนวตั้ง ดูต่อกันเป็นตอนๆ ได้, AI พากย์เสียงภาษาอื่นในไลฟ์</t>
+          <t>Google tests buying from Walmart-owned Flipkart through Gemini and AI Mode in India</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>YouTube เพิ่มฟีเจอร์ละครสั้นแนวตั้ง ดูต่อกันเป็นตอนๆ ได้, AI พากย์เสียงภาษาอื่นในไลฟ์ 
-     Body 
-                YouTube ประกาศเพิ่มฟีเจอร์หลายอย่างสำหรับผู้ใช้สายครีเอเตอร์ 
- เริ่มจากฟีเจอร์สาย Live มีดังนี้ 
-  React Live  เป็นการต่อยอดจากฟีเจอร์ Watch With เดิมที่ครีเอเตอร์มาร่วมไลฟ์และ re</t>
+          <t>The limited test covers select products and users, with a broader rollout planned for later in October.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>gemini, ai</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 01:30:36 +0000</t>
+          <t>Sun, 27 Sep 2026 01:30:00 +0000</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1806,63 +1801,216 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151764</t>
+          <t>https://techcrunch.com/2026/09/26/google-tests-buying-from-walmart-owned-flipkart-through-gemini-and-ai-mode-in-india/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>theinformation.com</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>China Weighs Allowing Purchases of New Nvidia Chips by ByteDance, Alibaba</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>China Weighs Allowing Purchases of New Nvidia Chips by ByteDance, Alibaba    The Information</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 27 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNl9kVzV0NlBYQ0pyQ1ltekFUemRHX0pKNkJMcHRJN2pBMzFEYXh2U3NLbnd1dkJaWGUza3NRR1VJYmE1bVk2SlNMS09EcGNDR3RDZkdDSWd4aGVKYTNZek5CQzRoM2NUd0VCOUMxWHNXLTd5eFA2d05tLVRab1ZWS0QxSjlBX1ZHN2xHcU9ndzZPMG5NVTFCem1tSm5HWlBtNXVpem44dUNNZw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>theguardian.com</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Pope Leo warns of AI threat to humanity at start of three-day France visit</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Pope Leo warns of AI threat to humanity at start of three-day France visit    theguardian.com</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>bangkokbiznews.com</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>‘อินฟินีออน’ ยักษ์ใหญ่ชิปเยอรมนีลงทุนไทย 4.8 หมื่นล้าน 'อนุทิน' เปิดโรงงานใหม่ 1 ต.ค.69</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>‘อินฟินีออน’ ยักษ์ใหญ่ชิปเยอรมนีลงทุนไทย 4.8 หมื่นล้าน 'อนุทิน' เปิดโรงงานใหม่ 1 ต.ค.69    bangkokbiznews</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>ชิป</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 27 Sep 2026 03:01:03 GMT</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9RUnJ4NlJKanVESTVKNFVrY182ME40T0dWZC02VmMxM0FsbDdGandxczZMY3UtR3JUdXVhUzJWRDZheXpfY3B6U1d3dUFHazRsNWttaS1VQ2RBZk1i?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>channelnewsasia.com</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Singapore proposes UN framework for global AI safeguards</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Foreign Affairs Minister Vivian Balakrishnan says countries need common rules, testing standards and potentially a new international institution to manage AI risks.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>ai</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 01:30:00 GMT</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="H29" s="2" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 27 Sep 2026 10:08:00 +0800</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPZ3g5REFXVVI4ZEFzU2p3NDNtckJDemE4Y3VFOVlpc1N2aTE1NzhQMUU0WjhYb0dKRHNkTWhsQkRGZkxWVmh2RlV6eEgxNzhvdTdwOV9FcUFEc05vZzQxRk5PbWFvMTEzSTZKWFpmQXZCa0hyS1ZZLXVzQktGSDI0TlpXdUVqeGRjZVU1WmozZm94SzZDdVdLWlFyNDNndndF?oc=5</t>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.channelnewsasia.com/singapore/un-ai-safeguards-singapore-national-statement-6413236</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>ft.com</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Big companies warn lack of ‘AI openness’ could hit investment in Europe</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Big companies warn lack of ‘AI openness’ could hit investment in Europe    Financial Times</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 27 Sep 2026 04:02:03 GMT</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQeVNjYkJKbWhmNEh3dDJTZVRZckxjcVVaT1I0MjA3eTlBalFsVElEVHNmc05Kc0R5cnMzcDlSVlo1WFFOQnAwQmp5Q0F2X3VfSDhGc3Rsb1o1NE5JSW5XcFphNy13NjBNSUR4a0tHTWozc3RpeWtPXzlKRmF0VUVBWHVtSDE?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K27"/>
+  <autoFilter ref="A1:K30"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1890,6 +2038,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1961,21 +2112,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4.16</v>
+        <v>4.78</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.76+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.18+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI says its bots have interacted with multiple U.S. government sites in unexpected AI activity</t>
+          <t>Gemini Live vs. ChatGPT Voice: Which AI offers a more natural conversation?</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>openai, chatgpt, gemini, ai</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -1983,12 +2134,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE5hYkN5dGZBNWtMczBXaVNSdEZwVExRdWk3Qmt1a0oxaURzYUVxaDBIOUNZUVItaFZSNHc1d3dsN1lFM2REbTV0Q3NCUk84Sl9LQnUzd3NhaU91b1hWODhicHVLOC1XTmtJQzJ3a19veUlkaVR2UHdiNXJB?oc=5</t>
+          <t>https://www.engadget.com/2266889/gemini-live-vs-gpt-live-which-offers-more-natural-conversation/</t>
         </is>
       </c>
     </row>
@@ -1997,21 +2148,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3.88</v>
+        <v>4.77</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.48+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.77+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI pauses training of its ‘most capable models’</t>
+          <t>Can Muse overcome Meta’s trust issues?</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>openai, inference</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -2019,12 +2170,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/1001049/openai-training-pause</t>
+          <t>https://techcrunch.com/2026/09/27/can-muse-overcome-metas-trust-issues/</t>
         </is>
       </c>
     </row>
@@ -2033,34 +2184,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.85</v>
+        <v>4.36</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec0.85+sig1.8+src1.2+corr0.0</t>
+          <t>rec0.56+sig1.8+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT-6 Astra cracks 85-year-old 1941 Enigma-coded message in two days — autonomous AI coded its own simulator to crack code that was unsolved since it was shared online back in 2005</t>
+          <t>Australia summons OpenAI and Anthropic CEOs to appear at AI inquiry</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>chatgpt, ai, autonomous</t>
+          <t>openai, anthropic, ai</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>aljazeera.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/chatgpt-6-astra-cracks-1941-enigma-coded-message-in-two-days-autonomous-ai-coded-its-own-simulator-to-crack-code-that-was-unsolved-since-it-was-shared-online-back-in-2005</t>
+          <t>https://www.aljazeera.com/news/2026/9/27/australia-summons-openai-and-anthropic-ceos-to-appear-at-ai-inquiry</t>
         </is>
       </c>
     </row>
@@ -2069,21 +2220,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.8</v>
+        <v>4.23</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr0.0</t>
+          <t>rec1.23+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Your old GPU could be worth more than you think</t>
+          <t>Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>ai, nvidia, gpu</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2091,12 +2242,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267877/your-old-gpu-worth-more-than-you-think/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/thieves-steal-nvidia-labeled-trailers-expecting-massive-ai-gpu-payday-but-score-40-000-pounds-of-sand-instead-crooks-duped-by-20-tons-of-ballast-sand</t>
         </is>
       </c>
     </row>
@@ -2105,21 +2256,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3.77</v>
+        <v>3.92</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.37+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.52+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Why NVIDIA's most powerful GPU is so rarely sold to consumers</t>
+          <t>OpenAI agents tried to ‘bruteforce’ a UN website</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>nvidia, gpu</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2127,12 +2278,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2265946/why-most-powerful-nvidia-gpu-rarely-sold-to-consumers/</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1001178/openai-agents-bruteforce-un-website</t>
         </is>
       </c>
     </row>
@@ -2141,21 +2292,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.9+sig0.6+src1.2+corr0.0</t>
+          <t>rec1.44+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Insurers claim AI is already increasing healthcare costs</t>
+          <t>Anthropic’s Dario Amodei gets the SNL treatment</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2168,7 +2319,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/26/insurers-claim-ai-is-already-increasing-healthcare-costs/</t>
+          <t>https://techcrunch.com/2026/09/27/anthropics-dario-amodei-gets-the-snl-treatment/</t>
         </is>
       </c>
     </row>
@@ -2177,21 +2328,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.78+sig0.6+src1.2+corr0.0</t>
+          <t>rec2.0+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>This external GPU uses Wi-Fi to transform any device into a gaming rig</t>
+          <t>Australia is run on legacy systems that AI agents can easily exploit, former UN cyber negotiator warns</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2199,12 +2350,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2269877/this-external-gpu-uses-wi-fi-to-transform-any-device-into-a-gaming-rig/</t>
+          <t>https://www.theguardian.com/technology/2026/sep/28/australia-is-run-on-legacy-systems-that-ai-agents-can-easily-exploit-former-un-cyber-negotiator-warns</t>
         </is>
       </c>
     </row>
@@ -2213,21 +2364,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.53</v>
+        <v>3.76</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.13+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.96+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Nvidia patents AI chatbot to streamline PC game optimization</t>
+          <t>โลกจะล่มสลายเพราะถูก AI ถล่ม?</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2235,12 +2386,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thansettakij.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/pc-gaming/an-nvidia-chatbot-could-one-day-help-developers-better-optimize-their-games-patent-filing-show-requests-can-be-made-in-plain-english</t>
+          <t>https://www.thansettakij.com/blogs/columnist/digital-myth-buster/669984</t>
         </is>
       </c>
     </row>
@@ -2249,16 +2400,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.7+sig0.6+src1.2+corr0.0</t>
+          <t>rec1.85+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AI agents are exposing a security gap between the data they read and the systems they can change</t>
+          <t>Engram is a sampler that turns broken AI hallucinations into music</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2271,12 +2422,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/security/ai-agents-are-exposing-a-security-gap-between-the-data-they-read-and-the-systems-they-can-change</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/1001193/engram-sampler-ai-hallucinations-music</t>
         </is>
       </c>
     </row>
@@ -2285,34 +2436,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.36</v>
+        <v>3.63</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec0.76+sig0.6+src1.2+corr0.8</t>
+          <t>rec1.83+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>China, US to open AI ‘communication channel’ after summit, White House says</t>
+          <t>Anthropic’s CEO is about to have dinner with President Trump</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.aljazeera.com/news/2026/9/26/china-us-to-open-ai-communication-channel-after-summit-white-house-says</t>
+          <t>https://techcrunch.com/2026/09/27/anthropics-ceo-is-about-to-have-dinner-with-president-trump/</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2426,24 +2577,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.36</v>
+        <v>6.9</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theinformation.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -2451,41 +2602,41 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Wall Street ends higher as investors buy AI stocks; Microsoft rallies</t>
+          <t>China Weighs Allowing Purchases of New Nvidia Chips by ByteDance, Alibaba</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Wall Street ends higher as investors buy AI stocks; Microsoft rallies    Reuters</t>
+          <t>Subscribe to read the full article China Weighs Allowing Purchases of New Nvidia Chips by ByteDance, Alibaba By Qianer Liu Sep 27, 2026 Subscribe to unlock Join high-powered tech and business leaders who read The Information every day. Subscribe now Continue with Google or Apple</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>nvidia, alibaba</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6.6</v>
+        <v>10.4</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 18:28:53 GMT</t>
+          <t>Sun, 27 Sep 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/video/business/</t>
+          <t>https://www.theinformation.com/articles/china-weighs-allowing-purchases-new-nvidia-chips-bytedance-alibaba</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6.1</v>
+        <v>6.47</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>2</v>
@@ -2497,12 +2648,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -2510,25 +2661,25 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Student protesters disrupt NVIDIA AI climate panel</t>
+          <t>Can Muse overcome Meta’s trust issues?</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>NewsFeed Student protesters disrupt NVIDIA AI climate panel Student protesters have interrupted an NVIDIA panel during NYC Climate Week, shouting about the environmental impact of data centres and the company’s business ties with Israel. Published On 26 Sep 2026 26 Sep 2026 Save Share Student protesters disrupt NVIDIA AI climate panel on social media Share Add Al Jazeera on Google</t>
+          <t>Last day to demo your breakthrough to 10,000+ tech leaders is on Oct 2 . Book Exhibit Table Now. Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Getty Images AI Can Muse overcome Meta’s trust issues? Anthony Ha 12:57 PM PDT · September 27, 2026 Listen on Apple Podcasts Listen on Spotify Meta’s new AI agent Muse took the spotlight a</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>meta, anthropic</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 22:15:35 GMT</t>
+          <t>Sun, 27 Sep 2026 19:57:30 +0000</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -2538,16 +2689,16 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.aljazeera.com/video/newsfeed/2026/9/26/student-protesters-disrupt-nvidia-ai-climate-panel</t>
+          <t>https://techcrunch.com/2026/09/27/can-muse-overcome-metas-trust-issues/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6</v>
+        <v>6.31</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -2556,12 +2707,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2569,58 +2720,58 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Wall Street ends higher as investors buy AI stocks; Microsoft rallies</t>
+          <t>Google tests buying from Walmart-owned Flipkart through Gemini and AI Mode in India</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Wall Street ends higher as investors buy AI stocks; Microsoft rallies    Reuters</t>
+          <t>Last day to demo your breakthrough to 10,000+ tech leaders is on Oct 2 . Book Exhibit Table Now. Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Anindito Mukherjee/Bloomberg / Getty Images AI Google tests buying from Walmart-owned Flipkart through Gemini and AI Mode in India Jagmeet Singh 6:30 PM PDT · September 26, 2026 Google has</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20.9</v>
+        <v>23.9</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 04:10:08 GMT</t>
+          <t>Sun, 27 Sep 2026 01:30:00 +0000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/video/watch/idRW545825092026RP1/</t>
+          <t>https://techcrunch.com/2026/09/26/google-tests-buying-from-walmart-owned-flipkart-through-gemini-and-ai-mode-in-india/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.59</v>
+        <v>6.31</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2628,25 +2779,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>LiveKit Agents Framework: Real-Time Outbound Voice AI on Oracle Cloud Infrastructure</t>
+          <t>Google tests buying from Walmart-owned Flipkart through Gemini and AI Mode in India</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>Google has started testing a way for shoppers in India to buy products from Walmart-owned Flipkart directly through Gemini and AI Mode, as the search giant looks to expand its AI services from product discovery into transactions. Users in the test see a “Buy” button on select Flipkart product listings appearing in Gemini and Google’s AI Mode, which takes them directly to a Flipkart checkout flow w</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>oracle cloud, oracle</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.7</v>
+        <v>23.9</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 10:22:48 GMT</t>
+          <t>Sun, 27 Sep 2026 01:30:00 GMT</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2656,30 +2807,30 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/ai-and-datascience/livekit-agents-real-time-voice-ai-on-oci</t>
+          <t>https://techcrunch.com/2026/09/26/google-tests-buying-from-walmart-owned-flipkart-through-gemini-and-ai-mode-in-india/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.48</v>
+        <v>6.16</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2687,25 +2838,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Meta and YouTube say they will run ads for ‘Musk’ documentary after all</t>
+          <t>China May Let Alibaba Buy New Nvidia Chips, The Information Says</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Francis Chung/Politico/Bloomberg / Getty Images Media &amp; Entertainment Meta and YouTube say they will run ads for ‘Musk’ documentary after all Anthony Ha 10:44 AM PDT · September 26, 2026</t>
+          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>meta, elon musk</t>
+          <t>nvidia, alibaba</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 17:44:00 +0000</t>
+          <t>Sun, 27 Sep 2026 15:44:39 GMT</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2715,16 +2866,16 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/26/meta-says-it-will-run-ads-for-musk-documentary-after-all/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-27/china-may-let-alibaba-buy-new-nvidia-chips-the-information-says</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5.31</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -2733,12 +2884,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>koreaherald.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2746,25 +2897,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>At Meta Connect, the company’s smart glasses were everywhere</t>
+          <t>LG Electronics named Nvidia partner for AI data center cooling</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Disrupt 2026: OpenAI, Anthropic, Replit, and more take over 6 industry stages. 25% off tickets now Disrupt ticket savings of up to $200 + 50% off a second ends Sept 25, 11:59 p.m. PT. REGISTER HERE. Image Credits: Lucas Ropek Hardware At Meta Connect, the company’s smart glasses were everywhere Lucas Ropek 6:08 PM PDT · September 25, 2026 If there was one thing that was obvious from Meta Connect t</t>
+          <t>Jie Ye-eun Since 2018, I have covered South Korea’s economic and financial landscape, with experience spanning the economy, banking, financial markets and securities industry. My current beat focuses on Korea’s major chaebol groups and technology industry, including Samsung, SK and LG, as well as global technology companies operating in Korea such as Apple, Google and OpenAI. Key areas of coverage</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>meta, facebook, instagram</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>23.9</v>
+        <v>20.8</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 01:08:57 +0000</t>
+          <t>Sun, 27 Sep 2026 04:37:31 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -2774,16 +2925,16 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/25/at-meta-connect-the-companys-smart-glasses-were-everywhere/</t>
+          <t>https://www.koreaherald.com/article/10885239</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5.3</v>
+        <v>5.92</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -2792,7 +2943,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2805,25 +2956,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Your old GPU could be worth more than you think</t>
+          <t>Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">If the RAMaggedon's good for anything, it's turning your old GPU into a potential goldmine. Dikushin/Getty Images Add Engadget on Google: Preferred Source Google Discover Whether it's from excessive use, sheer age or an upgrade that outclasses it, there are plenty of reasons that you may switch from one GPU to another. If you end up with an extra GPU lying around, there's a lot you can do with it </t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>nvidia, gpu</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.3</v>
+        <v>11.2</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 23:45:00 +0000</t>
+          <t>Sun, 27 Sep 2026 14:14:40 +0000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2833,16 +2984,16 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267877/your-old-gpu-worth-more-than-you-think/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/thieves-steal-nvidia-labeled-trailers-expecting-massive-ai-gpu-payday-but-score-40-000-pounds-of-sand-instead-crooks-duped-by-20-tons-of-ballast-sand</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5.3</v>
+        <v>5.92</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -2851,12 +3002,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2864,25 +3015,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>How to factory reset your Google Home Mini</t>
+          <t>Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead — crooks duped by 20 tons of ballast sand</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>It takes seconds to reset your Google speakers and display models. Nathan Ingraham for Engadget Add Engadget on Google: Preferred Source Google Discover The Google Home Mini has been around for almost nine years at this point, and the company has even discontinued it , but the devices are still in perfect working order. Still, there are situations that call for a factory reset. Whether the speaker</t>
+          <t>PC Components GPUs Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead — crooks duped by 20 tons of ballast sand News By Jowi Morales Published 11 hours ago Surprise, it's sand! (Image credit: Getty Images) Share this article 7 Join the conversation Follow us Add us as a preferred source on Google Newsletter Subscribe to our newsletter Plu</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>nvidia, gpu</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.1</v>
+        <v>11.2</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 23:00:00 +0000</t>
+          <t>Sun, 27 Sep 2026 14:14:40 GMT</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -2892,13 +3043,13 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2266523/how-to-factory-reset-google-home-mini/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/thieves-steal-nvidia-labeled-trailers-expecting-massive-ai-gpu-payday-but-score-40-000-pounds-of-sand-instead-crooks-duped-by-20-tons-of-ballast-sand</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5.29</v>
+        <v>5.9</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -2910,12 +3061,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -2923,25 +3074,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Commentary: Zuckerberg’s ‘Tamagotchi-like’ AI could be Meta’s iPod moment</t>
+          <t>How to improve CarPlay navigation if you use Google Maps over Apple Maps</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Commentary Commentary: Zuckerberg’s ‘Tamagotchi-like’ AI could be Meta’s iPod moment For someone mocked as a robotic, out-of-touch nerd, Mark Zuckerberg has struck the right tone with the Muse assistant, says Dave Lee for Bloomberg Opinion. Meta CEO Mark Zuckerberg presents the Muse Charm during the Meta Connect event at the company's headquarters in Menlo Park, California, Sep 23, 2026. REUTERS/C</t>
+          <t xml:space="preserve">A few tricks provide a seamless Google Maps experience in your car with CarPlay. Chinnapong/Shutterstock Add Engadget on Google: Preferred Source Google Discover Apple Maps has improved a lot since its troubled launch, but many people still prefer Google Maps. That could be because of the traffic data, better business listings or just out of habit. The good news is that you can use Google Maps in </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 22:00:00 GMT</t>
+          <t>Sun, 27 Sep 2026 23:00:00 +0000</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -2951,16 +3102,16 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/commentary/mark-zuckerberg-meta-muse-ai-agent-6411051</t>
+          <t>https://www.engadget.com/2267714/how-to-improve-carplay-navigation-use-google-maps-not-apple-maps/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5.27</v>
+        <v>5.87</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -2974,7 +3125,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -2982,25 +3133,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Why NVIDIA's most powerful GPU is so rarely sold to consumers</t>
+          <t>Gemini Live vs. ChatGPT Voice: Which AI offers a more natural conversation?</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA's $16,000 RTX PRO 6000 can beat the RTX 5090, but gamers aren't who it's built for. NVIDIA Add Engadget on Google: Preferred Source Google Discover By most measures, NVIDIA's GeForce RTX 5090 is a more powerful GPU than most will ever need. Priced at $1,999 when it was announced, it has 32GB of GDDR7 memory and can consume 575W when pushed. Despite all that power, though, there's still anot</t>
+          <t>It's actually too natural for some. Ascannio/Shutterstock Add Engadget on Google: Preferred Source Google Discover When ChatGPT first launched in 2022, the only way to interact with it was through your keyboard. But it didn't take long for another breakthrough: real-time voice chat. ChatGPT's Voice Mode was the first feature of this kind, but we soon got competition from Google in the form of Gemi</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>gpu, nvidia</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9.6</v>
+        <v>11.7</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 15:30:00 +0000</t>
+          <t>Sun, 27 Sep 2026 13:45:00 +0000</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3010,16 +3161,16 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2265946/why-most-powerful-nvidia-gpu-rarely-sold-to-consumers/</t>
+          <t>https://www.engadget.com/2266889/gemini-live-vs-gpt-live-which-offers-more-natural-conversation/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5.24</v>
+        <v>5.87</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -3028,12 +3179,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3041,25 +3192,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Apple hit with $5.7 billion in damages over haptic patents</t>
+          <t>Can Muse overcome Meta’s trust issues?</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech News Policy Apple hit with $5.7 billion in damages over haptic patents </t>
+          <t>Listen on Apple Podcasts Listen on Spotify Meta’s new AI agent Muse took the spotlight at the company’s annual Connect event, where CEO Mark Zuckerberg made it clear that Facebook’s parent company plans to push AI features everywhere. On the latest episode of TechCrunch’s Equity podcast, Kirsten Korosec, Sean O’Kane, and I discussed Meta’s AI announcements seemed to steal the spotlight during a we</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T17:30:01-04:00</t>
+          <t>Sun, 27 Sep 2026 19:57:30 GMT</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3069,30 +3220,30 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/1001118/apple-hit-with-5-7-billion-in-damages-over-haptic-patents</t>
+          <t>https://techcrunch.com/2026/09/27/can-muse-overcome-metas-trust-issues/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5.13</v>
+        <v>5.7</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3100,25 +3251,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Microsoft quietly drops Copilot+ branding from new laptops</t>
+          <t>Connectivity Patterns for Using Private OCI Object Storage with Cloudflare@OCI</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>copilot, microsoft</t>
+          <t>oci, oracle</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 14:00:00 +0000</t>
+          <t>Sun, 27 Sep 2026 11:52:52 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3128,13 +3279,13 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tablets/microsoft-surface/microsoft-quietly-drops-copilot-branding-from-its-new-laptops-surface-cvp-confirms-new-devices-meet-hardware-requirements-but-lack-controversial-branding</t>
+          <t>https://blogs.oracle.com/cloud-infrastructure/connectivity-oci-cloudflare</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5.08</v>
+        <v>5.51</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -3146,12 +3297,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3159,25 +3310,26 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>This external GPU uses Wi-Fi to transform any device into a gaming rig</t>
+          <t>Googlebooks might be the real deal</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>The WiCi One is available for preorders starting at $1,999.</t>
+          <t>Hi, friends! Welcome to  Installer  No. 145, your guide to the best and  Verge -iest stuff in the world. (If you're new here, welcome, I'm happy to be done traveling for a bit, and also you can read all the old editions at the   Installer  homepage .)  
+ This week, I flew to San Francisco to try out</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>apple, meta, mark zuckerberg</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5.3</v>
+        <v>13.4</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 19:45:00 +0000</t>
+          <t>2026-09-27T08:00:00-04:00</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3187,16 +3339,16 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2269877/this-external-gpu-uses-wi-fi-to-transform-any-device-into-a-gaming-rig/</t>
+          <t>https://www.theverge.com/tech/1000424/googlebooks-meta-ray-ban-audio-control-resonant-microsoft-surface-mouse</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.82</v>
+        <v>5.27</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -3210,7 +3362,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3218,25 +3370,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Apple hit with a $5.7 billion verdict for alleged patent infringement</t>
+          <t>Gemini Live Vs. ChatGPT Voice: Which AI Offers A More Natural Conversation?</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Apple is reportedly looking to appeal the jury verdict.</t>
+          <t>Gemini Live Vs. ChatGPT Voice: Which AI Offers A More Natural Conversation?    Engadget</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>8</v>
+        <v>11.7</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 17:02:42 +0000</t>
+          <t>Sun, 27 Sep 2026 13:45:00 GMT</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3246,13 +3398,13 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2269826/apple-hit-with-a-57-billion-verdict-for-alleged-patent-infringement/</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxObnZGa1lhUlVVZDZVbVNVR3NZWHZlV0VQZVNUM1hwSDlqSEhwWjNDalc5cTFQNFR4aDRBSndaZzZTSFhyemRaWXNrQmU2UUp1Sy05ZXFfbXRlZl81Uk8wYURaWnJ0QjVFelh6U2Nvc0Z3N1dZY0FBZG5GSXBtV215elR1VXl5OWFPb09pUlhyMTJUOGpZWFhiUjNyb3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.6</v>
+        <v>5.13</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -3264,12 +3416,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -3277,27 +3429,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>ไมโครซอฟท์ปรับวิธีการคิดราคา Copilot มีโควตาฟรีในค่ารายเดือน หากใช้เกินซื้อโทเค็นเพิ่มได้</t>
+          <t>Anthropic’s CEO is about to have dinner with President Trump</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>ไมโครซอฟท์ปรับวิธีการคิดราคา Copilot มีโควตาฟรีในค่ารายเดือน หากใช้เกินซื้อโทเค็นเพิ่มได้ 
-     Body 
-                ไมโครซอฟท์ปรับวิธีการคิดค่าใช้งานของแอป Copilot ที่ เพิ่งรวมเป็นแอปเดียว  จากเดิมที่คิดเป็นค่าบริการรายเดือนอย่างเดียว (user subscription license - USL) ตอนนี้ปรับมาเป็นการคิดแบ</t>
+          <t>This will be the first one-on-one meeting between Dario Amodei and Donald Trump</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>copilot</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>10.4</v>
+        <v>4.8</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 14:42:11 +0000</t>
+          <t>Sun, 27 Sep 2026 20:34:28 +0000</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -3307,13 +3457,13 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151769</t>
+          <t>https://techcrunch.com/2026/09/27/anthropics-ceo-is-about-to-have-dinner-with-president-trump/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.43</v>
+        <v>5</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -3325,12 +3475,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -3338,25 +3488,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Nvidia patents AI chatbot to streamline PC game optimization</t>
+          <t>Bill Gates says it's 'completely irresponsible' for AI to not have safeguards</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Oliver Haslam has written about technology of all shapes and sizes for over 15 years, both online and in print.  Having grown up using PCs and spending far too much money on graphics cards and fancy RAM, Oliver switched to the Mac with a G5 iMac. Nowadays, he uses both macOS and Windows depending on</t>
+          <t>The Microsoft co-founder said that the more present danger is bad actors with access to AI tools.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>12.1</v>
+        <v>6.2</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 13:00:00 +0000</t>
+          <t>Sun, 27 Sep 2026 19:12:29 +0000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -3366,16 +3516,16 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/pc-gaming/an-nvidia-chatbot-could-one-day-help-developers-better-optimize-their-games-patent-filing-show-requests-can-be-made-in-plain-english</t>
+          <t>https://www.engadget.com/2270166/bill-gates-says-that-its-completely-irresponsible-for-ai-to-not-have-safeguards/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.43</v>
+        <v>4.97</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -3384,12 +3534,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -3397,25 +3547,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Sandisk Optimus GX Pro 850P 2TB SSD review: A PS5 SSD you recognize at a price you don’t</t>
+          <t>Apple buried Copland 30 years ago. Now the failed OS boots in a browser</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shane has a background in computer engineering and has worked as a freelance consultant in multiple industries. He has a strong affection for history and loves to game. He worked his way up from a Commodore 64 and has always been interested in technology and writing. He particularly enjoys breaking </t>
+          <t>Thirty years after Apple abandoned Copland, its doomed attempt to create a modern Mac operating system, a new emulator lets you try the final developer build in your browser. Copland was intended to replace Apple's System 7 with a PowerPC-native operating system built around a microkernel, protected</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>optimus</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12.1</v>
+        <v>14.9</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 13:00:00 +0000</t>
+          <t>Sun, 27 Sep 2026 12:30:00 +0200</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -3425,13 +3575,13 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/ssds/sandisk-optimus-gx-pro-850p-2tb-ssd-review</t>
+          <t>https://www.theregister.com/os-platforms/2026/09/27/apple-buried-copland-30-years-ago-now-the-failed-os-boots-in-a-browser/5299201</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.43</v>
+        <v>4.76</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -3443,12 +3593,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -3456,25 +3606,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Nvidia patents AI chatbot to streamline PC game optimization — could one day help developers better optimize their games with requests made in plain English</t>
+          <t>Why the iPhone Duo could be beneficial for Samsung's Galaxy Z Fold 8</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Nvidia patents AI chatbot to streamline PC game optimization — could one day help developers better optimize their games with requests made in plain English    Tom's Hardware</t>
+          <t>Apple's iPhone Duo is far from the first foldable phone, but it could upset the foldable market in all-new ways.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 13:00:00 GMT</t>
+          <t>Sun, 27 Sep 2026 16:45:00 +0000</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -3484,13 +3634,13 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxQbU9YMldVYS01YnNFc1ZYdG1qVENadVNYVjZUeVRaejlJZjVVM2ZtR2M2XzFjeWRJbU5vY0ZZUGhoYlR2RWFfUHJ2RzVoYzRVZlNnbDJuWVJBcE5jdkJxWUYwUnZ0ZEo0c0xxRVNWbm9yMVlrckZ3a3VHbFRrMHY3T1VxSjJiRXlINGowRGtWbWFhMmttOTZ0MlBBNVdKdVFmaG5jTWgwblRqRVk4VEh6LU42bzNOSVIxNDJ1bVFobWdhckNpT0xhTmtZRGlycG5wLWdmb3ByOXJhb3hNVzhUQlVaVDFNRjFqMk80S3pPN2hmS1VCYkxOb1lXWmZQakhEdkthNDZYaFpoUVJzeGM0dg?oc=5</t>
+          <t>https://www.engadget.com/2267585/why-iphone-duo-benefitcial-for-samsung-galaxy-fold-8/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.39</v>
+        <v>4.74</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -3502,12 +3652,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -3515,25 +3665,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Nvidia’s RTX Mega Geometry 2.0 streams ray-tracing geometry into VRAM on demand</t>
+          <t>Anthropic’s Dario Amodei gets the SNL treatment</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shane has a background in computer engineering and has worked as a freelance consultant in multiple industries. He has a strong affection for history and loves to game. He worked his way up from a Commodore 64 and has always been interested in technology and writing. He particularly enjoys breaking </t>
+          <t>"AI is the devil and I its maker."</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>12.6</v>
+        <v>8.9</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 12:30:00 +0000</t>
+          <t>Sun, 27 Sep 2026 16:30:00 +0000</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3543,13 +3693,13 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/nvidias-rtx-mega-geometry-2-0-streams-ray-tracing-geometry-into-vram-on-demand-nanite-inspired-design-drops-detail-instead-of-dropping-out</t>
+          <t>https://techcrunch.com/2026/09/27/anthropics-dario-amodei-gets-the-snl-treatment/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.34</v>
+        <v>4.72</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -3561,12 +3711,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -3574,25 +3724,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Pokémon card resellers have turned collecting into an online blood sport</t>
+          <t>Apple faces $5.7 billion hit over tech that makes iPhones ‘tap’ back - All you need to know</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Earlier this month,  Pokémon  card   content creator Natalie Roush  posted a video to her YouTube and Instagram pages  that enraged the larger collection community. In the now-deleted video, Roush shows off two premium boxes of cards that had not yet been officially released, and implores viewers no</t>
+          <t>Apple faces $5.7 billion hit over tech that makes iPhones ‘tap’ back - All you need to know    Livemint</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13.1</v>
+        <v>9.1</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26T08:00:00-04:00</t>
+          <t>Sun, 27 Sep 2026 16:16:22 GMT</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3602,13 +3752,13 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/games/1001002/pokemon-30th-celebration-scalping-resellers</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQSXc0Ml9odjROMXdUUUwtUXZ3RFIwYURmS2NYMGRCNFR5U2dmbkpYWFYtZkYtY05tc2RKYl9RZDFLdnJvTjlEOFNQMHlCRHlxbkVMbXVjMEJVTmM1X3hnM0NjUXYtUkEycXpTSk1ESHF5VmxBTF8zVzVtUTNtb2RhYU1ZMVJ3VUp6RFBqUHRQYnFEVkFxZUJDUU91dXVLNGlHVnNrX0VtbUFUMmRuLVJYX3JqV3ZoU1Vtd1UtUFZxQ2tOcU9KODQ5eUI2R2NGWk40cmZyRDkxWndjTDdUT3Z30gHkAUFVX3lxTE4tVDBWMnBGSVdRdHBZa1BYMkxPQnpvUGZiSTBQSzMyQWYwdy1RR2V3NjJRdF9zRWY1UEh6T1hUT3FSTlRFOW4wdmhubGZwa1hycFZoMlJ3Q25Vb0tPVkpxRjNoREllWjA5ZVgxM3BsVWR4dDBKcktFOGF1TVBFUEpGM2NaQl92THpLQmRRWUdHSjBxSGNfOXVQR3E5YVlLUHBHbHlfVS00VDVzcUFNSk96OFh2cXNSZXZjWUZVeXh2WDBVbTdYMmJxQjRqREtFNDdzRTJJOG5ER3F5QmpSY04wOUFIeQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4.29</v>
+        <v>4.65</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -3620,12 +3770,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -3633,25 +3783,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>PNY allegedly refuses to cover melted RTX 5090 powered by native power supply cable</t>
+          <t>Meta’s Muse-fuelled rally: Stock jumps 36% in September as investors warm to its $140 billion AI bet</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
+          <t>Meta’s Muse-fuelled rally: Stock jumps 36% in September as investors warm to its $140 billion AI bet    Livemint</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>13.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 11:30:00 +0000</t>
+          <t>Sun, 27 Sep 2026 15:34:30 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3661,13 +3811,13 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/pny-allegedly-refuses-to-cover-melted-rtx-5090-powered-by-native-power-supply-cable-company-closes-users-ticket-when-questioned-on-policy</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPT2lJVlJYY2hfWjNhOUk2MnlYUmMydmxuanNwcUFnbVhVTzVyWGI0MlE0Z1RFTzJSR3JCR2NpMXlXWEFkbEkxeUNHNWt0VzVvbV9jMllHamFBOE5UZWFjeG80Y051ZFVZYmdYcTF1bHg2dm5kcWFvWUxLNW1iQkd3OXVRMFF4VkU5T2FNcEV5ekNlOG15TXZZczdWcUJLT3B1ZUxyck9BYTM4R1dPeVRVSlhEa3FNTDNDWHRNUXpyT19yLVJ5bl9IeFJKRHRBS3otNlZ0RWh0eVZXOW9iYk5RTGNRTWlaZlhIRURheVFMTzlQeDlOUkJ5V9IB_gFBVV95cUxQbUxuRzFKOG1FWFE2TndiMTVMN084TFhjUFdaSW5FX3cza3lyV1AyZy1adGtMZl81bVVWRnFUTWdvN1hJd2pVN1lFVUpoVnpkS200X0kybGhYNmx4WDBzTXRHX2VYSTRuTEtnMU1NM1FJT092WVhLc0hlMVExZElEVC1ySy1KVm5lakpyMUM2Z2p1WlY5S2lacmFITGtPZGdtMUR2TFhUUjdZeXRuNFlFLXVfUlFwNWtWV0t0V203QWF1Qk1qaFVkamdlWC1SUWdsLXVfMlBha2FDVC1UTWxpTUswdHB6MDVjcURCbjVUZFJkYWYtdTBBSGtEcGZDZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -3679,12 +3829,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -3692,25 +3842,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>How Samsung turned months of inactivity into a very attention-seeking smartphone</t>
+          <t>Meta's Muse agent is attacking one of the economy's most profitable weak spots</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Our resident Microsoft-watcher Richard Speed last week wrote about his seven-hour odyssey bringing a Windows 11 box up to snuff with the latest patches. I’ll see you that struggle, Richard, and raise you my experience updating a 2022-vintage Samsung Galaxy A33 Android smartphone. I spent about a yea</t>
+          <t>Meta's Muse agent is attacking one of the economy's most profitable weak spots    CNBC</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.6</v>
+        <v>10.9</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 12:27:00 +0200</t>
+          <t>Sun, 27 Sep 2026 14:33:22 GMT</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3720,30 +3870,30 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/personal-tech/2026/09/26/how-samsung-turned-months-of-inactivity-into-a-very-attention-seeking-smartphone/5298736</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5ETGE2S1ZqMWk4djE5R3c5YnV6VGV0eUZqN0ZaNXZDaXlMY2RUcWNWdDI3V0stY2JrZXVMWjRzTUhGZ3dOTk8zSkUtY1ZmZlRiazkyYUVaYUZFdVlaT210WWdRYUlpa09yclZhb3JDWEVoQdIBd0FVX3lxTE12NGNnN0FJaVdSRWRVR0tQcklzNlRMTTBpSjFOcVB4OGhCeFBIWkUzUENxSXlpQThkY1FZX3F2NjRZSVhJaWVleHkxbDQtd3N4OVlkWVZuQ3FkYk02VjA4WTU4ZGdHUFdQWkxrYjlOVzNrRzZBQkhV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4.12</v>
+        <v>4.5</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -3751,25 +3901,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Gain Insights using AI Powered Conversations using the FDI MCP Server</t>
+          <t>Anthropic CEO Amodei to Meet Trump With AI Safety Concern Rising</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Gain Insights using AI Powered Conversations using the FDI MCP Server    Oracle Blogs</t>
+          <t>Anthropic CEO Amodei to Meet Trump With AI Safety Concern Rising    Bloomberg</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>23.8</v>
+        <v>4.1</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 01:17:06 GMT</t>
+          <t>Sun, 27 Sep 2026 21:15:30 GMT</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3779,30 +3929,30 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQU1hHcHAwcWtBa2tWTkxnYmgzS2hwRy1EcHFxcGRNTHJyWkJTSm9ySDB4bjhORTlOTVJRNWFRZGVfSkFUSlJmejJKb2gtOGhSU2F5eGo1MndVNkhBYjJIcTJzQi1WV0lSZ3NWMEE5Nk5aM3pFdGR4TGtOV3lxbWNEZS1HOE1ZZkFNRVV5dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRHFRLVNKbG5ZRElJX0ZuS05EczkzM2NfUE9aZzRFUUNhVklLVldPNTVNM0lKN1lDOXB4RDBqMkp4aEsxLTB3bFFwY1lUemRMV3RWU290SWk3Q2I0X1JBWWJQQkN0Nm5sUUNWRHhDZEtUX0dmdi1sYlltdjBRX0FpamJET1hOTFYtZzFqVjYxZmZxSHBoRGdvSlE0OVhWQUZlSDdjRWY3QV9rdWd0OXlZQUUwTnI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4.11</v>
+        <v>4.4</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -3810,25 +3960,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>At Meta Connect, the company’s smart glasses were everywhere</t>
+          <t>Meta’s VR Glasses Are What the Apple Vision Pro Should Have Been</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>At Meta Connect, the company’s smart glasses were everywhere    TechCrunch</t>
+          <t>Meta’s VR Glasses Are What the Apple Vision Pro Should Have Been    Bloomberg</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple, meta</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>23.9</v>
+        <v>11.4</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 01:08:57 GMT</t>
+          <t>Sun, 27 Sep 2026 14:00:01 GMT</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3838,13 +3988,13 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNZjFPMGtJUkQzUUZNVFczdGtycGRFeGN0UnlZMVJVWEdsbEpVaUxUbDVLVUpHZkJaeU9aZzZ2aTFRLW1uUnlvb3ltdXRTXzg2VFJQYmNoVVFPNGxTRjNfUmpMT2hrX1luTjI2QkVKeFUzWE16bHhONXNwLTlaUG41VGFTS2ZwQXRLczBuX1R5bldacXhDM0hUTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQMjk0Q2VnTVNKdm1ubXYwSHdGSFlHcDRUN29YWkh5NmU0MjR5cGt1b0xJM21vTWE3aHFBTmhVaThPUXBNTXpiLUY3OFZTYUZPd21KQ2VmZklCU1c4R295cTZVMlpCMkFZblRUUGRDeGd1Q3dTZ2RaU1puQmFWeXJWLXJDSWNma0U1T1NGR1VQZWI1NEEzc3Fsczk3VEtteTMxMDZvV3ppUWd6UU9yZzQza0o3UFFiUmhSb00xbGpUa0NCQ19udmxxOGI2UUtZSDhW?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4.02</v>
+        <v>4.31</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -3856,12 +4006,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -3869,25 +4019,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Oracle layoffs offer a warning: 5 money moves to make before the pink slip arrives</t>
+          <t>The smart home graveyard is getting crowded</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Oracle layoffs offer a warning: 5 money moves to make before the pink slip arrives    Livemint</t>
+          <t xml:space="preserve">This is   The Stepback  , a weekly newsletter breaking down one essential story from the tech world. For more on the fragile state of your connected devices, follow  Jennifer Pattison Tuohy .  The Stepback  arrives in our subscribers' inboxes on Sunday at 8AM ET. Opt in for  The Stepback    here  . </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>16.4</v>
+        <v>13.4</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 08:39:00 GMT</t>
+          <t>2026-09-27T08:00:00-04:00</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3897,13 +4047,13 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNQThwWGNKeUJTUk5oQ05Zb0NlaVMydUo0enRPZDE0ZE9CRTV5Z3BXM0FYalR6b1pWZExLRlRqcm1abXZ4U1Z1TDVOZ1JxVWQ2bVJuVmFvN3pmWGRveDRSOTh5M3BySEZjYXFSLS1keVNaejNtcTkyUmtnV2dvbGZIRnhZbUJmZHhEdzVRVERKNHJ2dEotSnVULTVHMHctbUdDX3NkYjFSTGtGd0M4Z0hWMHJTdEt2cjBnSzcyV1haVlZWNmE2enVTd3dGclJMNkJpZHfSAdIBQVVfeXFMTUE4cFhjSnlCU1JOaENOWW9DZWlTMnVKNHp0T2QxNGRPQkU1eWdwVzNBWGpUem9aVmRMS0ZUanJtWm12eFNWdUw1TmdScVVkNm1SblZhbzd6Zlhkb3g0Ujk4eTNwckhGY2FxUi0tZHlTWnozbXE5MlJrZ1dnb2xmSEZ4WW1CZmR4RHc1UVRESjRydnRKLUp1VC01RzB3LW1HQ19zZGIxUkxrRndDOGdIVjByU3RLdnIwZ0s3MldYWlZWVjZhNnp1U3d3RnJSTDZCaWR3?oc=5</t>
+          <t>https://www.theverge.com/column/1000778/smart-home-june-oven-graveyard</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3.6</v>
+        <v>4.28</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -3915,12 +4065,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>abc.net.au</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -3928,25 +4078,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Who is Jensen Huang, the AI boss Trump calls at night?</t>
+          <t>Wisesight ถอดรหัส 5 ประเด็นร้อนโซเชียลฝ่าวิกฤตน้ำท่วมกรุง ดันเบอร์ฉุกเฉิน-Traffy Fondue พุ่ง 18 เท่า พร้อมส่งมีมคลายเครียด ‘สาดไปสมาชิก’</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Who is Jensen Huang, the AI boss Trump calls at night?    ABC News &amp; Headlines – Australian Broadcasting Corporation</t>
+          <t>วิกฤตฝนตกหนักและน้ำท่วมขังในพื้นที่กรุงเทพมหานครช่วงปลายเดือนกันยายน 2569 ได้ผลักดันให้โซเชียลมีเดียกลายเป็นพื้นที่หลักในการติดตามสถานการณ์แบบเรียลไทม์ โดย บริษัท ไวซ์ไซท์ (ประเทศไทย) จำกัด ได้เก็บข้อมูลผ่านเครื่องมือ Zocial Eye ระหว่างวันที่ 16-26 กันยายน 2569 พบว่ามีการพูดถึงประเด็นน้ำท่วมสูงถึง 1</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>jensen huang</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20.9</v>
+        <v>13.7</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 04:10:47 GMT</t>
+          <t>Sun, 27 Sep 2026 11:44:58 +0000</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3956,30 +4106,30 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQR3Y4eUtadkNtNzdRUkdsLVBHMTlWX2k2bnF1R0o1S1Q1OXVrWXRUS3hfc0xMU1lFREV5UWU2TzRkSkJfUnotNVdzQkhLczZGczg3SzZKd20xdnJ3WTEyTTNDeVJ4TFFmbUsyQ2RicVgxQ2hXbXJpSzlsOWgxbW90QjJhVUw3bFVHdU54TUhFMA?oc=5</t>
+          <t>https://thestandard.co/wisesight-deciphers-5-trending-social-media-topics-amidst/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -3987,25 +4137,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Tesla pullback a buying opportunity, expert says</t>
+          <t>Australia Senate Requests OpenAI, Anthropic CEOs Face AI Inquiry</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Tesla pullback a buying opportunity, expert says    Reuters</t>
+          <t>Australia Senate Requests OpenAI, Anthropic CEOs Face AI Inquiry    Bloomberg</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20.9</v>
+        <v>14.1</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 04:10:08 GMT</t>
+          <t>Sun, 27 Sep 2026 11:17:56 GMT</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4015,13 +4165,13 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBGR1ZxRno4dmFzc2oyTzhPNllxYlFMbVNqZ1dUY2FfYVFvbU4weGprMzVLNlFxNmNraWZNZ0N4SHJ0bmpqdi1kUzlhU3laa19Qd2M4SllwOXRBYkZyVlhZTTllOXg5SXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZXdVbk9icWx6SFl4QU9wRmd2blc0RTZrZUJ0N1h1czl0OU1xZkQyMXNtbmlFMzRBOFJaTFNTSjRLRjVISEh4dzBCU0tRbHBNbzJrS0FDc18xN2ZVQjNyTkdGa0d3TnljZ2p6c2RHZGJsMDZkVWtxVG5VeGhEb3Ywck1mZ2hLS2JTaU1hOVR1bzRBakcyaFdFaDMweV9mTmJFUU9Id09sQWVTaDdaX0FsM0g3S3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -4033,12 +4183,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4046,25 +4196,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Meta's AI tools, leadership boost bullish case, market expert says</t>
+          <t>Google's birthday: Why the September 27 celebration doesn't match its official September 4 incorporation date</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Meta's AI tools, leadership boost bullish case, market expert says    Reuters</t>
+          <t>Google's birthday: Why the September 27 celebration doesn't match its official September 4 incorporation date    Livemint</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Sat, 26 Sep 2026 04:10:08 GMT</t>
+          <t>Sun, 27 Sep 2026 03:31:13 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4074,71 +4224,12 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFAzT0U2aks0aDhiSUtqQVJtVFNyVDBJSmd2d0duNUtaamhTbmhIeEN3akxaTDRFaS03bnYtdHZ2d1pselJtUmRxaGZZcDdMWGpCUGxxeTcxTm5nWF9id1V4akRLU0EyMEE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>screening</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>wired.com</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Meta’s Muse Is Adults-Only. Why Does It Look Like a Kids’ Toy?</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Meta’s Muse Is Adults-Only. Why Does It Look Like a Kids’ Toy?    wired.com</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 26 Sep 2026 10:30:00 GMT</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVkJsbXcxMThtdVU2QTZ1RGRpcVRNbzZncTZIa2Zsa3VpSTNCam9uSDlsYkNOQ1ZJMDRWVENmRllEOE1lOGl5R0pHM2R0ZElDV3FrRERaa0kyeC04T3VvNEFEZW85U2NUaTJzQkRIaXpPUkl1SGM1UUQwZDJITkJ2QUZjLUNDS2ROcUpUbUZlUkhBSTluOWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOZDM1eXRnQjZRRVp2QzNRSTZ3VTJwTENsbnZMeG04YUVaVnY2VkJONTNUdUtIeEl5UW5Fc2FxRE5XY2xpTXJjM2ZWd0RpYmhRRTdkSGJqb3hDUldneVFwVi0xM2VlMVQtODZueDJtX3pweEYyVlk1RXVhejM3Q3oxY05NNkJUMUFNZUlqa2d0X0hWVHhZSXJqbk4xd1JaOHVEbTFnRkFFMTh1cWZJRUZZUFRIYnhXS2RXVHRhU1dibUhfWDFqUFRJa1lmRllFQ2k0eHl2YVlfOUVaVEpoVTRkSXduUWdsRExBTWNyNlEtdE1obHhuVVHSAfsBQVVfeXFMUEQzVUNFS0ZBemVoODFGZEF3TzJnZ3dkRVBzQzVXZUIyZUFsc2Nvc0xsQTF6TExkSWlWM1JNMkZHTHJnRnJUVl8tN3oxUWQ1RTgydjlpaHp5cnh2ekMxakhnRUdWdm5FOXhwUXU5a3BRMVZBNVJucmVKMXU1MGVycGU4anV6eUFHaGJLa2dfWU5obE9udEZJaE5GQkJiNklmZ3ZzbFJ2M1ZfVHJMQzE0WXRvMW5OckMtb05CbVprMlhtNEZ1dWhoWnZuVWx2T1J0eldyeHdnM0R1dHNIZ0ZkTWhtTkZxXzYwOGlnWjhPMXlicmloRkdnQ25EZlk?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M30"/>
+  <autoFilter ref="A1:M29"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -4168,7 +4259,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4246,39 +4336,39 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.36</v>
+        <v>6.9</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.66+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.3+sig1.2+src0.5+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Wall Street ends higher as investors buy AI stocks; Microsoft rallies</t>
+          <t>China Weighs Allowing Purchases of New Nvidia Chips by ByteDance, Alibaba</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>nvidia, alibaba</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theinformation.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/video/business/</t>
+          <t>https://www.theinformation.com/articles/china-weighs-allowing-purchases-new-nvidia-chips-bytedance-alibaba</t>
         </is>
       </c>
     </row>
@@ -4287,26 +4377,26 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6.1</v>
+        <v>6.47</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.77+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Student protesters disrupt NVIDIA AI climate panel</t>
+          <t>Can Muse overcome Meta’s trust issues?</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>meta, anthropic</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -4314,12 +4404,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.aljazeera.com/video/newsfeed/2026/9/26/student-protesters-disrupt-nvidia-ai-climate-panel</t>
+          <t>https://techcrunch.com/2026/09/27/can-muse-overcome-metas-trust-issues/</t>
         </is>
       </c>
     </row>
@@ -4328,39 +4418,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>6.31</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec0.3+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec0.01+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Wall Street ends higher as investors buy AI stocks; Microsoft rallies</t>
+          <t>Google tests buying from Walmart-owned Flipkart through Gemini and AI Mode in India</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/video/watch/idRW545825092026RP1/</t>
+          <t>https://techcrunch.com/2026/09/26/google-tests-buying-from-walmart-owned-flipkart-through-gemini-and-ai-mode-in-india/</t>
         </is>
       </c>
     </row>
@@ -4369,39 +4459,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.59</v>
+        <v>6.31</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec0.89+sig1.2+src2.0+corr0.0+wl1.5</t>
+          <t>rec0.01+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>LiveKit Agents Framework: Real-Time Outbound Voice AI on Oracle Cloud Infrastructure</t>
+          <t>Google tests buying from Walmart-owned Flipkart through Gemini and AI Mode in India</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>oracle cloud, oracle</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/ai-and-datascience/livekit-agents-real-time-voice-ai-on-oci</t>
+          <t>https://techcrunch.com/2026/09/26/google-tests-buying-from-walmart-owned-flipkart-through-gemini-and-ai-mode-in-india/</t>
         </is>
       </c>
     </row>
@@ -4410,39 +4500,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.48</v>
+        <v>6.16</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.58+sig1.2+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.36+sig1.2+src0.5+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Meta and YouTube say they will run ads for ‘Musk’ documentary after all</t>
+          <t>China May Let Alibaba Buy New Nvidia Chips, The Information Says</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>meta, elon musk</t>
+          <t>nvidia, alibaba</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/26/meta-says-it-will-run-ads-for-musk-documentary-after-all/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-09-27/china-may-let-alibaba-buy-new-nvidia-chips-the-information-says</t>
         </is>
       </c>
     </row>
@@ -4451,39 +4541,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5.31</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec0.01+sig1.8+src1.2+corr0.8+wl1.5</t>
+          <t>rec0.3+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>At Meta Connect, the company’s smart glasses were everywhere</t>
+          <t>LG Electronics named Nvidia partner for AI data center cooling</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>meta, facebook, instagram</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>koreaherald.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/25/at-meta-connect-the-companys-smart-glasses-were-everywhere/</t>
+          <t>https://www.koreaherald.com/article/10885239</t>
         </is>
       </c>
     </row>
@@ -4492,16 +4582,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.3</v>
+        <v>5.92</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.22+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Your old GPU could be worth more than you think</t>
+          <t>Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4511,20 +4601,20 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>nvidia, gpu</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267877/your-old-gpu-worth-more-than-you-think/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/thieves-steal-nvidia-labeled-trailers-expecting-massive-ai-gpu-payday-but-score-40-000-pounds-of-sand-instead-crooks-duped-by-20-tons-of-ballast-sand</t>
         </is>
       </c>
     </row>
@@ -4533,39 +4623,39 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5.3</v>
+        <v>5.92</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.22+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>How to factory reset your Google Home Mini</t>
+          <t>Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead — crooks duped by 20 tons of ballast sand</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>nvidia, gpu</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2266523/how-to-factory-reset-google-home-mini/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/thieves-steal-nvidia-labeled-trailers-expecting-massive-ai-gpu-payday-but-score-40-000-pounds-of-sand-instead-crooks-duped-by-20-tons-of-ballast-sand</t>
         </is>
       </c>
     </row>
@@ -4574,26 +4664,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.29</v>
+        <v>5.9</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.99+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Commentary: Zuckerberg’s ‘Tamagotchi-like’ AI could be Meta’s iPod moment</t>
+          <t>How to improve CarPlay navigation if you use Google Maps over Apple Maps</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -4601,12 +4691,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/commentary/mark-zuckerberg-meta-muse-ai-agent-6411051</t>
+          <t>https://www.engadget.com/2267714/how-to-improve-carplay-navigation-use-google-maps-not-apple-maps/</t>
         </is>
       </c>
     </row>
@@ -4615,30 +4705,30 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5.27</v>
+        <v>5.87</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.37+sig1.2+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.17+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Why NVIDIA's most powerful GPU is so rarely sold to consumers</t>
+          <t>Gemini Live vs. ChatGPT Voice: Which AI offers a more natural conversation?</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>gpu, nvidia</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -4647,7 +4737,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2265946/why-most-powerful-nvidia-gpu-rarely-sold-to-consumers/</t>
+          <t>https://www.engadget.com/2266889/gemini-live-vs-gpt-live-which-offers-more-natural-conversation/</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4693,57 +4783,57 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Nvidia  (Tier 1 · 8 stories)</t>
+          <t>Alphabet  (Tier 1 · 6 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6.1</v>
+        <v>6.31</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Student protesters disrupt NVIDIA AI climate panel</t>
+          <t>Google tests buying from Walmart-owned Flipkart through Gemini and AI Mode in India</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>aljazeera.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.aljazeera.com/video/newsfeed/2026/9/26/student-protesters-disrupt-nvidia-ai-climate-panel</t>
+          <t>https://techcrunch.com/2026/09/26/google-tests-buying-from-walmart-owned-flipkart-through-gemini-and-ai-mode-in-india/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.3</v>
+        <v>6.31</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Your old GPU could be worth more than you think</t>
+          <t>Google tests buying from Walmart-owned Flipkart through Gemini and AI Mode in India</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2267877/your-old-gpu-worth-more-than-you-think/</t>
+          <t>https://techcrunch.com/2026/09/26/google-tests-buying-from-walmart-owned-flipkart-through-gemini-and-ai-mode-in-india/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.27</v>
+        <v>5.9</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Why NVIDIA's most powerful GPU is so rarely sold to consumers</t>
+          <t>How to improve CarPlay navigation if you use Google Maps over Apple Maps</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -4753,17 +4843,17 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2265946/why-most-powerful-nvidia-gpu-rarely-sold-to-consumers/</t>
+          <t>https://www.engadget.com/2267714/how-to-improve-carplay-navigation-use-google-maps-not-apple-maps/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5.08</v>
+        <v>5.87</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>This external GPU uses Wi-Fi to transform any device into a gaming rig</t>
+          <t>Gemini Live vs. ChatGPT Voice: Which AI offers a more natural conversation?</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4773,405 +4863,405 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2269877/this-external-gpu-uses-wi-fi-to-transform-any-device-into-a-gaming-rig/</t>
+          <t>https://www.engadget.com/2266889/gemini-live-vs-gpt-live-which-offers-more-natural-conversation/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.43</v>
+        <v>5.27</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Nvidia patents AI chatbot to streamline PC game optimization</t>
+          <t>Gemini Live Vs. ChatGPT Voice: Which AI Offers A More Natural Conversation?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/pc-gaming/an-nvidia-chatbot-could-one-day-help-developers-better-optimize-their-games-patent-filing-show-requests-can-be-made-in-plain-english</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxObnZGa1lhUlVVZDZVbVNVR3NZWHZlV0VQZVNUM1hwSDlqSEhwWjNDalc5cTFQNFR4aDRBSndaZzZTSFhyemRaWXNrQmU2UUp1Sy05ZXFfbXRlZl81Uk8wYURaWnJ0QjVFelh6U2Nvc0Z3N1dZY0FBZG5GSXBtV215elR1VXl5OWFPb09pUlhyMTJUOGpZWFhiUjNyb3k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.43</v>
+        <v>3.5</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Nvidia patents AI chatbot to streamline PC game optimization — could one day help developers better optimize their games with requests made in plain English</t>
+          <t>Google's birthday: Why the September 27 celebration doesn't match its official September 4 incorporation date</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxQbU9YMldVYS01YnNFc1ZYdG1qVENadVNYVjZUeVRaejlJZjVVM2ZtR2M2XzFjeWRJbU5vY0ZZUGhoYlR2RWFfUHJ2RzVoYzRVZlNnbDJuWVJBcE5jdkJxWUYwUnZ0ZEo0c0xxRVNWbm9yMVlrckZ3a3VHbFRrMHY3T1VxSjJiRXlINGowRGtWbWFhMmttOTZ0MlBBNVdKdVFmaG5jTWgwblRqRVk4VEh6LU42bzNOSVIxNDJ1bVFobWdhckNpT0xhTmtZRGlycG5wLWdmb3ByOXJhb3hNVzhUQlVaVDFNRjFqMk80S3pPN2hmS1VCYkxOb1lXWmZQakhEdkthNDZYaFpoUVJzeGM0dg?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia’s RTX Mega Geometry 2.0 streams ray-tracing geometry into VRAM on demand</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/nvidias-rtx-mega-geometry-2-0-streams-ray-tracing-geometry-into-vram-on-demand-nanite-inspired-design-drops-detail-instead-of-dropping-out</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxOZDM1eXRnQjZRRVp2QzNRSTZ3VTJwTENsbnZMeG04YUVaVnY2VkJONTNUdUtIeEl5UW5Fc2FxRE5XY2xpTXJjM2ZWd0RpYmhRRTdkSGJqb3hDUldneVFwVi0xM2VlMVQtODZueDJtX3pweEYyVlk1RXVhejM3Q3oxY05NNkJUMUFNZUlqa2d0X0hWVHhZSXJqbk4xd1JaOHVEbTFnRkFFMTh1cWZJRUZZUFRIYnhXS2RXVHRhU1dibUhfWDFqUFRJa1lmRllFQ2k0eHl2YVlfOUVaVEpoVTRkSXduUWdsRExBTWNyNlEtdE1obHhuVVHSAfsBQVVfeXFMUEQzVUNFS0ZBemVoODFGZEF3TzJnZ3dkRVBzQzVXZUIyZUFsc2Nvc0xsQTF6TExkSWlWM1JNMkZHTHJnRnJUVl8tN3oxUWQ1RTgydjlpaHp5cnh2ekMxakhnRUdWdm5FOXhwUXU5a3BRMVZBNVJucmVKMXU1MGVycGU4anV6eUFHaGJLa2dfWU5obE9udEZJaE5GQkJiNklmZ3ZzbFJ2M1ZfVHJMQzE0WXRvMW5OckMtb05CbVprMlhtNEZ1dWhoWnZuVWx2T1J0eldyeHdnM0R1dHNIZ0ZkTWhtTkZxXzYwOGlnWjhPMXlicmloRkdnQ25EZlk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Who is Jensen Huang, the AI boss Trump calls at night?</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>abc.net.au</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQR3Y4eUtadkNtNzdRUkdsLVBHMTlWX2k2bnF1R0o1S1Q1OXVrWXRUS3hfc0xMU1lFREV5UWU2TzRkSkJfUnotNVdzQkhLczZGczg3SzZKd20xdnJ3WTEyTTNDeVJ4TFFmbUsyQ2RicVgxQ2hXbXJpSzlsOWgxbW90QjJhVUw3bFVHdU54TUhFMA?oc=5</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 6 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Googlebooks might be the real deal</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/1000424/googlebooks-meta-ray-ban-audio-control-resonant-microsoft-surface-mouse</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Meta Platforms  (Tier 1 · 6 stories)</t>
+      <c r="A13" s="2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Apple buried Copland 30 years ago. Now the failed OS boots in a browser</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>theregister.com</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theregister.com/os-platforms/2026/09/27/apple-buried-copland-30-years-ago-now-the-failed-os-boots-in-a-browser/5299201</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5.31</v>
+        <v>4.76</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>At Meta Connect, the company’s smart glasses were everywhere</t>
+          <t>Why the iPhone Duo could be beneficial for Samsung's Galaxy Z Fold 8</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/25/at-meta-connect-the-companys-smart-glasses-were-everywhere/</t>
+          <t>https://www.engadget.com/2267585/why-iphone-duo-benefitcial-for-samsung-galaxy-fold-8/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.29</v>
+        <v>4.72</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Commentary: Zuckerberg’s ‘Tamagotchi-like’ AI could be Meta’s iPod moment</t>
+          <t>Apple faces $5.7 billion hit over tech that makes iPhones ‘tap’ back - All you need to know</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/commentary/mark-zuckerberg-meta-muse-ai-agent-6411051</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxQSXc0Ml9odjROMXdUUUwtUXZ3RFIwYURmS2NYMGRCNFR5U2dmbkpYWFYtZkYtY05tc2RKYl9RZDFLdnJvTjlEOFNQMHlCRHlxbkVMbXVjMEJVTmM1X3hnM0NjUXYtUkEycXpTSk1ESHF5VmxBTF8zVzVtUTNtb2RhYU1ZMVJ3VUp6RFBqUHRQYnFEVkFxZUJDUU91dXVLNGlHVnNrX0VtbUFUMmRuLVJYX3JqV3ZoU1Vtd1UtUFZxQ2tOcU9KODQ5eUI2R2NGWk40cmZyRDkxWndjTDdUT3Z30gHkAUFVX3lxTE4tVDBWMnBGSVdRdHBZa1BYMkxPQnpvUGZiSTBQSzMyQWYwdy1RR2V3NjJRdF9zRWY1UEh6T1hUT3FSTlRFOW4wdmhubGZwa1hycFZoMlJ3Q25Vb0tPVkpxRjNoREllWjA5ZVgxM3BsVWR4dDBKcktFOGF1TVBFUEpGM2NaQl92THpLQmRRWUdHSjBxSGNfOXVQR3E5YVlLUHBHbHlfVS00VDVzcUFNSk96OFh2cXNSZXZjWUZVeXh2WDBVbTdYMmJxQjRqREtFNDdzRTJJOG5ER3F5QmpSY04wOUFIeQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Pokémon card resellers have turned collecting into an online blood sport</t>
+          <t>Meta’s VR Glasses Are What the Apple Vision Pro Should Have Been</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/games/1001002/pokemon-30th-celebration-scalping-resellers</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQMjk0Q2VnTVNKdm1ubXYwSHdGSFlHcDRUN29YWkh5NmU0MjR5cGt1b0xJM21vTWE3aHFBTmhVaThPUXBNTXpiLUY3OFZTYUZPd21KQ2VmZklCU1c4R295cTZVMlpCMkFZblRUUGRDeGd1Q3dTZ2RaU1puQmFWeXJWLXJDSWNma0U1T1NGR1VQZWI1NEEzc3Fsczk3VEtteTMxMDZvV3ppUWd6UU9yZzQza0o3UFFiUmhSb00xbGpUa0NCQ19udmxxOGI2UUtZSDhW?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.11</v>
+        <v>4.31</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>At Meta Connect, the company’s smart glasses were everywhere</t>
+          <t>The smart home graveyard is getting crowded</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/column/1000778/smart-home-june-oven-graveyard</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Amazon  (Tier 1 · 5 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Can Muse overcome Meta’s trust issues?</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>techcrunch.com</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNZjFPMGtJUkQzUUZNVFczdGtycGRFeGN0UnlZMVJVWEdsbEpVaUxUbDVLVUpHZkJaeU9aZzZ2aTFRLW1uUnlvb3ltdXRTXzg2VFJQYmNoVVFPNGxTRjNfUmpMT2hrX1luTjI2QkVKeFUzWE16bHhONXNwLTlaUG41VGFTS2ZwQXRLczBuX1R5bldacXhDM0hUTQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Meta's AI tools, leadership boost bullish case, market expert says</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFAzT0U2aks0aDhiSUtqQVJtVFNyVDBJSmd2d0duNUtaamhTbmhIeEN3akxaTDRFaS03bnYtdHZ2d1pselJtUmRxaGZZcDdMWGpCUGxxeTcxTm5nWF9id1V4akRLU0EyMEE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Meta’s Muse Is Adults-Only. Why Does It Look Like a Kids’ Toy?</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>wired.com</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVkJsbXcxMThtdVU2QTZ1RGRpcVRNbzZncTZIa2Zsa3VpSTNCam9uSDlsYkNOQ1ZJMDRWVENmRllEOE1lOGl5R0pHM2R0ZElDV3FrRERaa0kyeC04T3VvNEFEZW85U2NUaTJzQkRIaXpPUkl1SGM1UUQwZDJITkJ2QUZjLUNDS2ROcUpUbUZlUkhBSTluOWc?oc=5</t>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/27/can-muse-overcome-metas-trust-issues/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 5 stories)</t>
+      <c r="A21" s="2" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic’s CEO is about to have dinner with President Trump</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/27/anthropics-ceo-is-about-to-have-dinner-with-president-trump/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7.36</v>
+        <v>4.74</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Wall Street ends higher as investors buy AI stocks; Microsoft rallies</t>
+          <t>Anthropic’s Dario Amodei gets the SNL treatment</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/video/business/</t>
+          <t>https://techcrunch.com/2026/09/27/anthropics-dario-amodei-gets-the-snl-treatment/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Wall Street ends higher as investors buy AI stocks; Microsoft rallies</t>
+          <t>Anthropic CEO Amodei to Meet Trump With AI Safety Concern Rising</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/video/watch/idRW545825092026RP1/</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRHFRLVNKbG5ZRElJX0ZuS05EczkzM2NfUE9aZzRFUUNhVklLVldPNTVNM0lKN1lDOXB4RDBqMkp4aEsxLTB3bFFwY1lUemRMV3RWU290SWk3Q2I0X1JBWWJQQkN0Nm5sUUNWRHhDZEtUX0dmdi1sYlltdjBRX0FpamJET1hOTFYtZzFqVjYxZmZxSHBoRGdvSlE0OVhWQUZlSDdjRWY3QV9rdWd0OXlZQUUwTnI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.13</v>
+        <v>3.54</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Microsoft quietly drops Copilot+ branding from new laptops</t>
+          <t>Australia Senate Requests OpenAI, Anthropic CEOs Face AI Inquiry</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tablets/microsoft-surface/microsoft-quietly-drops-copilot-branding-from-its-new-laptops-surface-cvp-confirms-new-devices-meet-hardware-requirements-but-lack-controversial-branding</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>ไมโครซอฟท์ปรับวิธีการคิดราคา Copilot มีโควตาฟรีในค่ารายเดือน หากใช้เกินซื้อโทเค็นเพิ่มได้</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>blognone.com</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>https://www.blognone.com/node/151769</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOZXdVbk9icWx6SFl4QU9wRmd2blc0RTZrZUJ0N1h1czl0OU1xZkQyMXNtbmlFMzRBOFJaTFNTSjRLRjVISEh4dzBCU0tRbHBNbzJrS0FDc18xN2ZVQjNyTkdGa0d3TnljZ2p6c2RHZGJsMDZkVWtxVG5VeGhEb3Ywck1mZ2hLS2JTaU1hOVR1bzRBakcyaFdFaDMweV9mTmJFUU9Id09sQWVTaDdaX0FsM0g3S3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>How Samsung turned months of inactivity into a very attention-seeking smartphone</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theregister.com/personal-tech/2026/09/26/how-samsung-turned-months-of-inactivity-into-a-very-attention-seeking-smartphone/5298736</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Nvidia  (Tier 1 · 5 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>China Weighs Allowing Purchases of New Nvidia Chips by ByteDance, Alibaba</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>theinformation.com</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theinformation.com/articles/china-weighs-allowing-purchases-new-nvidia-chips-bytedance-alibaba</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 3 stories)</t>
+      <c r="A28" s="2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>China May Let Alibaba Buy New Nvidia Chips, The Information Says</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-09-27/china-may-let-alibaba-buy-new-nvidia-chips-the-information-says</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.59</v>
+        <v>6</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>LiveKit Agents Framework: Real-Time Outbound Voice AI on Oracle Cloud Infrastructure</t>
+          <t>LG Electronics named Nvidia partner for AI data center cooling</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>koreaherald.com</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/ai-and-datascience/livekit-agents-real-time-voice-ai-on-oci</t>
+          <t>https://www.koreaherald.com/article/10885239</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4.12</v>
+        <v>5.92</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Gain Insights using AI Powered Conversations using the FDI MCP Server</t>
+          <t>Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQU1hHcHAwcWtBa2tWTkxnYmgzS2hwRy1EcHFxcGRNTHJyWkJTSm9ySDB4bjhORTlOTVJRNWFRZGVfSkFUSlJmejJKb2gtOGhSU2F5eGo1MndVNkhBYjJIcTJzQi1WV0lSZ3NWMEE5Nk5aM3pFdGR4TGtOV3lxbWNEZS1HOE1ZZkFNRVV5dw?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/thieves-steal-nvidia-labeled-trailers-expecting-massive-ai-gpu-payday-but-score-40-000-pounds-of-sand-instead-crooks-duped-by-20-tons-of-ballast-sand</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4.02</v>
+        <v>5.92</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Oracle layoffs offer a warning: 5 money moves to make before the pink slip arrives</t>
+          <t>Thieves steal Nvidia-labeled trailers expecting massive AI GPU payday, but score 40,000 pounds of sand instead — crooks duped by 20 tons of ballast sand</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNQThwWGNKeUJTUk5oQ05Zb0NlaVMydUo0enRPZDE0ZE9CRTV5Z3BXM0FYalR6b1pWZExLRlRqcm1abXZ4U1Z1TDVOZ1JxVWQ2bVJuVmFvN3pmWGRveDRSOTh5M3BySEZjYXFSLS1keVNaejNtcTkyUmtnV2dvbGZIRnhZbUJmZHhEdzVRVERKNHJ2dEotSnVULTVHMHctbUdDX3NkYjFSTGtGd0M4Z0hWMHJTdEt2cjBnSzcyV1haVlZWNmE2enVTd3dGclJMNkJpZHfSAdIBQVVfeXFMTUE4cFhjSnlCU1JOaENOWW9DZWlTMnVKNHp0T2QxNGRPQkU1eWdwVzNBWGpUem9aVmRMS0ZUanJtWm12eFNWdUw1TmdScVVkNm1SblZhbzd6Zlhkb3g0Ujk4eTNwckhGY2FxUi0tZHlTWnozbXE5MlJrZ1dnb2xmSEZ4WW1CZmR4RHc1UVRESjRydnRKLUp1VC01RzB3LW1HQ19zZGIxUkxrRndDOGdIVjByU3RLdnIwZ0s3MldYWlZWVjZhNnp1U3d3RnJSTDZCaWR3?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/thieves-steal-nvidia-labeled-trailers-expecting-massive-ai-gpu-payday-but-score-40-000-pounds-of-sand-instead-crooks-duped-by-20-tons-of-ballast-sand</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Tesla  (Tier 1 · 3 stories)</t>
+          <t>Meta Platforms  (Tier 1 · 4 stories)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.48</v>
+        <v>5.87</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Meta and YouTube say they will run ads for ‘Musk’ documentary after all</t>
+          <t>Can Muse overcome Meta’s trust issues?</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5181,84 +5271,84 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/26/meta-says-it-will-run-ads-for-musk-documentary-after-all/</t>
+          <t>https://techcrunch.com/2026/09/27/can-muse-overcome-metas-trust-issues/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>4.43</v>
+        <v>4.65</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Sandisk Optimus GX Pro 850P 2TB SSD review: A PS5 SSD you recognize at a price you don’t</t>
+          <t>Meta’s Muse-fuelled rally: Stock jumps 36% in September as investors warm to its $140 billion AI bet</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/ssds/sandisk-optimus-gx-pro-850p-2tb-ssd-review</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPT2lJVlJYY2hfWjNhOUk2MnlYUmMydmxuanNwcUFnbVhVTzVyWGI0MlE0Z1RFTzJSR3JCR2NpMXlXWEFkbEkxeUNHNWt0VzVvbV9jMllHamFBOE5UZWFjeG80Y051ZFVZYmdYcTF1bHg2dm5kcWFvWUxLNW1iQkd3OXVRMFF4VkU5T2FNcEV5ekNlOG15TXZZczdWcUJLT3B1ZUxyck9BYTM4R1dPeVRVSlhEa3FNTDNDWHRNUXpyT19yLVJ5bl9IeFJKRHRBS3otNlZ0RWh0eVZXOW9iYk5RTGNRTWlaZlhIRURheVFMTzlQeDlOUkJ5V9IB_gFBVV95cUxQbUxuRzFKOG1FWFE2TndiMTVMN084TFhjUFdaSW5FX3cza3lyV1AyZy1adGtMZl81bVVWRnFUTWdvN1hJd2pVN1lFVUpoVnpkS200X0kybGhYNmx4WDBzTXRHX2VYSTRuTEtnMU1NM1FJT092WVhLc0hlMVExZElEVC1ySy1KVm5lakpyMUM2Z2p1WlY5S2lacmFITGtPZGdtMUR2TFhUUjdZeXRuNFlFLXVfUlFwNWtWV0t0V203QWF1Qk1qaFVkamdlWC1SUWdsLXVfMlBha2FDVC1UTWxpTUswdHB6MDVjcURCbjVUZFJkYWYtdTBBSGtEcGZDZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Tesla pullback a buying opportunity, expert says</t>
+          <t>Meta's Muse agent is attacking one of the economy's most profitable weak spots</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBGR1ZxRno4dmFzc2oyTzhPNllxYlFMbVNqZ1dUY2FfYVFvbU4weGprMzVLNlFxNmNraWZNZ0N4SHJ0bmpqdi1kUzlhU3laa19Qd2M4SllwOXRBYkZyVlhZTTllOXg5SXc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Apple  (Tier 1 · 2 stories)</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5ETGE2S1ZqMWk4djE5R3c5YnV6VGV0eUZqN0ZaNXZDaXlMY2RUcWNWdDI3V0stY2JrZXVMWjRzTUhGZ3dOTk8zSkUtY1ZmZlRiazkyYUVaYUZFdVlaT210WWdRYUlpa09yclZhb3JDWEVoQdIBd0FVX3lxTE12NGNnN0FJaVdSRWRVR0tQcklzNlRMTTBpSjFOcVB4OGhCeFBIWkUzUENxSXlpQThkY1FZX3F2NjRZSVhJaWVleHkxbDQtd3N4OVlkWVZuQ3FkYk02VjA4WTU4ZGdHUFdQWkxrYjlOVzNrRzZBQkhV?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Wisesight ถอดรหัส 5 ประเด็นร้อนโซเชียลฝ่าวิกฤตน้ำท่วมกรุง ดันเบอร์ฉุกเฉิน-Traffy Fondue พุ่ง 18 เท่า พร้อมส่งมีมคลายเครียด ‘สาดไปสมาชิก’</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>thestandard.co</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>https://thestandard.co/wisesight-deciphers-5-trending-social-media-topics-amidst/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Apple hit with $5.7 billion in damages over haptic patents</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/tech/1001118/apple-hit-with-5-7-billion-in-damages-over-haptic-patents</t>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Apple hit with a $5.7 billion verdict for alleged patent infringement</t>
+          <t>Bill Gates says it's 'completely irresponsible' for AI to not have safeguards</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5268,61 +5358,34 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2269826/apple-hit-with-a-57-billion-verdict-for-alleged-patent-infringement/</t>
+          <t>https://www.engadget.com/2270166/bill-gates-says-that-its-completely-irresponsible-for-ai-to-not-have-safeguards/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>AMD  (Tier 1 · 1 stories)</t>
+          <t>Oracle  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>4.29</v>
+        <v>5.7</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>PNY allegedly refuses to cover melted RTX 5090 powered by native power supply cable</t>
+          <t>Connectivity Patterns for Using Private OCI Object Storage with Cloudflare@OCI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/pny-allegedly-refuses-to-cover-melted-rtx-5090-powered-by-native-power-supply-cable-company-closes-users-ticket-when-questioned-on-policy</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Alphabet  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>How to factory reset your Google Home Mini</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2266523/how-to-factory-reset-google-home-mini/</t>
+          <t>https://blogs.oracle.com/cloud-infrastructure/connectivity-oci-cloudflare</t>
         </is>
       </c>
     </row>
@@ -5334,29 +5397,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
